--- a/docs/harness/wirelist/A-cabin-wirelist.xlsx
+++ b/docs/harness/wirelist/A-cabin-wirelist.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Mates" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wire list'!$A$2:$AG$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wire list'!$A$2:$AG$95</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Wire list'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Splices'!$A$2:$L$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Splices'!$1:$2</definedName>
@@ -745,12 +745,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AG100"/>
+  <dimension ref="A1:AG95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -3330,7 +3330,7 @@
       <c r="AD21" s="38" t="inlineStr"/>
       <c r="AE21" s="38" t="inlineStr">
         <is>
-          <t>splice sp_trig2 named in SoT; channels.csv ecu_a A9 Trigger 2 (TRIG2_CAM)</t>
+          <t>channels.csv ecu_a A9 Trigger 2 (TRIG2_CAM); splice sp_trig2 named in SoT</t>
         </is>
       </c>
       <c r="AF21" s="38" t="inlineStr">
@@ -3560,7 +3560,7 @@
       <c r="AD23" s="38" t="inlineStr"/>
       <c r="AE23" s="38" t="inlineStr">
         <is>
-          <t>channels.csv a9 pull-up ext-1k8-to-8v; splice sp_trig2 named in SoT</t>
+          <t>splice sp_trig2 named in SoT</t>
         </is>
       </c>
       <c r="AF23" s="38" t="inlineStr">
@@ -3679,7 +3679,7 @@
       <c r="AD24" s="54" t="inlineStr"/>
       <c r="AE24" s="54" t="inlineStr">
         <is>
-          <t>splice sp_8v named in SoT; channels.csv a9 pull-up ext-1k8-to-8v</t>
+          <t>splice sp_8v named in SoT</t>
         </is>
       </c>
       <c r="AF24" s="54" t="inlineStr">
@@ -4036,7 +4036,7 @@
       <c r="AD27" s="38" t="inlineStr"/>
       <c r="AE27" s="38" t="inlineStr">
         <is>
-          <t>splice sp_5v named in SoT; channels.csv ecu_a A32 +5V Out (P5V)</t>
+          <t>channels.csv ecu_a A32 +5V Out (P5V); splice sp_5v named in SoT</t>
         </is>
       </c>
       <c r="AF27" s="38" t="inlineStr">
@@ -5075,7 +5075,7 @@
       <c r="AD36" s="54" t="inlineStr"/>
       <c r="AE36" s="54" t="inlineStr">
         <is>
-          <t>splice sp_5v named in SoT; break BR_W_RAIL_5V_B_C (other drawn half w_rail_5v_b_c on B-cabin)</t>
+          <t>splice sp_5v named in SoT; splice sp_5v_b named in SoT</t>
         </is>
       </c>
       <c r="AF36" s="54" t="inlineStr">
@@ -5147,7 +5147,9 @@
           <t>resistor r_cruise on CSB3</t>
         </is>
       </c>
-      <c r="N37" s="28" t="inlineStr"/>
+      <c r="N37" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="O37" s="29" t="inlineStr">
         <is>
           <t>+5 V cruise ladder</t>
@@ -5200,7 +5202,7 @@
       <c r="AD37" s="38" t="inlineStr"/>
       <c r="AE37" s="38" t="inlineStr">
         <is>
-          <t>splice sp_5v_2 named in SoT; break BR_W_CRU_5V (other drawn half w_cru_5v on CSB3)</t>
+          <t>splice sp_5v_2 named in SoT</t>
         </is>
       </c>
       <c r="AF37" s="38" t="inlineStr">
@@ -5325,7 +5327,7 @@
       <c r="AD38" s="54" t="inlineStr"/>
       <c r="AE38" s="54" t="inlineStr">
         <is>
-          <t>splice sp_gndout named in SoT; channels.csv ecu_a A24 Gnd Out (GNDOUT)</t>
+          <t>channels.csv ecu_a A24 Gnd Out (GNDOUT); splice sp_gndout named in SoT</t>
         </is>
       </c>
       <c r="AF38" s="54" t="inlineStr">
@@ -6122,7 +6124,7 @@
       <c r="P45" s="29" t="inlineStr"/>
       <c r="Q45" s="30" t="inlineStr">
         <is>
-          <t>LOGIC.SW12</t>
+          <t>LOGIC.BUS2-2</t>
         </is>
       </c>
       <c r="R45" s="31" t="inlineStr">
@@ -6162,7 +6164,7 @@
       <c r="AD45" s="38" t="inlineStr"/>
       <c r="AE45" s="38" t="inlineStr">
         <is>
-          <t>break BR_W_FB_SW12 (other drawn half w_fb_sw12_cp on CabinPower); splice sp_sw12 named in SoT</t>
+          <t>splice sp_sw12 named in SoT</t>
         </is>
       </c>
       <c r="AF45" s="38" t="inlineStr">
@@ -6243,7 +6245,7 @@
       <c r="P46" s="45" t="inlineStr"/>
       <c r="Q46" s="46" t="inlineStr">
         <is>
-          <t>LOGIC.SW12</t>
+          <t>LOGIC.BUS2-2</t>
         </is>
       </c>
       <c r="R46" s="47" t="inlineStr">
@@ -6358,7 +6360,7 @@
       <c r="P47" s="29" t="inlineStr"/>
       <c r="Q47" s="30" t="inlineStr">
         <is>
-          <t>LOGIC.SW12</t>
+          <t>LOGIC.BUS2-2</t>
         </is>
       </c>
       <c r="R47" s="31" t="inlineStr">
@@ -6481,7 +6483,7 @@
       </c>
       <c r="Q48" s="46" t="inlineStr">
         <is>
-          <t>LOGIC.SW12</t>
+          <t>LOGIC.BUS2-2</t>
         </is>
       </c>
       <c r="R48" s="47" t="inlineStr">
@@ -6521,7 +6523,7 @@
       <c r="AD48" s="54" t="inlineStr"/>
       <c r="AE48" s="54" t="inlineStr">
         <is>
-          <t>splice sp_sw12 named in SoT; break BR_W_RAIL_SW12_B_C (other drawn half w_rail_sw12_b_c on B-cabin); DRB102 90 = section B c20 'Switched 12V to gearbox VSS (from sp_sw12)'</t>
+          <t>splice sp_sw12 named in SoT; DRB102 90 = section B c20 'Switched 12V to gearbox VSS (from sp_sw12)'</t>
         </is>
       </c>
       <c r="AF48" s="54" t="inlineStr">
@@ -6538,24 +6540,24 @@
     <row r="49">
       <c r="A49" s="23" t="inlineStr">
         <is>
-          <t>INJ</t>
+          <t>EPSEN</t>
         </is>
       </c>
       <c r="B49" s="23" t="inlineStr">
         <is>
-          <t>w_inj_pwr_ac</t>
+          <t>w_fb_mrs_en</t>
         </is>
       </c>
       <c r="C49" s="23" t="inlineStr">
         <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D49" s="23" t="inlineStr">
+        <is>
           <t>CabinPower</t>
         </is>
       </c>
-      <c r="D49" s="23" t="inlineStr">
-        <is>
-          <t>A-cabin</t>
-        </is>
-      </c>
       <c r="E49" s="24" t="inlineStr">
         <is>
           <t>connector</t>
@@ -6573,17 +6575,17 @@
       </c>
       <c r="H49" s="25" t="inlineStr">
         <is>
-          <t>BUS2-4</t>
+          <t>BUS2-12</t>
         </is>
       </c>
       <c r="I49" s="26" t="inlineStr">
         <is>
-          <t>Injector +12 V feed</t>
+          <t>EHPS enable +12 V</t>
         </is>
       </c>
       <c r="J49" s="26" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) fuse INJ 15A</t>
+          <t>LOGIC box (glove box) fuse MRS 7.5A Fuse fed from EPS enable relay k_eps_en pin 87 (ignition-switched).</t>
         </is>
       </c>
       <c r="K49" s="27" t="inlineStr">
@@ -6602,28 +6604,28 @@
         </is>
       </c>
       <c r="N49" s="28" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="O49" s="29" t="inlineStr">
         <is>
-          <t>Injector +12 V feed</t>
+          <t>EHPS enable +12 V</t>
         </is>
       </c>
       <c r="P49" s="29" t="inlineStr"/>
       <c r="Q49" s="30" t="inlineStr">
         <is>
-          <t>LOGIC.BUS2-4</t>
+          <t>LOGIC.BUS2-12</t>
         </is>
       </c>
       <c r="R49" s="31" t="inlineStr">
         <is>
-          <t>+12V injectors (LOGIC INJ 15A)</t>
+          <t>+12V EHPS enable (LOGIC MRS 7.5A)</t>
         </is>
       </c>
       <c r="S49" s="32" t="inlineStr"/>
       <c r="T49" s="32" t="inlineStr"/>
       <c r="U49" s="33" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="V49" s="34" t="inlineStr">
         <is>
@@ -6633,11 +6635,11 @@
       <c r="W49" s="34" t="inlineStr"/>
       <c r="X49" s="34" t="inlineStr">
         <is>
-          <t>Blue-White-Blue</t>
+          <t>Blue-White</t>
         </is>
       </c>
       <c r="Y49" s="34" t="n">
-        <v>180</v>
+        <v>530</v>
       </c>
       <c r="Z49" s="35" t="inlineStr">
         <is>
@@ -6650,7 +6652,7 @@
       <c r="AD49" s="38" t="inlineStr"/>
       <c r="AE49" s="38" t="inlineStr">
         <is>
-          <t>break BR_W_INJ_PWR_C (other drawn half w_inj_pwr_c_ac on CabinPower); fuse-box plan LOGIC BUS2-4; DRB102 1 = section A c48 'Switched 12V - INJECTOR power feed, fuse LOGIC INJ'</t>
+          <t>fuse-box plan fb_logic BUS2-12 (20 AWG); DRB102 42 = section A c35 'MRS EPS pump logic enable (fuse box LOGIC MRS, 7.5'</t>
         </is>
       </c>
       <c r="AF49" s="38" t="inlineStr">
@@ -6660,31 +6662,27 @@
       </c>
       <c r="AG49" s="38" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_inj_pwr_ac on A-cabin, 180 mm; w_inj_pwr_c_ac on CabinPower, 250 mm)</t>
+          <t>fuse fed from EPS enable relay k_eps_en pin 87 (ignition-switched); owner proposed: longer half (drawn today as w_fb_mrs_en on A-cabin, 530 mm; w_fb_mrs_en_cp on CabinPower, 250 mm)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="39" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>GND</t>
         </is>
       </c>
       <c r="B50" s="39" t="inlineStr">
         <is>
-          <t>w_cop_pwr_ac</t>
+          <t>w70</t>
         </is>
       </c>
       <c r="C50" s="39" t="inlineStr">
         <is>
-          <t>CabinPower</t>
-        </is>
-      </c>
-      <c r="D50" s="39" t="inlineStr">
-        <is>
           <t>A-cabin</t>
         </is>
       </c>
+      <c r="D50" s="39" t="inlineStr"/>
       <c r="E50" s="40" t="inlineStr">
         <is>
           <t>connector</t>
@@ -6692,85 +6690,81 @@
       </c>
       <c r="F50" s="41" t="inlineStr">
         <is>
-          <t>fb_logic</t>
+          <t>ecu_a</t>
         </is>
       </c>
       <c r="G50" s="42" t="inlineStr">
         <is>
-          <t>FB-LOGIC</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="H50" s="41" t="inlineStr">
         <is>
-          <t>BUS2-3</t>
+          <t>A25</t>
         </is>
       </c>
       <c r="I50" s="42" t="inlineStr">
         <is>
-          <t>Coil +12 V feed</t>
-        </is>
-      </c>
-      <c r="J50" s="42" t="inlineStr">
-        <is>
-          <t>LOGIC box (glove box) fuse COP 15A</t>
-        </is>
-      </c>
+          <t>ECU power ground</t>
+        </is>
+      </c>
+      <c r="J50" s="42" t="inlineStr"/>
       <c r="K50" s="43" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="L50" s="44" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>sp_chassis</t>
         </is>
       </c>
       <c r="M50" s="45" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
-        </is>
-      </c>
-      <c r="N50" s="44" t="n">
-        <v>2</v>
-      </c>
+          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
+        </is>
+      </c>
+      <c r="N50" s="44" t="inlineStr"/>
       <c r="O50" s="45" t="inlineStr">
         <is>
-          <t>Coil +12 V feed</t>
+          <t>ECU power ground</t>
         </is>
       </c>
       <c r="P50" s="45" t="inlineStr"/>
       <c r="Q50" s="46" t="inlineStr">
         <is>
-          <t>LOGIC.BUS2-3</t>
+          <t>STUD.M6-ECU</t>
         </is>
       </c>
       <c r="R50" s="47" t="inlineStr">
         <is>
-          <t>+12V coils (LOGIC COP 15A)</t>
-        </is>
-      </c>
-      <c r="S50" s="48" t="inlineStr"/>
+          <t>Chassis GND (cabin stud M6 at ECU)</t>
+        </is>
+      </c>
+      <c r="S50" s="48" t="inlineStr">
+        <is>
+          <t>sp_chassis</t>
+        </is>
+      </c>
       <c r="T50" s="48" t="inlineStr"/>
       <c r="U50" s="49" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="V50" s="50" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="W50" s="50" t="inlineStr"/>
       <c r="X50" s="50" t="inlineStr">
         <is>
-          <t>Blue-White-Yellow</t>
-        </is>
-      </c>
-      <c r="Y50" s="50" t="n">
-        <v>180</v>
-      </c>
+          <t>Yellow-White-White</t>
+        </is>
+      </c>
+      <c r="Y50" s="50" t="inlineStr"/>
       <c r="Z50" s="51" t="inlineStr">
         <is>
-          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
+          <t>at ECU-A plug</t>
         </is>
       </c>
       <c r="AA50" s="52" t="inlineStr"/>
@@ -6779,7 +6773,7 @@
       <c r="AD50" s="54" t="inlineStr"/>
       <c r="AE50" s="54" t="inlineStr">
         <is>
-          <t>break BR_W_COP_PWR_C (other drawn half w_cop_pwr_c_ac on CabinPower); fuse-box plan LOGIC BUS2-3; DRB102 2 = section A c49 'Switched 12V - COP / ignition coil power feed, fus'</t>
+          <t>channels.csv ecu_a A25 Ground (GND_ECU); splice sp_chassis named in SoT</t>
         </is>
       </c>
       <c r="AF50" s="54" t="inlineStr">
@@ -6787,21 +6781,17 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG50" s="54" t="inlineStr">
-        <is>
-          <t>owner proposed: longer half (drawn today as w_cop_pwr_ac on A-cabin, 180 mm; w_cop_pwr_c_ac on CabinPower, 250 mm)</t>
-        </is>
-      </c>
+      <c r="AG50" s="54" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="23" t="inlineStr">
         <is>
-          <t>EPSEN</t>
+          <t>GND</t>
         </is>
       </c>
       <c r="B51" s="23" t="inlineStr">
         <is>
-          <t>w_fb_mrs_en</t>
+          <t>w_a34</t>
         </is>
       </c>
       <c r="C51" s="23" t="inlineStr">
@@ -6809,11 +6799,7 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D51" s="23" t="inlineStr">
-        <is>
-          <t>CabinPower</t>
-        </is>
-      </c>
+      <c r="D51" s="23" t="inlineStr"/>
       <c r="E51" s="24" t="inlineStr">
         <is>
           <t>connector</t>
@@ -6821,85 +6807,81 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>fb_logic</t>
+          <t>ecu_a</t>
         </is>
       </c>
       <c r="G51" s="26" t="inlineStr">
         <is>
-          <t>FB-LOGIC</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="H51" s="25" t="inlineStr">
         <is>
-          <t>BUS2-12</t>
+          <t>A34</t>
         </is>
       </c>
       <c r="I51" s="26" t="inlineStr">
         <is>
-          <t>EHPS enable +12 V</t>
-        </is>
-      </c>
-      <c r="J51" s="26" t="inlineStr">
-        <is>
-          <t>LOGIC box (glove box) fuse MRS 7.5A Fuse fed from EPS enable relay k_eps_en pin 87 (ignition-switched).</t>
-        </is>
-      </c>
+          <t>ECU power ground</t>
+        </is>
+      </c>
+      <c r="J51" s="26" t="inlineStr"/>
       <c r="K51" s="27" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="L51" s="28" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>sp_chassis</t>
         </is>
       </c>
       <c r="M51" s="29" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
-        </is>
-      </c>
-      <c r="N51" s="28" t="n">
-        <v>42</v>
-      </c>
+          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
+        </is>
+      </c>
+      <c r="N51" s="28" t="inlineStr"/>
       <c r="O51" s="29" t="inlineStr">
         <is>
-          <t>EHPS enable +12 V</t>
+          <t>ECU power ground</t>
         </is>
       </c>
       <c r="P51" s="29" t="inlineStr"/>
       <c r="Q51" s="30" t="inlineStr">
         <is>
-          <t>LOGIC.BUS2-12</t>
+          <t>STUD.M6-ECU</t>
         </is>
       </c>
       <c r="R51" s="31" t="inlineStr">
         <is>
-          <t>+12V EHPS enable (LOGIC MRS 7.5A)</t>
-        </is>
-      </c>
-      <c r="S51" s="32" t="inlineStr"/>
+          <t>Chassis GND (cabin stud M6 at ECU)</t>
+        </is>
+      </c>
+      <c r="S51" s="32" t="inlineStr">
+        <is>
+          <t>sp_chassis</t>
+        </is>
+      </c>
       <c r="T51" s="32" t="inlineStr"/>
       <c r="U51" s="33" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="V51" s="34" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="W51" s="34" t="inlineStr"/>
       <c r="X51" s="34" t="inlineStr">
         <is>
-          <t>Blue-White</t>
-        </is>
-      </c>
-      <c r="Y51" s="34" t="n">
-        <v>530</v>
-      </c>
+          <t>Yellow-White-White</t>
+        </is>
+      </c>
+      <c r="Y51" s="34" t="inlineStr"/>
       <c r="Z51" s="35" t="inlineStr">
         <is>
-          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
+          <t>at ECU-A plug</t>
         </is>
       </c>
       <c r="AA51" s="36" t="inlineStr"/>
@@ -6908,7 +6890,7 @@
       <c r="AD51" s="38" t="inlineStr"/>
       <c r="AE51" s="38" t="inlineStr">
         <is>
-          <t>break BR_W_FB_MRS_EN (other drawn half w_fb_mrs_en_cp on CabinPower); fuse-box plan LOGIC BUS2-12; DRB102 42 = section A c35 'MRS EPS pump logic enable (fuse box LOGIC MRS, 7.5'</t>
+          <t>channels.csv ecu_a A34 Ground (GND_ECU); splice sp_chassis named in SoT</t>
         </is>
       </c>
       <c r="AF51" s="38" t="inlineStr">
@@ -6916,11 +6898,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG51" s="38" t="inlineStr">
-        <is>
-          <t>fuse fed from EPS enable relay k_eps_en pin 87 (ignition-switched); owner proposed: longer half (drawn today as w_fb_mrs_en on A-cabin, 530 mm; w_fb_mrs_en_cp on CabinPower, 250 mm)</t>
-        </is>
-      </c>
+      <c r="AG51" s="38" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="39" t="inlineStr">
@@ -6930,7 +6908,7 @@
       </c>
       <c r="B52" s="39" t="inlineStr">
         <is>
-          <t>w70</t>
+          <t>w_b25_ac</t>
         </is>
       </c>
       <c r="C52" s="39" t="inlineStr">
@@ -6938,27 +6916,27 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D52" s="39" t="inlineStr"/>
+      <c r="D52" s="39" t="inlineStr">
+        <is>
+          <t>B-cabin</t>
+        </is>
+      </c>
       <c r="E52" s="40" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="F52" s="41" t="inlineStr">
         <is>
-          <t>ecu_a</t>
+          <t>sp_chassis</t>
         </is>
       </c>
       <c r="G52" s="42" t="inlineStr">
         <is>
-          <t>ECU-A</t>
-        </is>
-      </c>
-      <c r="H52" s="41" t="inlineStr">
-        <is>
-          <t>A25</t>
-        </is>
-      </c>
+          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
+        </is>
+      </c>
+      <c r="H52" s="41" t="inlineStr"/>
       <c r="I52" s="42" t="inlineStr">
         <is>
           <t>ECU power ground</t>
@@ -6967,26 +6945,34 @@
       <c r="J52" s="42" t="inlineStr"/>
       <c r="K52" s="43" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="L52" s="44" t="inlineStr">
         <is>
-          <t>sp_chassis</t>
+          <t>ecu_b</t>
         </is>
       </c>
       <c r="M52" s="45" t="inlineStr">
         <is>
-          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
-        </is>
-      </c>
-      <c r="N52" s="44" t="inlineStr"/>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
+        </is>
+      </c>
+      <c r="N52" s="44" t="inlineStr">
+        <is>
+          <t>B25</t>
+        </is>
+      </c>
       <c r="O52" s="45" t="inlineStr">
         <is>
           <t>ECU power ground</t>
         </is>
       </c>
-      <c r="P52" s="45" t="inlineStr"/>
+      <c r="P52" s="45" t="inlineStr">
+        <is>
+          <t>ECU-B plug pin B25 (Link G4X, centre dash)</t>
+        </is>
+      </c>
       <c r="Q52" s="46" t="inlineStr">
         <is>
           <t>STUD.M6-ECU</t>
@@ -7020,7 +7006,7 @@
       <c r="Y52" s="50" t="inlineStr"/>
       <c r="Z52" s="51" t="inlineStr">
         <is>
-          <t>at ECU-A plug</t>
+          <t>to ECU-B plug (beside ECU-A)</t>
         </is>
       </c>
       <c r="AA52" s="52" t="inlineStr"/>
@@ -7029,7 +7015,7 @@
       <c r="AD52" s="54" t="inlineStr"/>
       <c r="AE52" s="54" t="inlineStr">
         <is>
-          <t>splice sp_chassis named in SoT; channels.csv ecu_a A25 Ground (GND_ECU)</t>
+          <t>splice sp_chassis named in SoT; channels.csv ecu_b B25 Ground (GND_ECU)</t>
         </is>
       </c>
       <c r="AF52" s="54" t="inlineStr">
@@ -7037,7 +7023,11 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG52" s="54" t="inlineStr"/>
+      <c r="AG52" s="54" t="inlineStr">
+        <is>
+          <t>owner TBD: a half has no length estimate (drawn today as w_b25_ac on A-cabin, ? mm; w_b25 on B-cabin, 120 mm)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="23" t="inlineStr">
@@ -7047,7 +7037,7 @@
       </c>
       <c r="B53" s="23" t="inlineStr">
         <is>
-          <t>w_a34</t>
+          <t>w_b34_ac</t>
         </is>
       </c>
       <c r="C53" s="23" t="inlineStr">
@@ -7055,27 +7045,27 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D53" s="23" t="inlineStr"/>
+      <c r="D53" s="23" t="inlineStr">
+        <is>
+          <t>B-cabin</t>
+        </is>
+      </c>
       <c r="E53" s="24" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="F53" s="25" t="inlineStr">
         <is>
-          <t>ecu_a</t>
+          <t>sp_chassis</t>
         </is>
       </c>
       <c r="G53" s="26" t="inlineStr">
         <is>
-          <t>ECU-A</t>
-        </is>
-      </c>
-      <c r="H53" s="25" t="inlineStr">
-        <is>
-          <t>A34</t>
-        </is>
-      </c>
+          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
+        </is>
+      </c>
+      <c r="H53" s="25" t="inlineStr"/>
       <c r="I53" s="26" t="inlineStr">
         <is>
           <t>ECU power ground</t>
@@ -7084,26 +7074,34 @@
       <c r="J53" s="26" t="inlineStr"/>
       <c r="K53" s="27" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="L53" s="28" t="inlineStr">
         <is>
-          <t>sp_chassis</t>
+          <t>ecu_b</t>
         </is>
       </c>
       <c r="M53" s="29" t="inlineStr">
         <is>
-          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
-        </is>
-      </c>
-      <c r="N53" s="28" t="inlineStr"/>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
+        </is>
+      </c>
+      <c r="N53" s="28" t="inlineStr">
+        <is>
+          <t>B34</t>
+        </is>
+      </c>
       <c r="O53" s="29" t="inlineStr">
         <is>
           <t>ECU power ground</t>
         </is>
       </c>
-      <c r="P53" s="29" t="inlineStr"/>
+      <c r="P53" s="29" t="inlineStr">
+        <is>
+          <t>ECU-B plug pin B34 (Link G4X, centre dash)</t>
+        </is>
+      </c>
       <c r="Q53" s="30" t="inlineStr">
         <is>
           <t>STUD.M6-ECU</t>
@@ -7137,7 +7135,7 @@
       <c r="Y53" s="34" t="inlineStr"/>
       <c r="Z53" s="35" t="inlineStr">
         <is>
-          <t>at ECU-A plug</t>
+          <t>to ECU-B plug (beside ECU-A)</t>
         </is>
       </c>
       <c r="AA53" s="36" t="inlineStr"/>
@@ -7146,7 +7144,7 @@
       <c r="AD53" s="38" t="inlineStr"/>
       <c r="AE53" s="38" t="inlineStr">
         <is>
-          <t>splice sp_chassis named in SoT; channels.csv ecu_a A34 Ground (GND_ECU)</t>
+          <t>splice sp_chassis named in SoT; channels.csv ecu_b B34 Ground (GND_ECU)</t>
         </is>
       </c>
       <c r="AF53" s="38" t="inlineStr">
@@ -7154,17 +7152,21 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG53" s="38" t="inlineStr"/>
+      <c r="AG53" s="38" t="inlineStr">
+        <is>
+          <t>owner TBD: a half has no length estimate (drawn today as w_b34_ac on A-cabin, ? mm; w_b34 on B-cabin, 120 mm)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="39" t="inlineStr">
         <is>
-          <t>GND</t>
+          <t>LAM</t>
         </is>
       </c>
       <c r="B54" s="39" t="inlineStr">
         <is>
-          <t>w_b25_ac</t>
+          <t>w_lamg_ac</t>
         </is>
       </c>
       <c r="C54" s="39" t="inlineStr">
@@ -7179,56 +7181,54 @@
       </c>
       <c r="E54" s="40" t="inlineStr">
         <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F54" s="41" t="inlineStr">
+        <is>
+          <t>bh_b_fw</t>
+        </is>
+      </c>
+      <c r="G54" s="42" t="inlineStr">
+        <is>
+          <t>BH-B (firewall bulkhead DRB102, RH)</t>
+        </is>
+      </c>
+      <c r="H54" s="41" t="n">
+        <v>96</v>
+      </c>
+      <c r="I54" s="42" t="inlineStr">
+        <is>
+          <t>CAN-Lambda ground</t>
+        </is>
+      </c>
+      <c r="J54" s="42" t="inlineStr">
+        <is>
+          <t>(firewall bulkhead, RH)</t>
+        </is>
+      </c>
+      <c r="K54" s="43" t="inlineStr">
+        <is>
           <t>splice</t>
         </is>
       </c>
-      <c r="F54" s="41" t="inlineStr">
+      <c r="L54" s="44" t="inlineStr">
         <is>
           <t>sp_chassis</t>
         </is>
       </c>
-      <c r="G54" s="42" t="inlineStr">
+      <c r="M54" s="45" t="inlineStr">
         <is>
           <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
         </is>
       </c>
-      <c r="H54" s="41" t="inlineStr"/>
-      <c r="I54" s="42" t="inlineStr">
-        <is>
-          <t>ECU power ground</t>
-        </is>
-      </c>
-      <c r="J54" s="42" t="inlineStr"/>
-      <c r="K54" s="43" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="L54" s="44" t="inlineStr">
-        <is>
-          <t>ecu_b</t>
-        </is>
-      </c>
-      <c r="M54" s="45" t="inlineStr">
-        <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
-        </is>
-      </c>
-      <c r="N54" s="44" t="inlineStr">
-        <is>
-          <t>B25</t>
-        </is>
-      </c>
+      <c r="N54" s="44" t="inlineStr"/>
       <c r="O54" s="45" t="inlineStr">
         <is>
-          <t>ECU power ground</t>
-        </is>
-      </c>
-      <c r="P54" s="45" t="inlineStr">
-        <is>
-          <t>ECU-B plug pin B25 (Link G4X, centre dash)</t>
-        </is>
-      </c>
+          <t>CAN-Lambda ground</t>
+        </is>
+      </c>
+      <c r="P54" s="45" t="inlineStr"/>
       <c r="Q54" s="46" t="inlineStr">
         <is>
           <t>STUD.M6-ECU</t>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="T54" s="48" t="inlineStr"/>
       <c r="U54" s="49" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="V54" s="50" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
       <c r="W54" s="50" t="inlineStr"/>
       <c r="X54" s="50" t="inlineStr">
         <is>
-          <t>Yellow-White-White</t>
+          <t>Blue-White-White</t>
         </is>
       </c>
       <c r="Y54" s="50" t="inlineStr"/>
@@ -7271,7 +7271,7 @@
       <c r="AD54" s="54" t="inlineStr"/>
       <c r="AE54" s="54" t="inlineStr">
         <is>
-          <t>splice sp_chassis named in SoT; break BR_W_B25 (other drawn half w_b25 on B-cabin); channels.csv ecu_b B25 Ground (GND_ECU)</t>
+          <t>DRB102 96 = section B c4 'CAN-Lambda ground to cabin chassis ground (14 AWG)'; splice sp_chassis named in SoT</t>
         </is>
       </c>
       <c r="AF54" s="54" t="inlineStr">
@@ -7281,19 +7281,19 @@
       </c>
       <c r="AG54" s="54" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as w_b25_ac on A-cabin, ? mm; w_b25 on B-cabin, 120 mm)</t>
+          <t>owner TBD: a half has no length estimate (drawn today as w_lamg_ac on A-cabin, ? mm; w_lamg_bc on B-cabin, 120 mm)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="23" t="inlineStr">
         <is>
-          <t>GND</t>
+          <t>CSB</t>
         </is>
       </c>
       <c r="B55" s="23" t="inlineStr">
         <is>
-          <t>w_b34_ac</t>
+          <t>w_csbg_ac</t>
         </is>
       </c>
       <c r="C55" s="23" t="inlineStr">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="D55" s="23" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>CSB3</t>
         </is>
       </c>
       <c r="E55" s="24" t="inlineStr">
@@ -7324,38 +7324,34 @@
       <c r="H55" s="25" t="inlineStr"/>
       <c r="I55" s="26" t="inlineStr">
         <is>
-          <t>ECU power ground</t>
+          <t>CSB3 + opto ground</t>
         </is>
       </c>
       <c r="J55" s="26" t="inlineStr"/>
       <c r="K55" s="27" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="L55" s="28" t="inlineStr">
         <is>
-          <t>ecu_b</t>
+          <t>sp_csb_gnd</t>
         </is>
       </c>
       <c r="M55" s="29" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
-        </is>
-      </c>
-      <c r="N55" s="28" t="inlineStr">
-        <is>
-          <t>B34</t>
-        </is>
-      </c>
+          <t>splice sp_csb_gnd on CSB3</t>
+        </is>
+      </c>
+      <c r="N55" s="28" t="inlineStr"/>
       <c r="O55" s="29" t="inlineStr">
         <is>
-          <t>ECU power ground</t>
+          <t>CSB3 + opto ground</t>
         </is>
       </c>
       <c r="P55" s="29" t="inlineStr">
         <is>
-          <t>ECU-B plug pin B34 (Link G4X, centre dash)</t>
+          <t>(CSB3 loom, under centre cluster)</t>
         </is>
       </c>
       <c r="Q55" s="30" t="inlineStr">
@@ -7375,7 +7371,7 @@
       </c>
       <c r="T55" s="32" t="inlineStr"/>
       <c r="U55" s="33" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V55" s="34" t="inlineStr">
         <is>
@@ -7385,13 +7381,13 @@
       <c r="W55" s="34" t="inlineStr"/>
       <c r="X55" s="34" t="inlineStr">
         <is>
-          <t>Yellow-White-White</t>
+          <t>Yellow-Blue-Blue</t>
         </is>
       </c>
       <c r="Y55" s="34" t="inlineStr"/>
       <c r="Z55" s="35" t="inlineStr">
         <is>
-          <t>to ECU-B plug (beside ECU-A)</t>
+          <t>CSB3 branch (centre console)</t>
         </is>
       </c>
       <c r="AA55" s="36" t="inlineStr"/>
@@ -7400,7 +7396,7 @@
       <c r="AD55" s="38" t="inlineStr"/>
       <c r="AE55" s="38" t="inlineStr">
         <is>
-          <t>splice sp_chassis named in SoT; break BR_W_B34 (other drawn half w_b34 on B-cabin); channels.csv ecu_b B34 Ground (GND_ECU)</t>
+          <t>splice sp_chassis named in SoT; splice sp_csb_gnd named in SoT</t>
         </is>
       </c>
       <c r="AF55" s="38" t="inlineStr">
@@ -7410,19 +7406,19 @@
       </c>
       <c r="AG55" s="38" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as w_b34_ac on A-cabin, ? mm; w_b34 on B-cabin, 120 mm)</t>
+          <t>owner TBD: a half has no length estimate (drawn today as w_csbg_ac on A-cabin, ? mm; w_csbg_br on CSB3, ? mm)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="39" t="inlineStr">
         <is>
-          <t>LAM</t>
+          <t>GND</t>
         </is>
       </c>
       <c r="B56" s="39" t="inlineStr">
         <is>
-          <t>w_lamg_ac</t>
+          <t>w66</t>
         </is>
       </c>
       <c r="C56" s="39" t="inlineStr">
@@ -7430,37 +7426,31 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D56" s="39" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
+      <c r="D56" s="39" t="inlineStr"/>
       <c r="E56" s="40" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>terminal</t>
         </is>
       </c>
       <c r="F56" s="41" t="inlineStr">
         <is>
-          <t>bh_b_fw</t>
+          <t>chassis_ring</t>
         </is>
       </c>
       <c r="G56" s="42" t="inlineStr">
         <is>
-          <t>BH-B (firewall bulkhead DRB102, RH)</t>
-        </is>
-      </c>
-      <c r="H56" s="41" t="n">
-        <v>96</v>
-      </c>
+          <t>Ground ring M6, cabin chassis stud at ECU</t>
+        </is>
+      </c>
+      <c r="H56" s="41" t="inlineStr"/>
       <c r="I56" s="42" t="inlineStr">
         <is>
-          <t>CAN-Lambda ground</t>
+          <t>ECU ground chassis</t>
         </is>
       </c>
       <c r="J56" s="42" t="inlineStr">
         <is>
-          <t>(firewall bulkhead, RH)</t>
+          <t>Ground ring M6 on a cabin chassis stud at the ECU (TBD - EWD ground point ID)</t>
         </is>
       </c>
       <c r="K56" s="43" t="inlineStr">
@@ -7481,7 +7471,7 @@
       <c r="N56" s="44" t="inlineStr"/>
       <c r="O56" s="45" t="inlineStr">
         <is>
-          <t>CAN-Lambda ground</t>
+          <t>ECU ground chassis</t>
         </is>
       </c>
       <c r="P56" s="45" t="inlineStr"/>
@@ -7502,7 +7492,7 @@
       </c>
       <c r="T56" s="48" t="inlineStr"/>
       <c r="U56" s="49" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V56" s="50" t="inlineStr">
         <is>
@@ -7512,13 +7502,13 @@
       <c r="W56" s="50" t="inlineStr"/>
       <c r="X56" s="50" t="inlineStr">
         <is>
-          <t>Blue-White-White</t>
+          <t>Yellow-White-White</t>
         </is>
       </c>
       <c r="Y56" s="50" t="inlineStr"/>
       <c r="Z56" s="51" t="inlineStr">
         <is>
-          <t>to ECU-B plug (beside ECU-A)</t>
+          <t>ground stud at ECU</t>
         </is>
       </c>
       <c r="AA56" s="52" t="inlineStr"/>
@@ -7527,29 +7517,25 @@
       <c r="AD56" s="54" t="inlineStr"/>
       <c r="AE56" s="54" t="inlineStr">
         <is>
-          <t>break BR_W_LAMG_B (other drawn half w_lamg_bc on B-cabin); splice sp_chassis named in SoT; DRB102 96 = section B c4 'CAN-Lambda ground to cabin chassis ground (14 AWG)'</t>
+          <t>splice sp_chassis named in SoT</t>
         </is>
       </c>
       <c r="AF56" s="54" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG56" s="54" t="inlineStr">
-        <is>
-          <t>owner TBD: a half has no length estimate (drawn today as w_lamg_ac on A-cabin, ? mm; w_lamg_bc on B-cabin, 120 mm)</t>
-        </is>
-      </c>
+          <t>SOT GAP: end chassis_ring (Ground ring M6, cabin chassis stud at ECU) is drawing-only: not named in the SoT</t>
+        </is>
+      </c>
+      <c r="AG56" s="54" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="23" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>SHLD</t>
         </is>
       </c>
       <c r="B57" s="23" t="inlineStr">
         <is>
-          <t>w_csbg_ac</t>
+          <t>w_drain_ecu_a</t>
         </is>
       </c>
       <c r="C57" s="23" t="inlineStr">
@@ -7557,11 +7543,7 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D57" s="23" t="inlineStr">
-        <is>
-          <t>CSB3</t>
-        </is>
-      </c>
+      <c r="D57" s="23" t="inlineStr"/>
       <c r="E57" s="24" t="inlineStr">
         <is>
           <t>splice</t>
@@ -7569,60 +7551,60 @@
       </c>
       <c r="F57" s="25" t="inlineStr">
         <is>
-          <t>sp_chassis</t>
+          <t>sp_shield_a</t>
         </is>
       </c>
       <c r="G57" s="26" t="inlineStr">
         <is>
-          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
+          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
         </is>
       </c>
       <c r="H57" s="25" t="inlineStr"/>
       <c r="I57" s="26" t="inlineStr">
         <is>
-          <t>CSB3 + opto ground</t>
+          <t>Shield drain</t>
         </is>
       </c>
       <c r="J57" s="26" t="inlineStr"/>
       <c r="K57" s="27" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="L57" s="28" t="inlineStr">
         <is>
-          <t>sp_csb_gnd</t>
+          <t>ecu_a</t>
         </is>
       </c>
       <c r="M57" s="29" t="inlineStr">
         <is>
-          <t>splice sp_csb_gnd on CSB3</t>
-        </is>
-      </c>
-      <c r="N57" s="28" t="inlineStr"/>
+          <t>ECU-A</t>
+        </is>
+      </c>
+      <c r="N57" s="28" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
       <c r="O57" s="29" t="inlineStr">
         <is>
-          <t>CSB3 + opto ground</t>
-        </is>
-      </c>
-      <c r="P57" s="29" t="inlineStr">
-        <is>
-          <t>(CSB3 loom, under centre cluster)</t>
-        </is>
-      </c>
+          <t>Shield drain</t>
+        </is>
+      </c>
+      <c r="P57" s="29" t="inlineStr"/>
       <c r="Q57" s="30" t="inlineStr">
         <is>
-          <t>STUD.M6-ECU</t>
+          <t>ECU-A.A7</t>
         </is>
       </c>
       <c r="R57" s="31" t="inlineStr">
         <is>
-          <t>Chassis GND (cabin stud M6 at ECU)</t>
+          <t>Screen A (ECU A7, SHIELD_A)</t>
         </is>
       </c>
       <c r="S57" s="32" t="inlineStr">
         <is>
-          <t>sp_chassis</t>
+          <t>sp_shield_a</t>
         </is>
       </c>
       <c r="T57" s="32" t="inlineStr"/>
@@ -7634,16 +7616,20 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="W57" s="34" t="inlineStr"/>
+      <c r="W57" s="34" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
       <c r="X57" s="34" t="inlineStr">
         <is>
-          <t>Yellow-Blue-Blue</t>
+          <t>White-Yellow-Blue</t>
         </is>
       </c>
       <c r="Y57" s="34" t="inlineStr"/>
       <c r="Z57" s="35" t="inlineStr">
         <is>
-          <t>CSB3 branch (centre console)</t>
+          <t>at ECU-A plug</t>
         </is>
       </c>
       <c r="AA57" s="36" t="inlineStr"/>
@@ -7652,7 +7638,7 @@
       <c r="AD57" s="38" t="inlineStr"/>
       <c r="AE57" s="38" t="inlineStr">
         <is>
-          <t>splice sp_chassis named in SoT; break BR_W_CSBG (other drawn half w_csbg_br on CSB3)</t>
+          <t>splice sp_shield_a named in SoT; channels.csv ecu_a A7 Shield/Gnd (SHIELD_A)</t>
         </is>
       </c>
       <c r="AF57" s="38" t="inlineStr">
@@ -7662,19 +7648,19 @@
       </c>
       <c r="AG57" s="38" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as w_csbg_ac on A-cabin, ? mm; w_csbg_br on CSB3, ? mm)</t>
+          <t>build (R30): the crank drain is the one crimped into A7; the other drains are soldered onto it 6 mm behind the plug</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="39" t="inlineStr">
         <is>
-          <t>GND</t>
+          <t>CRANKC</t>
         </is>
       </c>
       <c r="B58" s="39" t="inlineStr">
         <is>
-          <t>w66</t>
+          <t>w_shc_crank</t>
         </is>
       </c>
       <c r="C58" s="39" t="inlineStr">
@@ -7685,30 +7671,28 @@
       <c r="D58" s="39" t="inlineStr"/>
       <c r="E58" s="40" t="inlineStr">
         <is>
-          <t>terminal</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="F58" s="41" t="inlineStr">
         <is>
-          <t>chassis_ring</t>
+          <t>bh_a_fw</t>
         </is>
       </c>
       <c r="G58" s="42" t="inlineStr">
         <is>
-          <t>Ground ring M6, cabin chassis stud at ECU</t>
-        </is>
-      </c>
-      <c r="H58" s="41" t="inlineStr"/>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="H58" s="41" t="n">
+        <v>11</v>
+      </c>
       <c r="I58" s="42" t="inlineStr">
         <is>
-          <t>ECU ground chassis</t>
-        </is>
-      </c>
-      <c r="J58" s="42" t="inlineStr">
-        <is>
-          <t>Ground ring M6 on a cabin chassis stud at the ECU (TBD - EWD ground point ID)</t>
-        </is>
-      </c>
+          <t>Crank sensor shield</t>
+        </is>
+      </c>
+      <c r="J58" s="42" t="inlineStr"/>
       <c r="K58" s="43" t="inlineStr">
         <is>
           <t>splice</t>
@@ -7716,55 +7700,59 @@
       </c>
       <c r="L58" s="44" t="inlineStr">
         <is>
-          <t>sp_chassis</t>
+          <t>sp_shield_a</t>
         </is>
       </c>
       <c r="M58" s="45" t="inlineStr">
         <is>
-          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
+          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
         </is>
       </c>
       <c r="N58" s="44" t="inlineStr"/>
       <c r="O58" s="45" t="inlineStr">
         <is>
-          <t>ECU ground chassis</t>
+          <t>Crank sensor shield</t>
         </is>
       </c>
       <c r="P58" s="45" t="inlineStr"/>
       <c r="Q58" s="46" t="inlineStr">
         <is>
-          <t>STUD.M6-ECU</t>
+          <t>ECU-A.A7</t>
         </is>
       </c>
       <c r="R58" s="47" t="inlineStr">
         <is>
-          <t>Chassis GND (cabin stud M6 at ECU)</t>
+          <t>Screen A (ECU A7, SHIELD_A)</t>
         </is>
       </c>
       <c r="S58" s="48" t="inlineStr">
         <is>
-          <t>sp_chassis</t>
+          <t>sp_shield_a</t>
         </is>
       </c>
       <c r="T58" s="48" t="inlineStr"/>
       <c r="U58" s="49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="V58" s="50" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="W58" s="50" t="inlineStr"/>
+      <c r="W58" s="50" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
       <c r="X58" s="50" t="inlineStr">
         <is>
-          <t>Yellow-White-White</t>
+          <t>White-Blue-White</t>
         </is>
       </c>
       <c r="Y58" s="50" t="inlineStr"/>
       <c r="Z58" s="51" t="inlineStr">
         <is>
-          <t>ground stud at ECU</t>
+          <t>trunk ECU-A to bulkhead (RH firewall)</t>
         </is>
       </c>
       <c r="AA58" s="52" t="inlineStr"/>
@@ -7773,7 +7761,7 @@
       <c r="AD58" s="54" t="inlineStr"/>
       <c r="AE58" s="54" t="inlineStr">
         <is>
-          <t>splice sp_chassis named in SoT</t>
+          <t>DRB102 11 = section A c33 'Crank VR screen'; splice sp_shield_a named in SoT</t>
         </is>
       </c>
       <c r="AF58" s="54" t="inlineStr">
@@ -7781,17 +7769,21 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG58" s="54" t="inlineStr"/>
+      <c r="AG58" s="54" t="inlineStr">
+        <is>
+          <t>build (R30): this drain is the one crimped into A7</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="23" t="inlineStr">
         <is>
-          <t>SHLD</t>
+          <t>CAM</t>
         </is>
       </c>
       <c r="B59" s="23" t="inlineStr">
         <is>
-          <t>w_drain_ecu_a</t>
+          <t>w_shc_cam</t>
         </is>
       </c>
       <c r="C59" s="23" t="inlineStr">
@@ -7802,49 +7794,47 @@
       <c r="D59" s="23" t="inlineStr"/>
       <c r="E59" s="24" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="F59" s="25" t="inlineStr">
         <is>
-          <t>sp_shield_a</t>
+          <t>bh_a_fw</t>
         </is>
       </c>
       <c r="G59" s="26" t="inlineStr">
         <is>
-          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
-        </is>
-      </c>
-      <c r="H59" s="25" t="inlineStr"/>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="H59" s="25" t="n">
+        <v>15</v>
+      </c>
       <c r="I59" s="26" t="inlineStr">
         <is>
-          <t>Shield drain</t>
+          <t>Cam sensor shield</t>
         </is>
       </c>
       <c r="J59" s="26" t="inlineStr"/>
       <c r="K59" s="27" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="L59" s="28" t="inlineStr">
         <is>
-          <t>ecu_a</t>
+          <t>sp_shield_a</t>
         </is>
       </c>
       <c r="M59" s="29" t="inlineStr">
         <is>
-          <t>ECU-A</t>
-        </is>
-      </c>
-      <c r="N59" s="28" t="inlineStr">
-        <is>
-          <t>A7</t>
-        </is>
-      </c>
+          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
+        </is>
+      </c>
+      <c r="N59" s="28" t="inlineStr"/>
       <c r="O59" s="29" t="inlineStr">
         <is>
-          <t>Shield drain</t>
+          <t>Cam sensor shield</t>
         </is>
       </c>
       <c r="P59" s="29" t="inlineStr"/>
@@ -7879,13 +7869,13 @@
       </c>
       <c r="X59" s="34" t="inlineStr">
         <is>
-          <t>White-Yellow-Blue</t>
+          <t>Yellow-Yellow</t>
         </is>
       </c>
       <c r="Y59" s="34" t="inlineStr"/>
       <c r="Z59" s="35" t="inlineStr">
         <is>
-          <t>at ECU-A plug</t>
+          <t>trunk ECU-A to bulkhead (RH firewall)</t>
         </is>
       </c>
       <c r="AA59" s="36" t="inlineStr"/>
@@ -7894,7 +7884,7 @@
       <c r="AD59" s="38" t="inlineStr"/>
       <c r="AE59" s="38" t="inlineStr">
         <is>
-          <t>splice sp_shield_a named in SoT; channels.csv ecu_a A7 Shield/Gnd (SHIELD_A)</t>
+          <t>DRB102 15 = section A c34 'Cam Hall screen'; splice sp_shield_a named in SoT</t>
         </is>
       </c>
       <c r="AF59" s="38" t="inlineStr">
@@ -7902,21 +7892,17 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG59" s="38" t="inlineStr">
-        <is>
-          <t>build (R30): the crank drain is the one crimped into A7; the other drains are soldered onto it 6 mm behind the plug</t>
-        </is>
-      </c>
+      <c r="AG59" s="38" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="39" t="inlineStr">
         <is>
-          <t>CRANKC</t>
+          <t>TURBO</t>
         </is>
       </c>
       <c r="B60" s="39" t="inlineStr">
         <is>
-          <t>w_shc_crank</t>
+          <t>w_shc_turbo</t>
         </is>
       </c>
       <c r="C60" s="39" t="inlineStr">
@@ -7941,11 +7927,11 @@
         </is>
       </c>
       <c r="H60" s="41" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I60" s="42" t="inlineStr">
         <is>
-          <t>Crank sensor shield</t>
+          <t>Turbo speed shield</t>
         </is>
       </c>
       <c r="J60" s="42" t="inlineStr"/>
@@ -7967,7 +7953,7 @@
       <c r="N60" s="44" t="inlineStr"/>
       <c r="O60" s="45" t="inlineStr">
         <is>
-          <t>Crank sensor shield</t>
+          <t>Turbo speed shield</t>
         </is>
       </c>
       <c r="P60" s="45" t="inlineStr"/>
@@ -8002,7 +7988,7 @@
       </c>
       <c r="X60" s="50" t="inlineStr">
         <is>
-          <t>White-Blue-White</t>
+          <t>White</t>
         </is>
       </c>
       <c r="Y60" s="50" t="inlineStr"/>
@@ -8017,7 +8003,7 @@
       <c r="AD60" s="54" t="inlineStr"/>
       <c r="AE60" s="54" t="inlineStr">
         <is>
-          <t>splice sp_shield_a named in SoT; DRB102 11 = section A c33 'Crank VR screen'</t>
+          <t>DRB102 19 = section A c6 'Turbo speed screen (to A7)'; splice sp_shield_a named in SoT</t>
         </is>
       </c>
       <c r="AF60" s="54" t="inlineStr">
@@ -8025,21 +8011,17 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG60" s="54" t="inlineStr">
-        <is>
-          <t>build (R30): this drain is the one crimped into A7</t>
-        </is>
-      </c>
+      <c r="AG60" s="54" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="23" t="inlineStr">
         <is>
-          <t>CAM</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="B61" s="23" t="inlineStr">
         <is>
-          <t>w_shc_cam</t>
+          <t>w_shc_flex</t>
         </is>
       </c>
       <c r="C61" s="23" t="inlineStr">
@@ -8064,11 +8046,11 @@
         </is>
       </c>
       <c r="H61" s="25" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I61" s="26" t="inlineStr">
         <is>
-          <t>Cam sensor shield</t>
+          <t>Flex fuel shield</t>
         </is>
       </c>
       <c r="J61" s="26" t="inlineStr"/>
@@ -8090,7 +8072,7 @@
       <c r="N61" s="28" t="inlineStr"/>
       <c r="O61" s="29" t="inlineStr">
         <is>
-          <t>Cam sensor shield</t>
+          <t>Flex fuel shield</t>
         </is>
       </c>
       <c r="P61" s="29" t="inlineStr"/>
@@ -8125,7 +8107,7 @@
       </c>
       <c r="X61" s="34" t="inlineStr">
         <is>
-          <t>Yellow-Yellow</t>
+          <t>White-Blue</t>
         </is>
       </c>
       <c r="Y61" s="34" t="inlineStr"/>
@@ -8140,7 +8122,7 @@
       <c r="AD61" s="38" t="inlineStr"/>
       <c r="AE61" s="38" t="inlineStr">
         <is>
-          <t>splice sp_shield_a named in SoT; DRB102 15 = section A c34 'Cam Hall screen'</t>
+          <t>DRB102 22 = section A c10 'Flex fuel screen (to A7)'; splice sp_shield_a named in SoT</t>
         </is>
       </c>
       <c r="AF61" s="38" t="inlineStr">
@@ -8153,12 +8135,12 @@
     <row r="62">
       <c r="A62" s="39" t="inlineStr">
         <is>
-          <t>TURBO</t>
+          <t>ETBS</t>
         </is>
       </c>
       <c r="B62" s="39" t="inlineStr">
         <is>
-          <t>w_shc_turbo</t>
+          <t>w_shc_etbs</t>
         </is>
       </c>
       <c r="C62" s="39" t="inlineStr">
@@ -8183,11 +8165,11 @@
         </is>
       </c>
       <c r="H62" s="41" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I62" s="42" t="inlineStr">
         <is>
-          <t>Turbo speed shield</t>
+          <t>Throttle shield</t>
         </is>
       </c>
       <c r="J62" s="42" t="inlineStr"/>
@@ -8209,7 +8191,7 @@
       <c r="N62" s="44" t="inlineStr"/>
       <c r="O62" s="45" t="inlineStr">
         <is>
-          <t>Turbo speed shield</t>
+          <t>Throttle shield</t>
         </is>
       </c>
       <c r="P62" s="45" t="inlineStr"/>
@@ -8244,7 +8226,7 @@
       </c>
       <c r="X62" s="50" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="Y62" s="50" t="inlineStr"/>
@@ -8259,7 +8241,7 @@
       <c r="AD62" s="54" t="inlineStr"/>
       <c r="AE62" s="54" t="inlineStr">
         <is>
-          <t>splice sp_shield_a named in SoT; DRB102 19 = section A c6 'Turbo speed screen (to A7)'</t>
+          <t>DRB102 27 = section A c11 'ETB sensor group screen (to A7)'; splice sp_shield_a named in SoT</t>
         </is>
       </c>
       <c r="AF62" s="54" t="inlineStr">
@@ -8272,12 +8254,12 @@
     <row r="63">
       <c r="A63" s="23" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>FP</t>
         </is>
       </c>
       <c r="B63" s="23" t="inlineStr">
         <is>
-          <t>w_shc_flex</t>
+          <t>w_fp85</t>
         </is>
       </c>
       <c r="C63" s="23" t="inlineStr">
@@ -8285,7 +8267,11 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D63" s="23" t="inlineStr"/>
+      <c r="D63" s="23" t="inlineStr">
+        <is>
+          <t>HeavyDC</t>
+        </is>
+      </c>
       <c r="E63" s="24" t="inlineStr">
         <is>
           <t>connector</t>
@@ -8293,83 +8279,85 @@
       </c>
       <c r="F63" s="25" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>k_fp</t>
         </is>
       </c>
       <c r="G63" s="26" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>FP RELAY K1</t>
         </is>
       </c>
       <c r="H63" s="25" t="n">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="I63" s="26" t="inlineStr">
         <is>
-          <t>Flex fuel shield</t>
-        </is>
-      </c>
-      <c r="J63" s="26" t="inlineStr"/>
+          <t>Fuel pump relay (-)</t>
+        </is>
+      </c>
+      <c r="J63" s="26" t="inlineStr">
+        <is>
+          <t>Battery relay block (trunk) relay K1 fuel pump, pin 85</t>
+        </is>
+      </c>
       <c r="K63" s="27" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="L63" s="28" t="inlineStr">
         <is>
-          <t>sp_shield_a</t>
+          <t>ecu_a</t>
         </is>
       </c>
       <c r="M63" s="29" t="inlineStr">
         <is>
-          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
-        </is>
-      </c>
-      <c r="N63" s="28" t="inlineStr"/>
+          <t>ECU-A</t>
+        </is>
+      </c>
+      <c r="N63" s="28" t="inlineStr">
+        <is>
+          <t>A19</t>
+        </is>
+      </c>
       <c r="O63" s="29" t="inlineStr">
         <is>
-          <t>Flex fuel shield</t>
+          <t>Fuel pump relay (-)</t>
         </is>
       </c>
       <c r="P63" s="29" t="inlineStr"/>
       <c r="Q63" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A7</t>
+          <t>ECU-A.A19</t>
         </is>
       </c>
       <c r="R63" s="31" t="inlineStr">
         <is>
-          <t>Screen A (ECU A7, SHIELD_A)</t>
-        </is>
-      </c>
-      <c r="S63" s="32" t="inlineStr">
-        <is>
-          <t>sp_shield_a</t>
-        </is>
-      </c>
+          <t>Fuel pump relay (-) (ECU-A A19)</t>
+        </is>
+      </c>
+      <c r="S63" s="32" t="inlineStr"/>
       <c r="T63" s="32" t="inlineStr"/>
       <c r="U63" s="33" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="V63" s="34" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W63" s="34" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="W63" s="34" t="inlineStr"/>
       <c r="X63" s="34" t="inlineStr">
         <is>
-          <t>White-Blue</t>
-        </is>
-      </c>
-      <c r="Y63" s="34" t="inlineStr"/>
+          <t>White-White-Blue</t>
+        </is>
+      </c>
+      <c r="Y63" s="34" t="n">
+        <v>390</v>
+      </c>
       <c r="Z63" s="35" t="inlineStr">
         <is>
-          <t>trunk ECU-A to bulkhead (RH firewall)</t>
+          <t>glove-box branch (POWER / LOGIC boxes)</t>
         </is>
       </c>
       <c r="AA63" s="36" t="inlineStr"/>
@@ -8378,7 +8366,7 @@
       <c r="AD63" s="38" t="inlineStr"/>
       <c r="AE63" s="38" t="inlineStr">
         <is>
-          <t>splice sp_shield_a named in SoT; DRB102 22 = section A c10 'Flex fuel screen (to A7)'</t>
+          <t>fuse-box plan k_fp 85 (18 AWG); channels.csv ecu_a A19 Aux 3 (AUX3_FP_RLY)</t>
         </is>
       </c>
       <c r="AF63" s="38" t="inlineStr">
@@ -8386,17 +8374,21 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG63" s="38" t="inlineStr"/>
+      <c r="AG63" s="38" t="inlineStr">
+        <is>
+          <t>owner proposed: longer half (drawn today as w_fp85 on A-cabin, 390 mm; w_fp85_h on HeavyDC, 150 mm)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="39" t="inlineStr">
         <is>
-          <t>ETBS</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="B64" s="39" t="inlineStr">
         <is>
-          <t>w_shc_etbs</t>
+          <t>w_str85</t>
         </is>
       </c>
       <c r="C64" s="39" t="inlineStr">
@@ -8404,7 +8396,11 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D64" s="39" t="inlineStr"/>
+      <c r="D64" s="39" t="inlineStr">
+        <is>
+          <t>CabinPower</t>
+        </is>
+      </c>
       <c r="E64" s="40" t="inlineStr">
         <is>
           <t>connector</t>
@@ -8412,83 +8408,85 @@
       </c>
       <c r="F64" s="41" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>k_str</t>
         </is>
       </c>
       <c r="G64" s="42" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>POWER R3</t>
         </is>
       </c>
       <c r="H64" s="41" t="n">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="I64" s="42" t="inlineStr">
         <is>
-          <t>Throttle shield</t>
-        </is>
-      </c>
-      <c r="J64" s="42" t="inlineStr"/>
+          <t>Start relay coil (-)</t>
+        </is>
+      </c>
+      <c r="J64" s="42" t="inlineStr">
+        <is>
+          <t>POWER box (glove box) relay R3 start, pin 85</t>
+        </is>
+      </c>
       <c r="K64" s="43" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="L64" s="44" t="inlineStr">
         <is>
-          <t>sp_shield_a</t>
+          <t>ecu_a</t>
         </is>
       </c>
       <c r="M64" s="45" t="inlineStr">
         <is>
-          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
-        </is>
-      </c>
-      <c r="N64" s="44" t="inlineStr"/>
+          <t>ECU-A</t>
+        </is>
+      </c>
+      <c r="N64" s="44" t="inlineStr">
+        <is>
+          <t>A26</t>
+        </is>
+      </c>
       <c r="O64" s="45" t="inlineStr">
         <is>
-          <t>Throttle shield</t>
+          <t>Start relay coil (-)</t>
         </is>
       </c>
       <c r="P64" s="45" t="inlineStr"/>
       <c r="Q64" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A7</t>
+          <t>ECU-A.A26</t>
         </is>
       </c>
       <c r="R64" s="47" t="inlineStr">
         <is>
-          <t>Screen A (ECU A7, SHIELD_A)</t>
-        </is>
-      </c>
-      <c r="S64" s="48" t="inlineStr">
-        <is>
-          <t>sp_shield_a</t>
-        </is>
-      </c>
+          <t>Start relay coil (-) (ECU-A A26)</t>
+        </is>
+      </c>
+      <c r="S64" s="48" t="inlineStr"/>
       <c r="T64" s="48" t="inlineStr"/>
       <c r="U64" s="49" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="V64" s="50" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W64" s="50" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="W64" s="50" t="inlineStr"/>
       <c r="X64" s="50" t="inlineStr">
         <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="Y64" s="50" t="inlineStr"/>
+          <t>White-Yellow</t>
+        </is>
+      </c>
+      <c r="Y64" s="50" t="n">
+        <v>400</v>
+      </c>
       <c r="Z64" s="51" t="inlineStr">
         <is>
-          <t>trunk ECU-A to bulkhead (RH firewall)</t>
+          <t>glove-box branch (POWER / LOGIC boxes)</t>
         </is>
       </c>
       <c r="AA64" s="52" t="inlineStr"/>
@@ -8497,7 +8495,7 @@
       <c r="AD64" s="54" t="inlineStr"/>
       <c r="AE64" s="54" t="inlineStr">
         <is>
-          <t>splice sp_shield_a named in SoT; DRB102 27 = section A c11 'ETB sensor group screen (to A7)'</t>
+          <t>fuse-box plan k_str 85 (18 AWG); channels.csv ecu_a A26 Aux 8 (AUX8_START_RLY)</t>
         </is>
       </c>
       <c r="AF64" s="54" t="inlineStr">
@@ -8505,17 +8503,21 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG64" s="54" t="inlineStr"/>
+      <c r="AG64" s="54" t="inlineStr">
+        <is>
+          <t>owner proposed: longer half (drawn today as w_str85 on A-cabin, 400 mm; w_str85_cp on CabinPower, 400 mm)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="23" t="inlineStr">
         <is>
-          <t>FP</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="B65" s="23" t="inlineStr">
         <is>
-          <t>w_fp85</t>
+          <t>w_fan85</t>
         </is>
       </c>
       <c r="C65" s="23" t="inlineStr">
@@ -8525,7 +8527,7 @@
       </c>
       <c r="D65" s="23" t="inlineStr">
         <is>
-          <t>HeavyDC</t>
+          <t>CabinPower</t>
         </is>
       </c>
       <c r="E65" s="24" t="inlineStr">
@@ -8535,12 +8537,12 @@
       </c>
       <c r="F65" s="25" t="inlineStr">
         <is>
-          <t>k_fp</t>
+          <t>k_fan</t>
         </is>
       </c>
       <c r="G65" s="26" t="inlineStr">
         <is>
-          <t>FP RELAY K1</t>
+          <t>POWER R4</t>
         </is>
       </c>
       <c r="H65" s="25" t="n">
@@ -8548,12 +8550,12 @@
       </c>
       <c r="I65" s="26" t="inlineStr">
         <is>
-          <t>Fuel pump relay (-)</t>
+          <t>Rad fan relay (-)</t>
         </is>
       </c>
       <c r="J65" s="26" t="inlineStr">
         <is>
-          <t>Battery relay block (trunk) relay K1 fuel pump, pin 85</t>
+          <t>POWER box (glove box) relay R4 radiator fan, pin 85</t>
         </is>
       </c>
       <c r="K65" s="27" t="inlineStr">
@@ -8573,23 +8575,23 @@
       </c>
       <c r="N65" s="28" t="inlineStr">
         <is>
-          <t>A19</t>
+          <t>A29</t>
         </is>
       </c>
       <c r="O65" s="29" t="inlineStr">
         <is>
-          <t>Fuel pump relay (-)</t>
+          <t>Rad fan relay (-)</t>
         </is>
       </c>
       <c r="P65" s="29" t="inlineStr"/>
       <c r="Q65" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A19</t>
+          <t>ECU-A.A29</t>
         </is>
       </c>
       <c r="R65" s="31" t="inlineStr">
         <is>
-          <t>Fuel pump relay (-) (ECU-A A19)</t>
+          <t>Rad fan relay (-) (ECU-A A29)</t>
         </is>
       </c>
       <c r="S65" s="32" t="inlineStr"/>
@@ -8605,11 +8607,11 @@
       <c r="W65" s="34" t="inlineStr"/>
       <c r="X65" s="34" t="inlineStr">
         <is>
-          <t>White-White-Blue</t>
+          <t>Yellow-White</t>
         </is>
       </c>
       <c r="Y65" s="34" t="n">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="Z65" s="35" t="inlineStr">
         <is>
@@ -8622,7 +8624,7 @@
       <c r="AD65" s="38" t="inlineStr"/>
       <c r="AE65" s="38" t="inlineStr">
         <is>
-          <t>break BR_W_FP85 (other drawn half w_fp85_h on HeavyDC); relay pin from the HeavyDC drawing (no channels.csv row); channels.csv ecu_a A19 Aux 3 (AUX3_FP_RLY)</t>
+          <t>fuse-box plan k_fan 85 (18 AWG); channels.csv ecu_a A29 Aux 5 (AUX5_RAD_FAN)</t>
         </is>
       </c>
       <c r="AF65" s="38" t="inlineStr">
@@ -8632,31 +8634,31 @@
       </c>
       <c r="AG65" s="38" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_fp85 on A-cabin, 390 mm; w_fp85_h on HeavyDC, 150 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_fan85 on A-cabin, 410 mm; w_fan85_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="39" t="inlineStr">
         <is>
-          <t>ETB</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="B66" s="39" t="inlineStr">
         <is>
-          <t>w81</t>
+          <t>w_eps_rly</t>
         </is>
       </c>
       <c r="C66" s="39" t="inlineStr">
         <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D66" s="39" t="inlineStr">
+        <is>
           <t>CabinPower</t>
         </is>
       </c>
-      <c r="D66" s="39" t="inlineStr">
-        <is>
-          <t>A-cabin</t>
-        </is>
-      </c>
       <c r="E66" s="40" t="inlineStr">
         <is>
           <t>connector</t>
@@ -8664,12 +8666,12 @@
       </c>
       <c r="F66" s="41" t="inlineStr">
         <is>
-          <t>k_etb</t>
+          <t>k_eps</t>
         </is>
       </c>
       <c r="G66" s="42" t="inlineStr">
         <is>
-          <t>LOGIC M4</t>
+          <t>EHPS RELAY</t>
         </is>
       </c>
       <c r="H66" s="41" t="n">
@@ -8677,12 +8679,12 @@
       </c>
       <c r="I66" s="42" t="inlineStr">
         <is>
-          <t>ETB relay coil (-)</t>
+          <t>EHPS relay coil (-)</t>
         </is>
       </c>
       <c r="J66" s="42" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) relay M14 ETB power, pin 85</t>
+          <t>EHPS pump relay (glove box), pin 85</t>
         </is>
       </c>
       <c r="K66" s="43" t="inlineStr">
@@ -8692,57 +8694,55 @@
       </c>
       <c r="L66" s="44" t="inlineStr">
         <is>
-          <t>ecu_a</t>
+          <t>bh_a_fw</t>
         </is>
       </c>
       <c r="M66" s="45" t="inlineStr">
         <is>
-          <t>ECU-A</t>
-        </is>
-      </c>
-      <c r="N66" s="44" t="inlineStr">
-        <is>
-          <t>A20</t>
-        </is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="N66" s="44" t="n">
+        <v>56</v>
       </c>
       <c r="O66" s="45" t="inlineStr">
         <is>
-          <t>ETB relay coil (-)</t>
+          <t>EHPS relay coil (-)</t>
         </is>
       </c>
       <c r="P66" s="45" t="inlineStr"/>
       <c r="Q66" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A20</t>
+          <t>DRB102.56</t>
         </is>
       </c>
       <c r="R66" s="47" t="inlineStr">
         <is>
-          <t>ETB relay coil (-) (ECU-A A20)</t>
+          <t>EHPS relay coil (-) (DRB102 56)</t>
         </is>
       </c>
       <c r="S66" s="48" t="inlineStr"/>
       <c r="T66" s="48" t="inlineStr"/>
       <c r="U66" s="49" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="V66" s="50" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Violet</t>
         </is>
       </c>
       <c r="W66" s="50" t="inlineStr"/>
       <c r="X66" s="50" t="inlineStr">
         <is>
-          <t>White-White</t>
+          <t>Blue-Blue-Blue</t>
         </is>
       </c>
       <c r="Y66" s="50" t="n">
-        <v>380</v>
+        <v>530</v>
       </c>
       <c r="Z66" s="51" t="inlineStr">
         <is>
-          <t>glove-box branch (POWER / LOGIC boxes)</t>
+          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
         </is>
       </c>
       <c r="AA66" s="52" t="inlineStr"/>
@@ -8751,7 +8751,7 @@
       <c r="AD66" s="54" t="inlineStr"/>
       <c r="AE66" s="54" t="inlineStr">
         <is>
-          <t>break BR_W81 (other drawn half w81_cp on CabinPower); relay pin from the CabinPower drawing (no channels.csv row); fuse-box plan LOGIC M4 85; channels.csv ecu_a A20 Aux 2 (AUX2_ETB_RLY)</t>
+          <t>channels.csv k_eps c2 Coil 85 (MRS_RLY); DRB102 56 = section A c27 'EPS relay coil 85 (R22) - from the MR-S pump B5'</t>
         </is>
       </c>
       <c r="AF66" s="54" t="inlineStr">
@@ -8761,19 +8761,19 @@
       </c>
       <c r="AG66" s="54" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w81 on A-cabin, 380 mm; w81_cp on CabinPower, 400 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_eps_rly on A-cabin, 530 mm; w_eps_rly_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="23" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>ACKILL</t>
         </is>
       </c>
       <c r="B67" s="23" t="inlineStr">
         <is>
-          <t>w_str85</t>
+          <t>w_ac_kill</t>
         </is>
       </c>
       <c r="C67" s="23" t="inlineStr">
@@ -8781,11 +8781,7 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D67" s="23" t="inlineStr">
-        <is>
-          <t>CabinPower</t>
-        </is>
-      </c>
+      <c r="D67" s="23" t="inlineStr"/>
       <c r="E67" s="24" t="inlineStr">
         <is>
           <t>connector</t>
@@ -8793,94 +8789,110 @@
       </c>
       <c r="F67" s="25" t="inlineStr">
         <is>
-          <t>k_str</t>
+          <t>ecu_a</t>
         </is>
       </c>
       <c r="G67" s="26" t="inlineStr">
         <is>
-          <t>POWER R3</t>
-        </is>
-      </c>
-      <c r="H67" s="25" t="n">
-        <v>85</v>
+          <t>ECU-A</t>
+        </is>
+      </c>
+      <c r="H67" s="25" t="inlineStr">
+        <is>
+          <t>A18</t>
+        </is>
       </c>
       <c r="I67" s="26" t="inlineStr">
         <is>
-          <t>Start relay coil (-)</t>
-        </is>
-      </c>
-      <c r="J67" s="26" t="inlineStr">
-        <is>
-          <t>POWER box (glove box) relay R3 start, pin 85</t>
-        </is>
-      </c>
+          <t>A/C cancel (ACT)</t>
+        </is>
+      </c>
+      <c r="J67" s="26" t="inlineStr"/>
       <c r="K67" s="27" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="L67" s="28" t="inlineStr">
         <is>
-          <t>ecu_a</t>
+          <t>A18 (factory)</t>
         </is>
       </c>
       <c r="M67" s="29" t="inlineStr">
         <is>
-          <t>ECU-A</t>
-        </is>
-      </c>
-      <c r="N67" s="28" t="inlineStr">
-        <is>
-          <t>A26</t>
-        </is>
+          <t>OEM A/C amplifier</t>
+        </is>
+      </c>
+      <c r="N67" s="28" t="n">
+        <v>11</v>
       </c>
       <c r="O67" s="29" t="inlineStr">
         <is>
-          <t>Start relay coil (-)</t>
-        </is>
-      </c>
-      <c r="P67" s="29" t="inlineStr"/>
+          <t>A/C cancel (ACT)</t>
+        </is>
+      </c>
+      <c r="P67" s="29" t="inlineStr">
+        <is>
+          <t>A/C amp A18 pin 11 (1993: A15), behind the glove box. Solder splice onto the factory G-Y lead. EWD 1992 p.93 / p.218; locator 1990 p.17.</t>
+        </is>
+      </c>
       <c r="Q67" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A26</t>
+          <t>ECU-A.A18</t>
         </is>
       </c>
       <c r="R67" s="31" t="inlineStr">
         <is>
-          <t>Start relay coil (-) (ECU-A A26)</t>
+          <t>A/C cancel (ACT) (ECU-A A18)</t>
         </is>
       </c>
       <c r="S67" s="32" t="inlineStr"/>
       <c r="T67" s="32" t="inlineStr"/>
       <c r="U67" s="33" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V67" s="34" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Gray</t>
         </is>
       </c>
       <c r="W67" s="34" t="inlineStr"/>
       <c r="X67" s="34" t="inlineStr">
         <is>
-          <t>White-Yellow</t>
+          <t>White-Yellow-Yellow</t>
         </is>
       </c>
       <c r="Y67" s="34" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="Z67" s="35" t="inlineStr">
         <is>
-          <t>glove-box branch (POWER / LOGIC boxes)</t>
-        </is>
-      </c>
-      <c r="AA67" s="36" t="inlineStr"/>
-      <c r="AB67" s="37" t="inlineStr"/>
-      <c r="AC67" s="38" t="inlineStr"/>
-      <c r="AD67" s="38" t="inlineStr"/>
+          <t>A/C amp branch (behind dash)</t>
+        </is>
+      </c>
+      <c r="AA67" s="36" t="inlineStr">
+        <is>
+          <t>A/C amplifier A18 (1993 book: A15), passenger side behind the glove box, on the bottom of the evaporator housing; tap point on the lead at the amplifier, distance TBD</t>
+        </is>
+      </c>
+      <c r="AB67" s="37" t="inlineStr">
+        <is>
+          <t>G-Y</t>
+        </is>
+      </c>
+      <c r="AC67" s="38" t="inlineStr">
+        <is>
+          <t>1992 Celica EWD132U p.93 and p.218 (docs/electrical/ewd-snips/1992-celica-ewd132u-a17-act-p093.png, 1992-celica-ewd132u-a17-clutch-p218.png); 1990 ST185 book locator A18; 1992 EWD132U p.93 and p.218 (A17-11 = A18-11); locator 1990 ST185 EWD p.17 Instrument Panel (ewd-snips/1990-st185-locations-dash.png); Mitchell locations (docs/research/AUTO-AC-AMP-OPTIONS.html)</t>
+        </is>
+      </c>
+      <c r="AD67" s="38" t="inlineStr">
+        <is>
+          <t>solder splice onto the factory G-Y ACT lead at the A/C amplifier</t>
+        </is>
+      </c>
       <c r="AE67" s="38" t="inlineStr">
         <is>
-          <t>break BR_W_STR85 (other drawn half w_str85_cp on CabinPower); relay pin from the CabinPower drawing (no channels.csv row); fuse-box plan POWER R3 85; channels.csv ecu_a A26 Aux 8 (AUX8_START_RLY)</t>
+          <t>channels.csv ecu_a A18 Aux 4 (AUX4_AC_KILL); flying lead FL_ACAMP_ACT: EWD A18 pin 11 G-Y</t>
         </is>
       </c>
       <c r="AF67" s="38" t="inlineStr">
@@ -8888,128 +8900,142 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG67" s="38" t="inlineStr">
-        <is>
-          <t>owner proposed: longer half (drawn today as w_str85 on A-cabin, 400 mm; w_str85_cp on CabinPower, 400 mm)</t>
-        </is>
-      </c>
+      <c r="AG67" s="38" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="39" t="inlineStr">
         <is>
-          <t>EFI</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B68" s="39" t="inlineStr">
         <is>
-          <t>w76</t>
+          <t>w_ac_psw_in</t>
         </is>
       </c>
       <c r="C68" s="39" t="inlineStr">
         <is>
-          <t>CabinPower</t>
+          <t>A-cabin</t>
         </is>
       </c>
       <c r="D68" s="39" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>EngineRoom-C</t>
         </is>
       </c>
       <c r="E68" s="40" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F68" s="41" t="inlineStr">
         <is>
-          <t>k_efi</t>
+          <t>A5 (factory)</t>
         </is>
       </c>
       <c r="G68" s="42" t="inlineStr">
         <is>
-          <t>POWER R2</t>
+          <t>OEM A5, factory Y-R lead</t>
         </is>
       </c>
       <c r="H68" s="41" t="n">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="I68" s="42" t="inlineStr">
         <is>
-          <t>EFI relay coil (-)</t>
+          <t>A/C pressure sw out</t>
         </is>
       </c>
       <c r="J68" s="42" t="inlineStr">
         <is>
-          <t>POWER box (glove box) relay R2 EFI main, pin 85</t>
+          <t>Runs on in ST185-EngineRoom-C to A/C pressure switch A5 pin 4 (engine bay): new wire to the switch's own mating plug, plug part TBD. EWD 1990 p.152.</t>
         </is>
       </c>
       <c r="K68" s="43" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="L68" s="44" t="inlineStr">
         <is>
-          <t>ecu_a</t>
+          <t>sp_ac_psw</t>
         </is>
       </c>
       <c r="M68" s="45" t="inlineStr">
         <is>
-          <t>ECU-A</t>
-        </is>
-      </c>
-      <c r="N68" s="44" t="inlineStr">
-        <is>
-          <t>A28</t>
-        </is>
-      </c>
+          <t>splice sp_ac_psw (SP-AC-PSW: A/C pressure switch output)</t>
+        </is>
+      </c>
+      <c r="N68" s="44" t="inlineStr"/>
       <c r="O68" s="45" t="inlineStr">
         <is>
-          <t>EFI relay coil (-)</t>
+          <t>A/C pressure sw out</t>
         </is>
       </c>
       <c r="P68" s="45" t="inlineStr"/>
       <c r="Q68" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A28</t>
+          <t>A5.4</t>
         </is>
       </c>
       <c r="R68" s="47" t="inlineStr">
         <is>
-          <t>EFI relay coil (-) (ECU-A A28)</t>
-        </is>
-      </c>
-      <c r="S68" s="48" t="inlineStr"/>
+          <t>A/C pressure-switched relay coil +</t>
+        </is>
+      </c>
+      <c r="S68" s="48" t="inlineStr">
+        <is>
+          <t>sp_ac_psw</t>
+        </is>
+      </c>
       <c r="T68" s="48" t="inlineStr"/>
       <c r="U68" s="49" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V68" s="50" t="inlineStr">
         <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="W68" s="50" t="inlineStr"/>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="W68" s="50" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="X68" s="50" t="inlineStr">
         <is>
-          <t>Blue-Yellow</t>
-        </is>
-      </c>
-      <c r="Y68" s="50" t="n">
-        <v>370</v>
-      </c>
+          <t>Yellow-Blue</t>
+        </is>
+      </c>
+      <c r="Y68" s="50" t="inlineStr"/>
       <c r="Z68" s="51" t="inlineStr">
         <is>
-          <t>glove-box branch (POWER / LOGIC boxes)</t>
-        </is>
-      </c>
-      <c r="AA68" s="52" t="inlineStr"/>
-      <c r="AB68" s="53" t="inlineStr"/>
-      <c r="AC68" s="54" t="inlineStr"/>
-      <c r="AD68" s="54" t="inlineStr"/>
+          <t>A/C amp branch (behind dash)</t>
+        </is>
+      </c>
+      <c r="AA68" s="52" t="inlineStr">
+        <is>
+          <t>A/C pressure switch A5, engine bay; exact spot TBD (no locator figure in the repo)</t>
+        </is>
+      </c>
+      <c r="AB68" s="53" t="inlineStr">
+        <is>
+          <t>Y-R (factory wiring; new wire here)</t>
+        </is>
+      </c>
+      <c r="AC68" s="54" t="inlineStr">
+        <is>
+          <t>1990 ST185 EWD p.152 (docs/electrical/ewd-snips/1990-st185-autoac-pressure-clutch-p152.png); 1990 ST185 EWD p.152 (A5 pin 4 Y-R)</t>
+        </is>
+      </c>
+      <c r="AD68" s="54" t="inlineStr">
+        <is>
+          <t>new-wire run terminated at the switch's own mating plug (no factory engine-bay wire reused, Section 39, 2026-10-04); plug part number not yet chosen</t>
+        </is>
+      </c>
       <c r="AE68" s="54" t="inlineStr">
         <is>
-          <t>break BR_W76 (other drawn half w76_cp on CabinPower); relay pin from the CabinPower drawing (no channels.csv row); fuse-box plan POWER R2 85; channels.csv ecu_a A28 Aux 6 (AUX6_EFI_HOLD)</t>
+          <t>flying lead FL_A5_4: EWD A5 pin 4 Y-R (factory wiring; new wire here); splice sp_ac_psw named in SoT</t>
         </is>
       </c>
       <c r="AF68" s="54" t="inlineStr">
@@ -9019,19 +9045,19 @@
       </c>
       <c r="AG68" s="54" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w76 on A-cabin, 370 mm; w76_cp on CabinPower, 400 mm)</t>
+          <t>owner TBD: a half has no length estimate (drawn today as w_ac_psw_in on A-cabin, ? mm; w_ac_psw on EngineRoom-C, 100 mm)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="23" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B69" s="23" t="inlineStr">
         <is>
-          <t>w_fan85</t>
+          <t>w_ac_psw_sw</t>
         </is>
       </c>
       <c r="C69" s="23" t="inlineStr">
@@ -9039,106 +9065,120 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D69" s="23" t="inlineStr">
-        <is>
-          <t>CabinPower</t>
-        </is>
-      </c>
+      <c r="D69" s="23" t="inlineStr"/>
       <c r="E69" s="24" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F69" s="25" t="inlineStr">
         <is>
-          <t>k_fan</t>
+          <t>A18 (factory)</t>
         </is>
       </c>
       <c r="G69" s="26" t="inlineStr">
         <is>
-          <t>POWER R4</t>
+          <t>OEM A/C amplifier</t>
         </is>
       </c>
       <c r="H69" s="25" t="n">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="I69" s="26" t="inlineStr">
         <is>
-          <t>Rad fan relay (-)</t>
+          <t>A/C pressure sw out</t>
         </is>
       </c>
       <c r="J69" s="26" t="inlineStr">
         <is>
-          <t>POWER box (glove box) relay R4 radiator fan, pin 85</t>
+          <t>A/C amp A18 pin 13 (1993: A15), behind the glove box. Solder splice onto the factory Y-R lead. EWD 1990 p.152; locator 1990 p.17.</t>
         </is>
       </c>
       <c r="K69" s="27" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="L69" s="28" t="inlineStr">
         <is>
-          <t>ecu_a</t>
+          <t>sp_ac_psw</t>
         </is>
       </c>
       <c r="M69" s="29" t="inlineStr">
         <is>
-          <t>ECU-A</t>
-        </is>
-      </c>
-      <c r="N69" s="28" t="inlineStr">
-        <is>
-          <t>A29</t>
-        </is>
-      </c>
+          <t>splice sp_ac_psw (SP-AC-PSW: A/C pressure switch output)</t>
+        </is>
+      </c>
+      <c r="N69" s="28" t="inlineStr"/>
       <c r="O69" s="29" t="inlineStr">
         <is>
-          <t>Rad fan relay (-)</t>
+          <t>A/C pressure sw out</t>
         </is>
       </c>
       <c r="P69" s="29" t="inlineStr"/>
       <c r="Q69" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A29</t>
+          <t>A5.4</t>
         </is>
       </c>
       <c r="R69" s="31" t="inlineStr">
         <is>
-          <t>Rad fan relay (-) (ECU-A A29)</t>
-        </is>
-      </c>
-      <c r="S69" s="32" t="inlineStr"/>
+          <t>A/C pressure-switched relay coil +</t>
+        </is>
+      </c>
+      <c r="S69" s="32" t="inlineStr">
+        <is>
+          <t>sp_ac_psw</t>
+        </is>
+      </c>
       <c r="T69" s="32" t="inlineStr"/>
       <c r="U69" s="33" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V69" s="34" t="inlineStr">
         <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="W69" s="34" t="inlineStr"/>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="W69" s="34" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="X69" s="34" t="inlineStr">
         <is>
-          <t>Yellow-White</t>
-        </is>
-      </c>
-      <c r="Y69" s="34" t="n">
-        <v>410</v>
-      </c>
+          <t>Yellow-Blue</t>
+        </is>
+      </c>
+      <c r="Y69" s="34" t="inlineStr"/>
       <c r="Z69" s="35" t="inlineStr">
         <is>
-          <t>glove-box branch (POWER / LOGIC boxes)</t>
-        </is>
-      </c>
-      <c r="AA69" s="36" t="inlineStr"/>
-      <c r="AB69" s="37" t="inlineStr"/>
-      <c r="AC69" s="38" t="inlineStr"/>
-      <c r="AD69" s="38" t="inlineStr"/>
+          <t>A/C amp branch (behind dash)</t>
+        </is>
+      </c>
+      <c r="AA69" s="36" t="inlineStr">
+        <is>
+          <t>A/C amplifier A18 (1993 book: A15), passenger side behind the glove box, on the bottom of the evaporator housing; tap point on the lead at the amplifier, distance TBD</t>
+        </is>
+      </c>
+      <c r="AB69" s="37" t="inlineStr">
+        <is>
+          <t>Y-R</t>
+        </is>
+      </c>
+      <c r="AC69" s="38" t="inlineStr">
+        <is>
+          <t>1990 ST185 EWD p.152 (docs/electrical/ewd-snips/1990-st185-autoac-pressure-clutch-p152.png); 1992 EWD132U p.219 A17-13 (ewd-snips/1992-celica-ewd132u-a17-pressure-p219.png); 1990 ST185 EWD p.152; 1992 EWD132U p.219 (A17-13); locator 1990 ST185 EWD p.17 Instrument Panel (ewd-snips/1990-st185-locations-dash.png); Mitchell locations (docs/research/AUTO-AC-AMP-OPTIONS.html)</t>
+        </is>
+      </c>
+      <c r="AD69" s="38" t="inlineStr">
+        <is>
+          <t>solder splice onto the factory Y-R lead at the A/C amplifier</t>
+        </is>
+      </c>
       <c r="AE69" s="38" t="inlineStr">
         <is>
-          <t>break BR_W_FAN85 (other drawn half w_fan85_cp on CabinPower); relay pin from the CabinPower drawing (no channels.csv row); fuse-box plan POWER R4 85; channels.csv ecu_a A29 Aux 5 (AUX5_RAD_FAN)</t>
+          <t>flying lead FL_ACAMP_PSW: EWD A18 pin 13 Y-R; splice sp_ac_psw named in SoT</t>
         </is>
       </c>
       <c r="AF69" s="38" t="inlineStr">
@@ -9146,21 +9186,17 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG69" s="38" t="inlineStr">
-        <is>
-          <t>owner proposed: longer half (drawn today as w_fan85 on A-cabin, 410 mm; w_fan85_cp on CabinPower, 400 mm)</t>
-        </is>
-      </c>
+      <c r="AG69" s="38" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="39" t="inlineStr">
         <is>
-          <t>EPS</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B70" s="39" t="inlineStr">
         <is>
-          <t>w_eps_rly</t>
+          <t>w_acc86</t>
         </is>
       </c>
       <c r="C70" s="39" t="inlineStr">
@@ -9175,88 +9211,92 @@
       </c>
       <c r="E70" s="40" t="inlineStr">
         <is>
+          <t>splice</t>
+        </is>
+      </c>
+      <c r="F70" s="41" t="inlineStr">
+        <is>
+          <t>sp_ac_psw</t>
+        </is>
+      </c>
+      <c r="G70" s="42" t="inlineStr">
+        <is>
+          <t>splice sp_ac_psw (SP-AC-PSW: A/C pressure switch output)</t>
+        </is>
+      </c>
+      <c r="H70" s="41" t="inlineStr"/>
+      <c r="I70" s="42" t="inlineStr">
+        <is>
+          <t>A/C clutch relay (+)</t>
+        </is>
+      </c>
+      <c r="J70" s="42" t="inlineStr"/>
+      <c r="K70" s="43" t="inlineStr">
+        <is>
           <t>connector</t>
         </is>
       </c>
-      <c r="F70" s="41" t="inlineStr">
-        <is>
-          <t>k_eps</t>
-        </is>
-      </c>
-      <c r="G70" s="42" t="inlineStr">
-        <is>
-          <t>EHPS RELAY</t>
-        </is>
-      </c>
-      <c r="H70" s="41" t="n">
-        <v>85</v>
-      </c>
-      <c r="I70" s="42" t="inlineStr">
-        <is>
-          <t>EHPS relay coil (-)</t>
-        </is>
-      </c>
-      <c r="J70" s="42" t="inlineStr">
-        <is>
-          <t>EHPS pump relay (glove box), pin 85</t>
-        </is>
-      </c>
-      <c r="K70" s="43" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
       <c r="L70" s="44" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>k_acc</t>
         </is>
       </c>
       <c r="M70" s="45" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>LOGIC M5</t>
         </is>
       </c>
       <c r="N70" s="44" t="n">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="O70" s="45" t="inlineStr">
         <is>
-          <t>EHPS relay coil (-)</t>
-        </is>
-      </c>
-      <c r="P70" s="45" t="inlineStr"/>
+          <t>A/C clutch relay (+)</t>
+        </is>
+      </c>
+      <c r="P70" s="45" t="inlineStr">
+        <is>
+          <t>LOGIC box (glove box) relay M15 A/C clutch, pin 86</t>
+        </is>
+      </c>
       <c r="Q70" s="46" t="inlineStr">
         <is>
-          <t>bh_a_fw.56</t>
+          <t>A5.4</t>
         </is>
       </c>
       <c r="R70" s="47" t="inlineStr">
         <is>
-          <t>EHPS relay coil (-) (bh_a_fw 56)</t>
-        </is>
-      </c>
-      <c r="S70" s="48" t="inlineStr"/>
+          <t>A/C pressure-switched relay coil +</t>
+        </is>
+      </c>
+      <c r="S70" s="48" t="inlineStr">
+        <is>
+          <t>sp_ac_psw</t>
+        </is>
+      </c>
       <c r="T70" s="48" t="inlineStr"/>
       <c r="U70" s="49" t="n">
         <v>18</v>
       </c>
       <c r="V70" s="50" t="inlineStr">
         <is>
-          <t>Violet</t>
-        </is>
-      </c>
-      <c r="W70" s="50" t="inlineStr"/>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="W70" s="50" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="X70" s="50" t="inlineStr">
         <is>
-          <t>Blue-Blue-Blue</t>
-        </is>
-      </c>
-      <c r="Y70" s="50" t="n">
-        <v>530</v>
-      </c>
+          <t>Yellow-Blue</t>
+        </is>
+      </c>
+      <c r="Y70" s="50" t="inlineStr"/>
       <c r="Z70" s="51" t="inlineStr">
         <is>
-          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
+          <t>A/C amp branch (behind dash)</t>
         </is>
       </c>
       <c r="AA70" s="52" t="inlineStr"/>
@@ -9265,7 +9305,7 @@
       <c r="AD70" s="54" t="inlineStr"/>
       <c r="AE70" s="54" t="inlineStr">
         <is>
-          <t>break BR_W_EPS_RLY (other drawn half w_eps_rly_cp on CabinPower); relay pin from the CabinPower drawing (no channels.csv row); DRB102 56 = section A c27 'EPS relay coil 85 (R22) - from the MR-S pump B5'</t>
+          <t>splice sp_ac_psw named in SoT; fuse-box plan k_acc 86 (18 AWG)</t>
         </is>
       </c>
       <c r="AF70" s="54" t="inlineStr">
@@ -9275,19 +9315,19 @@
       </c>
       <c r="AG70" s="54" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_eps_rly on A-cabin, 530 mm; w_eps_rly_cp on CabinPower, 400 mm)</t>
+          <t>owner TBD: a half has no length estimate (drawn today as w_acc86 on A-cabin, ? mm; w_acc86_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="23" t="inlineStr">
         <is>
-          <t>ACKILL</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="B71" s="23" t="inlineStr">
         <is>
-          <t>w_ac_kill</t>
+          <t>w_aps_vc1</t>
         </is>
       </c>
       <c r="C71" s="23" t="inlineStr">
@@ -9303,110 +9343,92 @@
       </c>
       <c r="F71" s="25" t="inlineStr">
         <is>
-          <t>ecu_a</t>
+          <t>aps</t>
         </is>
       </c>
       <c r="G71" s="26" t="inlineStr">
         <is>
-          <t>ECU-A</t>
-        </is>
-      </c>
-      <c r="H71" s="25" t="inlineStr">
-        <is>
-          <t>A18</t>
-        </is>
+          <t>PEDAL</t>
+        </is>
+      </c>
+      <c r="H71" s="25" t="n">
+        <v>4</v>
       </c>
       <c r="I71" s="26" t="inlineStr">
         <is>
-          <t>A/C cancel (ACT)</t>
+          <t>+5 V pedal sensor 1</t>
         </is>
       </c>
       <c r="J71" s="26" t="inlineStr"/>
       <c r="K71" s="27" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="L71" s="28" t="inlineStr">
         <is>
-          <t>A18 (factory)</t>
+          <t>sp_5v_2</t>
         </is>
       </c>
       <c r="M71" s="29" t="inlineStr">
         <is>
-          <t>OEM A/C amplifier</t>
-        </is>
-      </c>
-      <c r="N71" s="28" t="n">
-        <v>11</v>
-      </c>
+          <t>splice sp_5v_2 (SP-5V-PEDAL: +5 V to pedal + cruise)</t>
+        </is>
+      </c>
+      <c r="N71" s="28" t="inlineStr"/>
       <c r="O71" s="29" t="inlineStr">
         <is>
-          <t>A/C cancel (ACT)</t>
-        </is>
-      </c>
-      <c r="P71" s="29" t="inlineStr">
-        <is>
-          <t>A/C amp A18 pin 11 (1993: A15), behind the glove box. Solder splice onto the factory G-Y lead. EWD 1992 p.93 / p.218; locator 1990 p.17.</t>
-        </is>
-      </c>
+          <t>+5 V pedal sensor 1</t>
+        </is>
+      </c>
+      <c r="P71" s="29" t="inlineStr"/>
       <c r="Q71" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A18</t>
+          <t>ECU-A.A32</t>
         </is>
       </c>
       <c r="R71" s="31" t="inlineStr">
         <is>
-          <t>A/C cancel (ACT) (ECU-A A18)</t>
-        </is>
-      </c>
-      <c r="S71" s="32" t="inlineStr"/>
-      <c r="T71" s="32" t="inlineStr"/>
+          <t>+5V sensor (ECU-A A32)</t>
+        </is>
+      </c>
+      <c r="S71" s="32" t="inlineStr">
+        <is>
+          <t>sp_5v_2</t>
+        </is>
+      </c>
+      <c r="T71" s="32" t="inlineStr">
+        <is>
+          <t>cab_aps1</t>
+        </is>
+      </c>
       <c r="U71" s="33" t="n">
         <v>20</v>
       </c>
       <c r="V71" s="34" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W71" s="34" t="inlineStr"/>
       <c r="X71" s="34" t="inlineStr">
         <is>
-          <t>White-Yellow-Yellow</t>
-        </is>
-      </c>
-      <c r="Y71" s="34" t="n">
-        <v>600</v>
-      </c>
+          <t>Blue-Blue</t>
+        </is>
+      </c>
+      <c r="Y71" s="34" t="inlineStr"/>
       <c r="Z71" s="35" t="inlineStr">
         <is>
-          <t>A/C amp branch (behind dash)</t>
-        </is>
-      </c>
-      <c r="AA71" s="36" t="inlineStr">
-        <is>
-          <t>A/C amplifier A18 (1993 book: A15), passenger side behind the glove box, on the bottom of the evaporator housing; tap point on the lead at the amplifier, distance TBD</t>
-        </is>
-      </c>
-      <c r="AB71" s="37" t="inlineStr">
-        <is>
-          <t>G-Y</t>
-        </is>
-      </c>
-      <c r="AC71" s="38" t="inlineStr">
-        <is>
-          <t>1992 Celica EWD132U p.93 and p.218 (docs/electrical/ewd-snips/1992-celica-ewd132u-a17-act-p093.png, 1992-celica-ewd132u-a17-clutch-p218.png); 1990 ST185 book locator A18; 1992 EWD132U p.93 and p.218 (A17-11 = A18-11); locator 1990 ST185 EWD p.17 Instrument Panel (ewd-snips/1990-st185-locations-dash.png); Mitchell locations (docs/research/AUTO-AC-AMP-OPTIONS.html)</t>
-        </is>
-      </c>
-      <c r="AD71" s="38" t="inlineStr">
-        <is>
-          <t>solder splice onto the factory G-Y ACT lead at the A/C amplifier</t>
-        </is>
-      </c>
+          <t>pedal branch (driver footwell)</t>
+        </is>
+      </c>
+      <c r="AA71" s="36" t="inlineStr"/>
+      <c r="AB71" s="37" t="inlineStr"/>
+      <c r="AC71" s="38" t="inlineStr"/>
+      <c r="AD71" s="38" t="inlineStr"/>
       <c r="AE71" s="38" t="inlineStr">
         <is>
-          <t>flying lead FL_ACAMP_ACT: EWD A18 pin 11 G-Y; channels.csv ecu_a A18 Aux 4 (AUX4_AC_KILL)</t>
+          <t>splice sp_5v_2 named in SoT</t>
         </is>
       </c>
       <c r="AF71" s="38" t="inlineStr">
@@ -9414,17 +9436,21 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG71" s="38" t="inlineStr"/>
+      <c r="AG71" s="38" t="inlineStr">
+        <is>
+          <t>pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="39" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>SGND</t>
         </is>
       </c>
       <c r="B72" s="39" t="inlineStr">
         <is>
-          <t>w_ac_psw_in</t>
+          <t>w40</t>
         </is>
       </c>
       <c r="C72" s="39" t="inlineStr">
@@ -9432,39 +9458,31 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D72" s="39" t="inlineStr">
-        <is>
-          <t>EngineRoom-C</t>
-        </is>
-      </c>
+      <c r="D72" s="39" t="inlineStr"/>
       <c r="E72" s="40" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="F72" s="41" t="inlineStr">
         <is>
-          <t>A5 (factory)</t>
+          <t>aps</t>
         </is>
       </c>
       <c r="G72" s="42" t="inlineStr">
         <is>
-          <t>OEM A5, factory Y-R lead</t>
+          <t>PEDAL</t>
         </is>
       </c>
       <c r="H72" s="41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I72" s="42" t="inlineStr">
         <is>
-          <t>A/C pressure sw out</t>
-        </is>
-      </c>
-      <c r="J72" s="42" t="inlineStr">
-        <is>
-          <t>Runs on in ST185-EngineRoom-C to A/C pressure switch A5 pin 4 (engine bay): new wire to the switch's own mating plug, plug part TBD. EWD 1990 p.152.</t>
-        </is>
-      </c>
+          <t>Pedal 1 ground</t>
+        </is>
+      </c>
+      <c r="J72" s="42" t="inlineStr"/>
       <c r="K72" s="43" t="inlineStr">
         <is>
           <t>splice</t>
@@ -9472,37 +9490,41 @@
       </c>
       <c r="L72" s="44" t="inlineStr">
         <is>
-          <t>sp_ac_psw</t>
+          <t>sp_gndout</t>
         </is>
       </c>
       <c r="M72" s="45" t="inlineStr">
         <is>
-          <t>splice sp_ac_psw (SP-AC-PSW: A/C pressure switch output)</t>
+          <t>splice sp_gndout (SP-GNDOUT-A: sensor ground)</t>
         </is>
       </c>
       <c r="N72" s="44" t="inlineStr"/>
       <c r="O72" s="45" t="inlineStr">
         <is>
-          <t>A/C pressure sw out</t>
+          <t>Pedal 1 ground</t>
         </is>
       </c>
       <c r="P72" s="45" t="inlineStr"/>
       <c r="Q72" s="46" t="inlineStr">
         <is>
-          <t>A5.4</t>
+          <t>ECU-A.A24</t>
         </is>
       </c>
       <c r="R72" s="47" t="inlineStr">
         <is>
-          <t>A/C pressure-switched relay coil +</t>
+          <t>Sensor GND (ECU-A A24)</t>
         </is>
       </c>
       <c r="S72" s="48" t="inlineStr">
         <is>
-          <t>sp_ac_psw</t>
-        </is>
-      </c>
-      <c r="T72" s="48" t="inlineStr"/>
+          <t>sp_gndout</t>
+        </is>
+      </c>
+      <c r="T72" s="48" t="inlineStr">
+        <is>
+          <t>cab_aps1</t>
+        </is>
+      </c>
       <c r="U72" s="49" t="n">
         <v>20</v>
       </c>
@@ -9511,45 +9533,25 @@
           <t>Yellow</t>
         </is>
       </c>
-      <c r="W72" s="50" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
+      <c r="W72" s="50" t="inlineStr"/>
       <c r="X72" s="50" t="inlineStr">
         <is>
-          <t>Yellow-Blue</t>
+          <t>Yellow-Yellow-Blue</t>
         </is>
       </c>
       <c r="Y72" s="50" t="inlineStr"/>
       <c r="Z72" s="51" t="inlineStr">
         <is>
-          <t>A/C amp branch (behind dash)</t>
-        </is>
-      </c>
-      <c r="AA72" s="52" t="inlineStr">
-        <is>
-          <t>A/C pressure switch A5, engine bay; exact spot TBD (no locator figure in the repo)</t>
-        </is>
-      </c>
-      <c r="AB72" s="53" t="inlineStr">
-        <is>
-          <t>Y-R (factory wiring; new wire here)</t>
-        </is>
-      </c>
-      <c r="AC72" s="54" t="inlineStr">
-        <is>
-          <t>1990 ST185 EWD p.152 (docs/electrical/ewd-snips/1990-st185-autoac-pressure-clutch-p152.png); 1990 ST185 EWD p.152 (A5 pin 4 Y-R)</t>
-        </is>
-      </c>
-      <c r="AD72" s="54" t="inlineStr">
-        <is>
-          <t>new-wire run terminated at the switch's own mating plug (no factory engine-bay wire reused, Section 39, 2026-10-04); plug part number not yet chosen</t>
-        </is>
-      </c>
+          <t>pedal branch (driver footwell)</t>
+        </is>
+      </c>
+      <c r="AA72" s="52" t="inlineStr"/>
+      <c r="AB72" s="53" t="inlineStr"/>
+      <c r="AC72" s="54" t="inlineStr"/>
+      <c r="AD72" s="54" t="inlineStr"/>
       <c r="AE72" s="54" t="inlineStr">
         <is>
-          <t>flying lead on EngineRoom-C: EWD A5 pin 4 Y-R (factory wiring; new wire here); break BR_AC_PSW (other drawn half w_ac_psw on EngineRoom-C); splice sp_ac_psw named in SoT</t>
+          <t>splice sp_gndout named in SoT</t>
         </is>
       </c>
       <c r="AF72" s="54" t="inlineStr">
@@ -9559,19 +9561,19 @@
       </c>
       <c r="AG72" s="54" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as w_ac_psw_in on A-cabin, ? mm; w_ac_psw on EngineRoom-C, 100 mm)</t>
+          <t>pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="23" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="B73" s="23" t="inlineStr">
         <is>
-          <t>w_ac_psw_sw</t>
+          <t>w38</t>
         </is>
       </c>
       <c r="C73" s="23" t="inlineStr">
@@ -9582,117 +9584,99 @@
       <c r="D73" s="23" t="inlineStr"/>
       <c r="E73" s="24" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="F73" s="25" t="inlineStr">
         <is>
-          <t>A18 (factory)</t>
+          <t>aps</t>
         </is>
       </c>
       <c r="G73" s="26" t="inlineStr">
         <is>
-          <t>OEM A/C amplifier</t>
+          <t>PEDAL</t>
         </is>
       </c>
       <c r="H73" s="25" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I73" s="26" t="inlineStr">
         <is>
-          <t>A/C pressure sw out</t>
-        </is>
-      </c>
-      <c r="J73" s="26" t="inlineStr">
-        <is>
-          <t>A/C amp A18 pin 13 (1993: A15), behind the glove box. Solder splice onto the factory Y-R lead. EWD 1990 p.152; locator 1990 p.17.</t>
-        </is>
-      </c>
+          <t>Pedal 1 signal main</t>
+        </is>
+      </c>
+      <c r="J73" s="26" t="inlineStr"/>
       <c r="K73" s="27" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="L73" s="28" t="inlineStr">
         <is>
-          <t>sp_ac_psw</t>
+          <t>ecu_a</t>
         </is>
       </c>
       <c r="M73" s="29" t="inlineStr">
         <is>
-          <t>splice sp_ac_psw (SP-AC-PSW: A/C pressure switch output)</t>
-        </is>
-      </c>
-      <c r="N73" s="28" t="inlineStr"/>
+          <t>ECU-A</t>
+        </is>
+      </c>
+      <c r="N73" s="28" t="inlineStr">
+        <is>
+          <t>A14</t>
+        </is>
+      </c>
       <c r="O73" s="29" t="inlineStr">
         <is>
-          <t>A/C pressure sw out</t>
+          <t>Pedal 1 signal main</t>
         </is>
       </c>
       <c r="P73" s="29" t="inlineStr"/>
       <c r="Q73" s="30" t="inlineStr">
         <is>
-          <t>A5.4</t>
+          <t>ECU-A.A14</t>
         </is>
       </c>
       <c r="R73" s="31" t="inlineStr">
         <is>
-          <t>A/C pressure-switched relay coil +</t>
-        </is>
-      </c>
-      <c r="S73" s="32" t="inlineStr">
-        <is>
-          <t>sp_ac_psw</t>
-        </is>
-      </c>
-      <c r="T73" s="32" t="inlineStr"/>
+          <t>Pedal 1 signal main (ECU-A A14)</t>
+        </is>
+      </c>
+      <c r="S73" s="32" t="inlineStr"/>
+      <c r="T73" s="32" t="inlineStr">
+        <is>
+          <t>cab_aps1</t>
+        </is>
+      </c>
       <c r="U73" s="33" t="n">
         <v>20</v>
       </c>
       <c r="V73" s="34" t="inlineStr">
         <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="W73" s="34" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W73" s="34" t="inlineStr"/>
       <c r="X73" s="34" t="inlineStr">
         <is>
-          <t>Yellow-Blue</t>
-        </is>
-      </c>
-      <c r="Y73" s="34" t="inlineStr"/>
+          <t>White-Blue-Yellow</t>
+        </is>
+      </c>
+      <c r="Y73" s="34" t="n">
+        <v>1050</v>
+      </c>
       <c r="Z73" s="35" t="inlineStr">
         <is>
-          <t>A/C amp branch (behind dash)</t>
-        </is>
-      </c>
-      <c r="AA73" s="36" t="inlineStr">
-        <is>
-          <t>A/C amplifier A18 (1993 book: A15), passenger side behind the glove box, on the bottom of the evaporator housing; tap point on the lead at the amplifier, distance TBD</t>
-        </is>
-      </c>
-      <c r="AB73" s="37" t="inlineStr">
-        <is>
-          <t>Y-R</t>
-        </is>
-      </c>
-      <c r="AC73" s="38" t="inlineStr">
-        <is>
-          <t>1990 ST185 EWD p.152 (docs/electrical/ewd-snips/1990-st185-autoac-pressure-clutch-p152.png); 1992 EWD132U p.219 A17-13 (ewd-snips/1992-celica-ewd132u-a17-pressure-p219.png); 1990 ST185 EWD p.152; 1992 EWD132U p.219 (A17-13); locator 1990 ST185 EWD p.17 Instrument Panel (ewd-snips/1990-st185-locations-dash.png); Mitchell locations (docs/research/AUTO-AC-AMP-OPTIONS.html)</t>
-        </is>
-      </c>
-      <c r="AD73" s="38" t="inlineStr">
-        <is>
-          <t>solder splice onto the factory Y-R lead at the A/C amplifier</t>
-        </is>
-      </c>
+          <t>pedal branch (driver footwell)</t>
+        </is>
+      </c>
+      <c r="AA73" s="36" t="inlineStr"/>
+      <c r="AB73" s="37" t="inlineStr"/>
+      <c r="AC73" s="38" t="inlineStr"/>
+      <c r="AD73" s="38" t="inlineStr"/>
       <c r="AE73" s="38" t="inlineStr">
         <is>
-          <t>flying lead FL_ACAMP_PSW: EWD A18 pin 13 Y-R; splice sp_ac_psw named in SoT</t>
+          <t>channels.csv ecu_a A14 An Volt 4 (AV4_APS_MAIN)</t>
         </is>
       </c>
       <c r="AF73" s="38" t="inlineStr">
@@ -9700,17 +9684,21 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG73" s="38" t="inlineStr"/>
+      <c r="AG73" s="38" t="inlineStr">
+        <is>
+          <t>pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="39" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="B74" s="39" t="inlineStr">
         <is>
-          <t>w_acc86</t>
+          <t>cab_aps1_sh</t>
         </is>
       </c>
       <c r="C74" s="39" t="inlineStr">
@@ -9718,99 +9706,87 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D74" s="39" t="inlineStr">
-        <is>
-          <t>CabinPower</t>
-        </is>
-      </c>
+      <c r="D74" s="39" t="inlineStr"/>
       <c r="E74" s="40" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>cable screen</t>
         </is>
       </c>
       <c r="F74" s="41" t="inlineStr">
         <is>
-          <t>sp_ac_psw</t>
+          <t>cab_aps1</t>
         </is>
       </c>
       <c r="G74" s="42" t="inlineStr">
         <is>
-          <t>splice sp_ac_psw (SP-AC-PSW: A/C pressure switch output)</t>
+          <t>cable screen (one end only)</t>
         </is>
       </c>
       <c r="H74" s="41" t="inlineStr"/>
       <c r="I74" s="42" t="inlineStr">
         <is>
-          <t>A/C clutch relay (+)</t>
+          <t>Pedal 1 cable shield</t>
         </is>
       </c>
       <c r="J74" s="42" t="inlineStr"/>
       <c r="K74" s="43" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="L74" s="44" t="inlineStr">
         <is>
-          <t>k_acc</t>
+          <t>sp_shield_a</t>
         </is>
       </c>
       <c r="M74" s="45" t="inlineStr">
         <is>
-          <t>LOGIC M5</t>
-        </is>
-      </c>
-      <c r="N74" s="44" t="n">
-        <v>86</v>
-      </c>
+          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
+        </is>
+      </c>
+      <c r="N74" s="44" t="inlineStr"/>
       <c r="O74" s="45" t="inlineStr">
         <is>
-          <t>A/C clutch relay (+)</t>
-        </is>
-      </c>
-      <c r="P74" s="45" t="inlineStr">
-        <is>
-          <t>LOGIC box (glove box) relay M15 A/C clutch, pin 86</t>
-        </is>
-      </c>
+          <t>Pedal 1 cable shield</t>
+        </is>
+      </c>
+      <c r="P74" s="45" t="inlineStr"/>
       <c r="Q74" s="46" t="inlineStr">
         <is>
-          <t>A5.4</t>
+          <t>ECU-A.A7</t>
         </is>
       </c>
       <c r="R74" s="47" t="inlineStr">
         <is>
-          <t>A/C pressure-switched relay coil +</t>
+          <t>Screen A (ECU A7, SHIELD_A)</t>
         </is>
       </c>
       <c r="S74" s="48" t="inlineStr">
         <is>
-          <t>sp_ac_psw</t>
-        </is>
-      </c>
-      <c r="T74" s="48" t="inlineStr"/>
-      <c r="U74" s="49" t="n">
-        <v>18</v>
-      </c>
+          <t>sp_shield_a</t>
+        </is>
+      </c>
+      <c r="T74" s="48" t="inlineStr">
+        <is>
+          <t>cab_aps1</t>
+        </is>
+      </c>
+      <c r="U74" s="49" t="inlineStr"/>
       <c r="V74" s="50" t="inlineStr">
         <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="W74" s="50" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="W74" s="50" t="inlineStr"/>
       <c r="X74" s="50" t="inlineStr">
         <is>
-          <t>Yellow-Blue</t>
+          <t>White-Blue-Yellow</t>
         </is>
       </c>
       <c r="Y74" s="50" t="inlineStr"/>
       <c r="Z74" s="51" t="inlineStr">
         <is>
-          <t>A/C amp branch (behind dash)</t>
+          <t>at ECU-A plug</t>
         </is>
       </c>
       <c r="AA74" s="52" t="inlineStr"/>
@@ -9819,7 +9795,7 @@
       <c r="AD74" s="54" t="inlineStr"/>
       <c r="AE74" s="54" t="inlineStr">
         <is>
-          <t>splice sp_ac_psw named in SoT; break BR_W_ACC86 (other drawn half w_acc86_cp on CabinPower); relay pin from the CabinPower drawing (no channels.csv row); fuse-box plan LOGIC M5 86</t>
+          <t>splice sp_shield_a named in SoT</t>
         </is>
       </c>
       <c r="AF74" s="54" t="inlineStr">
@@ -9829,7 +9805,7 @@
       </c>
       <c r="AG74" s="54" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as w_acc86 on A-cabin, ? mm; w_acc86_cp on CabinPower, 400 mm)</t>
+          <t>screen floats at the far end; pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
         </is>
       </c>
     </row>
@@ -9841,7 +9817,7 @@
       </c>
       <c r="B75" s="23" t="inlineStr">
         <is>
-          <t>w_aps_vc1</t>
+          <t>w210</t>
         </is>
       </c>
       <c r="C75" s="23" t="inlineStr">
@@ -9866,11 +9842,11 @@
         </is>
       </c>
       <c r="H75" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I75" s="26" t="inlineStr">
         <is>
-          <t>+5 V pedal sensor 1</t>
+          <t>+5 V pedal sensor 2</t>
         </is>
       </c>
       <c r="J75" s="26" t="inlineStr"/>
@@ -9892,7 +9868,7 @@
       <c r="N75" s="28" t="inlineStr"/>
       <c r="O75" s="29" t="inlineStr">
         <is>
-          <t>+5 V pedal sensor 1</t>
+          <t>+5 V pedal sensor 2</t>
         </is>
       </c>
       <c r="P75" s="29" t="inlineStr"/>
@@ -9913,7 +9889,7 @@
       </c>
       <c r="T75" s="32" t="inlineStr">
         <is>
-          <t>cab_aps1</t>
+          <t>cab_aps2</t>
         </is>
       </c>
       <c r="U75" s="33" t="n">
@@ -9964,7 +9940,7 @@
       </c>
       <c r="B76" s="39" t="inlineStr">
         <is>
-          <t>w40</t>
+          <t>w_aps_gnd2</t>
         </is>
       </c>
       <c r="C76" s="39" t="inlineStr">
@@ -9989,11 +9965,11 @@
         </is>
       </c>
       <c r="H76" s="41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I76" s="42" t="inlineStr">
         <is>
-          <t>Pedal 1 ground</t>
+          <t>Pedal 2 ground</t>
         </is>
       </c>
       <c r="J76" s="42" t="inlineStr"/>
@@ -10015,7 +9991,7 @@
       <c r="N76" s="44" t="inlineStr"/>
       <c r="O76" s="45" t="inlineStr">
         <is>
-          <t>Pedal 1 ground</t>
+          <t>Pedal 2 ground</t>
         </is>
       </c>
       <c r="P76" s="45" t="inlineStr"/>
@@ -10036,7 +10012,7 @@
       </c>
       <c r="T76" s="48" t="inlineStr">
         <is>
-          <t>cab_aps1</t>
+          <t>cab_aps2</t>
         </is>
       </c>
       <c r="U76" s="49" t="n">
@@ -10087,7 +10063,7 @@
       </c>
       <c r="B77" s="23" t="inlineStr">
         <is>
-          <t>w38</t>
+          <t>w_aps_vpa2</t>
         </is>
       </c>
       <c r="C77" s="23" t="inlineStr">
@@ -10095,7 +10071,11 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D77" s="23" t="inlineStr"/>
+      <c r="D77" s="23" t="inlineStr">
+        <is>
+          <t>B-cabin</t>
+        </is>
+      </c>
       <c r="E77" s="24" t="inlineStr">
         <is>
           <t>connector</t>
@@ -10112,11 +10092,11 @@
         </is>
       </c>
       <c r="H77" s="25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I77" s="26" t="inlineStr">
         <is>
-          <t>Pedal 1 signal main</t>
+          <t>Pedal 2 signal sub</t>
         </is>
       </c>
       <c r="J77" s="26" t="inlineStr"/>
@@ -10127,39 +10107,43 @@
       </c>
       <c r="L77" s="28" t="inlineStr">
         <is>
-          <t>ecu_a</t>
+          <t>ecu_b</t>
         </is>
       </c>
       <c r="M77" s="29" t="inlineStr">
         <is>
-          <t>ECU-A</t>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
         </is>
       </c>
       <c r="N77" s="28" t="inlineStr">
         <is>
-          <t>A14</t>
+          <t>B33</t>
         </is>
       </c>
       <c r="O77" s="29" t="inlineStr">
         <is>
-          <t>Pedal 1 signal main</t>
-        </is>
-      </c>
-      <c r="P77" s="29" t="inlineStr"/>
+          <t>Pedal 2 signal sub</t>
+        </is>
+      </c>
+      <c r="P77" s="29" t="inlineStr">
+        <is>
+          <t>ECU-B plug pin B33 (Link G4X, centre dash); VPA2</t>
+        </is>
+      </c>
       <c r="Q77" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A14</t>
+          <t>ECU-B.B33</t>
         </is>
       </c>
       <c r="R77" s="31" t="inlineStr">
         <is>
-          <t>Pedal 1 signal main (ECU-A A14)</t>
+          <t>Pedal 2 signal sub (ECU-B B33)</t>
         </is>
       </c>
       <c r="S77" s="32" t="inlineStr"/>
       <c r="T77" s="32" t="inlineStr">
         <is>
-          <t>cab_aps1</t>
+          <t>cab_aps2</t>
         </is>
       </c>
       <c r="U77" s="33" t="n">
@@ -10177,11 +10161,11 @@
         </is>
       </c>
       <c r="Y77" s="34" t="n">
-        <v>1050</v>
+        <v>1720</v>
       </c>
       <c r="Z77" s="35" t="inlineStr">
         <is>
-          <t>pedal branch (driver footwell)</t>
+          <t>pedal branch (driver footwell) / to ECU-B plug (beside ECU-A)</t>
         </is>
       </c>
       <c r="AA77" s="36" t="inlineStr"/>
@@ -10190,7 +10174,7 @@
       <c r="AD77" s="38" t="inlineStr"/>
       <c r="AE77" s="38" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A14 An Volt 4 (AV4_APS_MAIN)</t>
+          <t>channels.csv ecu_b B33 An Volt 5 (AV5_APS_SUB)</t>
         </is>
       </c>
       <c r="AF77" s="38" t="inlineStr">
@@ -10200,7 +10184,7 @@
       </c>
       <c r="AG77" s="38" t="inlineStr">
         <is>
-          <t>pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
+          <t>pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143); owner proposed: longer half (drawn today as w_aps_vpa2 on A-cabin, 1720 mm; w39 on B-cabin, 1250 mm)</t>
         </is>
       </c>
     </row>
@@ -10212,7 +10196,7 @@
       </c>
       <c r="B78" s="39" t="inlineStr">
         <is>
-          <t>cab_aps1_sh</t>
+          <t>cab_aps_sh</t>
         </is>
       </c>
       <c r="C78" s="39" t="inlineStr">
@@ -10228,7 +10212,7 @@
       </c>
       <c r="F78" s="41" t="inlineStr">
         <is>
-          <t>cab_aps1</t>
+          <t>cab_aps2</t>
         </is>
       </c>
       <c r="G78" s="42" t="inlineStr">
@@ -10239,7 +10223,7 @@
       <c r="H78" s="41" t="inlineStr"/>
       <c r="I78" s="42" t="inlineStr">
         <is>
-          <t>Pedal 1 cable shield</t>
+          <t>Pedal 2 cable shield</t>
         </is>
       </c>
       <c r="J78" s="42" t="inlineStr"/>
@@ -10261,7 +10245,7 @@
       <c r="N78" s="44" t="inlineStr"/>
       <c r="O78" s="45" t="inlineStr">
         <is>
-          <t>Pedal 1 cable shield</t>
+          <t>Pedal 2 cable shield</t>
         </is>
       </c>
       <c r="P78" s="45" t="inlineStr"/>
@@ -10282,7 +10266,7 @@
       </c>
       <c r="T78" s="48" t="inlineStr">
         <is>
-          <t>cab_aps1</t>
+          <t>cab_aps2</t>
         </is>
       </c>
       <c r="U78" s="49" t="inlineStr"/>
@@ -10331,7 +10315,7 @@
       </c>
       <c r="B79" s="23" t="inlineStr">
         <is>
-          <t>w210</t>
+          <t>cab_fspur_5v</t>
         </is>
       </c>
       <c r="C79" s="23" t="inlineStr">
@@ -10347,12 +10331,12 @@
       </c>
       <c r="F79" s="25" t="inlineStr">
         <is>
-          <t>aps</t>
+          <t>ix_ws_front_p</t>
         </is>
       </c>
       <c r="G79" s="26" t="inlineStr">
         <is>
-          <t>PEDAL</t>
+          <t>FRONT WS INLINE</t>
         </is>
       </c>
       <c r="H79" s="25" t="n">
@@ -10360,7 +10344,7 @@
       </c>
       <c r="I79" s="26" t="inlineStr">
         <is>
-          <t>+5 V pedal sensor 2</t>
+          <t>VRC-F +5V</t>
         </is>
       </c>
       <c r="J79" s="26" t="inlineStr"/>
@@ -10371,18 +10355,18 @@
       </c>
       <c r="L79" s="28" t="inlineStr">
         <is>
-          <t>sp_5v_2</t>
+          <t>sp_5v</t>
         </is>
       </c>
       <c r="M79" s="29" t="inlineStr">
         <is>
-          <t>splice sp_5v_2 (SP-5V-PEDAL: +5 V to pedal + cruise)</t>
+          <t>splice sp_5v (SP-5V-A: +5 V sensor supply)</t>
         </is>
       </c>
       <c r="N79" s="28" t="inlineStr"/>
       <c r="O79" s="29" t="inlineStr">
         <is>
-          <t>+5 V pedal sensor 2</t>
+          <t>VRC-F +5V</t>
         </is>
       </c>
       <c r="P79" s="29" t="inlineStr"/>
@@ -10398,12 +10382,12 @@
       </c>
       <c r="S79" s="32" t="inlineStr">
         <is>
-          <t>sp_5v_2</t>
+          <t>sp_5v</t>
         </is>
       </c>
       <c r="T79" s="32" t="inlineStr">
         <is>
-          <t>cab_aps2</t>
+          <t>cab_fspur</t>
         </is>
       </c>
       <c r="U79" s="33" t="n">
@@ -10423,7 +10407,7 @@
       <c r="Y79" s="34" t="inlineStr"/>
       <c r="Z79" s="35" t="inlineStr">
         <is>
-          <t>pedal branch (driver footwell)</t>
+          <t>dash branch (front WS inline)</t>
         </is>
       </c>
       <c r="AA79" s="36" t="inlineStr"/>
@@ -10432,7 +10416,7 @@
       <c r="AD79" s="38" t="inlineStr"/>
       <c r="AE79" s="38" t="inlineStr">
         <is>
-          <t>splice sp_5v_2 named in SoT</t>
+          <t>splice sp_5v named in SoT</t>
         </is>
       </c>
       <c r="AF79" s="38" t="inlineStr">
@@ -10440,11 +10424,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG79" s="38" t="inlineStr">
-        <is>
-          <t>pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
-        </is>
-      </c>
+      <c r="AG79" s="38" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="39" t="inlineStr">
@@ -10454,7 +10434,7 @@
       </c>
       <c r="B80" s="39" t="inlineStr">
         <is>
-          <t>w_aps_gnd2</t>
+          <t>cab_fspur_gnd</t>
         </is>
       </c>
       <c r="C80" s="39" t="inlineStr">
@@ -10470,12 +10450,12 @@
       </c>
       <c r="F80" s="41" t="inlineStr">
         <is>
-          <t>aps</t>
+          <t>ix_ws_front_p</t>
         </is>
       </c>
       <c r="G80" s="42" t="inlineStr">
         <is>
-          <t>PEDAL</t>
+          <t>FRONT WS INLINE</t>
         </is>
       </c>
       <c r="H80" s="41" t="n">
@@ -10483,7 +10463,7 @@
       </c>
       <c r="I80" s="42" t="inlineStr">
         <is>
-          <t>Pedal 2 ground</t>
+          <t>VRC-F GND</t>
         </is>
       </c>
       <c r="J80" s="42" t="inlineStr"/>
@@ -10505,7 +10485,7 @@
       <c r="N80" s="44" t="inlineStr"/>
       <c r="O80" s="45" t="inlineStr">
         <is>
-          <t>Pedal 2 ground</t>
+          <t>VRC-F GND</t>
         </is>
       </c>
       <c r="P80" s="45" t="inlineStr"/>
@@ -10526,7 +10506,7 @@
       </c>
       <c r="T80" s="48" t="inlineStr">
         <is>
-          <t>cab_aps2</t>
+          <t>cab_fspur</t>
         </is>
       </c>
       <c r="U80" s="49" t="n">
@@ -10546,7 +10526,7 @@
       <c r="Y80" s="50" t="inlineStr"/>
       <c r="Z80" s="51" t="inlineStr">
         <is>
-          <t>pedal branch (driver footwell)</t>
+          <t>dash branch (front WS inline)</t>
         </is>
       </c>
       <c r="AA80" s="52" t="inlineStr"/>
@@ -10563,21 +10543,17 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG80" s="54" t="inlineStr">
-        <is>
-          <t>pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
-        </is>
-      </c>
+      <c r="AG80" s="54" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="23" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>WSSF</t>
         </is>
       </c>
       <c r="B81" s="23" t="inlineStr">
         <is>
-          <t>w_aps_vpa2</t>
+          <t>cab_fspur_l</t>
         </is>
       </c>
       <c r="C81" s="23" t="inlineStr">
@@ -10585,11 +10561,7 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D81" s="23" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
+      <c r="D81" s="23" t="inlineStr"/>
       <c r="E81" s="24" t="inlineStr">
         <is>
           <t>connector</t>
@@ -10597,12 +10569,12 @@
       </c>
       <c r="F81" s="25" t="inlineStr">
         <is>
-          <t>aps</t>
+          <t>ix_ws_front_p</t>
         </is>
       </c>
       <c r="G81" s="26" t="inlineStr">
         <is>
-          <t>PEDAL</t>
+          <t>FRONT WS INLINE</t>
         </is>
       </c>
       <c r="H81" s="25" t="n">
@@ -10610,7 +10582,7 @@
       </c>
       <c r="I81" s="26" t="inlineStr">
         <is>
-          <t>Pedal 2 signal sub</t>
+          <t>FL conditioned out</t>
         </is>
       </c>
       <c r="J81" s="26" t="inlineStr"/>
@@ -10621,43 +10593,39 @@
       </c>
       <c r="L81" s="28" t="inlineStr">
         <is>
-          <t>ecu_b</t>
+          <t>ecu_a</t>
         </is>
       </c>
       <c r="M81" s="29" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
+          <t>ECU-A</t>
         </is>
       </c>
       <c r="N81" s="28" t="inlineStr">
         <is>
-          <t>B33</t>
+          <t>A23</t>
         </is>
       </c>
       <c r="O81" s="29" t="inlineStr">
         <is>
-          <t>Pedal 2 signal sub</t>
-        </is>
-      </c>
-      <c r="P81" s="29" t="inlineStr">
-        <is>
-          <t>ECU-B plug pin B33 (Link G4X, centre dash); VPA2</t>
-        </is>
-      </c>
+          <t>FL conditioned out</t>
+        </is>
+      </c>
+      <c r="P81" s="29" t="inlineStr"/>
       <c r="Q81" s="30" t="inlineStr">
         <is>
-          <t>ECU-B.B33</t>
+          <t>ECU-A.A23</t>
         </is>
       </c>
       <c r="R81" s="31" t="inlineStr">
         <is>
-          <t>Pedal 2 signal sub (ECU-B B33)</t>
+          <t>FL conditioned out (ECU-A A23)</t>
         </is>
       </c>
       <c r="S81" s="32" t="inlineStr"/>
       <c r="T81" s="32" t="inlineStr">
         <is>
-          <t>cab_aps2</t>
+          <t>cab_fspur</t>
         </is>
       </c>
       <c r="U81" s="33" t="n">
@@ -10671,15 +10639,15 @@
       <c r="W81" s="34" t="inlineStr"/>
       <c r="X81" s="34" t="inlineStr">
         <is>
-          <t>White-Blue-Yellow</t>
+          <t>White-Blue-Blue</t>
         </is>
       </c>
       <c r="Y81" s="34" t="n">
-        <v>1720</v>
+        <v>330</v>
       </c>
       <c r="Z81" s="35" t="inlineStr">
         <is>
-          <t>pedal branch (driver footwell) / to ECU-B plug (beside ECU-A)</t>
+          <t>dash branch (front WS inline)</t>
         </is>
       </c>
       <c r="AA81" s="36" t="inlineStr"/>
@@ -10688,7 +10656,7 @@
       <c r="AD81" s="38" t="inlineStr"/>
       <c r="AE81" s="38" t="inlineStr">
         <is>
-          <t>break BR_W39 (other drawn half w39 on B-cabin); channels.csv ecu_b B33 An Volt 5 (AV5_APS_SUB)</t>
+          <t>channels.csv ecu_a A23 DI 3 (DI3_WSS_FL)</t>
         </is>
       </c>
       <c r="AF81" s="38" t="inlineStr">
@@ -10696,21 +10664,17 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG81" s="38" t="inlineStr">
-        <is>
-          <t>pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143); owner proposed: longer half (drawn today as w_aps_vpa2 on A-cabin, 1720 mm; w39 on B-cabin, 1250 mm)</t>
-        </is>
-      </c>
+      <c r="AG81" s="38" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="39" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>WSSF</t>
         </is>
       </c>
       <c r="B82" s="39" t="inlineStr">
         <is>
-          <t>cab_aps_sh</t>
+          <t>cab_fspur_sh</t>
         </is>
       </c>
       <c r="C82" s="39" t="inlineStr">
@@ -10721,23 +10685,25 @@
       <c r="D82" s="39" t="inlineStr"/>
       <c r="E82" s="40" t="inlineStr">
         <is>
-          <t>cable screen</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="F82" s="41" t="inlineStr">
         <is>
-          <t>cab_aps2</t>
+          <t>ix_ws_front_p</t>
         </is>
       </c>
       <c r="G82" s="42" t="inlineStr">
         <is>
-          <t>cable screen (one end only)</t>
-        </is>
-      </c>
-      <c r="H82" s="41" t="inlineStr"/>
+          <t>FRONT WS INLINE</t>
+        </is>
+      </c>
+      <c r="H82" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="I82" s="42" t="inlineStr">
         <is>
-          <t>Pedal 2 cable shield</t>
+          <t>WS-F screen drain</t>
         </is>
       </c>
       <c r="J82" s="42" t="inlineStr"/>
@@ -10759,7 +10725,7 @@
       <c r="N82" s="44" t="inlineStr"/>
       <c r="O82" s="45" t="inlineStr">
         <is>
-          <t>Pedal 2 cable shield</t>
+          <t>WS-F screen drain</t>
         </is>
       </c>
       <c r="P82" s="45" t="inlineStr"/>
@@ -10780,7 +10746,7 @@
       </c>
       <c r="T82" s="48" t="inlineStr">
         <is>
-          <t>cab_aps2</t>
+          <t>cab_fspur</t>
         </is>
       </c>
       <c r="U82" s="49" t="inlineStr"/>
@@ -10792,13 +10758,13 @@
       <c r="W82" s="50" t="inlineStr"/>
       <c r="X82" s="50" t="inlineStr">
         <is>
-          <t>White-Blue-Yellow</t>
+          <t>White-Blue-Blue</t>
         </is>
       </c>
       <c r="Y82" s="50" t="inlineStr"/>
       <c r="Z82" s="51" t="inlineStr">
         <is>
-          <t>at ECU-A plug</t>
+          <t>dash branch (front WS inline)</t>
         </is>
       </c>
       <c r="AA82" s="52" t="inlineStr"/>
@@ -10815,21 +10781,17 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG82" s="54" t="inlineStr">
-        <is>
-          <t>screen floats at the far end; pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
-        </is>
-      </c>
+      <c r="AG82" s="54" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="23" t="inlineStr">
         <is>
-          <t>5V</t>
+          <t>WSSF</t>
         </is>
       </c>
       <c r="B83" s="23" t="inlineStr">
         <is>
-          <t>cab_fspur_5v</t>
+          <t>cab_fspur_fr_sh_ac</t>
         </is>
       </c>
       <c r="C83" s="23" t="inlineStr">
@@ -10837,28 +10799,30 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D83" s="23" t="inlineStr"/>
+      <c r="D83" s="23" t="inlineStr">
+        <is>
+          <t>B-cabin</t>
+        </is>
+      </c>
       <c r="E83" s="24" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>cable screen</t>
         </is>
       </c>
       <c r="F83" s="25" t="inlineStr">
         <is>
-          <t>ix_ws_front_p</t>
+          <t>cab_fspur_fr_ac</t>
         </is>
       </c>
       <c r="G83" s="26" t="inlineStr">
         <is>
-          <t>FRONT WS INLINE</t>
-        </is>
-      </c>
-      <c r="H83" s="25" t="n">
-        <v>1</v>
-      </c>
+          <t>cable screen (one end only)</t>
+        </is>
+      </c>
+      <c r="H83" s="25" t="inlineStr"/>
       <c r="I83" s="26" t="inlineStr">
         <is>
-          <t>VRC-F +5V</t>
+          <t>FR wheel spd shield</t>
         </is>
       </c>
       <c r="J83" s="26" t="inlineStr"/>
@@ -10869,53 +10833,51 @@
       </c>
       <c r="L83" s="28" t="inlineStr">
         <is>
-          <t>sp_5v</t>
+          <t>sp_shield_b</t>
         </is>
       </c>
       <c r="M83" s="29" t="inlineStr">
         <is>
-          <t>splice sp_5v (SP-5V-A: +5 V sensor supply)</t>
+          <t>splice sp_shield_b on B-cabin</t>
         </is>
       </c>
       <c r="N83" s="28" t="inlineStr"/>
       <c r="O83" s="29" t="inlineStr">
         <is>
-          <t>VRC-F +5V</t>
-        </is>
-      </c>
-      <c r="P83" s="29" t="inlineStr"/>
+          <t>FR wheel spd shield</t>
+        </is>
+      </c>
+      <c r="P83" s="29" t="inlineStr">
+        <is>
+          <t>at the ECU-B plug (B-cabin); to ECU-B B17</t>
+        </is>
+      </c>
       <c r="Q83" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A32</t>
+          <t>ECU-B.B17</t>
         </is>
       </c>
       <c r="R83" s="31" t="inlineStr">
         <is>
-          <t>+5V sensor (ECU-A A32)</t>
-        </is>
-      </c>
-      <c r="S83" s="32" t="inlineStr">
-        <is>
-          <t>sp_5v</t>
-        </is>
-      </c>
+          <t>Screen B (ECU B17, SHIELD_B)</t>
+        </is>
+      </c>
+      <c r="S83" s="32" t="inlineStr"/>
       <c r="T83" s="32" t="inlineStr">
         <is>
-          <t>cab_fspur</t>
-        </is>
-      </c>
-      <c r="U83" s="33" t="n">
-        <v>20</v>
-      </c>
+          <t>cab_fspur_fr_ac</t>
+        </is>
+      </c>
+      <c r="U83" s="33" t="inlineStr"/>
       <c r="V83" s="34" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Shield</t>
         </is>
       </c>
       <c r="W83" s="34" t="inlineStr"/>
       <c r="X83" s="34" t="inlineStr">
         <is>
-          <t>Blue-Blue</t>
+          <t>White-Blue-Blue</t>
         </is>
       </c>
       <c r="Y83" s="34" t="inlineStr"/>
@@ -10930,7 +10892,7 @@
       <c r="AD83" s="38" t="inlineStr"/>
       <c r="AE83" s="38" t="inlineStr">
         <is>
-          <t>splice sp_5v named in SoT</t>
+          <t>splice sp_shield_b named in SoT</t>
         </is>
       </c>
       <c r="AF83" s="38" t="inlineStr">
@@ -10938,19 +10900,15 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG83" s="38" t="inlineStr"/>
+      <c r="AG83" s="38" t="inlineStr">
+        <is>
+          <t>screen floats at the far end; owner TBD: a half has no length estimate (drawn today as cab_fspur_fr_sh_ac on A-cabin, ? mm; cab_fspur_fr_sh on B-cabin, ? mm)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="39" t="inlineStr">
-        <is>
-          <t>SGND</t>
-        </is>
-      </c>
-      <c r="B84" s="39" t="inlineStr">
-        <is>
-          <t>cab_fspur_gnd</t>
-        </is>
-      </c>
+      <c r="A84" s="39" t="inlineStr"/>
+      <c r="B84" s="39" t="inlineStr"/>
       <c r="C84" s="39" t="inlineStr">
         <is>
           <t>A-cabin</t>
@@ -10964,92 +10922,54 @@
       </c>
       <c r="F84" s="41" t="inlineStr">
         <is>
-          <t>ix_ws_front_p</t>
+          <t>bh_a_fw</t>
         </is>
       </c>
       <c r="G84" s="42" t="inlineStr">
         <is>
-          <t>FRONT WS INLINE</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="H84" s="41" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="I84" s="42" t="inlineStr">
         <is>
-          <t>VRC-F GND</t>
+          <t>spare, sealing plug</t>
         </is>
       </c>
       <c r="J84" s="42" t="inlineStr"/>
-      <c r="K84" s="43" t="inlineStr">
-        <is>
-          <t>splice</t>
-        </is>
-      </c>
-      <c r="L84" s="44" t="inlineStr">
-        <is>
-          <t>sp_gndout</t>
-        </is>
-      </c>
-      <c r="M84" s="45" t="inlineStr">
-        <is>
-          <t>splice sp_gndout (SP-GNDOUT-A: sensor ground)</t>
-        </is>
-      </c>
+      <c r="K84" s="43" t="inlineStr"/>
+      <c r="L84" s="44" t="inlineStr"/>
+      <c r="M84" s="45" t="inlineStr"/>
       <c r="N84" s="44" t="inlineStr"/>
-      <c r="O84" s="45" t="inlineStr">
-        <is>
-          <t>VRC-F GND</t>
-        </is>
-      </c>
+      <c r="O84" s="45" t="inlineStr"/>
       <c r="P84" s="45" t="inlineStr"/>
       <c r="Q84" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A24</t>
+          <t>DRB102.45</t>
         </is>
       </c>
       <c r="R84" s="47" t="inlineStr">
         <is>
-          <t>Sensor GND (ECU-A A24)</t>
-        </is>
-      </c>
-      <c r="S84" s="48" t="inlineStr">
-        <is>
-          <t>sp_gndout</t>
-        </is>
-      </c>
-      <c r="T84" s="48" t="inlineStr">
-        <is>
-          <t>cab_fspur</t>
-        </is>
-      </c>
-      <c r="U84" s="49" t="n">
-        <v>20</v>
-      </c>
-      <c r="V84" s="50" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
+          <t>spare (DRB102 45)</t>
+        </is>
+      </c>
+      <c r="S84" s="48" t="inlineStr"/>
+      <c r="T84" s="48" t="inlineStr"/>
+      <c r="U84" s="49" t="inlineStr"/>
+      <c r="V84" s="50" t="inlineStr"/>
       <c r="W84" s="50" t="inlineStr"/>
-      <c r="X84" s="50" t="inlineStr">
-        <is>
-          <t>Yellow-Yellow-Blue</t>
-        </is>
-      </c>
+      <c r="X84" s="50" t="inlineStr"/>
       <c r="Y84" s="50" t="inlineStr"/>
-      <c r="Z84" s="51" t="inlineStr">
-        <is>
-          <t>dash branch (front WS inline)</t>
-        </is>
-      </c>
+      <c r="Z84" s="51" t="inlineStr"/>
       <c r="AA84" s="52" t="inlineStr"/>
       <c r="AB84" s="53" t="inlineStr"/>
       <c r="AC84" s="54" t="inlineStr"/>
       <c r="AD84" s="54" t="inlineStr"/>
       <c r="AE84" s="54" t="inlineStr">
         <is>
-          <t>splice sp_gndout named in SoT</t>
+          <t>DRB102 45 = 'spare (size 16) - was the A/C coolant switch signal, deleted (S35)'</t>
         </is>
       </c>
       <c r="AF84" s="54" t="inlineStr">
@@ -11060,16 +10980,8 @@
       <c r="AG84" s="54" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="23" t="inlineStr">
-        <is>
-          <t>WSSF</t>
-        </is>
-      </c>
-      <c r="B85" s="23" t="inlineStr">
-        <is>
-          <t>cab_fspur_l</t>
-        </is>
-      </c>
+      <c r="A85" s="23" t="inlineStr"/>
+      <c r="B85" s="23" t="inlineStr"/>
       <c r="C85" s="23" t="inlineStr">
         <is>
           <t>A-cabin</t>
@@ -11083,94 +10995,54 @@
       </c>
       <c r="F85" s="25" t="inlineStr">
         <is>
-          <t>ix_ws_front_p</t>
+          <t>bh_a_fw</t>
         </is>
       </c>
       <c r="G85" s="26" t="inlineStr">
         <is>
-          <t>FRONT WS INLINE</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="H85" s="25" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="I85" s="26" t="inlineStr">
         <is>
-          <t>FL conditioned out</t>
+          <t>spare, sealing plug</t>
         </is>
       </c>
       <c r="J85" s="26" t="inlineStr"/>
-      <c r="K85" s="27" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="L85" s="28" t="inlineStr">
-        <is>
-          <t>ecu_a</t>
-        </is>
-      </c>
-      <c r="M85" s="29" t="inlineStr">
-        <is>
-          <t>ECU-A</t>
-        </is>
-      </c>
-      <c r="N85" s="28" t="inlineStr">
-        <is>
-          <t>A23</t>
-        </is>
-      </c>
-      <c r="O85" s="29" t="inlineStr">
-        <is>
-          <t>FL conditioned out</t>
-        </is>
-      </c>
+      <c r="K85" s="27" t="inlineStr"/>
+      <c r="L85" s="28" t="inlineStr"/>
+      <c r="M85" s="29" t="inlineStr"/>
+      <c r="N85" s="28" t="inlineStr"/>
+      <c r="O85" s="29" t="inlineStr"/>
       <c r="P85" s="29" t="inlineStr"/>
       <c r="Q85" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A23</t>
+          <t>DRB102.46</t>
         </is>
       </c>
       <c r="R85" s="31" t="inlineStr">
         <is>
-          <t>FL conditioned out (ECU-A A23)</t>
+          <t>spare (DRB102 46)</t>
         </is>
       </c>
       <c r="S85" s="32" t="inlineStr"/>
-      <c r="T85" s="32" t="inlineStr">
-        <is>
-          <t>cab_fspur</t>
-        </is>
-      </c>
-      <c r="U85" s="33" t="n">
-        <v>20</v>
-      </c>
-      <c r="V85" s="34" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+      <c r="T85" s="32" t="inlineStr"/>
+      <c r="U85" s="33" t="inlineStr"/>
+      <c r="V85" s="34" t="inlineStr"/>
       <c r="W85" s="34" t="inlineStr"/>
-      <c r="X85" s="34" t="inlineStr">
-        <is>
-          <t>White-Blue-Blue</t>
-        </is>
-      </c>
-      <c r="Y85" s="34" t="n">
-        <v>330</v>
-      </c>
-      <c r="Z85" s="35" t="inlineStr">
-        <is>
-          <t>dash branch (front WS inline)</t>
-        </is>
-      </c>
+      <c r="X85" s="34" t="inlineStr"/>
+      <c r="Y85" s="34" t="inlineStr"/>
+      <c r="Z85" s="35" t="inlineStr"/>
       <c r="AA85" s="36" t="inlineStr"/>
       <c r="AB85" s="37" t="inlineStr"/>
       <c r="AC85" s="38" t="inlineStr"/>
       <c r="AD85" s="38" t="inlineStr"/>
       <c r="AE85" s="38" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A23 DI 3 (DI3_WSS_FL)</t>
+          <t>DRB102 46 = 'spare (size 16) - was the A/C coolant switch return, deleted (S35)'</t>
         </is>
       </c>
       <c r="AF85" s="38" t="inlineStr">
@@ -11181,16 +11053,8 @@
       <c r="AG85" s="38" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="39" t="inlineStr">
-        <is>
-          <t>WSSF</t>
-        </is>
-      </c>
-      <c r="B86" s="39" t="inlineStr">
-        <is>
-          <t>cab_fspur_sh</t>
-        </is>
-      </c>
+      <c r="A86" s="39" t="inlineStr"/>
+      <c r="B86" s="39" t="inlineStr"/>
       <c r="C86" s="39" t="inlineStr">
         <is>
           <t>A-cabin</t>
@@ -11204,90 +11068,54 @@
       </c>
       <c r="F86" s="41" t="inlineStr">
         <is>
-          <t>ix_ws_front_p</t>
+          <t>bh_a_fw</t>
         </is>
       </c>
       <c r="G86" s="42" t="inlineStr">
         <is>
-          <t>FRONT WS INLINE</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="H86" s="41" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="I86" s="42" t="inlineStr">
         <is>
-          <t>WS-F screen drain</t>
+          <t>spare, sealing plug</t>
         </is>
       </c>
       <c r="J86" s="42" t="inlineStr"/>
-      <c r="K86" s="43" t="inlineStr">
-        <is>
-          <t>splice</t>
-        </is>
-      </c>
-      <c r="L86" s="44" t="inlineStr">
-        <is>
-          <t>sp_shield_a</t>
-        </is>
-      </c>
-      <c r="M86" s="45" t="inlineStr">
-        <is>
-          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
-        </is>
-      </c>
+      <c r="K86" s="43" t="inlineStr"/>
+      <c r="L86" s="44" t="inlineStr"/>
+      <c r="M86" s="45" t="inlineStr"/>
       <c r="N86" s="44" t="inlineStr"/>
-      <c r="O86" s="45" t="inlineStr">
-        <is>
-          <t>WS-F screen drain</t>
-        </is>
-      </c>
+      <c r="O86" s="45" t="inlineStr"/>
       <c r="P86" s="45" t="inlineStr"/>
       <c r="Q86" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A7</t>
+          <t>DRB102.52</t>
         </is>
       </c>
       <c r="R86" s="47" t="inlineStr">
         <is>
-          <t>Screen A (ECU A7, SHIELD_A)</t>
-        </is>
-      </c>
-      <c r="S86" s="48" t="inlineStr">
-        <is>
-          <t>sp_shield_a</t>
-        </is>
-      </c>
-      <c r="T86" s="48" t="inlineStr">
-        <is>
-          <t>cab_fspur</t>
-        </is>
-      </c>
+          <t>spare (DRB102 52)</t>
+        </is>
+      </c>
+      <c r="S86" s="48" t="inlineStr"/>
+      <c r="T86" s="48" t="inlineStr"/>
       <c r="U86" s="49" t="inlineStr"/>
-      <c r="V86" s="50" t="inlineStr">
-        <is>
-          <t>Shield</t>
-        </is>
-      </c>
+      <c r="V86" s="50" t="inlineStr"/>
       <c r="W86" s="50" t="inlineStr"/>
-      <c r="X86" s="50" t="inlineStr">
-        <is>
-          <t>White-Blue-Blue</t>
-        </is>
-      </c>
+      <c r="X86" s="50" t="inlineStr"/>
       <c r="Y86" s="50" t="inlineStr"/>
-      <c r="Z86" s="51" t="inlineStr">
-        <is>
-          <t>dash branch (front WS inline)</t>
-        </is>
-      </c>
+      <c r="Z86" s="51" t="inlineStr"/>
       <c r="AA86" s="52" t="inlineStr"/>
       <c r="AB86" s="53" t="inlineStr"/>
       <c r="AC86" s="54" t="inlineStr"/>
       <c r="AD86" s="54" t="inlineStr"/>
       <c r="AE86" s="54" t="inlineStr">
         <is>
-          <t>splice sp_shield_a named in SoT</t>
+          <t>DRB102 52 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF86" s="54" t="inlineStr">
@@ -11298,26 +11126,14 @@
       <c r="AG86" s="54" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="23" t="inlineStr">
-        <is>
-          <t>WSSF</t>
-        </is>
-      </c>
-      <c r="B87" s="23" t="inlineStr">
-        <is>
-          <t>cab_fspur_r_ac</t>
-        </is>
-      </c>
+      <c r="A87" s="23" t="inlineStr"/>
+      <c r="B87" s="23" t="inlineStr"/>
       <c r="C87" s="23" t="inlineStr">
         <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
-      <c r="D87" s="23" t="inlineStr">
-        <is>
           <t>A-cabin</t>
         </is>
       </c>
+      <c r="D87" s="23" t="inlineStr"/>
       <c r="E87" s="24" t="inlineStr">
         <is>
           <t>connector</t>
@@ -11325,98 +11141,54 @@
       </c>
       <c r="F87" s="25" t="inlineStr">
         <is>
-          <t>ix_ws_front_p</t>
+          <t>bh_a_fw</t>
         </is>
       </c>
       <c r="G87" s="26" t="inlineStr">
         <is>
-          <t>FRONT WS INLINE</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="H87" s="25" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="I87" s="26" t="inlineStr">
         <is>
-          <t>FR conditioned out</t>
+          <t>spare, sealing plug</t>
         </is>
       </c>
       <c r="J87" s="26" t="inlineStr"/>
-      <c r="K87" s="27" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="L87" s="28" t="inlineStr">
-        <is>
-          <t>ecu_b</t>
-        </is>
-      </c>
-      <c r="M87" s="29" t="inlineStr">
-        <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
-        </is>
-      </c>
-      <c r="N87" s="28" t="inlineStr">
-        <is>
-          <t>B21</t>
-        </is>
-      </c>
-      <c r="O87" s="29" t="inlineStr">
-        <is>
-          <t>FR conditioned out</t>
-        </is>
-      </c>
-      <c r="P87" s="29" t="inlineStr">
-        <is>
-          <t>ECU-B plug pin B21 (Link G4X, centre dash); wheel speed</t>
-        </is>
-      </c>
+      <c r="K87" s="27" t="inlineStr"/>
+      <c r="L87" s="28" t="inlineStr"/>
+      <c r="M87" s="29" t="inlineStr"/>
+      <c r="N87" s="28" t="inlineStr"/>
+      <c r="O87" s="29" t="inlineStr"/>
+      <c r="P87" s="29" t="inlineStr"/>
       <c r="Q87" s="30" t="inlineStr">
         <is>
-          <t>ECU-B.B21</t>
+          <t>DRB102.53</t>
         </is>
       </c>
       <c r="R87" s="31" t="inlineStr">
         <is>
-          <t>FR conditioned out (ECU-B B21)</t>
+          <t>spare (DRB102 53)</t>
         </is>
       </c>
       <c r="S87" s="32" t="inlineStr"/>
-      <c r="T87" s="32" t="inlineStr">
-        <is>
-          <t>cab_fspur_fr_ac</t>
-        </is>
-      </c>
-      <c r="U87" s="33" t="n">
-        <v>20</v>
-      </c>
-      <c r="V87" s="34" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+      <c r="T87" s="32" t="inlineStr"/>
+      <c r="U87" s="33" t="inlineStr"/>
+      <c r="V87" s="34" t="inlineStr"/>
       <c r="W87" s="34" t="inlineStr"/>
-      <c r="X87" s="34" t="inlineStr">
-        <is>
-          <t>White-Blue-Blue</t>
-        </is>
-      </c>
-      <c r="Y87" s="34" t="n">
-        <v>350</v>
-      </c>
-      <c r="Z87" s="35" t="inlineStr">
-        <is>
-          <t>dash branch (front WS inline)</t>
-        </is>
-      </c>
+      <c r="X87" s="34" t="inlineStr"/>
+      <c r="Y87" s="34" t="inlineStr"/>
+      <c r="Z87" s="35" t="inlineStr"/>
       <c r="AA87" s="36" t="inlineStr"/>
       <c r="AB87" s="37" t="inlineStr"/>
       <c r="AC87" s="38" t="inlineStr"/>
       <c r="AD87" s="38" t="inlineStr"/>
       <c r="AE87" s="38" t="inlineStr">
         <is>
-          <t>break BR_CAB_FSPUR_R (other drawn half cab_fspur_r on B-cabin); channels.csv ecu_b B21 DI 4 (DI4_WSS_FR)</t>
+          <t>DRB102 53 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF87" s="38" t="inlineStr">
@@ -11424,122 +11196,72 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG87" s="38" t="inlineStr">
-        <is>
-          <t>owner proposed: longer half (drawn today as cab_fspur_r_ac on A-cabin, 350 mm; cab_fspur_r on B-cabin, 530 mm)</t>
-        </is>
-      </c>
+      <c r="AG87" s="38" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="39" t="inlineStr">
-        <is>
-          <t>WSSF</t>
-        </is>
-      </c>
-      <c r="B88" s="39" t="inlineStr">
-        <is>
-          <t>cab_fspur_fr_sh_ac</t>
-        </is>
-      </c>
+      <c r="A88" s="39" t="inlineStr"/>
+      <c r="B88" s="39" t="inlineStr"/>
       <c r="C88" s="39" t="inlineStr">
         <is>
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D88" s="39" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
+      <c r="D88" s="39" t="inlineStr"/>
       <c r="E88" s="40" t="inlineStr">
         <is>
-          <t>cable screen</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="F88" s="41" t="inlineStr">
         <is>
-          <t>cab_fspur_fr_ac</t>
+          <t>bh_a_fw</t>
         </is>
       </c>
       <c r="G88" s="42" t="inlineStr">
         <is>
-          <t>cable screen (one end only)</t>
-        </is>
-      </c>
-      <c r="H88" s="41" t="inlineStr"/>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="H88" s="41" t="n">
+        <v>57</v>
+      </c>
       <c r="I88" s="42" t="inlineStr">
         <is>
-          <t>FR wheel spd shield</t>
+          <t>spare, sealing plug</t>
         </is>
       </c>
       <c r="J88" s="42" t="inlineStr"/>
-      <c r="K88" s="43" t="inlineStr">
-        <is>
-          <t>splice</t>
-        </is>
-      </c>
-      <c r="L88" s="44" t="inlineStr">
-        <is>
-          <t>sp_shield_b</t>
-        </is>
-      </c>
-      <c r="M88" s="45" t="inlineStr">
-        <is>
-          <t>splice sp_shield_b on B-cabin</t>
-        </is>
-      </c>
+      <c r="K88" s="43" t="inlineStr"/>
+      <c r="L88" s="44" t="inlineStr"/>
+      <c r="M88" s="45" t="inlineStr"/>
       <c r="N88" s="44" t="inlineStr"/>
-      <c r="O88" s="45" t="inlineStr">
-        <is>
-          <t>FR wheel spd shield</t>
-        </is>
-      </c>
-      <c r="P88" s="45" t="inlineStr">
-        <is>
-          <t>at the ECU-B plug (B-cabin); to ECU-B B17</t>
-        </is>
-      </c>
+      <c r="O88" s="45" t="inlineStr"/>
+      <c r="P88" s="45" t="inlineStr"/>
       <c r="Q88" s="46" t="inlineStr">
         <is>
-          <t>ECU-B.B17</t>
+          <t>DRB102.57</t>
         </is>
       </c>
       <c r="R88" s="47" t="inlineStr">
         <is>
-          <t>Screen B (ECU B17, SHIELD_B)</t>
+          <t>spare (DRB102 57)</t>
         </is>
       </c>
       <c r="S88" s="48" t="inlineStr"/>
-      <c r="T88" s="48" t="inlineStr">
-        <is>
-          <t>cab_fspur_fr_ac</t>
-        </is>
-      </c>
+      <c r="T88" s="48" t="inlineStr"/>
       <c r="U88" s="49" t="inlineStr"/>
-      <c r="V88" s="50" t="inlineStr">
-        <is>
-          <t>Shield</t>
-        </is>
-      </c>
+      <c r="V88" s="50" t="inlineStr"/>
       <c r="W88" s="50" t="inlineStr"/>
-      <c r="X88" s="50" t="inlineStr">
-        <is>
-          <t>White-Blue-Blue</t>
-        </is>
-      </c>
+      <c r="X88" s="50" t="inlineStr"/>
       <c r="Y88" s="50" t="inlineStr"/>
-      <c r="Z88" s="51" t="inlineStr">
-        <is>
-          <t>dash branch (front WS inline)</t>
-        </is>
-      </c>
+      <c r="Z88" s="51" t="inlineStr"/>
       <c r="AA88" s="52" t="inlineStr"/>
       <c r="AB88" s="53" t="inlineStr"/>
       <c r="AC88" s="54" t="inlineStr"/>
       <c r="AD88" s="54" t="inlineStr"/>
       <c r="AE88" s="54" t="inlineStr">
         <is>
-          <t>break BR_CAB_FSPUR_FR_SH (other drawn half cab_fspur_fr_sh on B-cabin)</t>
+          <t>DRB102 57 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF88" s="54" t="inlineStr">
@@ -11547,11 +11269,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG88" s="54" t="inlineStr">
-        <is>
-          <t>screen floats at the far end; owner TBD: a half has no length estimate (drawn today as cab_fspur_fr_sh_ac on A-cabin, ? mm; cab_fspur_fr_sh on B-cabin, ? mm)</t>
-        </is>
-      </c>
+      <c r="AG88" s="54" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="23" t="inlineStr"/>
@@ -11578,7 +11296,7 @@
         </is>
       </c>
       <c r="H89" s="25" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I89" s="26" t="inlineStr">
         <is>
@@ -11594,12 +11312,12 @@
       <c r="P89" s="29" t="inlineStr"/>
       <c r="Q89" s="30" t="inlineStr">
         <is>
-          <t>bh_a_fw.45</t>
+          <t>DRB102.58</t>
         </is>
       </c>
       <c r="R89" s="31" t="inlineStr">
         <is>
-          <t>spare (bh_a_fw 45)</t>
+          <t>spare (DRB102 58)</t>
         </is>
       </c>
       <c r="S89" s="32" t="inlineStr"/>
@@ -11616,7 +11334,7 @@
       <c r="AD89" s="38" t="inlineStr"/>
       <c r="AE89" s="38" t="inlineStr">
         <is>
-          <t>DRB102 45 = 'spare (size 16) - was the A/C coolant switch signal, deleted (S35)'</t>
+          <t>DRB102 58 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF89" s="38" t="inlineStr">
@@ -11651,7 +11369,7 @@
         </is>
       </c>
       <c r="H90" s="41" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="I90" s="42" t="inlineStr">
         <is>
@@ -11667,12 +11385,12 @@
       <c r="P90" s="45" t="inlineStr"/>
       <c r="Q90" s="46" t="inlineStr">
         <is>
-          <t>bh_a_fw.46</t>
+          <t>DRB102.59</t>
         </is>
       </c>
       <c r="R90" s="47" t="inlineStr">
         <is>
-          <t>spare (bh_a_fw 46)</t>
+          <t>spare (DRB102 59)</t>
         </is>
       </c>
       <c r="S90" s="48" t="inlineStr"/>
@@ -11689,7 +11407,7 @@
       <c r="AD90" s="54" t="inlineStr"/>
       <c r="AE90" s="54" t="inlineStr">
         <is>
-          <t>DRB102 46 = 'spare (size 16) - was the A/C coolant switch return, deleted (S35)'</t>
+          <t>DRB102 59 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF90" s="54" t="inlineStr">
@@ -11724,7 +11442,7 @@
         </is>
       </c>
       <c r="H91" s="25" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="I91" s="26" t="inlineStr">
         <is>
@@ -11740,12 +11458,12 @@
       <c r="P91" s="29" t="inlineStr"/>
       <c r="Q91" s="30" t="inlineStr">
         <is>
-          <t>bh_a_fw.52</t>
+          <t>DRB102.61</t>
         </is>
       </c>
       <c r="R91" s="31" t="inlineStr">
         <is>
-          <t>spare (bh_a_fw 52)</t>
+          <t>spare (DRB102 61)</t>
         </is>
       </c>
       <c r="S91" s="32" t="inlineStr"/>
@@ -11762,7 +11480,7 @@
       <c r="AD91" s="38" t="inlineStr"/>
       <c r="AE91" s="38" t="inlineStr">
         <is>
-          <t>DRB102 52 = 'spare (size 16)'</t>
+          <t>DRB102 61 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF91" s="38" t="inlineStr">
@@ -11788,16 +11506,16 @@
       </c>
       <c r="F92" s="41" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>ix_ws_front_p</t>
         </is>
       </c>
       <c r="G92" s="42" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>FRONT WS INLINE</t>
         </is>
       </c>
       <c r="H92" s="41" t="n">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="I92" s="42" t="inlineStr">
         <is>
@@ -11813,12 +11531,12 @@
       <c r="P92" s="45" t="inlineStr"/>
       <c r="Q92" s="46" t="inlineStr">
         <is>
-          <t>bh_a_fw.53</t>
+          <t>ix_ws_front_p.6</t>
         </is>
       </c>
       <c r="R92" s="47" t="inlineStr">
         <is>
-          <t>spare (bh_a_fw 53)</t>
+          <t>spare (ix_ws_front_p 6)</t>
         </is>
       </c>
       <c r="S92" s="48" t="inlineStr"/>
@@ -11833,11 +11551,7 @@
       <c r="AB92" s="53" t="inlineStr"/>
       <c r="AC92" s="54" t="inlineStr"/>
       <c r="AD92" s="54" t="inlineStr"/>
-      <c r="AE92" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 53 = 'spare (size 16)'</t>
-        </is>
-      </c>
+      <c r="AE92" s="54" t="inlineStr"/>
       <c r="AF92" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11861,16 +11575,16 @@
       </c>
       <c r="F93" s="25" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>bus_5v_bha_p</t>
         </is>
       </c>
       <c r="G93" s="26" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>+5V BUS</t>
         </is>
       </c>
       <c r="H93" s="25" t="n">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="I93" s="26" t="inlineStr">
         <is>
@@ -11886,12 +11600,12 @@
       <c r="P93" s="29" t="inlineStr"/>
       <c r="Q93" s="30" t="inlineStr">
         <is>
-          <t>bh_a_fw.57</t>
+          <t>ECU-A.A32</t>
         </is>
       </c>
       <c r="R93" s="31" t="inlineStr">
         <is>
-          <t>spare (bh_a_fw 57)</t>
+          <t>+5V sensor (ECU-A A32)</t>
         </is>
       </c>
       <c r="S93" s="32" t="inlineStr"/>
@@ -11906,11 +11620,7 @@
       <c r="AB93" s="37" t="inlineStr"/>
       <c r="AC93" s="38" t="inlineStr"/>
       <c r="AD93" s="38" t="inlineStr"/>
-      <c r="AE93" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 57 = 'spare (size 16)'</t>
-        </is>
-      </c>
+      <c r="AE93" s="38" t="inlineStr"/>
       <c r="AF93" s="38" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11934,16 +11644,16 @@
       </c>
       <c r="F94" s="41" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>bus_gnd_bha_p</t>
         </is>
       </c>
       <c r="G94" s="42" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>SENSOR GND BUS</t>
         </is>
       </c>
       <c r="H94" s="41" t="n">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="I94" s="42" t="inlineStr">
         <is>
@@ -11959,12 +11669,12 @@
       <c r="P94" s="45" t="inlineStr"/>
       <c r="Q94" s="46" t="inlineStr">
         <is>
-          <t>bh_a_fw.58</t>
+          <t>ECU-A.A24</t>
         </is>
       </c>
       <c r="R94" s="47" t="inlineStr">
         <is>
-          <t>spare (bh_a_fw 58)</t>
+          <t>Sensor GND (ECU-A A24)</t>
         </is>
       </c>
       <c r="S94" s="48" t="inlineStr"/>
@@ -11979,11 +11689,7 @@
       <c r="AB94" s="53" t="inlineStr"/>
       <c r="AC94" s="54" t="inlineStr"/>
       <c r="AD94" s="54" t="inlineStr"/>
-      <c r="AE94" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 58 = 'spare (size 16)'</t>
-        </is>
-      </c>
+      <c r="AE94" s="54" t="inlineStr"/>
       <c r="AF94" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12007,16 +11713,16 @@
       </c>
       <c r="F95" s="25" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>bus_gnd_bha_p</t>
         </is>
       </c>
       <c r="G95" s="26" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>SENSOR GND BUS</t>
         </is>
       </c>
       <c r="H95" s="25" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="I95" s="26" t="inlineStr">
         <is>
@@ -12032,12 +11738,12 @@
       <c r="P95" s="29" t="inlineStr"/>
       <c r="Q95" s="30" t="inlineStr">
         <is>
-          <t>bh_a_fw.59</t>
+          <t>ECU-A.A24</t>
         </is>
       </c>
       <c r="R95" s="31" t="inlineStr">
         <is>
-          <t>spare (bh_a_fw 59)</t>
+          <t>Sensor GND (ECU-A A24)</t>
         </is>
       </c>
       <c r="S95" s="32" t="inlineStr"/>
@@ -12052,11 +11758,7 @@
       <c r="AB95" s="37" t="inlineStr"/>
       <c r="AC95" s="38" t="inlineStr"/>
       <c r="AD95" s="38" t="inlineStr"/>
-      <c r="AE95" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 59 = 'spare (size 16)'</t>
-        </is>
-      </c>
+      <c r="AE95" s="38" t="inlineStr"/>
       <c r="AF95" s="38" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12064,357 +11766,8 @@
       </c>
       <c r="AG95" s="38" t="inlineStr"/>
     </row>
-    <row r="96">
-      <c r="A96" s="39" t="inlineStr"/>
-      <c r="B96" s="39" t="inlineStr"/>
-      <c r="C96" s="39" t="inlineStr">
-        <is>
-          <t>A-cabin</t>
-        </is>
-      </c>
-      <c r="D96" s="39" t="inlineStr"/>
-      <c r="E96" s="40" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F96" s="41" t="inlineStr">
-        <is>
-          <t>bh_a_fw</t>
-        </is>
-      </c>
-      <c r="G96" s="42" t="inlineStr">
-        <is>
-          <t>BULKHEAD</t>
-        </is>
-      </c>
-      <c r="H96" s="41" t="n">
-        <v>61</v>
-      </c>
-      <c r="I96" s="42" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J96" s="42" t="inlineStr"/>
-      <c r="K96" s="43" t="inlineStr"/>
-      <c r="L96" s="44" t="inlineStr"/>
-      <c r="M96" s="45" t="inlineStr"/>
-      <c r="N96" s="44" t="inlineStr"/>
-      <c r="O96" s="45" t="inlineStr"/>
-      <c r="P96" s="45" t="inlineStr"/>
-      <c r="Q96" s="46" t="inlineStr">
-        <is>
-          <t>bh_a_fw.61</t>
-        </is>
-      </c>
-      <c r="R96" s="47" t="inlineStr">
-        <is>
-          <t>spare (bh_a_fw 61)</t>
-        </is>
-      </c>
-      <c r="S96" s="48" t="inlineStr"/>
-      <c r="T96" s="48" t="inlineStr"/>
-      <c r="U96" s="49" t="inlineStr"/>
-      <c r="V96" s="50" t="inlineStr"/>
-      <c r="W96" s="50" t="inlineStr"/>
-      <c r="X96" s="50" t="inlineStr"/>
-      <c r="Y96" s="50" t="inlineStr"/>
-      <c r="Z96" s="51" t="inlineStr"/>
-      <c r="AA96" s="52" t="inlineStr"/>
-      <c r="AB96" s="53" t="inlineStr"/>
-      <c r="AC96" s="54" t="inlineStr"/>
-      <c r="AD96" s="54" t="inlineStr"/>
-      <c r="AE96" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 61 = 'spare (size 16)'</t>
-        </is>
-      </c>
-      <c r="AF96" s="54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG96" s="54" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="23" t="inlineStr"/>
-      <c r="B97" s="23" t="inlineStr"/>
-      <c r="C97" s="23" t="inlineStr">
-        <is>
-          <t>A-cabin</t>
-        </is>
-      </c>
-      <c r="D97" s="23" t="inlineStr"/>
-      <c r="E97" s="24" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F97" s="25" t="inlineStr">
-        <is>
-          <t>ix_ws_front_p</t>
-        </is>
-      </c>
-      <c r="G97" s="26" t="inlineStr">
-        <is>
-          <t>FRONT WS INLINE</t>
-        </is>
-      </c>
-      <c r="H97" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="I97" s="26" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J97" s="26" t="inlineStr"/>
-      <c r="K97" s="27" t="inlineStr"/>
-      <c r="L97" s="28" t="inlineStr"/>
-      <c r="M97" s="29" t="inlineStr"/>
-      <c r="N97" s="28" t="inlineStr"/>
-      <c r="O97" s="29" t="inlineStr"/>
-      <c r="P97" s="29" t="inlineStr"/>
-      <c r="Q97" s="30" t="inlineStr">
-        <is>
-          <t>ix_ws_front_p.6</t>
-        </is>
-      </c>
-      <c r="R97" s="31" t="inlineStr">
-        <is>
-          <t>spare (ix_ws_front_p 6)</t>
-        </is>
-      </c>
-      <c r="S97" s="32" t="inlineStr"/>
-      <c r="T97" s="32" t="inlineStr"/>
-      <c r="U97" s="33" t="inlineStr"/>
-      <c r="V97" s="34" t="inlineStr"/>
-      <c r="W97" s="34" t="inlineStr"/>
-      <c r="X97" s="34" t="inlineStr"/>
-      <c r="Y97" s="34" t="inlineStr"/>
-      <c r="Z97" s="35" t="inlineStr"/>
-      <c r="AA97" s="36" t="inlineStr"/>
-      <c r="AB97" s="37" t="inlineStr"/>
-      <c r="AC97" s="38" t="inlineStr"/>
-      <c r="AD97" s="38" t="inlineStr"/>
-      <c r="AE97" s="38" t="inlineStr"/>
-      <c r="AF97" s="38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG97" s="38" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="39" t="inlineStr"/>
-      <c r="B98" s="39" t="inlineStr"/>
-      <c r="C98" s="39" t="inlineStr">
-        <is>
-          <t>A-cabin</t>
-        </is>
-      </c>
-      <c r="D98" s="39" t="inlineStr"/>
-      <c r="E98" s="40" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F98" s="41" t="inlineStr">
-        <is>
-          <t>bus_5v_bha_p</t>
-        </is>
-      </c>
-      <c r="G98" s="42" t="inlineStr">
-        <is>
-          <t>+5V BUS</t>
-        </is>
-      </c>
-      <c r="H98" s="41" t="n">
-        <v>8</v>
-      </c>
-      <c r="I98" s="42" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J98" s="42" t="inlineStr"/>
-      <c r="K98" s="43" t="inlineStr"/>
-      <c r="L98" s="44" t="inlineStr"/>
-      <c r="M98" s="45" t="inlineStr"/>
-      <c r="N98" s="44" t="inlineStr"/>
-      <c r="O98" s="45" t="inlineStr"/>
-      <c r="P98" s="45" t="inlineStr"/>
-      <c r="Q98" s="46" t="inlineStr">
-        <is>
-          <t>ECU-A.A32</t>
-        </is>
-      </c>
-      <c r="R98" s="47" t="inlineStr">
-        <is>
-          <t>+5V sensor (ECU-A A32)</t>
-        </is>
-      </c>
-      <c r="S98" s="48" t="inlineStr"/>
-      <c r="T98" s="48" t="inlineStr"/>
-      <c r="U98" s="49" t="inlineStr"/>
-      <c r="V98" s="50" t="inlineStr"/>
-      <c r="W98" s="50" t="inlineStr"/>
-      <c r="X98" s="50" t="inlineStr"/>
-      <c r="Y98" s="50" t="inlineStr"/>
-      <c r="Z98" s="51" t="inlineStr"/>
-      <c r="AA98" s="52" t="inlineStr"/>
-      <c r="AB98" s="53" t="inlineStr"/>
-      <c r="AC98" s="54" t="inlineStr"/>
-      <c r="AD98" s="54" t="inlineStr"/>
-      <c r="AE98" s="54" t="inlineStr"/>
-      <c r="AF98" s="54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG98" s="54" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="23" t="inlineStr"/>
-      <c r="B99" s="23" t="inlineStr"/>
-      <c r="C99" s="23" t="inlineStr">
-        <is>
-          <t>A-cabin</t>
-        </is>
-      </c>
-      <c r="D99" s="23" t="inlineStr"/>
-      <c r="E99" s="24" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F99" s="25" t="inlineStr">
-        <is>
-          <t>bus_gnd_bha_p</t>
-        </is>
-      </c>
-      <c r="G99" s="26" t="inlineStr">
-        <is>
-          <t>SENSOR GND BUS</t>
-        </is>
-      </c>
-      <c r="H99" s="25" t="n">
-        <v>7</v>
-      </c>
-      <c r="I99" s="26" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J99" s="26" t="inlineStr"/>
-      <c r="K99" s="27" t="inlineStr"/>
-      <c r="L99" s="28" t="inlineStr"/>
-      <c r="M99" s="29" t="inlineStr"/>
-      <c r="N99" s="28" t="inlineStr"/>
-      <c r="O99" s="29" t="inlineStr"/>
-      <c r="P99" s="29" t="inlineStr"/>
-      <c r="Q99" s="30" t="inlineStr">
-        <is>
-          <t>ECU-A.A24</t>
-        </is>
-      </c>
-      <c r="R99" s="31" t="inlineStr">
-        <is>
-          <t>Sensor GND (ECU-A A24)</t>
-        </is>
-      </c>
-      <c r="S99" s="32" t="inlineStr"/>
-      <c r="T99" s="32" t="inlineStr"/>
-      <c r="U99" s="33" t="inlineStr"/>
-      <c r="V99" s="34" t="inlineStr"/>
-      <c r="W99" s="34" t="inlineStr"/>
-      <c r="X99" s="34" t="inlineStr"/>
-      <c r="Y99" s="34" t="inlineStr"/>
-      <c r="Z99" s="35" t="inlineStr"/>
-      <c r="AA99" s="36" t="inlineStr"/>
-      <c r="AB99" s="37" t="inlineStr"/>
-      <c r="AC99" s="38" t="inlineStr"/>
-      <c r="AD99" s="38" t="inlineStr"/>
-      <c r="AE99" s="38" t="inlineStr"/>
-      <c r="AF99" s="38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG99" s="38" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="39" t="inlineStr"/>
-      <c r="B100" s="39" t="inlineStr"/>
-      <c r="C100" s="39" t="inlineStr">
-        <is>
-          <t>A-cabin</t>
-        </is>
-      </c>
-      <c r="D100" s="39" t="inlineStr"/>
-      <c r="E100" s="40" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F100" s="41" t="inlineStr">
-        <is>
-          <t>bus_gnd_bha_p</t>
-        </is>
-      </c>
-      <c r="G100" s="42" t="inlineStr">
-        <is>
-          <t>SENSOR GND BUS</t>
-        </is>
-      </c>
-      <c r="H100" s="41" t="n">
-        <v>8</v>
-      </c>
-      <c r="I100" s="42" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J100" s="42" t="inlineStr"/>
-      <c r="K100" s="43" t="inlineStr"/>
-      <c r="L100" s="44" t="inlineStr"/>
-      <c r="M100" s="45" t="inlineStr"/>
-      <c r="N100" s="44" t="inlineStr"/>
-      <c r="O100" s="45" t="inlineStr"/>
-      <c r="P100" s="45" t="inlineStr"/>
-      <c r="Q100" s="46" t="inlineStr">
-        <is>
-          <t>ECU-A.A24</t>
-        </is>
-      </c>
-      <c r="R100" s="47" t="inlineStr">
-        <is>
-          <t>Sensor GND (ECU-A A24)</t>
-        </is>
-      </c>
-      <c r="S100" s="48" t="inlineStr"/>
-      <c r="T100" s="48" t="inlineStr"/>
-      <c r="U100" s="49" t="inlineStr"/>
-      <c r="V100" s="50" t="inlineStr"/>
-      <c r="W100" s="50" t="inlineStr"/>
-      <c r="X100" s="50" t="inlineStr"/>
-      <c r="Y100" s="50" t="inlineStr"/>
-      <c r="Z100" s="51" t="inlineStr"/>
-      <c r="AA100" s="52" t="inlineStr"/>
-      <c r="AB100" s="53" t="inlineStr"/>
-      <c r="AC100" s="54" t="inlineStr"/>
-      <c r="AD100" s="54" t="inlineStr"/>
-      <c r="AE100" s="54" t="inlineStr"/>
-      <c r="AF100" s="54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG100" s="54" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:AG100"/>
+  <autoFilter ref="A2:AG95"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -12432,7 +11785,7 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="29" customWidth="1" min="7" max="7"/>
@@ -12570,12 +11923,12 @@
     <row r="3">
       <c r="A3" s="23" t="inlineStr">
         <is>
-          <t>sp_5v</t>
+          <t>sp_trig2</t>
         </is>
       </c>
       <c r="B3" s="55" t="inlineStr">
         <is>
-          <t>At ECU-A plug - SP-5V-A: +5 V sensor supply</t>
+          <t>At ECU-A plug - SP-CAM: cam signal + 1.8k pull-up to +8V</t>
         </is>
       </c>
       <c r="C3" s="23" t="inlineStr">
@@ -12585,27 +11938,27 @@
       </c>
       <c r="D3" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A32</t>
+          <t>ECU-A.A9</t>
         </is>
       </c>
       <c r="E3" s="31" t="inlineStr">
         <is>
-          <t>+5V sensor (ECU-A A32)</t>
+          <t>Cam sensor signal (ECU-A A9)</t>
         </is>
       </c>
       <c r="F3" s="32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G3" s="32" t="inlineStr">
         <is>
-          <t>18+18+18+18+20</t>
+          <t>20+20+20</t>
         </is>
       </c>
       <c r="H3" s="32" t="n">
-        <v>7518</v>
+        <v>3066</v>
       </c>
       <c r="I3" s="32" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J3" s="56" t="inlineStr">
         <is>
@@ -12614,7 +11967,7 @@
       </c>
       <c r="K3" s="36" t="inlineStr">
         <is>
-          <t>At ECU-A plug (layout node b_bp_900)</t>
+          <t>At ECU-A plug (layout node bp_960)</t>
         </is>
       </c>
       <c r="L3" s="38" t="inlineStr">
@@ -12626,12 +11979,12 @@
     <row r="4">
       <c r="A4" s="39" t="inlineStr">
         <is>
-          <t>sp_5v_2</t>
+          <t>sp_5v</t>
         </is>
       </c>
       <c r="B4" s="57" t="inlineStr">
         <is>
-          <t>At ECU-A plug - SP-5V-PEDAL: +5 V to pedal + cruise</t>
+          <t>At ECU-A plug - SP-5V-A: +5 V sensor supply</t>
         </is>
       </c>
       <c r="C4" s="39" t="inlineStr">
@@ -12650,18 +12003,18 @@
         </is>
       </c>
       <c r="F4" s="48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4" s="48" t="inlineStr">
         <is>
-          <t>18+20+20+20</t>
+          <t>18+18+18+18+20</t>
         </is>
       </c>
       <c r="H4" s="48" t="n">
-        <v>4690</v>
+        <v>7518</v>
       </c>
       <c r="I4" s="48" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J4" s="58" t="inlineStr">
         <is>
@@ -12682,12 +12035,12 @@
     <row r="5">
       <c r="A5" s="23" t="inlineStr">
         <is>
-          <t>sp_8v</t>
+          <t>sp_shield_a</t>
         </is>
       </c>
       <c r="B5" s="55" t="inlineStr">
         <is>
-          <t>At ECU-A plug - SP-8V: +8 V cam sensor supply</t>
+          <t>6 mm behind ECU-A plug - SP-SHIELD-A: shield drains</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
@@ -12697,27 +12050,27 @@
       </c>
       <c r="D5" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A6</t>
+          <t>ECU-A.A7</t>
         </is>
       </c>
       <c r="E5" s="31" t="inlineStr">
         <is>
-          <t>+8V cam sensor (ECU-A A6)</t>
+          <t>Screen A (ECU A7, SHIELD_A)</t>
         </is>
       </c>
       <c r="F5" s="32" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G5" s="32" t="inlineStr">
         <is>
-          <t>20+20+20</t>
+          <t>20+20+20+20+20+20 + shield</t>
         </is>
       </c>
       <c r="H5" s="32" t="n">
-        <v>3066</v>
+        <v>6132</v>
       </c>
       <c r="I5" s="32" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J5" s="56" t="inlineStr">
         <is>
@@ -12726,7 +12079,7 @@
       </c>
       <c r="K5" s="36" t="inlineStr">
         <is>
-          <t>At ECU-A plug (layout node b_bp_900)</t>
+          <t>6 mm behind ECU-A plug (layout node ecu_a)</t>
         </is>
       </c>
       <c r="L5" s="38" t="inlineStr">
@@ -12738,12 +12091,12 @@
     <row r="6">
       <c r="A6" s="39" t="inlineStr">
         <is>
-          <t>sp_trig2</t>
+          <t>sp_8v</t>
         </is>
       </c>
       <c r="B6" s="57" t="inlineStr">
         <is>
-          <t>At ECU-A plug - SP-CAM: cam signal + 1.8k pull-up to +8V</t>
+          <t>At ECU-A plug - SP-8V: +8 V cam sensor supply</t>
         </is>
       </c>
       <c r="C6" s="39" t="inlineStr">
@@ -12753,12 +12106,12 @@
       </c>
       <c r="D6" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A9</t>
+          <t>ECU-A.A6</t>
         </is>
       </c>
       <c r="E6" s="47" t="inlineStr">
         <is>
-          <t>Cam sensor signal (ECU-A A9)</t>
+          <t>+8V cam sensor (ECU-A A6)</t>
         </is>
       </c>
       <c r="F6" s="48" t="n">
@@ -12782,7 +12135,7 @@
       </c>
       <c r="K6" s="52" t="inlineStr">
         <is>
-          <t>At ECU-A plug (layout node bp_960)</t>
+          <t>At ECU-A plug (layout node b_bp_900)</t>
         </is>
       </c>
       <c r="L6" s="54" t="inlineStr">
@@ -12794,12 +12147,12 @@
     <row r="7">
       <c r="A7" s="23" t="inlineStr">
         <is>
-          <t>sp_gndout</t>
+          <t>sp_sw12</t>
         </is>
       </c>
       <c r="B7" s="55" t="inlineStr">
         <is>
-          <t>At ECU-A plug - SP-GNDOUT-A: sensor ground</t>
+          <t>At ECU-A plug - SP-SW12: switched +12 V</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -12809,24 +12162,24 @@
       </c>
       <c r="D7" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A24</t>
+          <t>LOGIC.BUS2-2</t>
         </is>
       </c>
       <c r="E7" s="31" t="inlineStr">
         <is>
-          <t>Sensor GND (ECU-A A24)</t>
+          <t>+12V switched (LOGIC SW12 bus)</t>
         </is>
       </c>
       <c r="F7" s="32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G7" s="32" t="inlineStr">
         <is>
-          <t>18+18+20+20+20</t>
+          <t>18+18+18+20</t>
         </is>
       </c>
       <c r="H7" s="32" t="n">
-        <v>6314</v>
+        <v>5894</v>
       </c>
       <c r="I7" s="32" t="n">
         <v>12</v>
@@ -12838,7 +12191,7 @@
       </c>
       <c r="K7" s="36" t="inlineStr">
         <is>
-          <t>At ECU-A plug (layout node b_bp_1140)</t>
+          <t>At ECU-A plug (layout node b_bp_1080)</t>
         </is>
       </c>
       <c r="L7" s="38" t="inlineStr">
@@ -12850,12 +12203,12 @@
     <row r="8">
       <c r="A8" s="39" t="inlineStr">
         <is>
-          <t>sp_sw12</t>
+          <t>sp_gndout</t>
         </is>
       </c>
       <c r="B8" s="57" t="inlineStr">
         <is>
-          <t>At ECU-A plug - SP-SW12: switched +12 V</t>
+          <t>At ECU-A plug - SP-GNDOUT-A: sensor ground</t>
         </is>
       </c>
       <c r="C8" s="39" t="inlineStr">
@@ -12865,24 +12218,24 @@
       </c>
       <c r="D8" s="46" t="inlineStr">
         <is>
-          <t>LOGIC.SW12</t>
+          <t>ECU-A.A24</t>
         </is>
       </c>
       <c r="E8" s="47" t="inlineStr">
         <is>
-          <t>+12V switched (LOGIC SW12 bus)</t>
+          <t>Sensor GND (ECU-A A24)</t>
         </is>
       </c>
       <c r="F8" s="48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8" s="48" t="inlineStr">
         <is>
-          <t>18+18+18+20</t>
+          <t>18+18+20+20+20</t>
         </is>
       </c>
       <c r="H8" s="48" t="n">
-        <v>5894</v>
+        <v>6314</v>
       </c>
       <c r="I8" s="48" t="n">
         <v>12</v>
@@ -12894,7 +12247,7 @@
       </c>
       <c r="K8" s="52" t="inlineStr">
         <is>
-          <t>At ECU-A plug (layout node b_bp_1080)</t>
+          <t>At ECU-A plug (layout node b_bp_1140)</t>
         </is>
       </c>
       <c r="L8" s="54" t="inlineStr">
@@ -12962,12 +12315,12 @@
     <row r="10">
       <c r="A10" s="39" t="inlineStr">
         <is>
-          <t>sp_shield_a</t>
+          <t>sp_5v_2</t>
         </is>
       </c>
       <c r="B10" s="57" t="inlineStr">
         <is>
-          <t>6 mm behind ECU-A plug - SP-SHIELD-A: shield drains</t>
+          <t>At ECU-A plug - SP-5V-PEDAL: +5 V to pedal + cruise</t>
         </is>
       </c>
       <c r="C10" s="39" t="inlineStr">
@@ -12977,24 +12330,24 @@
       </c>
       <c r="D10" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A7</t>
+          <t>ECU-A.A32</t>
         </is>
       </c>
       <c r="E10" s="47" t="inlineStr">
         <is>
-          <t>Screen A (ECU A7, SHIELD_A)</t>
+          <t>+5V sensor (ECU-A A32)</t>
         </is>
       </c>
       <c r="F10" s="48" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G10" s="48" t="inlineStr">
         <is>
-          <t>20+20+20+20+20+20 + shield</t>
+          <t>18+20+20+20</t>
         </is>
       </c>
       <c r="H10" s="48" t="n">
-        <v>6132</v>
+        <v>4690</v>
       </c>
       <c r="I10" s="48" t="n">
         <v>12</v>
@@ -13006,7 +12359,7 @@
       </c>
       <c r="K10" s="52" t="inlineStr">
         <is>
-          <t>6 mm behind ECU-A plug (layout node ecu_a)</t>
+          <t>At ECU-A plug (layout node b_bp_900)</t>
         </is>
       </c>
       <c r="L10" s="54" t="inlineStr">
@@ -15105,7 +14458,7 @@
     <row r="35">
       <c r="A35" s="23" t="inlineStr">
         <is>
-          <t>INJ</t>
+          <t>EPSEN</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
@@ -15114,11 +14467,11 @@
         </is>
       </c>
       <c r="C35" s="25" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="D35" s="26" t="inlineStr">
         <is>
-          <t>Injector +12 V feed</t>
+          <t>EHPS enable +12 V</t>
         </is>
       </c>
       <c r="E35" s="27" t="inlineStr">
@@ -15132,16 +14485,16 @@
         </is>
       </c>
       <c r="G35" s="28" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="H35" s="29" t="inlineStr">
         <is>
-          <t>Injector +12 V feed</t>
+          <t>EHPS enable +12 V</t>
         </is>
       </c>
       <c r="I35" s="59" t="inlineStr">
         <is>
-          <t>+12V injectors (LOGIC INJ 15A)</t>
+          <t>+12V EHPS enable (LOGIC MRS 7.5A)</t>
         </is>
       </c>
       <c r="J35" s="60" t="inlineStr">
@@ -15153,7 +14506,7 @@
     <row r="36">
       <c r="A36" s="39" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>CRANKC</t>
         </is>
       </c>
       <c r="B36" s="40" t="inlineStr">
@@ -15162,11 +14515,11 @@
         </is>
       </c>
       <c r="C36" s="41" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D36" s="42" t="inlineStr">
         <is>
-          <t>Coil +12 V feed</t>
+          <t>Crank sensor shield</t>
         </is>
       </c>
       <c r="E36" s="43" t="inlineStr">
@@ -15180,16 +14533,16 @@
         </is>
       </c>
       <c r="G36" s="44" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H36" s="45" t="inlineStr">
         <is>
-          <t>Coil +12 V feed</t>
+          <t>Crank sensor shield</t>
         </is>
       </c>
       <c r="I36" s="61" t="inlineStr">
         <is>
-          <t>+12V coils (LOGIC COP 15A)</t>
+          <t>Screen A (ECU A7, SHIELD_A)</t>
         </is>
       </c>
       <c r="J36" s="62" t="inlineStr">
@@ -15201,7 +14554,7 @@
     <row r="37">
       <c r="A37" s="23" t="inlineStr">
         <is>
-          <t>EPSEN</t>
+          <t>CAM</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">
@@ -15210,11 +14563,11 @@
         </is>
       </c>
       <c r="C37" s="25" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="D37" s="26" t="inlineStr">
         <is>
-          <t>EHPS enable +12 V</t>
+          <t>Cam sensor shield</t>
         </is>
       </c>
       <c r="E37" s="27" t="inlineStr">
@@ -15228,16 +14581,16 @@
         </is>
       </c>
       <c r="G37" s="28" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="H37" s="29" t="inlineStr">
         <is>
-          <t>EHPS enable +12 V</t>
+          <t>Cam sensor shield</t>
         </is>
       </c>
       <c r="I37" s="59" t="inlineStr">
         <is>
-          <t>+12V EHPS enable (LOGIC MRS 7.5A)</t>
+          <t>Screen A (ECU A7, SHIELD_A)</t>
         </is>
       </c>
       <c r="J37" s="60" t="inlineStr">
@@ -15249,7 +14602,7 @@
     <row r="38">
       <c r="A38" s="39" t="inlineStr">
         <is>
-          <t>CRANKC</t>
+          <t>TURBO</t>
         </is>
       </c>
       <c r="B38" s="40" t="inlineStr">
@@ -15258,11 +14611,11 @@
         </is>
       </c>
       <c r="C38" s="41" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D38" s="42" t="inlineStr">
         <is>
-          <t>Crank sensor shield</t>
+          <t>Turbo speed shield</t>
         </is>
       </c>
       <c r="E38" s="43" t="inlineStr">
@@ -15276,11 +14629,11 @@
         </is>
       </c>
       <c r="G38" s="44" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H38" s="45" t="inlineStr">
         <is>
-          <t>Crank sensor shield</t>
+          <t>Turbo speed shield</t>
         </is>
       </c>
       <c r="I38" s="61" t="inlineStr">
@@ -15297,7 +14650,7 @@
     <row r="39">
       <c r="A39" s="23" t="inlineStr">
         <is>
-          <t>CAM</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="B39" s="24" t="inlineStr">
@@ -15306,11 +14659,11 @@
         </is>
       </c>
       <c r="C39" s="25" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D39" s="26" t="inlineStr">
         <is>
-          <t>Cam sensor shield</t>
+          <t>Flex fuel shield</t>
         </is>
       </c>
       <c r="E39" s="27" t="inlineStr">
@@ -15324,11 +14677,11 @@
         </is>
       </c>
       <c r="G39" s="28" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H39" s="29" t="inlineStr">
         <is>
-          <t>Cam sensor shield</t>
+          <t>Flex fuel shield</t>
         </is>
       </c>
       <c r="I39" s="59" t="inlineStr">
@@ -15345,7 +14698,7 @@
     <row r="40">
       <c r="A40" s="39" t="inlineStr">
         <is>
-          <t>TURBO</t>
+          <t>ETBS</t>
         </is>
       </c>
       <c r="B40" s="40" t="inlineStr">
@@ -15354,11 +14707,11 @@
         </is>
       </c>
       <c r="C40" s="41" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D40" s="42" t="inlineStr">
         <is>
-          <t>Turbo speed shield</t>
+          <t>Throttle shield</t>
         </is>
       </c>
       <c r="E40" s="43" t="inlineStr">
@@ -15372,11 +14725,11 @@
         </is>
       </c>
       <c r="G40" s="44" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H40" s="45" t="inlineStr">
         <is>
-          <t>Turbo speed shield</t>
+          <t>Throttle shield</t>
         </is>
       </c>
       <c r="I40" s="61" t="inlineStr">
@@ -15393,7 +14746,7 @@
     <row r="41">
       <c r="A41" s="23" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="B41" s="24" t="inlineStr">
@@ -15402,11 +14755,11 @@
         </is>
       </c>
       <c r="C41" s="25" t="n">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="D41" s="26" t="inlineStr">
         <is>
-          <t>Flex fuel shield</t>
+          <t>EHPS relay coil (-)</t>
         </is>
       </c>
       <c r="E41" s="27" t="inlineStr">
@@ -15420,16 +14773,16 @@
         </is>
       </c>
       <c r="G41" s="28" t="n">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="H41" s="29" t="inlineStr">
         <is>
-          <t>Flex fuel shield</t>
+          <t>EHPS relay coil (-)</t>
         </is>
       </c>
       <c r="I41" s="59" t="inlineStr">
         <is>
-          <t>Screen A (ECU A7, SHIELD_A)</t>
+          <t>EHPS relay coil (-) (DRB102 56)</t>
         </is>
       </c>
       <c r="J41" s="60" t="inlineStr">
@@ -15441,7 +14794,7 @@
     <row r="42">
       <c r="A42" s="39" t="inlineStr">
         <is>
-          <t>ETBS</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B42" s="40" t="inlineStr">
@@ -15450,11 +14803,11 @@
         </is>
       </c>
       <c r="C42" s="41" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D42" s="42" t="inlineStr">
         <is>
-          <t>Throttle shield</t>
+          <t>Coil +12 V feed</t>
         </is>
       </c>
       <c r="E42" s="43" t="inlineStr">
@@ -15468,16 +14821,16 @@
         </is>
       </c>
       <c r="G42" s="44" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H42" s="45" t="inlineStr">
         <is>
-          <t>Throttle shield</t>
+          <t>Coil +12 V feed</t>
         </is>
       </c>
       <c r="I42" s="61" t="inlineStr">
         <is>
-          <t>Screen A (ECU A7, SHIELD_A)</t>
+          <t>+12V coils (LOGIC COP 15A)</t>
         </is>
       </c>
       <c r="J42" s="62" t="inlineStr">
@@ -15489,7 +14842,7 @@
     <row r="43">
       <c r="A43" s="23" t="inlineStr">
         <is>
-          <t>EPS</t>
+          <t>INJ</t>
         </is>
       </c>
       <c r="B43" s="24" t="inlineStr">
@@ -15498,11 +14851,11 @@
         </is>
       </c>
       <c r="C43" s="25" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="D43" s="26" t="inlineStr">
         <is>
-          <t>EHPS relay coil (-)</t>
+          <t>Injector +12 V feed</t>
         </is>
       </c>
       <c r="E43" s="27" t="inlineStr">
@@ -15516,16 +14869,16 @@
         </is>
       </c>
       <c r="G43" s="28" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="H43" s="29" t="inlineStr">
         <is>
-          <t>EHPS relay coil (-)</t>
+          <t>Injector +12 V feed</t>
         </is>
       </c>
       <c r="I43" s="59" t="inlineStr">
         <is>
-          <t>EHPS relay coil (-) (bh_a_fw 56)</t>
+          <t>+12V injectors (LOGIC INJ 15A)</t>
         </is>
       </c>
       <c r="J43" s="60" t="inlineStr">

--- a/docs/harness/wirelist/A-cabin-wirelist.xlsx
+++ b/docs/harness/wirelist/A-cabin-wirelist.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Mates" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wire list'!$A$2:$AG$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wire list'!$A$2:$AG$98</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Wire list'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Splices'!$A$2:$L$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Splices'!$A$2:$L$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Splices'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Connectors'!$A$2:$G$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Connectors'!$1:$2</definedName>
@@ -745,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AG95"/>
+  <dimension ref="A1:AG98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -753,7 +753,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
@@ -764,7 +764,7 @@
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="36" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="45" customWidth="1" min="17" max="17"/>
     <col width="32" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="18" customWidth="1" min="20" max="20"/>
@@ -3330,7 +3330,7 @@
       <c r="AD21" s="38" t="inlineStr"/>
       <c r="AE21" s="38" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A9 Trigger 2 (TRIG2_CAM); splice sp_trig2 named in SoT</t>
+          <t>channels.csv ecu_a A9 Trigger 2 (TRIG2_CAM); splice sp_trig2: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF21" s="38" t="inlineStr">
@@ -3445,7 +3445,7 @@
       <c r="AD22" s="54" t="inlineStr"/>
       <c r="AE22" s="54" t="inlineStr">
         <is>
-          <t>splice sp_trig2 named in SoT; DRB102 13 = section A c29 'ECU-A A9'</t>
+          <t>splice sp_trig2: node of the wire list (SoT); DRB102 13 = section A c29 'ECU-A A9'</t>
         </is>
       </c>
       <c r="AF22" s="54" t="inlineStr">
@@ -3560,7 +3560,7 @@
       <c r="AD23" s="38" t="inlineStr"/>
       <c r="AE23" s="38" t="inlineStr">
         <is>
-          <t>splice sp_trig2 named in SoT</t>
+          <t>splice sp_trig2: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF23" s="38" t="inlineStr">
@@ -3679,7 +3679,7 @@
       <c r="AD24" s="54" t="inlineStr"/>
       <c r="AE24" s="54" t="inlineStr">
         <is>
-          <t>splice sp_8v named in SoT</t>
+          <t>splice sp_8v: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF24" s="54" t="inlineStr">
@@ -3800,7 +3800,7 @@
       <c r="AD25" s="38" t="inlineStr"/>
       <c r="AE25" s="38" t="inlineStr">
         <is>
-          <t>splice sp_8v named in SoT; channels.csv ecu_a A6 +8V Out (P8V)</t>
+          <t>splice sp_8v: node of the wire list (SoT); channels.csv ecu_a A6 +8V Out (P8V)</t>
         </is>
       </c>
       <c r="AF25" s="38" t="inlineStr">
@@ -3919,7 +3919,7 @@
       <c r="AD26" s="54" t="inlineStr"/>
       <c r="AE26" s="54" t="inlineStr">
         <is>
-          <t>splice sp_8v named in SoT; DRB102 12 = section A c4 '+8V Out to cam Hall'</t>
+          <t>splice sp_8v: node of the wire list (SoT); DRB102 12 = section A c4 '+8V Out to cam Hall'</t>
         </is>
       </c>
       <c r="AF26" s="54" t="inlineStr">
@@ -4036,7 +4036,7 @@
       <c r="AD27" s="38" t="inlineStr"/>
       <c r="AE27" s="38" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A32 +5V Out (P5V); splice sp_5v named in SoT</t>
+          <t>channels.csv ecu_a A32 +5V Out (P5V); splice sp_5v: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF27" s="38" t="inlineStr">
@@ -4151,7 +4151,7 @@
       <c r="AD28" s="54" t="inlineStr"/>
       <c r="AE28" s="54" t="inlineStr">
         <is>
-          <t>splice sp_5v named in SoT</t>
+          <t>splice sp_5v: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF28" s="54" t="inlineStr">
@@ -4954,7 +4954,7 @@
       <c r="AD35" s="38" t="inlineStr"/>
       <c r="AE35" s="38" t="inlineStr">
         <is>
-          <t>splice sp_5v named in SoT; splice sp_5v_2 named in SoT</t>
+          <t>splice sp_5v: node of the wire list (SoT); splice sp_5v_2: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF35" s="38" t="inlineStr">
@@ -5075,7 +5075,7 @@
       <c r="AD36" s="54" t="inlineStr"/>
       <c r="AE36" s="54" t="inlineStr">
         <is>
-          <t>splice sp_5v named in SoT; splice sp_5v_b named in SoT</t>
+          <t>splice sp_5v: node of the wire list (SoT); splice sp_5v_b: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF36" s="54" t="inlineStr">
@@ -5202,7 +5202,7 @@
       <c r="AD37" s="38" t="inlineStr"/>
       <c r="AE37" s="38" t="inlineStr">
         <is>
-          <t>splice sp_5v_2 named in SoT</t>
+          <t>splice sp_5v_2: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF37" s="38" t="inlineStr">
@@ -5327,7 +5327,7 @@
       <c r="AD38" s="54" t="inlineStr"/>
       <c r="AE38" s="54" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A24 Gnd Out (GNDOUT); splice sp_gndout named in SoT</t>
+          <t>channels.csv ecu_a A24 Gnd Out (GNDOUT_A); splice sp_gndout: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF38" s="54" t="inlineStr">
@@ -5446,7 +5446,7 @@
       <c r="AD39" s="38" t="inlineStr"/>
       <c r="AE39" s="38" t="inlineStr">
         <is>
-          <t>splice sp_gndout named in SoT</t>
+          <t>splice sp_gndout: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF39" s="38" t="inlineStr">
@@ -6164,7 +6164,7 @@
       <c r="AD45" s="38" t="inlineStr"/>
       <c r="AE45" s="38" t="inlineStr">
         <is>
-          <t>splice sp_sw12 named in SoT</t>
+          <t>splice sp_sw12: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF45" s="38" t="inlineStr">
@@ -6219,24 +6219,20 @@
       <c r="J46" s="42" t="inlineStr"/>
       <c r="K46" s="43" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="L46" s="44" t="inlineStr">
         <is>
-          <t>ecu_a</t>
+          <t>sp_a5</t>
         </is>
       </c>
       <c r="M46" s="45" t="inlineStr">
         <is>
-          <t>ECU-A</t>
-        </is>
-      </c>
-      <c r="N46" s="44" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
+          <t>splice sp_a5 (SP-A5: ECU main feed, SW12 + IG2 diode)</t>
+        </is>
+      </c>
+      <c r="N46" s="44" t="inlineStr"/>
       <c r="O46" s="45" t="inlineStr">
         <is>
           <t>ECU main +12 V</t>
@@ -6255,7 +6251,7 @@
       </c>
       <c r="S46" s="48" t="inlineStr">
         <is>
-          <t>sp_sw12</t>
+          <t>sp_a5</t>
         </is>
       </c>
       <c r="T46" s="48" t="inlineStr"/>
@@ -6285,7 +6281,7 @@
       <c r="AD46" s="54" t="inlineStr"/>
       <c r="AE46" s="54" t="inlineStr">
         <is>
-          <t>splice sp_sw12 named in SoT; channels.csv ecu_a A5 14V + (P14V)</t>
+          <t>splice sp_sw12: node of the wire list (SoT); splice sp_a5: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF46" s="54" t="inlineStr">
@@ -6298,12 +6294,12 @@
     <row r="47">
       <c r="A47" s="23" t="inlineStr">
         <is>
-          <t>SW12</t>
+          <t>IG2WAKE</t>
         </is>
       </c>
       <c r="B47" s="23" t="inlineStr">
         <is>
-          <t>w_rail_sp_sw12_c</t>
+          <t>w_ig2_in</t>
         </is>
       </c>
       <c r="C47" s="23" t="inlineStr">
@@ -6314,93 +6310,109 @@
       <c r="D47" s="23" t="inlineStr"/>
       <c r="E47" s="24" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>sp_sw12</t>
+          <t>J/B No.1 1H (output of the 7.5A IGN fuse, fed from I13 IG2 pin 9 B-O via 1A-5), ECU wake tap (factory)</t>
         </is>
       </c>
       <c r="G47" s="26" t="inlineStr">
         <is>
-          <t>splice sp_sw12 (SP-SW12: switched +12 V)</t>
-        </is>
-      </c>
-      <c r="H47" s="25" t="inlineStr"/>
+          <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O</t>
+        </is>
+      </c>
+      <c r="H47" s="25" t="n">
+        <v>7</v>
+      </c>
       <c r="I47" s="26" t="inlineStr">
         <is>
-          <t>+12 V boost + flex</t>
+          <t>IG2 wake feed</t>
         </is>
       </c>
       <c r="J47" s="26" t="inlineStr"/>
       <c r="K47" s="27" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>diode</t>
         </is>
       </c>
       <c r="L47" s="28" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>d_ig2_wake</t>
         </is>
       </c>
       <c r="M47" s="29" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>IG2 wake diode (1N5822, anode)</t>
         </is>
       </c>
       <c r="N47" s="28" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="O47" s="29" t="inlineStr">
         <is>
-          <t>+12 V boost + flex</t>
+          <t>IG2 wake feed</t>
         </is>
       </c>
       <c r="P47" s="29" t="inlineStr"/>
       <c r="Q47" s="30" t="inlineStr">
         <is>
-          <t>LOGIC.BUS2-2</t>
+          <t>J/B No.1 1H (output of the 7.5A IGN fuse, fed from I13 IG2 pin 9 B-O via 1A-5), ECU wake tap (factory).7</t>
         </is>
       </c>
       <c r="R47" s="31" t="inlineStr">
         <is>
-          <t>+12V switched (LOGIC SW12 bus)</t>
-        </is>
-      </c>
-      <c r="S47" s="32" t="inlineStr">
-        <is>
-          <t>sp_sw12</t>
-        </is>
-      </c>
+          <t>IG2 wake feed (J/B No 1 1H (output of the 7 5A IGN fuse, fed from I13 IG2 pin 9 B-O via 1A-5), ECU wake tap (factory) 7)</t>
+        </is>
+      </c>
+      <c r="S47" s="32" t="inlineStr"/>
       <c r="T47" s="32" t="inlineStr"/>
       <c r="U47" s="33" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V47" s="34" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="W47" s="34" t="inlineStr"/>
       <c r="X47" s="34" t="inlineStr">
         <is>
-          <t>Blue</t>
-        </is>
-      </c>
-      <c r="Y47" s="34" t="inlineStr"/>
+          <t>White-Yellow-White</t>
+        </is>
+      </c>
+      <c r="Y47" s="34" t="n">
+        <v>900</v>
+      </c>
       <c r="Z47" s="35" t="inlineStr">
         <is>
-          <t>trunk ECU-A to bulkhead (RH firewall)</t>
-        </is>
-      </c>
-      <c r="AA47" s="36" t="inlineStr"/>
-      <c r="AB47" s="37" t="inlineStr"/>
-      <c r="AC47" s="38" t="inlineStr"/>
-      <c r="AD47" s="38" t="inlineStr"/>
+          <t>IG2 tap branch (LH kick panel)</t>
+        </is>
+      </c>
+      <c r="AA47" s="36" t="inlineStr">
+        <is>
+          <t>OEM J/B No.1 (LH kick panel) 1H pin 7, B-O - IGN fuse out (EWD 1993 p.62); same lead as the ECU-B B28 sense tap, own splice</t>
+        </is>
+      </c>
+      <c r="AB47" s="37" t="inlineStr">
+        <is>
+          <t>B-O</t>
+        </is>
+      </c>
+      <c r="AC47" s="38" t="inlineStr">
+        <is>
+          <t>1993 TIS EWD p.62 (Power Source)</t>
+        </is>
+      </c>
+      <c r="AD47" s="38" t="inlineStr">
+        <is>
+          <t>solder splice onto the factory lead</t>
+        </is>
+      </c>
       <c r="AE47" s="38" t="inlineStr">
         <is>
-          <t>splice sp_sw12 named in SoT; DRB102 20 = section A c5 'Switched 12V to engine sensors'</t>
+          <t>flying lead FL_IG2_WAKE_C1: EWD J/B No.1 1H (output of the 7.5A IGN fuse, fed from I13 IG2 pin 9 B-O via 1A-5), ECU wake tap pin 7 B-O</t>
         </is>
       </c>
       <c r="AF47" s="38" t="inlineStr">
@@ -6418,7 +6430,7 @@
       </c>
       <c r="B48" s="39" t="inlineStr">
         <is>
-          <t>w_rail_sw12_b_c_ac</t>
+          <t>w_ig2_diode</t>
         </is>
       </c>
       <c r="C48" s="39" t="inlineStr">
@@ -6426,61 +6438,53 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D48" s="39" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
+      <c r="D48" s="39" t="inlineStr"/>
       <c r="E48" s="40" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>diode</t>
         </is>
       </c>
       <c r="F48" s="41" t="inlineStr">
         <is>
-          <t>sp_sw12</t>
+          <t>d_ig2_wake</t>
         </is>
       </c>
       <c r="G48" s="42" t="inlineStr">
         <is>
-          <t>splice sp_sw12 (SP-SW12: switched +12 V)</t>
-        </is>
-      </c>
-      <c r="H48" s="41" t="inlineStr"/>
+          <t>IG2 wake diode (1N5822, cathode)</t>
+        </is>
+      </c>
+      <c r="H48" s="41" t="n">
+        <v>2</v>
+      </c>
       <c r="I48" s="42" t="inlineStr">
         <is>
-          <t>+12 V gearbox speed</t>
+          <t>ECU main +12 V</t>
         </is>
       </c>
       <c r="J48" s="42" t="inlineStr"/>
       <c r="K48" s="43" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="L48" s="44" t="inlineStr">
         <is>
-          <t>bh_b_fw</t>
+          <t>sp_a5</t>
         </is>
       </c>
       <c r="M48" s="45" t="inlineStr">
         <is>
-          <t>BH-B (firewall bulkhead DRB102, RH)</t>
-        </is>
-      </c>
-      <c r="N48" s="44" t="n">
-        <v>90</v>
-      </c>
+          <t>splice sp_a5 (SP-A5: ECU main feed, SW12 + IG2 diode)</t>
+        </is>
+      </c>
+      <c r="N48" s="44" t="inlineStr"/>
       <c r="O48" s="45" t="inlineStr">
         <is>
-          <t>+12 V gearbox speed</t>
-        </is>
-      </c>
-      <c r="P48" s="45" t="inlineStr">
-        <is>
-          <t>(firewall bulkhead, RH); sensor +12V</t>
-        </is>
-      </c>
+          <t>ECU main +12 V</t>
+        </is>
+      </c>
+      <c r="P48" s="45" t="inlineStr"/>
       <c r="Q48" s="46" t="inlineStr">
         <is>
           <t>LOGIC.BUS2-2</t>
@@ -6493,7 +6497,7 @@
       </c>
       <c r="S48" s="48" t="inlineStr">
         <is>
-          <t>sp_sw12</t>
+          <t>sp_a5</t>
         </is>
       </c>
       <c r="T48" s="48" t="inlineStr"/>
@@ -6514,7 +6518,7 @@
       <c r="Y48" s="50" t="inlineStr"/>
       <c r="Z48" s="51" t="inlineStr">
         <is>
-          <t>to ECU-B plug (beside ECU-A)</t>
+          <t>at ECU-A plug</t>
         </is>
       </c>
       <c r="AA48" s="52" t="inlineStr"/>
@@ -6523,7 +6527,7 @@
       <c r="AD48" s="54" t="inlineStr"/>
       <c r="AE48" s="54" t="inlineStr">
         <is>
-          <t>splice sp_sw12 named in SoT; DRB102 90 = section B c20 'Switched 12V to gearbox VSS (from sp_sw12)'</t>
+          <t>splice sp_a5: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF48" s="54" t="inlineStr">
@@ -6531,21 +6535,17 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG48" s="54" t="inlineStr">
-        <is>
-          <t>owner TBD: a half has no length estimate (drawn today as w_rail_sw12_b_c_ac on A-cabin, ? mm; w_rail_sw12_b_c on B-cabin, 520 mm)</t>
-        </is>
-      </c>
+      <c r="AG48" s="54" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="23" t="inlineStr">
         <is>
-          <t>EPSEN</t>
+          <t>SW12</t>
         </is>
       </c>
       <c r="B49" s="23" t="inlineStr">
         <is>
-          <t>w_fb_mrs_en</t>
+          <t>w_a5_pin</t>
         </is>
       </c>
       <c r="C49" s="23" t="inlineStr">
@@ -6553,79 +6553,73 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D49" s="23" t="inlineStr">
-        <is>
-          <t>CabinPower</t>
-        </is>
-      </c>
+      <c r="D49" s="23" t="inlineStr"/>
       <c r="E49" s="24" t="inlineStr">
         <is>
+          <t>splice</t>
+        </is>
+      </c>
+      <c r="F49" s="25" t="inlineStr">
+        <is>
+          <t>sp_a5</t>
+        </is>
+      </c>
+      <c r="G49" s="26" t="inlineStr">
+        <is>
+          <t>splice sp_a5 (SP-A5: ECU main feed, SW12 + IG2 diode)</t>
+        </is>
+      </c>
+      <c r="H49" s="25" t="inlineStr"/>
+      <c r="I49" s="26" t="inlineStr">
+        <is>
+          <t>ECU main +12 V</t>
+        </is>
+      </c>
+      <c r="J49" s="26" t="inlineStr"/>
+      <c r="K49" s="27" t="inlineStr">
+        <is>
           <t>connector</t>
         </is>
       </c>
-      <c r="F49" s="25" t="inlineStr">
-        <is>
-          <t>fb_logic</t>
-        </is>
-      </c>
-      <c r="G49" s="26" t="inlineStr">
-        <is>
-          <t>FB-LOGIC</t>
-        </is>
-      </c>
-      <c r="H49" s="25" t="inlineStr">
-        <is>
-          <t>BUS2-12</t>
-        </is>
-      </c>
-      <c r="I49" s="26" t="inlineStr">
-        <is>
-          <t>EHPS enable +12 V</t>
-        </is>
-      </c>
-      <c r="J49" s="26" t="inlineStr">
-        <is>
-          <t>LOGIC box (glove box) fuse MRS 7.5A Fuse fed from EPS enable relay k_eps_en pin 87 (ignition-switched).</t>
-        </is>
-      </c>
-      <c r="K49" s="27" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
       <c r="L49" s="28" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>ecu_a</t>
         </is>
       </c>
       <c r="M49" s="29" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
-        </is>
-      </c>
-      <c r="N49" s="28" t="n">
-        <v>42</v>
+          <t>ECU-A</t>
+        </is>
+      </c>
+      <c r="N49" s="28" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
       </c>
       <c r="O49" s="29" t="inlineStr">
         <is>
-          <t>EHPS enable +12 V</t>
+          <t>ECU main +12 V</t>
         </is>
       </c>
       <c r="P49" s="29" t="inlineStr"/>
       <c r="Q49" s="30" t="inlineStr">
         <is>
-          <t>LOGIC.BUS2-12</t>
+          <t>LOGIC.BUS2-2</t>
         </is>
       </c>
       <c r="R49" s="31" t="inlineStr">
         <is>
-          <t>+12V EHPS enable (LOGIC MRS 7.5A)</t>
-        </is>
-      </c>
-      <c r="S49" s="32" t="inlineStr"/>
+          <t>+12V switched (LOGIC SW12 bus)</t>
+        </is>
+      </c>
+      <c r="S49" s="32" t="inlineStr">
+        <is>
+          <t>sp_a5</t>
+        </is>
+      </c>
       <c r="T49" s="32" t="inlineStr"/>
       <c r="U49" s="33" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="V49" s="34" t="inlineStr">
         <is>
@@ -6635,15 +6629,13 @@
       <c r="W49" s="34" t="inlineStr"/>
       <c r="X49" s="34" t="inlineStr">
         <is>
-          <t>Blue-White</t>
-        </is>
-      </c>
-      <c r="Y49" s="34" t="n">
-        <v>530</v>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="Y49" s="34" t="inlineStr"/>
       <c r="Z49" s="35" t="inlineStr">
         <is>
-          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
+          <t>at ECU-A plug</t>
         </is>
       </c>
       <c r="AA49" s="36" t="inlineStr"/>
@@ -6652,7 +6644,7 @@
       <c r="AD49" s="38" t="inlineStr"/>
       <c r="AE49" s="38" t="inlineStr">
         <is>
-          <t>fuse-box plan fb_logic BUS2-12 (20 AWG); DRB102 42 = section A c35 'MRS EPS pump logic enable (fuse box LOGIC MRS, 7.5'</t>
+          <t>splice sp_a5: node of the wire list (SoT); channels.csv ecu_a A5 14V + (SW12)</t>
         </is>
       </c>
       <c r="AF49" s="38" t="inlineStr">
@@ -6660,21 +6652,17 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG49" s="38" t="inlineStr">
-        <is>
-          <t>fuse fed from EPS enable relay k_eps_en pin 87 (ignition-switched); owner proposed: longer half (drawn today as w_fb_mrs_en on A-cabin, 530 mm; w_fb_mrs_en_cp on CabinPower, 250 mm)</t>
-        </is>
-      </c>
+      <c r="AG49" s="38" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="39" t="inlineStr">
         <is>
-          <t>GND</t>
+          <t>SW12</t>
         </is>
       </c>
       <c r="B50" s="39" t="inlineStr">
         <is>
-          <t>w70</t>
+          <t>w_rail_sp_sw12_c</t>
         </is>
       </c>
       <c r="C50" s="39" t="inlineStr">
@@ -6685,65 +6673,63 @@
       <c r="D50" s="39" t="inlineStr"/>
       <c r="E50" s="40" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="F50" s="41" t="inlineStr">
         <is>
-          <t>ecu_a</t>
+          <t>sp_sw12</t>
         </is>
       </c>
       <c r="G50" s="42" t="inlineStr">
         <is>
-          <t>ECU-A</t>
-        </is>
-      </c>
-      <c r="H50" s="41" t="inlineStr">
-        <is>
-          <t>A25</t>
-        </is>
-      </c>
+          <t>splice sp_sw12 (SP-SW12: switched +12 V)</t>
+        </is>
+      </c>
+      <c r="H50" s="41" t="inlineStr"/>
       <c r="I50" s="42" t="inlineStr">
         <is>
-          <t>ECU power ground</t>
+          <t>+12 V boost + flex</t>
         </is>
       </c>
       <c r="J50" s="42" t="inlineStr"/>
       <c r="K50" s="43" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="L50" s="44" t="inlineStr">
         <is>
-          <t>sp_chassis</t>
+          <t>bh_a_fw</t>
         </is>
       </c>
       <c r="M50" s="45" t="inlineStr">
         <is>
-          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
-        </is>
-      </c>
-      <c r="N50" s="44" t="inlineStr"/>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="N50" s="44" t="n">
+        <v>20</v>
+      </c>
       <c r="O50" s="45" t="inlineStr">
         <is>
-          <t>ECU power ground</t>
+          <t>+12 V boost + flex</t>
         </is>
       </c>
       <c r="P50" s="45" t="inlineStr"/>
       <c r="Q50" s="46" t="inlineStr">
         <is>
-          <t>STUD.M6-ECU</t>
+          <t>LOGIC.BUS2-2</t>
         </is>
       </c>
       <c r="R50" s="47" t="inlineStr">
         <is>
-          <t>Chassis GND (cabin stud M6 at ECU)</t>
+          <t>+12V switched (LOGIC SW12 bus)</t>
         </is>
       </c>
       <c r="S50" s="48" t="inlineStr">
         <is>
-          <t>sp_chassis</t>
+          <t>sp_sw12</t>
         </is>
       </c>
       <c r="T50" s="48" t="inlineStr"/>
@@ -6752,19 +6738,19 @@
       </c>
       <c r="V50" s="50" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W50" s="50" t="inlineStr"/>
       <c r="X50" s="50" t="inlineStr">
         <is>
-          <t>Yellow-White-White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="Y50" s="50" t="inlineStr"/>
       <c r="Z50" s="51" t="inlineStr">
         <is>
-          <t>at ECU-A plug</t>
+          <t>trunk ECU-A to bulkhead (RH firewall)</t>
         </is>
       </c>
       <c r="AA50" s="52" t="inlineStr"/>
@@ -6773,7 +6759,7 @@
       <c r="AD50" s="54" t="inlineStr"/>
       <c r="AE50" s="54" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A25 Ground (GND_ECU); splice sp_chassis named in SoT</t>
+          <t>splice sp_sw12: node of the wire list (SoT); DRB102 20 = section A c5 'Switched 12V to engine sensors'</t>
         </is>
       </c>
       <c r="AF50" s="54" t="inlineStr">
@@ -6786,12 +6772,12 @@
     <row r="51">
       <c r="A51" s="23" t="inlineStr">
         <is>
-          <t>GND</t>
+          <t>SW12</t>
         </is>
       </c>
       <c r="B51" s="23" t="inlineStr">
         <is>
-          <t>w_a34</t>
+          <t>w_rail_sw12_b_c_ac</t>
         </is>
       </c>
       <c r="C51" s="23" t="inlineStr">
@@ -6799,89 +6785,95 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D51" s="23" t="inlineStr"/>
+      <c r="D51" s="23" t="inlineStr">
+        <is>
+          <t>B-cabin</t>
+        </is>
+      </c>
       <c r="E51" s="24" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>ecu_a</t>
+          <t>sp_sw12</t>
         </is>
       </c>
       <c r="G51" s="26" t="inlineStr">
         <is>
-          <t>ECU-A</t>
-        </is>
-      </c>
-      <c r="H51" s="25" t="inlineStr">
-        <is>
-          <t>A34</t>
-        </is>
-      </c>
+          <t>splice sp_sw12 (SP-SW12: switched +12 V)</t>
+        </is>
+      </c>
+      <c r="H51" s="25" t="inlineStr"/>
       <c r="I51" s="26" t="inlineStr">
         <is>
-          <t>ECU power ground</t>
+          <t>+12 V gearbox speed</t>
         </is>
       </c>
       <c r="J51" s="26" t="inlineStr"/>
       <c r="K51" s="27" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="L51" s="28" t="inlineStr">
         <is>
-          <t>sp_chassis</t>
+          <t>bh_b_fw</t>
         </is>
       </c>
       <c r="M51" s="29" t="inlineStr">
         <is>
-          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
-        </is>
-      </c>
-      <c r="N51" s="28" t="inlineStr"/>
+          <t>BH-B (firewall bulkhead DRB102, RH)</t>
+        </is>
+      </c>
+      <c r="N51" s="28" t="n">
+        <v>90</v>
+      </c>
       <c r="O51" s="29" t="inlineStr">
         <is>
-          <t>ECU power ground</t>
-        </is>
-      </c>
-      <c r="P51" s="29" t="inlineStr"/>
+          <t>+12 V gearbox speed</t>
+        </is>
+      </c>
+      <c r="P51" s="29" t="inlineStr">
+        <is>
+          <t>(firewall bulkhead, RH); sensor +12V</t>
+        </is>
+      </c>
       <c r="Q51" s="30" t="inlineStr">
         <is>
-          <t>STUD.M6-ECU</t>
+          <t>LOGIC.BUS2-2</t>
         </is>
       </c>
       <c r="R51" s="31" t="inlineStr">
         <is>
-          <t>Chassis GND (cabin stud M6 at ECU)</t>
+          <t>+12V switched (LOGIC SW12 bus)</t>
         </is>
       </c>
       <c r="S51" s="32" t="inlineStr">
         <is>
-          <t>sp_chassis</t>
+          <t>sp_sw12</t>
         </is>
       </c>
       <c r="T51" s="32" t="inlineStr"/>
       <c r="U51" s="33" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V51" s="34" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W51" s="34" t="inlineStr"/>
       <c r="X51" s="34" t="inlineStr">
         <is>
-          <t>Yellow-White-White</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="Y51" s="34" t="inlineStr"/>
       <c r="Z51" s="35" t="inlineStr">
         <is>
-          <t>at ECU-A plug</t>
+          <t>to ECU-B plug (beside ECU-A)</t>
         </is>
       </c>
       <c r="AA51" s="36" t="inlineStr"/>
@@ -6890,7 +6882,7 @@
       <c r="AD51" s="38" t="inlineStr"/>
       <c r="AE51" s="38" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A34 Ground (GND_ECU); splice sp_chassis named in SoT</t>
+          <t>splice sp_sw12: node of the wire list (SoT); DRB102 90 = section B c20 'Switched 12V to gearbox VSS (from sp_sw12)'</t>
         </is>
       </c>
       <c r="AF51" s="38" t="inlineStr">
@@ -6898,17 +6890,21 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG51" s="38" t="inlineStr"/>
+      <c r="AG51" s="38" t="inlineStr">
+        <is>
+          <t>owner TBD: a half has no length estimate (drawn today as w_rail_sw12_b_c_ac on A-cabin, ? mm; w_rail_sw12_b_c on B-cabin, 520 mm)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="39" t="inlineStr">
         <is>
-          <t>GND</t>
+          <t>EPSEN</t>
         </is>
       </c>
       <c r="B52" s="39" t="inlineStr">
         <is>
-          <t>w_b25_ac</t>
+          <t>w_fb_mrs_en</t>
         </is>
       </c>
       <c r="C52" s="39" t="inlineStr">
@@ -6918,31 +6914,39 @@
       </c>
       <c r="D52" s="39" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>CabinPower</t>
         </is>
       </c>
       <c r="E52" s="40" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="F52" s="41" t="inlineStr">
         <is>
-          <t>sp_chassis</t>
+          <t>fb_logic</t>
         </is>
       </c>
       <c r="G52" s="42" t="inlineStr">
         <is>
-          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
-        </is>
-      </c>
-      <c r="H52" s="41" t="inlineStr"/>
+          <t>FB-LOGIC</t>
+        </is>
+      </c>
+      <c r="H52" s="41" t="inlineStr">
+        <is>
+          <t>BUS2-12</t>
+        </is>
+      </c>
       <c r="I52" s="42" t="inlineStr">
         <is>
-          <t>ECU power ground</t>
-        </is>
-      </c>
-      <c r="J52" s="42" t="inlineStr"/>
+          <t>EHPS enable +12 V</t>
+        </is>
+      </c>
+      <c r="J52" s="42" t="inlineStr">
+        <is>
+          <t>LOGIC box (glove box) fuse MRS 7.5A Fuse fed from EPS enable relay k_eps_en pin 87 (ignition-switched).</t>
+        </is>
+      </c>
       <c r="K52" s="43" t="inlineStr">
         <is>
           <t>connector</t>
@@ -6950,63 +6954,55 @@
       </c>
       <c r="L52" s="44" t="inlineStr">
         <is>
-          <t>ecu_b</t>
+          <t>bh_a_fw</t>
         </is>
       </c>
       <c r="M52" s="45" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
-        </is>
-      </c>
-      <c r="N52" s="44" t="inlineStr">
-        <is>
-          <t>B25</t>
-        </is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="N52" s="44" t="n">
+        <v>42</v>
       </c>
       <c r="O52" s="45" t="inlineStr">
         <is>
-          <t>ECU power ground</t>
-        </is>
-      </c>
-      <c r="P52" s="45" t="inlineStr">
-        <is>
-          <t>ECU-B plug pin B25 (Link G4X, centre dash)</t>
-        </is>
-      </c>
+          <t>EHPS enable +12 V</t>
+        </is>
+      </c>
+      <c r="P52" s="45" t="inlineStr"/>
       <c r="Q52" s="46" t="inlineStr">
         <is>
-          <t>STUD.M6-ECU</t>
+          <t>LOGIC.BUS2-12</t>
         </is>
       </c>
       <c r="R52" s="47" t="inlineStr">
         <is>
-          <t>Chassis GND (cabin stud M6 at ECU)</t>
-        </is>
-      </c>
-      <c r="S52" s="48" t="inlineStr">
-        <is>
-          <t>sp_chassis</t>
-        </is>
-      </c>
+          <t>+12V EHPS enable (LOGIC MRS 7.5A)</t>
+        </is>
+      </c>
+      <c r="S52" s="48" t="inlineStr"/>
       <c r="T52" s="48" t="inlineStr"/>
       <c r="U52" s="49" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V52" s="50" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W52" s="50" t="inlineStr"/>
       <c r="X52" s="50" t="inlineStr">
         <is>
-          <t>Yellow-White-White</t>
-        </is>
-      </c>
-      <c r="Y52" s="50" t="inlineStr"/>
+          <t>Blue-White</t>
+        </is>
+      </c>
+      <c r="Y52" s="50" t="n">
+        <v>530</v>
+      </c>
       <c r="Z52" s="51" t="inlineStr">
         <is>
-          <t>to ECU-B plug (beside ECU-A)</t>
+          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
         </is>
       </c>
       <c r="AA52" s="52" t="inlineStr"/>
@@ -7015,7 +7011,7 @@
       <c r="AD52" s="54" t="inlineStr"/>
       <c r="AE52" s="54" t="inlineStr">
         <is>
-          <t>splice sp_chassis named in SoT; channels.csv ecu_b B25 Ground (GND_ECU)</t>
+          <t>fuse-box plan fb_logic BUS2-12 (20 AWG); DRB102 42 = section A c35 'MRS EPS pump logic enable (fuse box LOGIC MRS, 7.5'</t>
         </is>
       </c>
       <c r="AF52" s="54" t="inlineStr">
@@ -7025,7 +7021,7 @@
       </c>
       <c r="AG52" s="54" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as w_b25_ac on A-cabin, ? mm; w_b25 on B-cabin, 120 mm)</t>
+          <t>fuse fed from EPS enable relay k_eps_en pin 87 (ignition-switched); owner proposed: longer half (drawn today as w_fb_mrs_en on A-cabin, 530 mm; w_fb_mrs_en_cp on CabinPower, 250 mm)</t>
         </is>
       </c>
     </row>
@@ -7037,7 +7033,7 @@
       </c>
       <c r="B53" s="23" t="inlineStr">
         <is>
-          <t>w_b34_ac</t>
+          <t>w70</t>
         </is>
       </c>
       <c r="C53" s="23" t="inlineStr">
@@ -7045,27 +7041,27 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D53" s="23" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
+      <c r="D53" s="23" t="inlineStr"/>
       <c r="E53" s="24" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="F53" s="25" t="inlineStr">
         <is>
-          <t>sp_chassis</t>
+          <t>ecu_a</t>
         </is>
       </c>
       <c r="G53" s="26" t="inlineStr">
         <is>
-          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
-        </is>
-      </c>
-      <c r="H53" s="25" t="inlineStr"/>
+          <t>ECU-A</t>
+        </is>
+      </c>
+      <c r="H53" s="25" t="inlineStr">
+        <is>
+          <t>A25</t>
+        </is>
+      </c>
       <c r="I53" s="26" t="inlineStr">
         <is>
           <t>ECU power ground</t>
@@ -7074,34 +7070,26 @@
       <c r="J53" s="26" t="inlineStr"/>
       <c r="K53" s="27" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="L53" s="28" t="inlineStr">
         <is>
-          <t>ecu_b</t>
+          <t>sp_chassis</t>
         </is>
       </c>
       <c r="M53" s="29" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
-        </is>
-      </c>
-      <c r="N53" s="28" t="inlineStr">
-        <is>
-          <t>B34</t>
-        </is>
-      </c>
+          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
+        </is>
+      </c>
+      <c r="N53" s="28" t="inlineStr"/>
       <c r="O53" s="29" t="inlineStr">
         <is>
           <t>ECU power ground</t>
         </is>
       </c>
-      <c r="P53" s="29" t="inlineStr">
-        <is>
-          <t>ECU-B plug pin B34 (Link G4X, centre dash)</t>
-        </is>
-      </c>
+      <c r="P53" s="29" t="inlineStr"/>
       <c r="Q53" s="30" t="inlineStr">
         <is>
           <t>STUD.M6-ECU</t>
@@ -7135,7 +7123,7 @@
       <c r="Y53" s="34" t="inlineStr"/>
       <c r="Z53" s="35" t="inlineStr">
         <is>
-          <t>to ECU-B plug (beside ECU-A)</t>
+          <t>at ECU-A plug</t>
         </is>
       </c>
       <c r="AA53" s="36" t="inlineStr"/>
@@ -7144,7 +7132,7 @@
       <c r="AD53" s="38" t="inlineStr"/>
       <c r="AE53" s="38" t="inlineStr">
         <is>
-          <t>splice sp_chassis named in SoT; channels.csv ecu_b B34 Ground (GND_ECU)</t>
+          <t>channels.csv ecu_a A25 Ground (GND_ECU); splice sp_chassis: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF53" s="38" t="inlineStr">
@@ -7152,21 +7140,17 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG53" s="38" t="inlineStr">
-        <is>
-          <t>owner TBD: a half has no length estimate (drawn today as w_b34_ac on A-cabin, ? mm; w_b34 on B-cabin, 120 mm)</t>
-        </is>
-      </c>
+      <c r="AG53" s="38" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="39" t="inlineStr">
         <is>
-          <t>LAM</t>
+          <t>GND</t>
         </is>
       </c>
       <c r="B54" s="39" t="inlineStr">
         <is>
-          <t>w_lamg_ac</t>
+          <t>w_a34</t>
         </is>
       </c>
       <c r="C54" s="39" t="inlineStr">
@@ -7174,11 +7158,7 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D54" s="39" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
+      <c r="D54" s="39" t="inlineStr"/>
       <c r="E54" s="40" t="inlineStr">
         <is>
           <t>connector</t>
@@ -7186,27 +7166,25 @@
       </c>
       <c r="F54" s="41" t="inlineStr">
         <is>
-          <t>bh_b_fw</t>
+          <t>ecu_a</t>
         </is>
       </c>
       <c r="G54" s="42" t="inlineStr">
         <is>
-          <t>BH-B (firewall bulkhead DRB102, RH)</t>
-        </is>
-      </c>
-      <c r="H54" s="41" t="n">
-        <v>96</v>
+          <t>ECU-A</t>
+        </is>
+      </c>
+      <c r="H54" s="41" t="inlineStr">
+        <is>
+          <t>A34</t>
+        </is>
       </c>
       <c r="I54" s="42" t="inlineStr">
         <is>
-          <t>CAN-Lambda ground</t>
-        </is>
-      </c>
-      <c r="J54" s="42" t="inlineStr">
-        <is>
-          <t>(firewall bulkhead, RH)</t>
-        </is>
-      </c>
+          <t>ECU power ground</t>
+        </is>
+      </c>
+      <c r="J54" s="42" t="inlineStr"/>
       <c r="K54" s="43" t="inlineStr">
         <is>
           <t>splice</t>
@@ -7225,7 +7203,7 @@
       <c r="N54" s="44" t="inlineStr"/>
       <c r="O54" s="45" t="inlineStr">
         <is>
-          <t>CAN-Lambda ground</t>
+          <t>ECU power ground</t>
         </is>
       </c>
       <c r="P54" s="45" t="inlineStr"/>
@@ -7246,7 +7224,7 @@
       </c>
       <c r="T54" s="48" t="inlineStr"/>
       <c r="U54" s="49" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="V54" s="50" t="inlineStr">
         <is>
@@ -7256,13 +7234,13 @@
       <c r="W54" s="50" t="inlineStr"/>
       <c r="X54" s="50" t="inlineStr">
         <is>
-          <t>Blue-White-White</t>
+          <t>Yellow-White-White</t>
         </is>
       </c>
       <c r="Y54" s="50" t="inlineStr"/>
       <c r="Z54" s="51" t="inlineStr">
         <is>
-          <t>to ECU-B plug (beside ECU-A)</t>
+          <t>at ECU-A plug</t>
         </is>
       </c>
       <c r="AA54" s="52" t="inlineStr"/>
@@ -7271,7 +7249,7 @@
       <c r="AD54" s="54" t="inlineStr"/>
       <c r="AE54" s="54" t="inlineStr">
         <is>
-          <t>DRB102 96 = section B c4 'CAN-Lambda ground to cabin chassis ground (14 AWG)'; splice sp_chassis named in SoT</t>
+          <t>channels.csv ecu_a A34 Ground (GND_ECU); splice sp_chassis: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF54" s="54" t="inlineStr">
@@ -7279,21 +7257,17 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG54" s="54" t="inlineStr">
-        <is>
-          <t>owner TBD: a half has no length estimate (drawn today as w_lamg_ac on A-cabin, ? mm; w_lamg_bc on B-cabin, 120 mm)</t>
-        </is>
-      </c>
+      <c r="AG54" s="54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="23" t="inlineStr">
         <is>
-          <t>CSB</t>
+          <t>GND</t>
         </is>
       </c>
       <c r="B55" s="23" t="inlineStr">
         <is>
-          <t>w_csbg_ac</t>
+          <t>w_b25_ac</t>
         </is>
       </c>
       <c r="C55" s="23" t="inlineStr">
@@ -7303,7 +7277,7 @@
       </c>
       <c r="D55" s="23" t="inlineStr">
         <is>
-          <t>CSB3</t>
+          <t>B-cabin</t>
         </is>
       </c>
       <c r="E55" s="24" t="inlineStr">
@@ -7324,34 +7298,38 @@
       <c r="H55" s="25" t="inlineStr"/>
       <c r="I55" s="26" t="inlineStr">
         <is>
-          <t>CSB3 + opto ground</t>
+          <t>ECU power ground</t>
         </is>
       </c>
       <c r="J55" s="26" t="inlineStr"/>
       <c r="K55" s="27" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="L55" s="28" t="inlineStr">
         <is>
-          <t>sp_csb_gnd</t>
+          <t>ecu_b</t>
         </is>
       </c>
       <c r="M55" s="29" t="inlineStr">
         <is>
-          <t>splice sp_csb_gnd on CSB3</t>
-        </is>
-      </c>
-      <c r="N55" s="28" t="inlineStr"/>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
+        </is>
+      </c>
+      <c r="N55" s="28" t="inlineStr">
+        <is>
+          <t>B25</t>
+        </is>
+      </c>
       <c r="O55" s="29" t="inlineStr">
         <is>
-          <t>CSB3 + opto ground</t>
+          <t>ECU power ground</t>
         </is>
       </c>
       <c r="P55" s="29" t="inlineStr">
         <is>
-          <t>(CSB3 loom, under centre cluster)</t>
+          <t>ECU-B plug pin B25 (Link G4X, centre dash)</t>
         </is>
       </c>
       <c r="Q55" s="30" t="inlineStr">
@@ -7371,7 +7349,7 @@
       </c>
       <c r="T55" s="32" t="inlineStr"/>
       <c r="U55" s="33" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="V55" s="34" t="inlineStr">
         <is>
@@ -7381,13 +7359,13 @@
       <c r="W55" s="34" t="inlineStr"/>
       <c r="X55" s="34" t="inlineStr">
         <is>
-          <t>Yellow-Blue-Blue</t>
+          <t>Yellow-White-White</t>
         </is>
       </c>
       <c r="Y55" s="34" t="inlineStr"/>
       <c r="Z55" s="35" t="inlineStr">
         <is>
-          <t>CSB3 branch (centre console)</t>
+          <t>to ECU-B plug (beside ECU-A)</t>
         </is>
       </c>
       <c r="AA55" s="36" t="inlineStr"/>
@@ -7396,7 +7374,7 @@
       <c r="AD55" s="38" t="inlineStr"/>
       <c r="AE55" s="38" t="inlineStr">
         <is>
-          <t>splice sp_chassis named in SoT; splice sp_csb_gnd named in SoT</t>
+          <t>splice sp_chassis: node of the wire list (SoT); channels.csv ecu_b B25 Ground (GND_ECU)</t>
         </is>
       </c>
       <c r="AF55" s="38" t="inlineStr">
@@ -7406,7 +7384,7 @@
       </c>
       <c r="AG55" s="38" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as w_csbg_ac on A-cabin, ? mm; w_csbg_br on CSB3, ? mm)</t>
+          <t>owner TBD: a half has no length estimate (drawn today as w_b25_ac on A-cabin, ? mm; w_b25 on B-cabin, 120 mm)</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7396,7 @@
       </c>
       <c r="B56" s="39" t="inlineStr">
         <is>
-          <t>w66</t>
+          <t>w_b34_ac</t>
         </is>
       </c>
       <c r="C56" s="39" t="inlineStr">
@@ -7426,55 +7404,63 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D56" s="39" t="inlineStr"/>
+      <c r="D56" s="39" t="inlineStr">
+        <is>
+          <t>B-cabin</t>
+        </is>
+      </c>
       <c r="E56" s="40" t="inlineStr">
         <is>
-          <t>terminal</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="F56" s="41" t="inlineStr">
         <is>
-          <t>chassis_ring</t>
+          <t>sp_chassis</t>
         </is>
       </c>
       <c r="G56" s="42" t="inlineStr">
         <is>
-          <t>Ground ring M6, cabin chassis stud at ECU</t>
+          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
         </is>
       </c>
       <c r="H56" s="41" t="inlineStr"/>
       <c r="I56" s="42" t="inlineStr">
         <is>
-          <t>ECU ground chassis</t>
-        </is>
-      </c>
-      <c r="J56" s="42" t="inlineStr">
-        <is>
-          <t>Ground ring M6 on a cabin chassis stud at the ECU (TBD - EWD ground point ID)</t>
-        </is>
-      </c>
+          <t>ECU power ground</t>
+        </is>
+      </c>
+      <c r="J56" s="42" t="inlineStr"/>
       <c r="K56" s="43" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="L56" s="44" t="inlineStr">
         <is>
-          <t>sp_chassis</t>
+          <t>ecu_b</t>
         </is>
       </c>
       <c r="M56" s="45" t="inlineStr">
         <is>
-          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
-        </is>
-      </c>
-      <c r="N56" s="44" t="inlineStr"/>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
+        </is>
+      </c>
+      <c r="N56" s="44" t="inlineStr">
+        <is>
+          <t>B34</t>
+        </is>
+      </c>
       <c r="O56" s="45" t="inlineStr">
         <is>
-          <t>ECU ground chassis</t>
-        </is>
-      </c>
-      <c r="P56" s="45" t="inlineStr"/>
+          <t>ECU power ground</t>
+        </is>
+      </c>
+      <c r="P56" s="45" t="inlineStr">
+        <is>
+          <t>ECU-B plug pin B34 (Link G4X, centre dash)</t>
+        </is>
+      </c>
       <c r="Q56" s="46" t="inlineStr">
         <is>
           <t>STUD.M6-ECU</t>
@@ -7492,7 +7478,7 @@
       </c>
       <c r="T56" s="48" t="inlineStr"/>
       <c r="U56" s="49" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="V56" s="50" t="inlineStr">
         <is>
@@ -7508,7 +7494,7 @@
       <c r="Y56" s="50" t="inlineStr"/>
       <c r="Z56" s="51" t="inlineStr">
         <is>
-          <t>ground stud at ECU</t>
+          <t>to ECU-B plug (beside ECU-A)</t>
         </is>
       </c>
       <c r="AA56" s="52" t="inlineStr"/>
@@ -7517,25 +7503,29 @@
       <c r="AD56" s="54" t="inlineStr"/>
       <c r="AE56" s="54" t="inlineStr">
         <is>
-          <t>splice sp_chassis named in SoT</t>
+          <t>splice sp_chassis: node of the wire list (SoT); channels.csv ecu_b B34 Ground (GND_ECU)</t>
         </is>
       </c>
       <c r="AF56" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: end chassis_ring (Ground ring M6, cabin chassis stud at ECU) is drawing-only: not named in the SoT</t>
-        </is>
-      </c>
-      <c r="AG56" s="54" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG56" s="54" t="inlineStr">
+        <is>
+          <t>owner TBD: a half has no length estimate (drawn today as w_b34_ac on A-cabin, ? mm; w_b34 on B-cabin, 120 mm)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="23" t="inlineStr">
         <is>
-          <t>SHLD</t>
+          <t>LAM</t>
         </is>
       </c>
       <c r="B57" s="23" t="inlineStr">
         <is>
-          <t>w_drain_ecu_a</t>
+          <t>w_lamg_ac</t>
         </is>
       </c>
       <c r="C57" s="23" t="inlineStr">
@@ -7543,93 +7533,95 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D57" s="23" t="inlineStr"/>
+      <c r="D57" s="23" t="inlineStr">
+        <is>
+          <t>B-cabin</t>
+        </is>
+      </c>
       <c r="E57" s="24" t="inlineStr">
         <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F57" s="25" t="inlineStr">
+        <is>
+          <t>bh_b_fw</t>
+        </is>
+      </c>
+      <c r="G57" s="26" t="inlineStr">
+        <is>
+          <t>BH-B (firewall bulkhead DRB102, RH)</t>
+        </is>
+      </c>
+      <c r="H57" s="25" t="n">
+        <v>96</v>
+      </c>
+      <c r="I57" s="26" t="inlineStr">
+        <is>
+          <t>CAN-Lambda ground</t>
+        </is>
+      </c>
+      <c r="J57" s="26" t="inlineStr">
+        <is>
+          <t>(firewall bulkhead, RH)</t>
+        </is>
+      </c>
+      <c r="K57" s="27" t="inlineStr">
+        <is>
           <t>splice</t>
         </is>
       </c>
-      <c r="F57" s="25" t="inlineStr">
-        <is>
-          <t>sp_shield_a</t>
-        </is>
-      </c>
-      <c r="G57" s="26" t="inlineStr">
-        <is>
-          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
-        </is>
-      </c>
-      <c r="H57" s="25" t="inlineStr"/>
-      <c r="I57" s="26" t="inlineStr">
-        <is>
-          <t>Shield drain</t>
-        </is>
-      </c>
-      <c r="J57" s="26" t="inlineStr"/>
-      <c r="K57" s="27" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
       <c r="L57" s="28" t="inlineStr">
         <is>
-          <t>ecu_a</t>
+          <t>sp_chassis</t>
         </is>
       </c>
       <c r="M57" s="29" t="inlineStr">
         <is>
-          <t>ECU-A</t>
-        </is>
-      </c>
-      <c r="N57" s="28" t="inlineStr">
-        <is>
-          <t>A7</t>
-        </is>
-      </c>
+          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
+        </is>
+      </c>
+      <c r="N57" s="28" t="inlineStr"/>
       <c r="O57" s="29" t="inlineStr">
         <is>
-          <t>Shield drain</t>
+          <t>CAN-Lambda ground</t>
         </is>
       </c>
       <c r="P57" s="29" t="inlineStr"/>
       <c r="Q57" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A7</t>
+          <t>STUD.M6-ECU</t>
         </is>
       </c>
       <c r="R57" s="31" t="inlineStr">
         <is>
-          <t>Screen A (ECU A7, SHIELD_A)</t>
+          <t>Chassis GND (cabin stud M6 at ECU)</t>
         </is>
       </c>
       <c r="S57" s="32" t="inlineStr">
         <is>
-          <t>sp_shield_a</t>
+          <t>sp_chassis</t>
         </is>
       </c>
       <c r="T57" s="32" t="inlineStr"/>
       <c r="U57" s="33" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="V57" s="34" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="W57" s="34" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+      <c r="W57" s="34" t="inlineStr"/>
       <c r="X57" s="34" t="inlineStr">
         <is>
-          <t>White-Yellow-Blue</t>
+          <t>Blue-White-White</t>
         </is>
       </c>
       <c r="Y57" s="34" t="inlineStr"/>
       <c r="Z57" s="35" t="inlineStr">
         <is>
-          <t>at ECU-A plug</t>
+          <t>to ECU-B plug (beside ECU-A)</t>
         </is>
       </c>
       <c r="AA57" s="36" t="inlineStr"/>
@@ -7638,7 +7630,7 @@
       <c r="AD57" s="38" t="inlineStr"/>
       <c r="AE57" s="38" t="inlineStr">
         <is>
-          <t>splice sp_shield_a named in SoT; channels.csv ecu_a A7 Shield/Gnd (SHIELD_A)</t>
+          <t>DRB102 96 = section B c4 'CAN-Lambda ground to cabin chassis ground (14 AWG)'; splice sp_chassis: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF57" s="38" t="inlineStr">
@@ -7648,19 +7640,19 @@
       </c>
       <c r="AG57" s="38" t="inlineStr">
         <is>
-          <t>build (R30): the crank drain is the one crimped into A7; the other drains are soldered onto it 6 mm behind the plug</t>
+          <t>owner TBD: a half has no length estimate (drawn today as w_lamg_ac on A-cabin, ? mm; w_lamg_bc on B-cabin, 120 mm)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="39" t="inlineStr">
         <is>
-          <t>CRANKC</t>
+          <t>CSB</t>
         </is>
       </c>
       <c r="B58" s="39" t="inlineStr">
         <is>
-          <t>w_shc_crank</t>
+          <t>w_csbg_ac</t>
         </is>
       </c>
       <c r="C58" s="39" t="inlineStr">
@@ -7668,28 +7660,30 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D58" s="39" t="inlineStr"/>
+      <c r="D58" s="39" t="inlineStr">
+        <is>
+          <t>CSB3</t>
+        </is>
+      </c>
       <c r="E58" s="40" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="F58" s="41" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>sp_chassis</t>
         </is>
       </c>
       <c r="G58" s="42" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
-        </is>
-      </c>
-      <c r="H58" s="41" t="n">
-        <v>11</v>
-      </c>
+          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
+        </is>
+      </c>
+      <c r="H58" s="41" t="inlineStr"/>
       <c r="I58" s="42" t="inlineStr">
         <is>
-          <t>Crank sensor shield</t>
+          <t>CSB3 + opto ground</t>
         </is>
       </c>
       <c r="J58" s="42" t="inlineStr"/>
@@ -7700,34 +7694,38 @@
       </c>
       <c r="L58" s="44" t="inlineStr">
         <is>
-          <t>sp_shield_a</t>
+          <t>sp_csb_gnd</t>
         </is>
       </c>
       <c r="M58" s="45" t="inlineStr">
         <is>
-          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
+          <t>splice sp_csb_gnd on CSB3</t>
         </is>
       </c>
       <c r="N58" s="44" t="inlineStr"/>
       <c r="O58" s="45" t="inlineStr">
         <is>
-          <t>Crank sensor shield</t>
-        </is>
-      </c>
-      <c r="P58" s="45" t="inlineStr"/>
+          <t>CSB3 + opto ground</t>
+        </is>
+      </c>
+      <c r="P58" s="45" t="inlineStr">
+        <is>
+          <t>(CSB3 loom, under centre cluster)</t>
+        </is>
+      </c>
       <c r="Q58" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A7</t>
+          <t>STUD.M6-ECU</t>
         </is>
       </c>
       <c r="R58" s="47" t="inlineStr">
         <is>
-          <t>Screen A (ECU A7, SHIELD_A)</t>
+          <t>Chassis GND (cabin stud M6 at ECU)</t>
         </is>
       </c>
       <c r="S58" s="48" t="inlineStr">
         <is>
-          <t>sp_shield_a</t>
+          <t>sp_chassis</t>
         </is>
       </c>
       <c r="T58" s="48" t="inlineStr"/>
@@ -7739,20 +7737,16 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="W58" s="50" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+      <c r="W58" s="50" t="inlineStr"/>
       <c r="X58" s="50" t="inlineStr">
         <is>
-          <t>White-Blue-White</t>
+          <t>Yellow-Blue-Blue</t>
         </is>
       </c>
       <c r="Y58" s="50" t="inlineStr"/>
       <c r="Z58" s="51" t="inlineStr">
         <is>
-          <t>trunk ECU-A to bulkhead (RH firewall)</t>
+          <t>CSB3 branch (centre console)</t>
         </is>
       </c>
       <c r="AA58" s="52" t="inlineStr"/>
@@ -7761,7 +7755,7 @@
       <c r="AD58" s="54" t="inlineStr"/>
       <c r="AE58" s="54" t="inlineStr">
         <is>
-          <t>DRB102 11 = section A c33 'Crank VR screen'; splice sp_shield_a named in SoT</t>
+          <t>splice sp_chassis: node of the wire list (SoT); splice sp_csb_gnd: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF58" s="54" t="inlineStr">
@@ -7771,19 +7765,19 @@
       </c>
       <c r="AG58" s="54" t="inlineStr">
         <is>
-          <t>build (R30): this drain is the one crimped into A7</t>
+          <t>owner TBD: a half has no length estimate (drawn today as w_csbg_ac on A-cabin, ? mm; w_csbg_br on CSB3, ? mm)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="23" t="inlineStr">
         <is>
-          <t>CAM</t>
+          <t>GND</t>
         </is>
       </c>
       <c r="B59" s="23" t="inlineStr">
         <is>
-          <t>w_shc_cam</t>
+          <t>w66</t>
         </is>
       </c>
       <c r="C59" s="23" t="inlineStr">
@@ -7794,28 +7788,30 @@
       <c r="D59" s="23" t="inlineStr"/>
       <c r="E59" s="24" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>terminal</t>
         </is>
       </c>
       <c r="F59" s="25" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>chassis_ring</t>
         </is>
       </c>
       <c r="G59" s="26" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
-        </is>
-      </c>
-      <c r="H59" s="25" t="n">
-        <v>15</v>
-      </c>
+          <t>Ground ring M6, cabin chassis stud at ECU</t>
+        </is>
+      </c>
+      <c r="H59" s="25" t="inlineStr"/>
       <c r="I59" s="26" t="inlineStr">
         <is>
-          <t>Cam sensor shield</t>
-        </is>
-      </c>
-      <c r="J59" s="26" t="inlineStr"/>
+          <t>ECU ground chassis</t>
+        </is>
+      </c>
+      <c r="J59" s="26" t="inlineStr">
+        <is>
+          <t>Ground ring M6 on a cabin chassis stud at the ECU (TBD - EWD ground point ID)</t>
+        </is>
+      </c>
       <c r="K59" s="27" t="inlineStr">
         <is>
           <t>splice</t>
@@ -7823,59 +7819,55 @@
       </c>
       <c r="L59" s="28" t="inlineStr">
         <is>
-          <t>sp_shield_a</t>
+          <t>sp_chassis</t>
         </is>
       </c>
       <c r="M59" s="29" t="inlineStr">
         <is>
-          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
+          <t>splice sp_chassis (SP-GND-CHASSIS: ECU power ground)</t>
         </is>
       </c>
       <c r="N59" s="28" t="inlineStr"/>
       <c r="O59" s="29" t="inlineStr">
         <is>
-          <t>Cam sensor shield</t>
+          <t>ECU ground chassis</t>
         </is>
       </c>
       <c r="P59" s="29" t="inlineStr"/>
       <c r="Q59" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A7</t>
+          <t>STUD.M6-ECU</t>
         </is>
       </c>
       <c r="R59" s="31" t="inlineStr">
         <is>
-          <t>Screen A (ECU A7, SHIELD_A)</t>
+          <t>Chassis GND (cabin stud M6 at ECU)</t>
         </is>
       </c>
       <c r="S59" s="32" t="inlineStr">
         <is>
-          <t>sp_shield_a</t>
+          <t>sp_chassis</t>
         </is>
       </c>
       <c r="T59" s="32" t="inlineStr"/>
       <c r="U59" s="33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="V59" s="34" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="W59" s="34" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+      <c r="W59" s="34" t="inlineStr"/>
       <c r="X59" s="34" t="inlineStr">
         <is>
-          <t>Yellow-Yellow</t>
+          <t>Yellow-White-White</t>
         </is>
       </c>
       <c r="Y59" s="34" t="inlineStr"/>
       <c r="Z59" s="35" t="inlineStr">
         <is>
-          <t>trunk ECU-A to bulkhead (RH firewall)</t>
+          <t>ground stud at ECU</t>
         </is>
       </c>
       <c r="AA59" s="36" t="inlineStr"/>
@@ -7884,7 +7876,7 @@
       <c r="AD59" s="38" t="inlineStr"/>
       <c r="AE59" s="38" t="inlineStr">
         <is>
-          <t>DRB102 15 = section A c34 'Cam Hall screen'; splice sp_shield_a named in SoT</t>
+          <t>end chassis_ring: end row of the wire list (SoT); splice sp_chassis: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF59" s="38" t="inlineStr">
@@ -7897,12 +7889,12 @@
     <row r="60">
       <c r="A60" s="39" t="inlineStr">
         <is>
-          <t>TURBO</t>
+          <t>SHLD</t>
         </is>
       </c>
       <c r="B60" s="39" t="inlineStr">
         <is>
-          <t>w_shc_turbo</t>
+          <t>w_drain_ecu_a</t>
         </is>
       </c>
       <c r="C60" s="39" t="inlineStr">
@@ -7913,47 +7905,49 @@
       <c r="D60" s="39" t="inlineStr"/>
       <c r="E60" s="40" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="F60" s="41" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>sp_shield_a</t>
         </is>
       </c>
       <c r="G60" s="42" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
-        </is>
-      </c>
-      <c r="H60" s="41" t="n">
-        <v>19</v>
-      </c>
+          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
+        </is>
+      </c>
+      <c r="H60" s="41" t="inlineStr"/>
       <c r="I60" s="42" t="inlineStr">
         <is>
-          <t>Turbo speed shield</t>
+          <t>Shield drain</t>
         </is>
       </c>
       <c r="J60" s="42" t="inlineStr"/>
       <c r="K60" s="43" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="L60" s="44" t="inlineStr">
         <is>
-          <t>sp_shield_a</t>
+          <t>ecu_a</t>
         </is>
       </c>
       <c r="M60" s="45" t="inlineStr">
         <is>
-          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
-        </is>
-      </c>
-      <c r="N60" s="44" t="inlineStr"/>
+          <t>ECU-A</t>
+        </is>
+      </c>
+      <c r="N60" s="44" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
       <c r="O60" s="45" t="inlineStr">
         <is>
-          <t>Turbo speed shield</t>
+          <t>Shield drain</t>
         </is>
       </c>
       <c r="P60" s="45" t="inlineStr"/>
@@ -7988,13 +7982,13 @@
       </c>
       <c r="X60" s="50" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>White-Yellow-Blue</t>
         </is>
       </c>
       <c r="Y60" s="50" t="inlineStr"/>
       <c r="Z60" s="51" t="inlineStr">
         <is>
-          <t>trunk ECU-A to bulkhead (RH firewall)</t>
+          <t>at ECU-A plug</t>
         </is>
       </c>
       <c r="AA60" s="52" t="inlineStr"/>
@@ -8003,7 +7997,7 @@
       <c r="AD60" s="54" t="inlineStr"/>
       <c r="AE60" s="54" t="inlineStr">
         <is>
-          <t>DRB102 19 = section A c6 'Turbo speed screen (to A7)'; splice sp_shield_a named in SoT</t>
+          <t>splice sp_shield_a: node of the wire list (SoT); channels.csv ecu_a A7 Shield/Gnd (SHIELD_A)</t>
         </is>
       </c>
       <c r="AF60" s="54" t="inlineStr">
@@ -8011,17 +8005,21 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG60" s="54" t="inlineStr"/>
+      <c r="AG60" s="54" t="inlineStr">
+        <is>
+          <t>build (R30): the crank drain is the one crimped into A7; the other drains are soldered onto it 6 mm behind the plug</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="23" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>CRANKC</t>
         </is>
       </c>
       <c r="B61" s="23" t="inlineStr">
         <is>
-          <t>w_shc_flex</t>
+          <t>w_shc_crank</t>
         </is>
       </c>
       <c r="C61" s="23" t="inlineStr">
@@ -8046,11 +8044,11 @@
         </is>
       </c>
       <c r="H61" s="25" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I61" s="26" t="inlineStr">
         <is>
-          <t>Flex fuel shield</t>
+          <t>Crank sensor shield</t>
         </is>
       </c>
       <c r="J61" s="26" t="inlineStr"/>
@@ -8072,7 +8070,7 @@
       <c r="N61" s="28" t="inlineStr"/>
       <c r="O61" s="29" t="inlineStr">
         <is>
-          <t>Flex fuel shield</t>
+          <t>Crank sensor shield</t>
         </is>
       </c>
       <c r="P61" s="29" t="inlineStr"/>
@@ -8107,7 +8105,7 @@
       </c>
       <c r="X61" s="34" t="inlineStr">
         <is>
-          <t>White-Blue</t>
+          <t>White-Blue-White</t>
         </is>
       </c>
       <c r="Y61" s="34" t="inlineStr"/>
@@ -8122,7 +8120,7 @@
       <c r="AD61" s="38" t="inlineStr"/>
       <c r="AE61" s="38" t="inlineStr">
         <is>
-          <t>DRB102 22 = section A c10 'Flex fuel screen (to A7)'; splice sp_shield_a named in SoT</t>
+          <t>DRB102 11 = section A c33 'Crank VR screen'; splice sp_shield_a: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF61" s="38" t="inlineStr">
@@ -8130,17 +8128,21 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG61" s="38" t="inlineStr"/>
+      <c r="AG61" s="38" t="inlineStr">
+        <is>
+          <t>build (R30): this drain is the one crimped into A7</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="39" t="inlineStr">
         <is>
-          <t>ETBS</t>
+          <t>CAM</t>
         </is>
       </c>
       <c r="B62" s="39" t="inlineStr">
         <is>
-          <t>w_shc_etbs</t>
+          <t>w_shc_cam</t>
         </is>
       </c>
       <c r="C62" s="39" t="inlineStr">
@@ -8165,11 +8167,11 @@
         </is>
       </c>
       <c r="H62" s="41" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I62" s="42" t="inlineStr">
         <is>
-          <t>Throttle shield</t>
+          <t>Cam sensor shield</t>
         </is>
       </c>
       <c r="J62" s="42" t="inlineStr"/>
@@ -8191,7 +8193,7 @@
       <c r="N62" s="44" t="inlineStr"/>
       <c r="O62" s="45" t="inlineStr">
         <is>
-          <t>Throttle shield</t>
+          <t>Cam sensor shield</t>
         </is>
       </c>
       <c r="P62" s="45" t="inlineStr"/>
@@ -8226,7 +8228,7 @@
       </c>
       <c r="X62" s="50" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Yellow-Yellow</t>
         </is>
       </c>
       <c r="Y62" s="50" t="inlineStr"/>
@@ -8241,7 +8243,7 @@
       <c r="AD62" s="54" t="inlineStr"/>
       <c r="AE62" s="54" t="inlineStr">
         <is>
-          <t>DRB102 27 = section A c11 'ETB sensor group screen (to A7)'; splice sp_shield_a named in SoT</t>
+          <t>DRB102 15 = section A c34 'Cam Hall screen'; splice sp_shield_a: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF62" s="54" t="inlineStr">
@@ -8254,12 +8256,12 @@
     <row r="63">
       <c r="A63" s="23" t="inlineStr">
         <is>
-          <t>FP</t>
+          <t>TURBO</t>
         </is>
       </c>
       <c r="B63" s="23" t="inlineStr">
         <is>
-          <t>w_fp85</t>
+          <t>w_shc_turbo</t>
         </is>
       </c>
       <c r="C63" s="23" t="inlineStr">
@@ -8267,11 +8269,7 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D63" s="23" t="inlineStr">
-        <is>
-          <t>HeavyDC</t>
-        </is>
-      </c>
+      <c r="D63" s="23" t="inlineStr"/>
       <c r="E63" s="24" t="inlineStr">
         <is>
           <t>connector</t>
@@ -8279,85 +8277,83 @@
       </c>
       <c r="F63" s="25" t="inlineStr">
         <is>
-          <t>k_fp</t>
+          <t>bh_a_fw</t>
         </is>
       </c>
       <c r="G63" s="26" t="inlineStr">
         <is>
-          <t>FP RELAY K1</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="H63" s="25" t="n">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="I63" s="26" t="inlineStr">
         <is>
-          <t>Fuel pump relay (-)</t>
-        </is>
-      </c>
-      <c r="J63" s="26" t="inlineStr">
-        <is>
-          <t>Battery relay block (trunk) relay K1 fuel pump, pin 85</t>
-        </is>
-      </c>
+          <t>Turbo speed shield</t>
+        </is>
+      </c>
+      <c r="J63" s="26" t="inlineStr"/>
       <c r="K63" s="27" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="L63" s="28" t="inlineStr">
         <is>
-          <t>ecu_a</t>
+          <t>sp_shield_a</t>
         </is>
       </c>
       <c r="M63" s="29" t="inlineStr">
         <is>
-          <t>ECU-A</t>
-        </is>
-      </c>
-      <c r="N63" s="28" t="inlineStr">
-        <is>
-          <t>A19</t>
-        </is>
-      </c>
+          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
+        </is>
+      </c>
+      <c r="N63" s="28" t="inlineStr"/>
       <c r="O63" s="29" t="inlineStr">
         <is>
-          <t>Fuel pump relay (-)</t>
+          <t>Turbo speed shield</t>
         </is>
       </c>
       <c r="P63" s="29" t="inlineStr"/>
       <c r="Q63" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A19</t>
+          <t>ECU-A.A7</t>
         </is>
       </c>
       <c r="R63" s="31" t="inlineStr">
         <is>
-          <t>Fuel pump relay (-) (ECU-A A19)</t>
-        </is>
-      </c>
-      <c r="S63" s="32" t="inlineStr"/>
+          <t>Screen A (ECU A7, SHIELD_A)</t>
+        </is>
+      </c>
+      <c r="S63" s="32" t="inlineStr">
+        <is>
+          <t>sp_shield_a</t>
+        </is>
+      </c>
       <c r="T63" s="32" t="inlineStr"/>
       <c r="U63" s="33" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V63" s="34" t="inlineStr">
         <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="W63" s="34" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="X63" s="34" t="inlineStr">
+        <is>
           <t>White</t>
         </is>
       </c>
-      <c r="W63" s="34" t="inlineStr"/>
-      <c r="X63" s="34" t="inlineStr">
-        <is>
-          <t>White-White-Blue</t>
-        </is>
-      </c>
-      <c r="Y63" s="34" t="n">
-        <v>390</v>
-      </c>
+      <c r="Y63" s="34" t="inlineStr"/>
       <c r="Z63" s="35" t="inlineStr">
         <is>
-          <t>glove-box branch (POWER / LOGIC boxes)</t>
+          <t>trunk ECU-A to bulkhead (RH firewall)</t>
         </is>
       </c>
       <c r="AA63" s="36" t="inlineStr"/>
@@ -8366,7 +8362,7 @@
       <c r="AD63" s="38" t="inlineStr"/>
       <c r="AE63" s="38" t="inlineStr">
         <is>
-          <t>fuse-box plan k_fp 85 (18 AWG); channels.csv ecu_a A19 Aux 3 (AUX3_FP_RLY)</t>
+          <t>DRB102 19 = section A c6 'Turbo speed screen (to A7)'; splice sp_shield_a: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF63" s="38" t="inlineStr">
@@ -8374,21 +8370,17 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG63" s="38" t="inlineStr">
-        <is>
-          <t>owner proposed: longer half (drawn today as w_fp85 on A-cabin, 390 mm; w_fp85_h on HeavyDC, 150 mm)</t>
-        </is>
-      </c>
+      <c r="AG63" s="38" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="39" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="B64" s="39" t="inlineStr">
         <is>
-          <t>w_str85</t>
+          <t>w_shc_flex</t>
         </is>
       </c>
       <c r="C64" s="39" t="inlineStr">
@@ -8396,11 +8388,7 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D64" s="39" t="inlineStr">
-        <is>
-          <t>CabinPower</t>
-        </is>
-      </c>
+      <c r="D64" s="39" t="inlineStr"/>
       <c r="E64" s="40" t="inlineStr">
         <is>
           <t>connector</t>
@@ -8408,85 +8396,83 @@
       </c>
       <c r="F64" s="41" t="inlineStr">
         <is>
-          <t>k_str</t>
+          <t>bh_a_fw</t>
         </is>
       </c>
       <c r="G64" s="42" t="inlineStr">
         <is>
-          <t>POWER R3</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="H64" s="41" t="n">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="I64" s="42" t="inlineStr">
         <is>
-          <t>Start relay coil (-)</t>
-        </is>
-      </c>
-      <c r="J64" s="42" t="inlineStr">
-        <is>
-          <t>POWER box (glove box) relay R3 start, pin 85</t>
-        </is>
-      </c>
+          <t>Flex fuel shield</t>
+        </is>
+      </c>
+      <c r="J64" s="42" t="inlineStr"/>
       <c r="K64" s="43" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="L64" s="44" t="inlineStr">
         <is>
-          <t>ecu_a</t>
+          <t>sp_shield_a</t>
         </is>
       </c>
       <c r="M64" s="45" t="inlineStr">
         <is>
-          <t>ECU-A</t>
-        </is>
-      </c>
-      <c r="N64" s="44" t="inlineStr">
-        <is>
-          <t>A26</t>
-        </is>
-      </c>
+          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
+        </is>
+      </c>
+      <c r="N64" s="44" t="inlineStr"/>
       <c r="O64" s="45" t="inlineStr">
         <is>
-          <t>Start relay coil (-)</t>
+          <t>Flex fuel shield</t>
         </is>
       </c>
       <c r="P64" s="45" t="inlineStr"/>
       <c r="Q64" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A26</t>
+          <t>ECU-A.A7</t>
         </is>
       </c>
       <c r="R64" s="47" t="inlineStr">
         <is>
-          <t>Start relay coil (-) (ECU-A A26)</t>
-        </is>
-      </c>
-      <c r="S64" s="48" t="inlineStr"/>
+          <t>Screen A (ECU A7, SHIELD_A)</t>
+        </is>
+      </c>
+      <c r="S64" s="48" t="inlineStr">
+        <is>
+          <t>sp_shield_a</t>
+        </is>
+      </c>
       <c r="T64" s="48" t="inlineStr"/>
       <c r="U64" s="49" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V64" s="50" t="inlineStr">
         <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="W64" s="50" t="inlineStr"/>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="W64" s="50" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
       <c r="X64" s="50" t="inlineStr">
         <is>
-          <t>White-Yellow</t>
-        </is>
-      </c>
-      <c r="Y64" s="50" t="n">
-        <v>400</v>
-      </c>
+          <t>White-Blue</t>
+        </is>
+      </c>
+      <c r="Y64" s="50" t="inlineStr"/>
       <c r="Z64" s="51" t="inlineStr">
         <is>
-          <t>glove-box branch (POWER / LOGIC boxes)</t>
+          <t>trunk ECU-A to bulkhead (RH firewall)</t>
         </is>
       </c>
       <c r="AA64" s="52" t="inlineStr"/>
@@ -8495,7 +8481,7 @@
       <c r="AD64" s="54" t="inlineStr"/>
       <c r="AE64" s="54" t="inlineStr">
         <is>
-          <t>fuse-box plan k_str 85 (18 AWG); channels.csv ecu_a A26 Aux 8 (AUX8_START_RLY)</t>
+          <t>DRB102 22 = section A c10 'Flex fuel screen (to A7)'; splice sp_shield_a: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF64" s="54" t="inlineStr">
@@ -8503,21 +8489,17 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG64" s="54" t="inlineStr">
-        <is>
-          <t>owner proposed: longer half (drawn today as w_str85 on A-cabin, 400 mm; w_str85_cp on CabinPower, 400 mm)</t>
-        </is>
-      </c>
+      <c r="AG64" s="54" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="23" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>ETBS</t>
         </is>
       </c>
       <c r="B65" s="23" t="inlineStr">
         <is>
-          <t>w_fan85</t>
+          <t>w_shc_etbs</t>
         </is>
       </c>
       <c r="C65" s="23" t="inlineStr">
@@ -8525,11 +8507,7 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D65" s="23" t="inlineStr">
-        <is>
-          <t>CabinPower</t>
-        </is>
-      </c>
+      <c r="D65" s="23" t="inlineStr"/>
       <c r="E65" s="24" t="inlineStr">
         <is>
           <t>connector</t>
@@ -8537,85 +8515,83 @@
       </c>
       <c r="F65" s="25" t="inlineStr">
         <is>
-          <t>k_fan</t>
+          <t>bh_a_fw</t>
         </is>
       </c>
       <c r="G65" s="26" t="inlineStr">
         <is>
-          <t>POWER R4</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="H65" s="25" t="n">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="I65" s="26" t="inlineStr">
         <is>
-          <t>Rad fan relay (-)</t>
-        </is>
-      </c>
-      <c r="J65" s="26" t="inlineStr">
-        <is>
-          <t>POWER box (glove box) relay R4 radiator fan, pin 85</t>
-        </is>
-      </c>
+          <t>Throttle shield</t>
+        </is>
+      </c>
+      <c r="J65" s="26" t="inlineStr"/>
       <c r="K65" s="27" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="L65" s="28" t="inlineStr">
         <is>
-          <t>ecu_a</t>
+          <t>sp_shield_a</t>
         </is>
       </c>
       <c r="M65" s="29" t="inlineStr">
         <is>
-          <t>ECU-A</t>
-        </is>
-      </c>
-      <c r="N65" s="28" t="inlineStr">
-        <is>
-          <t>A29</t>
-        </is>
-      </c>
+          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
+        </is>
+      </c>
+      <c r="N65" s="28" t="inlineStr"/>
       <c r="O65" s="29" t="inlineStr">
         <is>
-          <t>Rad fan relay (-)</t>
+          <t>Throttle shield</t>
         </is>
       </c>
       <c r="P65" s="29" t="inlineStr"/>
       <c r="Q65" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A29</t>
+          <t>ECU-A.A7</t>
         </is>
       </c>
       <c r="R65" s="31" t="inlineStr">
         <is>
-          <t>Rad fan relay (-) (ECU-A A29)</t>
-        </is>
-      </c>
-      <c r="S65" s="32" t="inlineStr"/>
+          <t>Screen A (ECU A7, SHIELD_A)</t>
+        </is>
+      </c>
+      <c r="S65" s="32" t="inlineStr">
+        <is>
+          <t>sp_shield_a</t>
+        </is>
+      </c>
       <c r="T65" s="32" t="inlineStr"/>
       <c r="U65" s="33" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V65" s="34" t="inlineStr">
         <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="W65" s="34" t="inlineStr"/>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="W65" s="34" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
       <c r="X65" s="34" t="inlineStr">
         <is>
-          <t>Yellow-White</t>
-        </is>
-      </c>
-      <c r="Y65" s="34" t="n">
-        <v>410</v>
-      </c>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="Y65" s="34" t="inlineStr"/>
       <c r="Z65" s="35" t="inlineStr">
         <is>
-          <t>glove-box branch (POWER / LOGIC boxes)</t>
+          <t>trunk ECU-A to bulkhead (RH firewall)</t>
         </is>
       </c>
       <c r="AA65" s="36" t="inlineStr"/>
@@ -8624,7 +8600,7 @@
       <c r="AD65" s="38" t="inlineStr"/>
       <c r="AE65" s="38" t="inlineStr">
         <is>
-          <t>fuse-box plan k_fan 85 (18 AWG); channels.csv ecu_a A29 Aux 5 (AUX5_RAD_FAN)</t>
+          <t>DRB102 27 = section A c11 'ETB sensor group screen (to A7)'; splice sp_shield_a: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF65" s="38" t="inlineStr">
@@ -8632,21 +8608,17 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG65" s="38" t="inlineStr">
-        <is>
-          <t>owner proposed: longer half (drawn today as w_fan85 on A-cabin, 410 mm; w_fan85_cp on CabinPower, 400 mm)</t>
-        </is>
-      </c>
+      <c r="AG65" s="38" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="39" t="inlineStr">
         <is>
-          <t>EPS</t>
+          <t>FP</t>
         </is>
       </c>
       <c r="B66" s="39" t="inlineStr">
         <is>
-          <t>w_eps_rly</t>
+          <t>w_fp85</t>
         </is>
       </c>
       <c r="C66" s="39" t="inlineStr">
@@ -8656,7 +8628,7 @@
       </c>
       <c r="D66" s="39" t="inlineStr">
         <is>
-          <t>CabinPower</t>
+          <t>HeavyDC</t>
         </is>
       </c>
       <c r="E66" s="40" t="inlineStr">
@@ -8666,12 +8638,12 @@
       </c>
       <c r="F66" s="41" t="inlineStr">
         <is>
-          <t>k_eps</t>
+          <t>k_fp</t>
         </is>
       </c>
       <c r="G66" s="42" t="inlineStr">
         <is>
-          <t>EHPS RELAY</t>
+          <t>FP RELAY K1</t>
         </is>
       </c>
       <c r="H66" s="41" t="n">
@@ -8679,12 +8651,12 @@
       </c>
       <c r="I66" s="42" t="inlineStr">
         <is>
-          <t>EHPS relay coil (-)</t>
+          <t>Fuel pump relay (-)</t>
         </is>
       </c>
       <c r="J66" s="42" t="inlineStr">
         <is>
-          <t>EHPS pump relay (glove box), pin 85</t>
+          <t>Battery relay block (trunk) relay K1 fuel pump, pin 85</t>
         </is>
       </c>
       <c r="K66" s="43" t="inlineStr">
@@ -8694,31 +8666,33 @@
       </c>
       <c r="L66" s="44" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>ecu_a</t>
         </is>
       </c>
       <c r="M66" s="45" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
-        </is>
-      </c>
-      <c r="N66" s="44" t="n">
-        <v>56</v>
+          <t>ECU-A</t>
+        </is>
+      </c>
+      <c r="N66" s="44" t="inlineStr">
+        <is>
+          <t>A19</t>
+        </is>
       </c>
       <c r="O66" s="45" t="inlineStr">
         <is>
-          <t>EHPS relay coil (-)</t>
+          <t>Fuel pump relay (-)</t>
         </is>
       </c>
       <c r="P66" s="45" t="inlineStr"/>
       <c r="Q66" s="46" t="inlineStr">
         <is>
-          <t>DRB102.56</t>
+          <t>ECU-A.A19</t>
         </is>
       </c>
       <c r="R66" s="47" t="inlineStr">
         <is>
-          <t>EHPS relay coil (-) (DRB102 56)</t>
+          <t>Fuel pump relay (-) (ECU-A A19)</t>
         </is>
       </c>
       <c r="S66" s="48" t="inlineStr"/>
@@ -8728,21 +8702,21 @@
       </c>
       <c r="V66" s="50" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W66" s="50" t="inlineStr"/>
       <c r="X66" s="50" t="inlineStr">
         <is>
-          <t>Blue-Blue-Blue</t>
+          <t>White-White-Blue</t>
         </is>
       </c>
       <c r="Y66" s="50" t="n">
-        <v>530</v>
+        <v>390</v>
       </c>
       <c r="Z66" s="51" t="inlineStr">
         <is>
-          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
+          <t>glove-box branch (POWER / LOGIC boxes)</t>
         </is>
       </c>
       <c r="AA66" s="52" t="inlineStr"/>
@@ -8751,7 +8725,7 @@
       <c r="AD66" s="54" t="inlineStr"/>
       <c r="AE66" s="54" t="inlineStr">
         <is>
-          <t>channels.csv k_eps c2 Coil 85 (MRS_RLY); DRB102 56 = section A c27 'EPS relay coil 85 (R22) - from the MR-S pump B5'</t>
+          <t>fuse-box plan k_fp 85 (18 AWG); channels.csv ecu_a A19 Aux 3 (AUX3_FP_RLY)</t>
         </is>
       </c>
       <c r="AF66" s="54" t="inlineStr">
@@ -8761,19 +8735,19 @@
       </c>
       <c r="AG66" s="54" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_eps_rly on A-cabin, 530 mm; w_eps_rly_cp on CabinPower, 400 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_fp85 on A-cabin, 390 mm; w_fp85_h on HeavyDC, 150 mm)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="23" t="inlineStr">
         <is>
-          <t>ACKILL</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="B67" s="23" t="inlineStr">
         <is>
-          <t>w_ac_kill</t>
+          <t>w_str85</t>
         </is>
       </c>
       <c r="C67" s="23" t="inlineStr">
@@ -8781,7 +8755,11 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D67" s="23" t="inlineStr"/>
+      <c r="D67" s="23" t="inlineStr">
+        <is>
+          <t>CabinPower</t>
+        </is>
+      </c>
       <c r="E67" s="24" t="inlineStr">
         <is>
           <t>connector</t>
@@ -8789,110 +8767,94 @@
       </c>
       <c r="F67" s="25" t="inlineStr">
         <is>
+          <t>k_str</t>
+        </is>
+      </c>
+      <c r="G67" s="26" t="inlineStr">
+        <is>
+          <t>POWER R3</t>
+        </is>
+      </c>
+      <c r="H67" s="25" t="n">
+        <v>85</v>
+      </c>
+      <c r="I67" s="26" t="inlineStr">
+        <is>
+          <t>Start relay coil (-)</t>
+        </is>
+      </c>
+      <c r="J67" s="26" t="inlineStr">
+        <is>
+          <t>POWER box (glove box) relay R3 start, pin 85</t>
+        </is>
+      </c>
+      <c r="K67" s="27" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="L67" s="28" t="inlineStr">
+        <is>
           <t>ecu_a</t>
         </is>
       </c>
-      <c r="G67" s="26" t="inlineStr">
+      <c r="M67" s="29" t="inlineStr">
         <is>
           <t>ECU-A</t>
         </is>
       </c>
-      <c r="H67" s="25" t="inlineStr">
-        <is>
-          <t>A18</t>
-        </is>
-      </c>
-      <c r="I67" s="26" t="inlineStr">
-        <is>
-          <t>A/C cancel (ACT)</t>
-        </is>
-      </c>
-      <c r="J67" s="26" t="inlineStr"/>
-      <c r="K67" s="27" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="L67" s="28" t="inlineStr">
-        <is>
-          <t>A18 (factory)</t>
-        </is>
-      </c>
-      <c r="M67" s="29" t="inlineStr">
-        <is>
-          <t>OEM A/C amplifier</t>
-        </is>
-      </c>
-      <c r="N67" s="28" t="n">
-        <v>11</v>
+      <c r="N67" s="28" t="inlineStr">
+        <is>
+          <t>A26</t>
+        </is>
       </c>
       <c r="O67" s="29" t="inlineStr">
         <is>
-          <t>A/C cancel (ACT)</t>
-        </is>
-      </c>
-      <c r="P67" s="29" t="inlineStr">
-        <is>
-          <t>A/C amp A18 pin 11 (1993: A15), behind the glove box. Solder splice onto the factory G-Y lead. EWD 1992 p.93 / p.218; locator 1990 p.17.</t>
-        </is>
-      </c>
+          <t>Start relay coil (-)</t>
+        </is>
+      </c>
+      <c r="P67" s="29" t="inlineStr"/>
       <c r="Q67" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A18</t>
+          <t>ECU-A.A26</t>
         </is>
       </c>
       <c r="R67" s="31" t="inlineStr">
         <is>
-          <t>A/C cancel (ACT) (ECU-A A18)</t>
+          <t>Start relay coil (-) (ECU-A A26)</t>
         </is>
       </c>
       <c r="S67" s="32" t="inlineStr"/>
       <c r="T67" s="32" t="inlineStr"/>
       <c r="U67" s="33" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="V67" s="34" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W67" s="34" t="inlineStr"/>
       <c r="X67" s="34" t="inlineStr">
         <is>
-          <t>White-Yellow-Yellow</t>
+          <t>White-Yellow</t>
         </is>
       </c>
       <c r="Y67" s="34" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="Z67" s="35" t="inlineStr">
         <is>
-          <t>A/C amp branch (behind dash)</t>
-        </is>
-      </c>
-      <c r="AA67" s="36" t="inlineStr">
-        <is>
-          <t>A/C amplifier A18 (1993 book: A15), passenger side behind the glove box, on the bottom of the evaporator housing; tap point on the lead at the amplifier, distance TBD</t>
-        </is>
-      </c>
-      <c r="AB67" s="37" t="inlineStr">
-        <is>
-          <t>G-Y</t>
-        </is>
-      </c>
-      <c r="AC67" s="38" t="inlineStr">
-        <is>
-          <t>1992 Celica EWD132U p.93 and p.218 (docs/electrical/ewd-snips/1992-celica-ewd132u-a17-act-p093.png, 1992-celica-ewd132u-a17-clutch-p218.png); 1990 ST185 book locator A18; 1992 EWD132U p.93 and p.218 (A17-11 = A18-11); locator 1990 ST185 EWD p.17 Instrument Panel (ewd-snips/1990-st185-locations-dash.png); Mitchell locations (docs/research/AUTO-AC-AMP-OPTIONS.html)</t>
-        </is>
-      </c>
-      <c r="AD67" s="38" t="inlineStr">
-        <is>
-          <t>solder splice onto the factory G-Y ACT lead at the A/C amplifier</t>
-        </is>
-      </c>
+          <t>glove-box branch (POWER / LOGIC boxes)</t>
+        </is>
+      </c>
+      <c r="AA67" s="36" t="inlineStr"/>
+      <c r="AB67" s="37" t="inlineStr"/>
+      <c r="AC67" s="38" t="inlineStr"/>
+      <c r="AD67" s="38" t="inlineStr"/>
       <c r="AE67" s="38" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A18 Aux 4 (AUX4_AC_KILL); flying lead FL_ACAMP_ACT: EWD A18 pin 11 G-Y</t>
+          <t>fuse-box plan k_str 85 (18 AWG); channels.csv ecu_a A26 Aux 8 (AUX8_START_RLY)</t>
         </is>
       </c>
       <c r="AF67" s="38" t="inlineStr">
@@ -8900,17 +8862,21 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG67" s="38" t="inlineStr"/>
+      <c r="AG67" s="38" t="inlineStr">
+        <is>
+          <t>owner proposed: longer half (drawn today as w_str85 on A-cabin, 400 mm; w_str85_cp on CabinPower, 400 mm)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="39" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="B68" s="39" t="inlineStr">
         <is>
-          <t>w_ac_psw_in</t>
+          <t>w_fan85</t>
         </is>
       </c>
       <c r="C68" s="39" t="inlineStr">
@@ -8920,122 +8886,104 @@
       </c>
       <c r="D68" s="39" t="inlineStr">
         <is>
-          <t>EngineRoom-C</t>
+          <t>CabinPower</t>
         </is>
       </c>
       <c r="E68" s="40" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="F68" s="41" t="inlineStr">
         <is>
-          <t>A5 (factory)</t>
+          <t>k_fan</t>
         </is>
       </c>
       <c r="G68" s="42" t="inlineStr">
         <is>
-          <t>OEM A5, factory Y-R lead</t>
+          <t>POWER R4</t>
         </is>
       </c>
       <c r="H68" s="41" t="n">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="I68" s="42" t="inlineStr">
         <is>
-          <t>A/C pressure sw out</t>
+          <t>Rad fan relay (-)</t>
         </is>
       </c>
       <c r="J68" s="42" t="inlineStr">
         <is>
-          <t>Runs on in ST185-EngineRoom-C to A/C pressure switch A5 pin 4 (engine bay): new wire to the switch's own mating plug, plug part TBD. EWD 1990 p.152.</t>
+          <t>POWER box (glove box) relay R4 radiator fan, pin 85</t>
         </is>
       </c>
       <c r="K68" s="43" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="L68" s="44" t="inlineStr">
         <is>
-          <t>sp_ac_psw</t>
+          <t>ecu_a</t>
         </is>
       </c>
       <c r="M68" s="45" t="inlineStr">
         <is>
-          <t>splice sp_ac_psw (SP-AC-PSW: A/C pressure switch output)</t>
-        </is>
-      </c>
-      <c r="N68" s="44" t="inlineStr"/>
+          <t>ECU-A</t>
+        </is>
+      </c>
+      <c r="N68" s="44" t="inlineStr">
+        <is>
+          <t>A29</t>
+        </is>
+      </c>
       <c r="O68" s="45" t="inlineStr">
         <is>
-          <t>A/C pressure sw out</t>
+          <t>Rad fan relay (-)</t>
         </is>
       </c>
       <c r="P68" s="45" t="inlineStr"/>
       <c r="Q68" s="46" t="inlineStr">
         <is>
-          <t>A5.4</t>
+          <t>ECU-A.A29</t>
         </is>
       </c>
       <c r="R68" s="47" t="inlineStr">
         <is>
-          <t>A/C pressure-switched relay coil +</t>
-        </is>
-      </c>
-      <c r="S68" s="48" t="inlineStr">
-        <is>
-          <t>sp_ac_psw</t>
-        </is>
-      </c>
+          <t>Rad fan relay (-) (ECU-A A29)</t>
+        </is>
+      </c>
+      <c r="S68" s="48" t="inlineStr"/>
       <c r="T68" s="48" t="inlineStr"/>
       <c r="U68" s="49" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="V68" s="50" t="inlineStr">
         <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="W68" s="50" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="W68" s="50" t="inlineStr"/>
       <c r="X68" s="50" t="inlineStr">
         <is>
-          <t>Yellow-Blue</t>
-        </is>
-      </c>
-      <c r="Y68" s="50" t="inlineStr"/>
+          <t>Yellow-White</t>
+        </is>
+      </c>
+      <c r="Y68" s="50" t="n">
+        <v>410</v>
+      </c>
       <c r="Z68" s="51" t="inlineStr">
         <is>
-          <t>A/C amp branch (behind dash)</t>
-        </is>
-      </c>
-      <c r="AA68" s="52" t="inlineStr">
-        <is>
-          <t>A/C pressure switch A5, engine bay; exact spot TBD (no locator figure in the repo)</t>
-        </is>
-      </c>
-      <c r="AB68" s="53" t="inlineStr">
-        <is>
-          <t>Y-R (factory wiring; new wire here)</t>
-        </is>
-      </c>
-      <c r="AC68" s="54" t="inlineStr">
-        <is>
-          <t>1990 ST185 EWD p.152 (docs/electrical/ewd-snips/1990-st185-autoac-pressure-clutch-p152.png); 1990 ST185 EWD p.152 (A5 pin 4 Y-R)</t>
-        </is>
-      </c>
-      <c r="AD68" s="54" t="inlineStr">
-        <is>
-          <t>new-wire run terminated at the switch's own mating plug (no factory engine-bay wire reused, Section 39, 2026-10-04); plug part number not yet chosen</t>
-        </is>
-      </c>
+          <t>glove-box branch (POWER / LOGIC boxes)</t>
+        </is>
+      </c>
+      <c r="AA68" s="52" t="inlineStr"/>
+      <c r="AB68" s="53" t="inlineStr"/>
+      <c r="AC68" s="54" t="inlineStr"/>
+      <c r="AD68" s="54" t="inlineStr"/>
       <c r="AE68" s="54" t="inlineStr">
         <is>
-          <t>flying lead FL_A5_4: EWD A5 pin 4 Y-R (factory wiring; new wire here); splice sp_ac_psw named in SoT</t>
+          <t>fuse-box plan k_fan 85 (18 AWG); channels.csv ecu_a A29 Aux 5 (AUX5_RAD_FAN)</t>
         </is>
       </c>
       <c r="AF68" s="54" t="inlineStr">
@@ -9045,19 +8993,19 @@
       </c>
       <c r="AG68" s="54" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as w_ac_psw_in on A-cabin, ? mm; w_ac_psw on EngineRoom-C, 100 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_fan85 on A-cabin, 410 mm; w_fan85_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="23" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="B69" s="23" t="inlineStr">
         <is>
-          <t>w_ac_psw_sw</t>
+          <t>w_eps_rly</t>
         </is>
       </c>
       <c r="C69" s="23" t="inlineStr">
@@ -9065,120 +9013,104 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D69" s="23" t="inlineStr"/>
+      <c r="D69" s="23" t="inlineStr">
+        <is>
+          <t>CabinPower</t>
+        </is>
+      </c>
       <c r="E69" s="24" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="F69" s="25" t="inlineStr">
         <is>
-          <t>A18 (factory)</t>
+          <t>k_eps</t>
         </is>
       </c>
       <c r="G69" s="26" t="inlineStr">
         <is>
-          <t>OEM A/C amplifier</t>
+          <t>EHPS RELAY</t>
         </is>
       </c>
       <c r="H69" s="25" t="n">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="I69" s="26" t="inlineStr">
         <is>
-          <t>A/C pressure sw out</t>
+          <t>EHPS relay coil (-)</t>
         </is>
       </c>
       <c r="J69" s="26" t="inlineStr">
         <is>
-          <t>A/C amp A18 pin 13 (1993: A15), behind the glove box. Solder splice onto the factory Y-R lead. EWD 1990 p.152; locator 1990 p.17.</t>
+          <t>EHPS pump relay (glove box), pin 85</t>
         </is>
       </c>
       <c r="K69" s="27" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="L69" s="28" t="inlineStr">
         <is>
-          <t>sp_ac_psw</t>
+          <t>bh_a_fw</t>
         </is>
       </c>
       <c r="M69" s="29" t="inlineStr">
         <is>
-          <t>splice sp_ac_psw (SP-AC-PSW: A/C pressure switch output)</t>
-        </is>
-      </c>
-      <c r="N69" s="28" t="inlineStr"/>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="N69" s="28" t="n">
+        <v>56</v>
+      </c>
       <c r="O69" s="29" t="inlineStr">
         <is>
-          <t>A/C pressure sw out</t>
+          <t>EHPS relay coil (-)</t>
         </is>
       </c>
       <c r="P69" s="29" t="inlineStr"/>
       <c r="Q69" s="30" t="inlineStr">
         <is>
-          <t>A5.4</t>
+          <t>DRB102.56</t>
         </is>
       </c>
       <c r="R69" s="31" t="inlineStr">
         <is>
-          <t>A/C pressure-switched relay coil +</t>
-        </is>
-      </c>
-      <c r="S69" s="32" t="inlineStr">
-        <is>
-          <t>sp_ac_psw</t>
-        </is>
-      </c>
+          <t>EHPS relay coil (-) (DRB102 56)</t>
+        </is>
+      </c>
+      <c r="S69" s="32" t="inlineStr"/>
       <c r="T69" s="32" t="inlineStr"/>
       <c r="U69" s="33" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="V69" s="34" t="inlineStr">
         <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="W69" s="34" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
+          <t>Violet</t>
+        </is>
+      </c>
+      <c r="W69" s="34" t="inlineStr"/>
       <c r="X69" s="34" t="inlineStr">
         <is>
-          <t>Yellow-Blue</t>
-        </is>
-      </c>
-      <c r="Y69" s="34" t="inlineStr"/>
+          <t>Blue-Blue-Blue</t>
+        </is>
+      </c>
+      <c r="Y69" s="34" t="n">
+        <v>530</v>
+      </c>
       <c r="Z69" s="35" t="inlineStr">
         <is>
-          <t>A/C amp branch (behind dash)</t>
-        </is>
-      </c>
-      <c r="AA69" s="36" t="inlineStr">
-        <is>
-          <t>A/C amplifier A18 (1993 book: A15), passenger side behind the glove box, on the bottom of the evaporator housing; tap point on the lead at the amplifier, distance TBD</t>
-        </is>
-      </c>
-      <c r="AB69" s="37" t="inlineStr">
-        <is>
-          <t>Y-R</t>
-        </is>
-      </c>
-      <c r="AC69" s="38" t="inlineStr">
-        <is>
-          <t>1990 ST185 EWD p.152 (docs/electrical/ewd-snips/1990-st185-autoac-pressure-clutch-p152.png); 1992 EWD132U p.219 A17-13 (ewd-snips/1992-celica-ewd132u-a17-pressure-p219.png); 1990 ST185 EWD p.152; 1992 EWD132U p.219 (A17-13); locator 1990 ST185 EWD p.17 Instrument Panel (ewd-snips/1990-st185-locations-dash.png); Mitchell locations (docs/research/AUTO-AC-AMP-OPTIONS.html)</t>
-        </is>
-      </c>
-      <c r="AD69" s="38" t="inlineStr">
-        <is>
-          <t>solder splice onto the factory Y-R lead at the A/C amplifier</t>
-        </is>
-      </c>
+          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
+        </is>
+      </c>
+      <c r="AA69" s="36" t="inlineStr"/>
+      <c r="AB69" s="37" t="inlineStr"/>
+      <c r="AC69" s="38" t="inlineStr"/>
+      <c r="AD69" s="38" t="inlineStr"/>
       <c r="AE69" s="38" t="inlineStr">
         <is>
-          <t>flying lead FL_ACAMP_PSW: EWD A18 pin 13 Y-R; splice sp_ac_psw named in SoT</t>
+          <t>channels.csv k_eps c2 Coil 85 (MRS_RLY); DRB102 56 = section A c27 'EPS relay coil 85 (R22) - from the MR-S pump B5'</t>
         </is>
       </c>
       <c r="AF69" s="38" t="inlineStr">
@@ -9186,17 +9118,21 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG69" s="38" t="inlineStr"/>
+      <c r="AG69" s="38" t="inlineStr">
+        <is>
+          <t>owner proposed: longer half (drawn today as w_eps_rly on A-cabin, 530 mm; w_eps_rly_cp on CabinPower, 400 mm)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="39" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>ACKILL</t>
         </is>
       </c>
       <c r="B70" s="39" t="inlineStr">
         <is>
-          <t>w_acc86</t>
+          <t>w_ac_kill</t>
         </is>
       </c>
       <c r="C70" s="39" t="inlineStr">
@@ -9204,108 +9140,118 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D70" s="39" t="inlineStr">
-        <is>
-          <t>CabinPower</t>
-        </is>
-      </c>
+      <c r="D70" s="39" t="inlineStr"/>
       <c r="E70" s="40" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="F70" s="41" t="inlineStr">
         <is>
-          <t>sp_ac_psw</t>
+          <t>ecu_a</t>
         </is>
       </c>
       <c r="G70" s="42" t="inlineStr">
         <is>
-          <t>splice sp_ac_psw (SP-AC-PSW: A/C pressure switch output)</t>
-        </is>
-      </c>
-      <c r="H70" s="41" t="inlineStr"/>
+          <t>ECU-A</t>
+        </is>
+      </c>
+      <c r="H70" s="41" t="inlineStr">
+        <is>
+          <t>A18</t>
+        </is>
+      </c>
       <c r="I70" s="42" t="inlineStr">
         <is>
-          <t>A/C clutch relay (+)</t>
+          <t>A/C cancel (ACT)</t>
         </is>
       </c>
       <c r="J70" s="42" t="inlineStr"/>
       <c r="K70" s="43" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="L70" s="44" t="inlineStr">
         <is>
-          <t>k_acc</t>
+          <t>A18 (factory)</t>
         </is>
       </c>
       <c r="M70" s="45" t="inlineStr">
         <is>
-          <t>LOGIC M5</t>
+          <t>OEM A/C amplifier</t>
         </is>
       </c>
       <c r="N70" s="44" t="n">
-        <v>86</v>
+        <v>11</v>
       </c>
       <c r="O70" s="45" t="inlineStr">
         <is>
-          <t>A/C clutch relay (+)</t>
+          <t>A/C cancel (ACT)</t>
         </is>
       </c>
       <c r="P70" s="45" t="inlineStr">
         <is>
-          <t>LOGIC box (glove box) relay M15 A/C clutch, pin 86</t>
+          <t>A/C amp A18 pin 11 (1993: A15), behind the glove box. Solder splice onto the factory G-Y lead. EWD 1992 p.93 / p.218; locator 1990 p.17.</t>
         </is>
       </c>
       <c r="Q70" s="46" t="inlineStr">
         <is>
-          <t>A5.4</t>
+          <t>ECU-A.A18</t>
         </is>
       </c>
       <c r="R70" s="47" t="inlineStr">
         <is>
-          <t>A/C pressure-switched relay coil +</t>
-        </is>
-      </c>
-      <c r="S70" s="48" t="inlineStr">
-        <is>
-          <t>sp_ac_psw</t>
-        </is>
-      </c>
+          <t>A/C cancel (ACT) (ECU-A A18)</t>
+        </is>
+      </c>
+      <c r="S70" s="48" t="inlineStr"/>
       <c r="T70" s="48" t="inlineStr"/>
       <c r="U70" s="49" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V70" s="50" t="inlineStr">
         <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="W70" s="50" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
+          <t>Gray</t>
+        </is>
+      </c>
+      <c r="W70" s="50" t="inlineStr"/>
       <c r="X70" s="50" t="inlineStr">
         <is>
-          <t>Yellow-Blue</t>
-        </is>
-      </c>
-      <c r="Y70" s="50" t="inlineStr"/>
+          <t>White-Yellow-Yellow</t>
+        </is>
+      </c>
+      <c r="Y70" s="50" t="n">
+        <v>600</v>
+      </c>
       <c r="Z70" s="51" t="inlineStr">
         <is>
           <t>A/C amp branch (behind dash)</t>
         </is>
       </c>
-      <c r="AA70" s="52" t="inlineStr"/>
-      <c r="AB70" s="53" t="inlineStr"/>
-      <c r="AC70" s="54" t="inlineStr"/>
-      <c r="AD70" s="54" t="inlineStr"/>
+      <c r="AA70" s="52" t="inlineStr">
+        <is>
+          <t>A/C amplifier A18 (1993 book: A15), passenger side behind the glove box, on the bottom of the evaporator housing; tap point on the lead at the amplifier, distance TBD</t>
+        </is>
+      </c>
+      <c r="AB70" s="53" t="inlineStr">
+        <is>
+          <t>G-Y</t>
+        </is>
+      </c>
+      <c r="AC70" s="54" t="inlineStr">
+        <is>
+          <t>1992 Celica EWD132U p.93 and p.218 (docs/electrical/ewd-snips/1992-celica-ewd132u-a17-act-p093.png, 1992-celica-ewd132u-a17-clutch-p218.png); 1990 ST185 book locator A18; 1992 EWD132U p.93 and p.218 (A17-11 = A18-11); locator 1990 ST185 EWD p.17 Instrument Panel (ewd-snips/1990-st185-locations-dash.png); Mitchell locations (docs/research/AUTO-AC-AMP-OPTIONS.html)</t>
+        </is>
+      </c>
+      <c r="AD70" s="54" t="inlineStr">
+        <is>
+          <t>solder splice onto the factory G-Y ACT lead at the A/C amplifier</t>
+        </is>
+      </c>
       <c r="AE70" s="54" t="inlineStr">
         <is>
-          <t>splice sp_ac_psw named in SoT; fuse-box plan k_acc 86 (18 AWG)</t>
+          <t>channels.csv ecu_a A18 Aux 4 (AUX4_AC_KILL); flying lead FL_ACAMP_ACT: EWD A18 pin 11 G-Y</t>
         </is>
       </c>
       <c r="AF70" s="54" t="inlineStr">
@@ -9313,21 +9259,17 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG70" s="54" t="inlineStr">
-        <is>
-          <t>owner TBD: a half has no length estimate (drawn today as w_acc86 on A-cabin, ? mm; w_acc86_cp on CabinPower, 400 mm)</t>
-        </is>
-      </c>
+      <c r="AG70" s="54" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="23" t="inlineStr">
         <is>
-          <t>5V</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B71" s="23" t="inlineStr">
         <is>
-          <t>w_aps_vc1</t>
+          <t>w_ac_psw_in</t>
         </is>
       </c>
       <c r="C71" s="23" t="inlineStr">
@@ -9335,20 +9277,24 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D71" s="23" t="inlineStr"/>
+      <c r="D71" s="23" t="inlineStr">
+        <is>
+          <t>EngineRoom-C</t>
+        </is>
+      </c>
       <c r="E71" s="24" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F71" s="25" t="inlineStr">
         <is>
-          <t>aps</t>
+          <t>A5 (factory)</t>
         </is>
       </c>
       <c r="G71" s="26" t="inlineStr">
         <is>
-          <t>PEDAL</t>
+          <t>OEM A5, factory Y-R lead</t>
         </is>
       </c>
       <c r="H71" s="25" t="n">
@@ -9356,10 +9302,14 @@
       </c>
       <c r="I71" s="26" t="inlineStr">
         <is>
-          <t>+5 V pedal sensor 1</t>
-        </is>
-      </c>
-      <c r="J71" s="26" t="inlineStr"/>
+          <t>A/C pressure sw out</t>
+        </is>
+      </c>
+      <c r="J71" s="26" t="inlineStr">
+        <is>
+          <t>Runs on in ST185-EngineRoom-C to A/C pressure switch A5 pin 4 (engine bay): new wire to the switch's own mating plug, plug part TBD. EWD 1990 p.152.</t>
+        </is>
+      </c>
       <c r="K71" s="27" t="inlineStr">
         <is>
           <t>splice</t>
@@ -9367,68 +9317,84 @@
       </c>
       <c r="L71" s="28" t="inlineStr">
         <is>
-          <t>sp_5v_2</t>
+          <t>sp_ac_psw</t>
         </is>
       </c>
       <c r="M71" s="29" t="inlineStr">
         <is>
-          <t>splice sp_5v_2 (SP-5V-PEDAL: +5 V to pedal + cruise)</t>
+          <t>splice sp_ac_psw (SP-AC-PSW: A/C pressure switch output)</t>
         </is>
       </c>
       <c r="N71" s="28" t="inlineStr"/>
       <c r="O71" s="29" t="inlineStr">
         <is>
-          <t>+5 V pedal sensor 1</t>
+          <t>A/C pressure sw out</t>
         </is>
       </c>
       <c r="P71" s="29" t="inlineStr"/>
       <c r="Q71" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A32</t>
+          <t>A5.4</t>
         </is>
       </c>
       <c r="R71" s="31" t="inlineStr">
         <is>
-          <t>+5V sensor (ECU-A A32)</t>
+          <t>A/C pressure-switched relay coil +</t>
         </is>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
-          <t>sp_5v_2</t>
-        </is>
-      </c>
-      <c r="T71" s="32" t="inlineStr">
-        <is>
-          <t>cab_aps1</t>
-        </is>
-      </c>
+          <t>sp_ac_psw</t>
+        </is>
+      </c>
+      <c r="T71" s="32" t="inlineStr"/>
       <c r="U71" s="33" t="n">
         <v>20</v>
       </c>
       <c r="V71" s="34" t="inlineStr">
         <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="W71" s="34" t="inlineStr">
+        <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="W71" s="34" t="inlineStr"/>
       <c r="X71" s="34" t="inlineStr">
         <is>
-          <t>Blue-Blue</t>
+          <t>Yellow-Blue</t>
         </is>
       </c>
       <c r="Y71" s="34" t="inlineStr"/>
       <c r="Z71" s="35" t="inlineStr">
         <is>
-          <t>pedal branch (driver footwell)</t>
-        </is>
-      </c>
-      <c r="AA71" s="36" t="inlineStr"/>
-      <c r="AB71" s="37" t="inlineStr"/>
-      <c r="AC71" s="38" t="inlineStr"/>
-      <c r="AD71" s="38" t="inlineStr"/>
+          <t>A/C amp branch (behind dash)</t>
+        </is>
+      </c>
+      <c r="AA71" s="36" t="inlineStr">
+        <is>
+          <t>A/C pressure switch A5, engine bay; exact spot TBD (no locator figure in the repo)</t>
+        </is>
+      </c>
+      <c r="AB71" s="37" t="inlineStr">
+        <is>
+          <t>Y-R (factory wiring; new wire here)</t>
+        </is>
+      </c>
+      <c r="AC71" s="38" t="inlineStr">
+        <is>
+          <t>1990 ST185 EWD p.152 (docs/electrical/ewd-snips/1990-st185-autoac-pressure-clutch-p152.png); 1990 ST185 EWD p.152 (A5 pin 4 Y-R)</t>
+        </is>
+      </c>
+      <c r="AD71" s="38" t="inlineStr">
+        <is>
+          <t>new-wire run terminated at the switch's own mating plug (no factory engine-bay wire reused, Section 39, 2026-10-04); plug part number not yet chosen</t>
+        </is>
+      </c>
       <c r="AE71" s="38" t="inlineStr">
         <is>
-          <t>splice sp_5v_2 named in SoT</t>
+          <t>flying lead FL_A5_4: EWD A5 pin 4 Y-R (factory wiring; new wire here); splice sp_ac_psw: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF71" s="38" t="inlineStr">
@@ -9438,19 +9404,19 @@
       </c>
       <c r="AG71" s="38" t="inlineStr">
         <is>
-          <t>pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
+          <t>owner TBD: a half has no length estimate (drawn today as w_ac_psw_in on A-cabin, ? mm; w_ac_psw on EngineRoom-C, 100 mm)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="39" t="inlineStr">
         <is>
-          <t>SGND</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B72" s="39" t="inlineStr">
         <is>
-          <t>w40</t>
+          <t>w_ac_psw_sw</t>
         </is>
       </c>
       <c r="C72" s="39" t="inlineStr">
@@ -9461,28 +9427,32 @@
       <c r="D72" s="39" t="inlineStr"/>
       <c r="E72" s="40" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F72" s="41" t="inlineStr">
         <is>
-          <t>aps</t>
+          <t>A18 (factory)</t>
         </is>
       </c>
       <c r="G72" s="42" t="inlineStr">
         <is>
-          <t>PEDAL</t>
+          <t>OEM A/C amplifier</t>
         </is>
       </c>
       <c r="H72" s="41" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I72" s="42" t="inlineStr">
         <is>
-          <t>Pedal 1 ground</t>
-        </is>
-      </c>
-      <c r="J72" s="42" t="inlineStr"/>
+          <t>A/C pressure sw out</t>
+        </is>
+      </c>
+      <c r="J72" s="42" t="inlineStr">
+        <is>
+          <t>A/C amp A18 pin 13 (1993: A15), behind the glove box. Solder splice onto the factory Y-R lead. EWD 1990 p.152; locator 1990 p.17.</t>
+        </is>
+      </c>
       <c r="K72" s="43" t="inlineStr">
         <is>
           <t>splice</t>
@@ -9490,41 +9460,37 @@
       </c>
       <c r="L72" s="44" t="inlineStr">
         <is>
-          <t>sp_gndout</t>
+          <t>sp_ac_psw</t>
         </is>
       </c>
       <c r="M72" s="45" t="inlineStr">
         <is>
-          <t>splice sp_gndout (SP-GNDOUT-A: sensor ground)</t>
+          <t>splice sp_ac_psw (SP-AC-PSW: A/C pressure switch output)</t>
         </is>
       </c>
       <c r="N72" s="44" t="inlineStr"/>
       <c r="O72" s="45" t="inlineStr">
         <is>
-          <t>Pedal 1 ground</t>
+          <t>A/C pressure sw out</t>
         </is>
       </c>
       <c r="P72" s="45" t="inlineStr"/>
       <c r="Q72" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A24</t>
+          <t>A5.4</t>
         </is>
       </c>
       <c r="R72" s="47" t="inlineStr">
         <is>
-          <t>Sensor GND (ECU-A A24)</t>
+          <t>A/C pressure-switched relay coil +</t>
         </is>
       </c>
       <c r="S72" s="48" t="inlineStr">
         <is>
-          <t>sp_gndout</t>
-        </is>
-      </c>
-      <c r="T72" s="48" t="inlineStr">
-        <is>
-          <t>cab_aps1</t>
-        </is>
-      </c>
+          <t>sp_ac_psw</t>
+        </is>
+      </c>
+      <c r="T72" s="48" t="inlineStr"/>
       <c r="U72" s="49" t="n">
         <v>20</v>
       </c>
@@ -9533,25 +9499,45 @@
           <t>Yellow</t>
         </is>
       </c>
-      <c r="W72" s="50" t="inlineStr"/>
+      <c r="W72" s="50" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="X72" s="50" t="inlineStr">
         <is>
-          <t>Yellow-Yellow-Blue</t>
+          <t>Yellow-Blue</t>
         </is>
       </c>
       <c r="Y72" s="50" t="inlineStr"/>
       <c r="Z72" s="51" t="inlineStr">
         <is>
-          <t>pedal branch (driver footwell)</t>
-        </is>
-      </c>
-      <c r="AA72" s="52" t="inlineStr"/>
-      <c r="AB72" s="53" t="inlineStr"/>
-      <c r="AC72" s="54" t="inlineStr"/>
-      <c r="AD72" s="54" t="inlineStr"/>
+          <t>A/C amp branch (behind dash)</t>
+        </is>
+      </c>
+      <c r="AA72" s="52" t="inlineStr">
+        <is>
+          <t>A/C amplifier A18 (1993 book: A15), passenger side behind the glove box, on the bottom of the evaporator housing; tap point on the lead at the amplifier, distance TBD</t>
+        </is>
+      </c>
+      <c r="AB72" s="53" t="inlineStr">
+        <is>
+          <t>Y-R</t>
+        </is>
+      </c>
+      <c r="AC72" s="54" t="inlineStr">
+        <is>
+          <t>1990 ST185 EWD p.152 (docs/electrical/ewd-snips/1990-st185-autoac-pressure-clutch-p152.png); 1992 EWD132U p.219 A17-13 (ewd-snips/1992-celica-ewd132u-a17-pressure-p219.png); 1990 ST185 EWD p.152; 1992 EWD132U p.219 (A17-13); locator 1990 ST185 EWD p.17 Instrument Panel (ewd-snips/1990-st185-locations-dash.png); Mitchell locations (docs/research/AUTO-AC-AMP-OPTIONS.html)</t>
+        </is>
+      </c>
+      <c r="AD72" s="54" t="inlineStr">
+        <is>
+          <t>solder splice onto the factory Y-R lead at the A/C amplifier</t>
+        </is>
+      </c>
       <c r="AE72" s="54" t="inlineStr">
         <is>
-          <t>splice sp_gndout named in SoT</t>
+          <t>flying lead FL_ACAMP_PSW: EWD A18 pin 13 Y-R; splice sp_ac_psw: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF72" s="54" t="inlineStr">
@@ -9559,21 +9545,17 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG72" s="54" t="inlineStr">
-        <is>
-          <t>pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
-        </is>
-      </c>
+      <c r="AG72" s="54" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="23" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B73" s="23" t="inlineStr">
         <is>
-          <t>w38</t>
+          <t>w_acc86</t>
         </is>
       </c>
       <c r="C73" s="23" t="inlineStr">
@@ -9581,28 +9563,30 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D73" s="23" t="inlineStr"/>
+      <c r="D73" s="23" t="inlineStr">
+        <is>
+          <t>CabinPower</t>
+        </is>
+      </c>
       <c r="E73" s="24" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="F73" s="25" t="inlineStr">
         <is>
-          <t>aps</t>
+          <t>sp_ac_psw</t>
         </is>
       </c>
       <c r="G73" s="26" t="inlineStr">
         <is>
-          <t>PEDAL</t>
-        </is>
-      </c>
-      <c r="H73" s="25" t="n">
-        <v>6</v>
-      </c>
+          <t>splice sp_ac_psw (SP-AC-PSW: A/C pressure switch output)</t>
+        </is>
+      </c>
+      <c r="H73" s="25" t="inlineStr"/>
       <c r="I73" s="26" t="inlineStr">
         <is>
-          <t>Pedal 1 signal main</t>
+          <t>A/C clutch relay (+)</t>
         </is>
       </c>
       <c r="J73" s="26" t="inlineStr"/>
@@ -9613,61 +9597,65 @@
       </c>
       <c r="L73" s="28" t="inlineStr">
         <is>
-          <t>ecu_a</t>
+          <t>k_acc</t>
         </is>
       </c>
       <c r="M73" s="29" t="inlineStr">
         <is>
-          <t>ECU-A</t>
-        </is>
-      </c>
-      <c r="N73" s="28" t="inlineStr">
-        <is>
-          <t>A14</t>
-        </is>
+          <t>LOGIC M5</t>
+        </is>
+      </c>
+      <c r="N73" s="28" t="n">
+        <v>86</v>
       </c>
       <c r="O73" s="29" t="inlineStr">
         <is>
-          <t>Pedal 1 signal main</t>
-        </is>
-      </c>
-      <c r="P73" s="29" t="inlineStr"/>
+          <t>A/C clutch relay (+)</t>
+        </is>
+      </c>
+      <c r="P73" s="29" t="inlineStr">
+        <is>
+          <t>LOGIC box (glove box) relay M15 A/C clutch, pin 86</t>
+        </is>
+      </c>
       <c r="Q73" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A14</t>
+          <t>A5.4</t>
         </is>
       </c>
       <c r="R73" s="31" t="inlineStr">
         <is>
-          <t>Pedal 1 signal main (ECU-A A14)</t>
-        </is>
-      </c>
-      <c r="S73" s="32" t="inlineStr"/>
-      <c r="T73" s="32" t="inlineStr">
-        <is>
-          <t>cab_aps1</t>
-        </is>
-      </c>
+          <t>A/C pressure-switched relay coil +</t>
+        </is>
+      </c>
+      <c r="S73" s="32" t="inlineStr">
+        <is>
+          <t>sp_ac_psw</t>
+        </is>
+      </c>
+      <c r="T73" s="32" t="inlineStr"/>
       <c r="U73" s="33" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="V73" s="34" t="inlineStr">
         <is>
-          <t>Blue</t>
-        </is>
-      </c>
-      <c r="W73" s="34" t="inlineStr"/>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="W73" s="34" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="X73" s="34" t="inlineStr">
         <is>
-          <t>White-Blue-Yellow</t>
-        </is>
-      </c>
-      <c r="Y73" s="34" t="n">
-        <v>1050</v>
-      </c>
+          <t>Yellow-Blue</t>
+        </is>
+      </c>
+      <c r="Y73" s="34" t="inlineStr"/>
       <c r="Z73" s="35" t="inlineStr">
         <is>
-          <t>pedal branch (driver footwell)</t>
+          <t>A/C amp branch (behind dash)</t>
         </is>
       </c>
       <c r="AA73" s="36" t="inlineStr"/>
@@ -9676,7 +9664,7 @@
       <c r="AD73" s="38" t="inlineStr"/>
       <c r="AE73" s="38" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A14 An Volt 4 (AV4_APS_MAIN)</t>
+          <t>splice sp_ac_psw: node of the wire list (SoT); fuse-box plan k_acc 86 (18 AWG)</t>
         </is>
       </c>
       <c r="AF73" s="38" t="inlineStr">
@@ -9686,19 +9674,19 @@
       </c>
       <c r="AG73" s="38" t="inlineStr">
         <is>
-          <t>pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
+          <t>owner TBD: a half has no length estimate (drawn today as w_acc86 on A-cabin, ? mm; w_acc86_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="39" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="B74" s="39" t="inlineStr">
         <is>
-          <t>cab_aps1_sh</t>
+          <t>w_aps_vc1</t>
         </is>
       </c>
       <c r="C74" s="39" t="inlineStr">
@@ -9709,23 +9697,25 @@
       <c r="D74" s="39" t="inlineStr"/>
       <c r="E74" s="40" t="inlineStr">
         <is>
-          <t>cable screen</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="F74" s="41" t="inlineStr">
         <is>
-          <t>cab_aps1</t>
+          <t>aps</t>
         </is>
       </c>
       <c r="G74" s="42" t="inlineStr">
         <is>
-          <t>cable screen (one end only)</t>
-        </is>
-      </c>
-      <c r="H74" s="41" t="inlineStr"/>
+          <t>PEDAL</t>
+        </is>
+      </c>
+      <c r="H74" s="41" t="n">
+        <v>4</v>
+      </c>
       <c r="I74" s="42" t="inlineStr">
         <is>
-          <t>Pedal 1 cable shield</t>
+          <t>+5 V pedal sensor 1</t>
         </is>
       </c>
       <c r="J74" s="42" t="inlineStr"/>
@@ -9736,34 +9726,34 @@
       </c>
       <c r="L74" s="44" t="inlineStr">
         <is>
-          <t>sp_shield_a</t>
+          <t>sp_5v_2</t>
         </is>
       </c>
       <c r="M74" s="45" t="inlineStr">
         <is>
-          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
+          <t>splice sp_5v_2 (SP-5V-PEDAL: +5 V to pedal + cruise)</t>
         </is>
       </c>
       <c r="N74" s="44" t="inlineStr"/>
       <c r="O74" s="45" t="inlineStr">
         <is>
-          <t>Pedal 1 cable shield</t>
+          <t>+5 V pedal sensor 1</t>
         </is>
       </c>
       <c r="P74" s="45" t="inlineStr"/>
       <c r="Q74" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A7</t>
+          <t>ECU-A.A32</t>
         </is>
       </c>
       <c r="R74" s="47" t="inlineStr">
         <is>
-          <t>Screen A (ECU A7, SHIELD_A)</t>
+          <t>+5V sensor (ECU-A A32)</t>
         </is>
       </c>
       <c r="S74" s="48" t="inlineStr">
         <is>
-          <t>sp_shield_a</t>
+          <t>sp_5v_2</t>
         </is>
       </c>
       <c r="T74" s="48" t="inlineStr">
@@ -9771,22 +9761,24 @@
           <t>cab_aps1</t>
         </is>
       </c>
-      <c r="U74" s="49" t="inlineStr"/>
+      <c r="U74" s="49" t="n">
+        <v>20</v>
+      </c>
       <c r="V74" s="50" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W74" s="50" t="inlineStr"/>
       <c r="X74" s="50" t="inlineStr">
         <is>
-          <t>White-Blue-Yellow</t>
+          <t>Blue-Blue</t>
         </is>
       </c>
       <c r="Y74" s="50" t="inlineStr"/>
       <c r="Z74" s="51" t="inlineStr">
         <is>
-          <t>at ECU-A plug</t>
+          <t>pedal branch (driver footwell)</t>
         </is>
       </c>
       <c r="AA74" s="52" t="inlineStr"/>
@@ -9795,7 +9787,7 @@
       <c r="AD74" s="54" t="inlineStr"/>
       <c r="AE74" s="54" t="inlineStr">
         <is>
-          <t>splice sp_shield_a named in SoT</t>
+          <t>splice sp_5v_2: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF74" s="54" t="inlineStr">
@@ -9805,19 +9797,19 @@
       </c>
       <c r="AG74" s="54" t="inlineStr">
         <is>
-          <t>screen floats at the far end; pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
+          <t>pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="23" t="inlineStr">
         <is>
-          <t>5V</t>
+          <t>SGND</t>
         </is>
       </c>
       <c r="B75" s="23" t="inlineStr">
         <is>
-          <t>w210</t>
+          <t>w40</t>
         </is>
       </c>
       <c r="C75" s="23" t="inlineStr">
@@ -9842,11 +9834,11 @@
         </is>
       </c>
       <c r="H75" s="25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I75" s="26" t="inlineStr">
         <is>
-          <t>+5 V pedal sensor 2</t>
+          <t>Pedal 1 ground</t>
         </is>
       </c>
       <c r="J75" s="26" t="inlineStr"/>
@@ -9857,39 +9849,39 @@
       </c>
       <c r="L75" s="28" t="inlineStr">
         <is>
-          <t>sp_5v_2</t>
+          <t>sp_gndout</t>
         </is>
       </c>
       <c r="M75" s="29" t="inlineStr">
         <is>
-          <t>splice sp_5v_2 (SP-5V-PEDAL: +5 V to pedal + cruise)</t>
+          <t>splice sp_gndout (SP-GNDOUT-A: sensor ground)</t>
         </is>
       </c>
       <c r="N75" s="28" t="inlineStr"/>
       <c r="O75" s="29" t="inlineStr">
         <is>
-          <t>+5 V pedal sensor 2</t>
+          <t>Pedal 1 ground</t>
         </is>
       </c>
       <c r="P75" s="29" t="inlineStr"/>
       <c r="Q75" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A32</t>
+          <t>ECU-A.A24</t>
         </is>
       </c>
       <c r="R75" s="31" t="inlineStr">
         <is>
-          <t>+5V sensor (ECU-A A32)</t>
+          <t>Sensor GND (ECU-A A24)</t>
         </is>
       </c>
       <c r="S75" s="32" t="inlineStr">
         <is>
-          <t>sp_5v_2</t>
+          <t>sp_gndout</t>
         </is>
       </c>
       <c r="T75" s="32" t="inlineStr">
         <is>
-          <t>cab_aps2</t>
+          <t>cab_aps1</t>
         </is>
       </c>
       <c r="U75" s="33" t="n">
@@ -9897,13 +9889,13 @@
       </c>
       <c r="V75" s="34" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W75" s="34" t="inlineStr"/>
       <c r="X75" s="34" t="inlineStr">
         <is>
-          <t>Blue-Blue</t>
+          <t>Yellow-Yellow-Blue</t>
         </is>
       </c>
       <c r="Y75" s="34" t="inlineStr"/>
@@ -9918,7 +9910,7 @@
       <c r="AD75" s="38" t="inlineStr"/>
       <c r="AE75" s="38" t="inlineStr">
         <is>
-          <t>splice sp_5v_2 named in SoT</t>
+          <t>splice sp_gndout: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF75" s="38" t="inlineStr">
@@ -9935,12 +9927,12 @@
     <row r="76">
       <c r="A76" s="39" t="inlineStr">
         <is>
-          <t>SGND</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="B76" s="39" t="inlineStr">
         <is>
-          <t>w_aps_gnd2</t>
+          <t>w38</t>
         </is>
       </c>
       <c r="C76" s="39" t="inlineStr">
@@ -9965,54 +9957,54 @@
         </is>
       </c>
       <c r="H76" s="41" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I76" s="42" t="inlineStr">
         <is>
-          <t>Pedal 2 ground</t>
+          <t>Pedal 1 signal main</t>
         </is>
       </c>
       <c r="J76" s="42" t="inlineStr"/>
       <c r="K76" s="43" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="L76" s="44" t="inlineStr">
         <is>
-          <t>sp_gndout</t>
+          <t>ecu_a</t>
         </is>
       </c>
       <c r="M76" s="45" t="inlineStr">
         <is>
-          <t>splice sp_gndout (SP-GNDOUT-A: sensor ground)</t>
-        </is>
-      </c>
-      <c r="N76" s="44" t="inlineStr"/>
+          <t>ECU-A</t>
+        </is>
+      </c>
+      <c r="N76" s="44" t="inlineStr">
+        <is>
+          <t>A14</t>
+        </is>
+      </c>
       <c r="O76" s="45" t="inlineStr">
         <is>
-          <t>Pedal 2 ground</t>
+          <t>Pedal 1 signal main</t>
         </is>
       </c>
       <c r="P76" s="45" t="inlineStr"/>
       <c r="Q76" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A24</t>
+          <t>ECU-A.A14</t>
         </is>
       </c>
       <c r="R76" s="47" t="inlineStr">
         <is>
-          <t>Sensor GND (ECU-A A24)</t>
-        </is>
-      </c>
-      <c r="S76" s="48" t="inlineStr">
-        <is>
-          <t>sp_gndout</t>
-        </is>
-      </c>
+          <t>Pedal 1 signal main (ECU-A A14)</t>
+        </is>
+      </c>
+      <c r="S76" s="48" t="inlineStr"/>
       <c r="T76" s="48" t="inlineStr">
         <is>
-          <t>cab_aps2</t>
+          <t>cab_aps1</t>
         </is>
       </c>
       <c r="U76" s="49" t="n">
@@ -10020,16 +10012,18 @@
       </c>
       <c r="V76" s="50" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="W76" s="50" t="inlineStr"/>
       <c r="X76" s="50" t="inlineStr">
         <is>
-          <t>Yellow-Yellow-Blue</t>
-        </is>
-      </c>
-      <c r="Y76" s="50" t="inlineStr"/>
+          <t>White-Blue-Yellow</t>
+        </is>
+      </c>
+      <c r="Y76" s="50" t="n">
+        <v>1050</v>
+      </c>
       <c r="Z76" s="51" t="inlineStr">
         <is>
           <t>pedal branch (driver footwell)</t>
@@ -10041,7 +10035,7 @@
       <c r="AD76" s="54" t="inlineStr"/>
       <c r="AE76" s="54" t="inlineStr">
         <is>
-          <t>splice sp_gndout named in SoT</t>
+          <t>channels.csv ecu_a A14 An Volt 4 (AV4_APS_MAIN)</t>
         </is>
       </c>
       <c r="AF76" s="54" t="inlineStr">
@@ -10063,7 +10057,7 @@
       </c>
       <c r="B77" s="23" t="inlineStr">
         <is>
-          <t>w_aps_vpa2</t>
+          <t>cab_aps1_sh</t>
         </is>
       </c>
       <c r="C77" s="23" t="inlineStr">
@@ -10071,87 +10065,75 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D77" s="23" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
+      <c r="D77" s="23" t="inlineStr"/>
       <c r="E77" s="24" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>cable screen</t>
         </is>
       </c>
       <c r="F77" s="25" t="inlineStr">
         <is>
-          <t>aps</t>
+          <t>cab_aps1</t>
         </is>
       </c>
       <c r="G77" s="26" t="inlineStr">
         <is>
-          <t>PEDAL</t>
-        </is>
-      </c>
-      <c r="H77" s="25" t="n">
-        <v>3</v>
-      </c>
+          <t>cable screen (one end only)</t>
+        </is>
+      </c>
+      <c r="H77" s="25" t="inlineStr"/>
       <c r="I77" s="26" t="inlineStr">
         <is>
-          <t>Pedal 2 signal sub</t>
+          <t>Pedal 1 cable shield</t>
         </is>
       </c>
       <c r="J77" s="26" t="inlineStr"/>
       <c r="K77" s="27" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="L77" s="28" t="inlineStr">
         <is>
-          <t>ecu_b</t>
+          <t>sp_shield_a</t>
         </is>
       </c>
       <c r="M77" s="29" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
-        </is>
-      </c>
-      <c r="N77" s="28" t="inlineStr">
-        <is>
-          <t>B33</t>
-        </is>
-      </c>
+          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
+        </is>
+      </c>
+      <c r="N77" s="28" t="inlineStr"/>
       <c r="O77" s="29" t="inlineStr">
         <is>
-          <t>Pedal 2 signal sub</t>
-        </is>
-      </c>
-      <c r="P77" s="29" t="inlineStr">
-        <is>
-          <t>ECU-B plug pin B33 (Link G4X, centre dash); VPA2</t>
-        </is>
-      </c>
+          <t>Pedal 1 cable shield</t>
+        </is>
+      </c>
+      <c r="P77" s="29" t="inlineStr"/>
       <c r="Q77" s="30" t="inlineStr">
         <is>
-          <t>ECU-B.B33</t>
+          <t>ECU-A.A7</t>
         </is>
       </c>
       <c r="R77" s="31" t="inlineStr">
         <is>
-          <t>Pedal 2 signal sub (ECU-B B33)</t>
-        </is>
-      </c>
-      <c r="S77" s="32" t="inlineStr"/>
+          <t>Screen A (ECU A7, SHIELD_A)</t>
+        </is>
+      </c>
+      <c r="S77" s="32" t="inlineStr">
+        <is>
+          <t>sp_shield_a</t>
+        </is>
+      </c>
       <c r="T77" s="32" t="inlineStr">
         <is>
-          <t>cab_aps2</t>
-        </is>
-      </c>
-      <c r="U77" s="33" t="n">
-        <v>20</v>
-      </c>
+          <t>cab_aps1</t>
+        </is>
+      </c>
+      <c r="U77" s="33" t="inlineStr"/>
       <c r="V77" s="34" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Shield</t>
         </is>
       </c>
       <c r="W77" s="34" t="inlineStr"/>
@@ -10160,12 +10142,10 @@
           <t>White-Blue-Yellow</t>
         </is>
       </c>
-      <c r="Y77" s="34" t="n">
-        <v>1720</v>
-      </c>
+      <c r="Y77" s="34" t="inlineStr"/>
       <c r="Z77" s="35" t="inlineStr">
         <is>
-          <t>pedal branch (driver footwell) / to ECU-B plug (beside ECU-A)</t>
+          <t>at ECU-A plug</t>
         </is>
       </c>
       <c r="AA77" s="36" t="inlineStr"/>
@@ -10174,7 +10154,7 @@
       <c r="AD77" s="38" t="inlineStr"/>
       <c r="AE77" s="38" t="inlineStr">
         <is>
-          <t>channels.csv ecu_b B33 An Volt 5 (AV5_APS_SUB)</t>
+          <t>splice sp_shield_a: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF77" s="38" t="inlineStr">
@@ -10184,19 +10164,19 @@
       </c>
       <c r="AG77" s="38" t="inlineStr">
         <is>
-          <t>pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143); owner proposed: longer half (drawn today as w_aps_vpa2 on A-cabin, 1720 mm; w39 on B-cabin, 1250 mm)</t>
+          <t>screen floats at the far end; pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="39" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="B78" s="39" t="inlineStr">
         <is>
-          <t>cab_aps_sh</t>
+          <t>w210</t>
         </is>
       </c>
       <c r="C78" s="39" t="inlineStr">
@@ -10207,23 +10187,25 @@
       <c r="D78" s="39" t="inlineStr"/>
       <c r="E78" s="40" t="inlineStr">
         <is>
-          <t>cable screen</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="F78" s="41" t="inlineStr">
         <is>
-          <t>cab_aps2</t>
+          <t>aps</t>
         </is>
       </c>
       <c r="G78" s="42" t="inlineStr">
         <is>
-          <t>cable screen (one end only)</t>
-        </is>
-      </c>
-      <c r="H78" s="41" t="inlineStr"/>
+          <t>PEDAL</t>
+        </is>
+      </c>
+      <c r="H78" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="I78" s="42" t="inlineStr">
         <is>
-          <t>Pedal 2 cable shield</t>
+          <t>+5 V pedal sensor 2</t>
         </is>
       </c>
       <c r="J78" s="42" t="inlineStr"/>
@@ -10234,34 +10216,34 @@
       </c>
       <c r="L78" s="44" t="inlineStr">
         <is>
-          <t>sp_shield_a</t>
+          <t>sp_5v_2</t>
         </is>
       </c>
       <c r="M78" s="45" t="inlineStr">
         <is>
-          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
+          <t>splice sp_5v_2 (SP-5V-PEDAL: +5 V to pedal + cruise)</t>
         </is>
       </c>
       <c r="N78" s="44" t="inlineStr"/>
       <c r="O78" s="45" t="inlineStr">
         <is>
-          <t>Pedal 2 cable shield</t>
+          <t>+5 V pedal sensor 2</t>
         </is>
       </c>
       <c r="P78" s="45" t="inlineStr"/>
       <c r="Q78" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A7</t>
+          <t>ECU-A.A32</t>
         </is>
       </c>
       <c r="R78" s="47" t="inlineStr">
         <is>
-          <t>Screen A (ECU A7, SHIELD_A)</t>
+          <t>+5V sensor (ECU-A A32)</t>
         </is>
       </c>
       <c r="S78" s="48" t="inlineStr">
         <is>
-          <t>sp_shield_a</t>
+          <t>sp_5v_2</t>
         </is>
       </c>
       <c r="T78" s="48" t="inlineStr">
@@ -10269,22 +10251,24 @@
           <t>cab_aps2</t>
         </is>
       </c>
-      <c r="U78" s="49" t="inlineStr"/>
+      <c r="U78" s="49" t="n">
+        <v>20</v>
+      </c>
       <c r="V78" s="50" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W78" s="50" t="inlineStr"/>
       <c r="X78" s="50" t="inlineStr">
         <is>
-          <t>White-Blue-Yellow</t>
+          <t>Blue-Blue</t>
         </is>
       </c>
       <c r="Y78" s="50" t="inlineStr"/>
       <c r="Z78" s="51" t="inlineStr">
         <is>
-          <t>at ECU-A plug</t>
+          <t>pedal branch (driver footwell)</t>
         </is>
       </c>
       <c r="AA78" s="52" t="inlineStr"/>
@@ -10293,7 +10277,7 @@
       <c r="AD78" s="54" t="inlineStr"/>
       <c r="AE78" s="54" t="inlineStr">
         <is>
-          <t>splice sp_shield_a named in SoT</t>
+          <t>splice sp_5v_2: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF78" s="54" t="inlineStr">
@@ -10303,19 +10287,19 @@
       </c>
       <c r="AG78" s="54" t="inlineStr">
         <is>
-          <t>screen floats at the far end; pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
+          <t>pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="23" t="inlineStr">
         <is>
-          <t>5V</t>
+          <t>SGND</t>
         </is>
       </c>
       <c r="B79" s="23" t="inlineStr">
         <is>
-          <t>cab_fspur_5v</t>
+          <t>w_aps_gnd2</t>
         </is>
       </c>
       <c r="C79" s="23" t="inlineStr">
@@ -10331,20 +10315,20 @@
       </c>
       <c r="F79" s="25" t="inlineStr">
         <is>
-          <t>ix_ws_front_p</t>
+          <t>aps</t>
         </is>
       </c>
       <c r="G79" s="26" t="inlineStr">
         <is>
-          <t>FRONT WS INLINE</t>
+          <t>PEDAL</t>
         </is>
       </c>
       <c r="H79" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I79" s="26" t="inlineStr">
         <is>
-          <t>VRC-F +5V</t>
+          <t>Pedal 2 ground</t>
         </is>
       </c>
       <c r="J79" s="26" t="inlineStr"/>
@@ -10355,39 +10339,39 @@
       </c>
       <c r="L79" s="28" t="inlineStr">
         <is>
-          <t>sp_5v</t>
+          <t>sp_gndout</t>
         </is>
       </c>
       <c r="M79" s="29" t="inlineStr">
         <is>
-          <t>splice sp_5v (SP-5V-A: +5 V sensor supply)</t>
+          <t>splice sp_gndout (SP-GNDOUT-A: sensor ground)</t>
         </is>
       </c>
       <c r="N79" s="28" t="inlineStr"/>
       <c r="O79" s="29" t="inlineStr">
         <is>
-          <t>VRC-F +5V</t>
+          <t>Pedal 2 ground</t>
         </is>
       </c>
       <c r="P79" s="29" t="inlineStr"/>
       <c r="Q79" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A32</t>
+          <t>ECU-A.A24</t>
         </is>
       </c>
       <c r="R79" s="31" t="inlineStr">
         <is>
-          <t>+5V sensor (ECU-A A32)</t>
+          <t>Sensor GND (ECU-A A24)</t>
         </is>
       </c>
       <c r="S79" s="32" t="inlineStr">
         <is>
-          <t>sp_5v</t>
+          <t>sp_gndout</t>
         </is>
       </c>
       <c r="T79" s="32" t="inlineStr">
         <is>
-          <t>cab_fspur</t>
+          <t>cab_aps2</t>
         </is>
       </c>
       <c r="U79" s="33" t="n">
@@ -10395,19 +10379,19 @@
       </c>
       <c r="V79" s="34" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W79" s="34" t="inlineStr"/>
       <c r="X79" s="34" t="inlineStr">
         <is>
-          <t>Blue-Blue</t>
+          <t>Yellow-Yellow-Blue</t>
         </is>
       </c>
       <c r="Y79" s="34" t="inlineStr"/>
       <c r="Z79" s="35" t="inlineStr">
         <is>
-          <t>dash branch (front WS inline)</t>
+          <t>pedal branch (driver footwell)</t>
         </is>
       </c>
       <c r="AA79" s="36" t="inlineStr"/>
@@ -10416,7 +10400,7 @@
       <c r="AD79" s="38" t="inlineStr"/>
       <c r="AE79" s="38" t="inlineStr">
         <is>
-          <t>splice sp_5v named in SoT</t>
+          <t>splice sp_gndout: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF79" s="38" t="inlineStr">
@@ -10424,17 +10408,21 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG79" s="38" t="inlineStr"/>
+      <c r="AG79" s="38" t="inlineStr">
+        <is>
+          <t>pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="39" t="inlineStr">
         <is>
-          <t>SGND</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="B80" s="39" t="inlineStr">
         <is>
-          <t>cab_fspur_gnd</t>
+          <t>w_aps_vpa2</t>
         </is>
       </c>
       <c r="C80" s="39" t="inlineStr">
@@ -10442,7 +10430,11 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D80" s="39" t="inlineStr"/>
+      <c r="D80" s="39" t="inlineStr">
+        <is>
+          <t>B-cabin</t>
+        </is>
+      </c>
       <c r="E80" s="40" t="inlineStr">
         <is>
           <t>connector</t>
@@ -10450,63 +10442,67 @@
       </c>
       <c r="F80" s="41" t="inlineStr">
         <is>
-          <t>ix_ws_front_p</t>
+          <t>aps</t>
         </is>
       </c>
       <c r="G80" s="42" t="inlineStr">
         <is>
-          <t>FRONT WS INLINE</t>
+          <t>PEDAL</t>
         </is>
       </c>
       <c r="H80" s="41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I80" s="42" t="inlineStr">
         <is>
-          <t>VRC-F GND</t>
+          <t>Pedal 2 signal sub</t>
         </is>
       </c>
       <c r="J80" s="42" t="inlineStr"/>
       <c r="K80" s="43" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="L80" s="44" t="inlineStr">
         <is>
-          <t>sp_gndout</t>
+          <t>ecu_b</t>
         </is>
       </c>
       <c r="M80" s="45" t="inlineStr">
         <is>
-          <t>splice sp_gndout (SP-GNDOUT-A: sensor ground)</t>
-        </is>
-      </c>
-      <c r="N80" s="44" t="inlineStr"/>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
+        </is>
+      </c>
+      <c r="N80" s="44" t="inlineStr">
+        <is>
+          <t>B33</t>
+        </is>
+      </c>
       <c r="O80" s="45" t="inlineStr">
         <is>
-          <t>VRC-F GND</t>
-        </is>
-      </c>
-      <c r="P80" s="45" t="inlineStr"/>
+          <t>Pedal 2 signal sub</t>
+        </is>
+      </c>
+      <c r="P80" s="45" t="inlineStr">
+        <is>
+          <t>ECU-B plug pin B33 (Link G4X, centre dash); VPA2</t>
+        </is>
+      </c>
       <c r="Q80" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A24</t>
+          <t>ECU-B.B33</t>
         </is>
       </c>
       <c r="R80" s="47" t="inlineStr">
         <is>
-          <t>Sensor GND (ECU-A A24)</t>
-        </is>
-      </c>
-      <c r="S80" s="48" t="inlineStr">
-        <is>
-          <t>sp_gndout</t>
-        </is>
-      </c>
+          <t>Pedal 2 signal sub (ECU-B B33)</t>
+        </is>
+      </c>
+      <c r="S80" s="48" t="inlineStr"/>
       <c r="T80" s="48" t="inlineStr">
         <is>
-          <t>cab_fspur</t>
+          <t>cab_aps2</t>
         </is>
       </c>
       <c r="U80" s="49" t="n">
@@ -10514,19 +10510,21 @@
       </c>
       <c r="V80" s="50" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="W80" s="50" t="inlineStr"/>
       <c r="X80" s="50" t="inlineStr">
         <is>
-          <t>Yellow-Yellow-Blue</t>
-        </is>
-      </c>
-      <c r="Y80" s="50" t="inlineStr"/>
+          <t>White-Blue-Yellow</t>
+        </is>
+      </c>
+      <c r="Y80" s="50" t="n">
+        <v>1720</v>
+      </c>
       <c r="Z80" s="51" t="inlineStr">
         <is>
-          <t>dash branch (front WS inline)</t>
+          <t>pedal branch (driver footwell) / to ECU-B plug (beside ECU-A)</t>
         </is>
       </c>
       <c r="AA80" s="52" t="inlineStr"/>
@@ -10535,7 +10533,7 @@
       <c r="AD80" s="54" t="inlineStr"/>
       <c r="AE80" s="54" t="inlineStr">
         <is>
-          <t>splice sp_gndout named in SoT</t>
+          <t>channels.csv ecu_b B33 An Volt 5 (AV5_APS_SUB)</t>
         </is>
       </c>
       <c r="AF80" s="54" t="inlineStr">
@@ -10543,17 +10541,21 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG80" s="54" t="inlineStr"/>
+      <c r="AG80" s="54" t="inlineStr">
+        <is>
+          <t>pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143); owner proposed: longer half (drawn today as w_aps_vpa2 on A-cabin, 1720 mm; w39 on B-cabin, 1250 mm)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="23" t="inlineStr">
         <is>
-          <t>WSSF</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="B81" s="23" t="inlineStr">
         <is>
-          <t>cab_fspur_l</t>
+          <t>cab_aps_sh</t>
         </is>
       </c>
       <c r="C81" s="23" t="inlineStr">
@@ -10564,90 +10566,84 @@
       <c r="D81" s="23" t="inlineStr"/>
       <c r="E81" s="24" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>cable screen</t>
         </is>
       </c>
       <c r="F81" s="25" t="inlineStr">
         <is>
-          <t>ix_ws_front_p</t>
+          <t>cab_aps2</t>
         </is>
       </c>
       <c r="G81" s="26" t="inlineStr">
         <is>
-          <t>FRONT WS INLINE</t>
-        </is>
-      </c>
-      <c r="H81" s="25" t="n">
-        <v>3</v>
-      </c>
+          <t>cable screen (one end only)</t>
+        </is>
+      </c>
+      <c r="H81" s="25" t="inlineStr"/>
       <c r="I81" s="26" t="inlineStr">
         <is>
-          <t>FL conditioned out</t>
+          <t>Pedal 2 cable shield</t>
         </is>
       </c>
       <c r="J81" s="26" t="inlineStr"/>
       <c r="K81" s="27" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="L81" s="28" t="inlineStr">
         <is>
-          <t>ecu_a</t>
+          <t>sp_shield_a</t>
         </is>
       </c>
       <c r="M81" s="29" t="inlineStr">
         <is>
-          <t>ECU-A</t>
-        </is>
-      </c>
-      <c r="N81" s="28" t="inlineStr">
-        <is>
-          <t>A23</t>
-        </is>
-      </c>
+          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
+        </is>
+      </c>
+      <c r="N81" s="28" t="inlineStr"/>
       <c r="O81" s="29" t="inlineStr">
         <is>
-          <t>FL conditioned out</t>
+          <t>Pedal 2 cable shield</t>
         </is>
       </c>
       <c r="P81" s="29" t="inlineStr"/>
       <c r="Q81" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A23</t>
+          <t>ECU-A.A7</t>
         </is>
       </c>
       <c r="R81" s="31" t="inlineStr">
         <is>
-          <t>FL conditioned out (ECU-A A23)</t>
-        </is>
-      </c>
-      <c r="S81" s="32" t="inlineStr"/>
+          <t>Screen A (ECU A7, SHIELD_A)</t>
+        </is>
+      </c>
+      <c r="S81" s="32" t="inlineStr">
+        <is>
+          <t>sp_shield_a</t>
+        </is>
+      </c>
       <c r="T81" s="32" t="inlineStr">
         <is>
-          <t>cab_fspur</t>
-        </is>
-      </c>
-      <c r="U81" s="33" t="n">
-        <v>20</v>
-      </c>
+          <t>cab_aps2</t>
+        </is>
+      </c>
+      <c r="U81" s="33" t="inlineStr"/>
       <c r="V81" s="34" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Shield</t>
         </is>
       </c>
       <c r="W81" s="34" t="inlineStr"/>
       <c r="X81" s="34" t="inlineStr">
         <is>
-          <t>White-Blue-Blue</t>
-        </is>
-      </c>
-      <c r="Y81" s="34" t="n">
-        <v>330</v>
-      </c>
+          <t>White-Blue-Yellow</t>
+        </is>
+      </c>
+      <c r="Y81" s="34" t="inlineStr"/>
       <c r="Z81" s="35" t="inlineStr">
         <is>
-          <t>dash branch (front WS inline)</t>
+          <t>at ECU-A plug</t>
         </is>
       </c>
       <c r="AA81" s="36" t="inlineStr"/>
@@ -10656,7 +10652,7 @@
       <c r="AD81" s="38" t="inlineStr"/>
       <c r="AE81" s="38" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A23 DI 3 (DI3_WSS_FL)</t>
+          <t>splice sp_shield_a: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF81" s="38" t="inlineStr">
@@ -10664,17 +10660,21 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG81" s="38" t="inlineStr"/>
+      <c r="AG81" s="38" t="inlineStr">
+        <is>
+          <t>screen floats at the far end; pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="39" t="inlineStr">
         <is>
-          <t>WSSF</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="B82" s="39" t="inlineStr">
         <is>
-          <t>cab_fspur_sh</t>
+          <t>cab_fspur_5v</t>
         </is>
       </c>
       <c r="C82" s="39" t="inlineStr">
@@ -10699,11 +10699,11 @@
         </is>
       </c>
       <c r="H82" s="41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I82" s="42" t="inlineStr">
         <is>
-          <t>WS-F screen drain</t>
+          <t>VRC-F +5V</t>
         </is>
       </c>
       <c r="J82" s="42" t="inlineStr"/>
@@ -10714,34 +10714,34 @@
       </c>
       <c r="L82" s="44" t="inlineStr">
         <is>
-          <t>sp_shield_a</t>
+          <t>sp_5v</t>
         </is>
       </c>
       <c r="M82" s="45" t="inlineStr">
         <is>
-          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
+          <t>splice sp_5v (SP-5V-A: +5 V sensor supply)</t>
         </is>
       </c>
       <c r="N82" s="44" t="inlineStr"/>
       <c r="O82" s="45" t="inlineStr">
         <is>
-          <t>WS-F screen drain</t>
+          <t>VRC-F +5V</t>
         </is>
       </c>
       <c r="P82" s="45" t="inlineStr"/>
       <c r="Q82" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A7</t>
+          <t>ECU-A.A32</t>
         </is>
       </c>
       <c r="R82" s="47" t="inlineStr">
         <is>
-          <t>Screen A (ECU A7, SHIELD_A)</t>
+          <t>+5V sensor (ECU-A A32)</t>
         </is>
       </c>
       <c r="S82" s="48" t="inlineStr">
         <is>
-          <t>sp_shield_a</t>
+          <t>sp_5v</t>
         </is>
       </c>
       <c r="T82" s="48" t="inlineStr">
@@ -10749,16 +10749,18 @@
           <t>cab_fspur</t>
         </is>
       </c>
-      <c r="U82" s="49" t="inlineStr"/>
+      <c r="U82" s="49" t="n">
+        <v>20</v>
+      </c>
       <c r="V82" s="50" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W82" s="50" t="inlineStr"/>
       <c r="X82" s="50" t="inlineStr">
         <is>
-          <t>White-Blue-Blue</t>
+          <t>Blue-Blue</t>
         </is>
       </c>
       <c r="Y82" s="50" t="inlineStr"/>
@@ -10773,7 +10775,7 @@
       <c r="AD82" s="54" t="inlineStr"/>
       <c r="AE82" s="54" t="inlineStr">
         <is>
-          <t>splice sp_shield_a named in SoT</t>
+          <t>splice sp_5v: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF82" s="54" t="inlineStr">
@@ -10786,12 +10788,12 @@
     <row r="83">
       <c r="A83" s="23" t="inlineStr">
         <is>
-          <t>WSSF</t>
+          <t>SGND</t>
         </is>
       </c>
       <c r="B83" s="23" t="inlineStr">
         <is>
-          <t>cab_fspur_fr_sh_ac</t>
+          <t>cab_fspur_gnd</t>
         </is>
       </c>
       <c r="C83" s="23" t="inlineStr">
@@ -10799,30 +10801,28 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D83" s="23" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
+      <c r="D83" s="23" t="inlineStr"/>
       <c r="E83" s="24" t="inlineStr">
         <is>
-          <t>cable screen</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="F83" s="25" t="inlineStr">
         <is>
-          <t>cab_fspur_fr_ac</t>
+          <t>ix_ws_front_p</t>
         </is>
       </c>
       <c r="G83" s="26" t="inlineStr">
         <is>
-          <t>cable screen (one end only)</t>
-        </is>
-      </c>
-      <c r="H83" s="25" t="inlineStr"/>
+          <t>FRONT WS INLINE</t>
+        </is>
+      </c>
+      <c r="H83" s="25" t="n">
+        <v>2</v>
+      </c>
       <c r="I83" s="26" t="inlineStr">
         <is>
-          <t>FR wheel spd shield</t>
+          <t>VRC-F GND</t>
         </is>
       </c>
       <c r="J83" s="26" t="inlineStr"/>
@@ -10833,51 +10833,53 @@
       </c>
       <c r="L83" s="28" t="inlineStr">
         <is>
-          <t>sp_shield_b</t>
+          <t>sp_gndout</t>
         </is>
       </c>
       <c r="M83" s="29" t="inlineStr">
         <is>
-          <t>splice sp_shield_b on B-cabin</t>
+          <t>splice sp_gndout (SP-GNDOUT-A: sensor ground)</t>
         </is>
       </c>
       <c r="N83" s="28" t="inlineStr"/>
       <c r="O83" s="29" t="inlineStr">
         <is>
-          <t>FR wheel spd shield</t>
-        </is>
-      </c>
-      <c r="P83" s="29" t="inlineStr">
-        <is>
-          <t>at the ECU-B plug (B-cabin); to ECU-B B17</t>
-        </is>
-      </c>
+          <t>VRC-F GND</t>
+        </is>
+      </c>
+      <c r="P83" s="29" t="inlineStr"/>
       <c r="Q83" s="30" t="inlineStr">
         <is>
-          <t>ECU-B.B17</t>
+          <t>ECU-A.A24</t>
         </is>
       </c>
       <c r="R83" s="31" t="inlineStr">
         <is>
-          <t>Screen B (ECU B17, SHIELD_B)</t>
-        </is>
-      </c>
-      <c r="S83" s="32" t="inlineStr"/>
+          <t>Sensor GND (ECU-A A24)</t>
+        </is>
+      </c>
+      <c r="S83" s="32" t="inlineStr">
+        <is>
+          <t>sp_gndout</t>
+        </is>
+      </c>
       <c r="T83" s="32" t="inlineStr">
         <is>
-          <t>cab_fspur_fr_ac</t>
-        </is>
-      </c>
-      <c r="U83" s="33" t="inlineStr"/>
+          <t>cab_fspur</t>
+        </is>
+      </c>
+      <c r="U83" s="33" t="n">
+        <v>20</v>
+      </c>
       <c r="V83" s="34" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W83" s="34" t="inlineStr"/>
       <c r="X83" s="34" t="inlineStr">
         <is>
-          <t>White-Blue-Blue</t>
+          <t>Yellow-Yellow-Blue</t>
         </is>
       </c>
       <c r="Y83" s="34" t="inlineStr"/>
@@ -10892,7 +10894,7 @@
       <c r="AD83" s="38" t="inlineStr"/>
       <c r="AE83" s="38" t="inlineStr">
         <is>
-          <t>splice sp_shield_b named in SoT</t>
+          <t>splice sp_gndout: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF83" s="38" t="inlineStr">
@@ -10900,15 +10902,19 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG83" s="38" t="inlineStr">
-        <is>
-          <t>screen floats at the far end; owner TBD: a half has no length estimate (drawn today as cab_fspur_fr_sh_ac on A-cabin, ? mm; cab_fspur_fr_sh on B-cabin, ? mm)</t>
-        </is>
-      </c>
+      <c r="AG83" s="38" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="39" t="inlineStr"/>
-      <c r="B84" s="39" t="inlineStr"/>
+      <c r="A84" s="39" t="inlineStr">
+        <is>
+          <t>WSSF</t>
+        </is>
+      </c>
+      <c r="B84" s="39" t="inlineStr">
+        <is>
+          <t>cab_fspur_l</t>
+        </is>
+      </c>
       <c r="C84" s="39" t="inlineStr">
         <is>
           <t>A-cabin</t>
@@ -10922,54 +10928,94 @@
       </c>
       <c r="F84" s="41" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>ix_ws_front_p</t>
         </is>
       </c>
       <c r="G84" s="42" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>FRONT WS INLINE</t>
         </is>
       </c>
       <c r="H84" s="41" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="I84" s="42" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>FL conditioned out</t>
         </is>
       </c>
       <c r="J84" s="42" t="inlineStr"/>
-      <c r="K84" s="43" t="inlineStr"/>
-      <c r="L84" s="44" t="inlineStr"/>
-      <c r="M84" s="45" t="inlineStr"/>
-      <c r="N84" s="44" t="inlineStr"/>
-      <c r="O84" s="45" t="inlineStr"/>
+      <c r="K84" s="43" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="L84" s="44" t="inlineStr">
+        <is>
+          <t>ecu_a</t>
+        </is>
+      </c>
+      <c r="M84" s="45" t="inlineStr">
+        <is>
+          <t>ECU-A</t>
+        </is>
+      </c>
+      <c r="N84" s="44" t="inlineStr">
+        <is>
+          <t>A23</t>
+        </is>
+      </c>
+      <c r="O84" s="45" t="inlineStr">
+        <is>
+          <t>FL conditioned out</t>
+        </is>
+      </c>
       <c r="P84" s="45" t="inlineStr"/>
       <c r="Q84" s="46" t="inlineStr">
         <is>
-          <t>DRB102.45</t>
+          <t>ECU-A.A23</t>
         </is>
       </c>
       <c r="R84" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 45)</t>
+          <t>FL conditioned out (ECU-A A23)</t>
         </is>
       </c>
       <c r="S84" s="48" t="inlineStr"/>
-      <c r="T84" s="48" t="inlineStr"/>
-      <c r="U84" s="49" t="inlineStr"/>
-      <c r="V84" s="50" t="inlineStr"/>
+      <c r="T84" s="48" t="inlineStr">
+        <is>
+          <t>cab_fspur</t>
+        </is>
+      </c>
+      <c r="U84" s="49" t="n">
+        <v>20</v>
+      </c>
+      <c r="V84" s="50" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
       <c r="W84" s="50" t="inlineStr"/>
-      <c r="X84" s="50" t="inlineStr"/>
-      <c r="Y84" s="50" t="inlineStr"/>
-      <c r="Z84" s="51" t="inlineStr"/>
+      <c r="X84" s="50" t="inlineStr">
+        <is>
+          <t>White-Blue-Blue</t>
+        </is>
+      </c>
+      <c r="Y84" s="50" t="n">
+        <v>330</v>
+      </c>
+      <c r="Z84" s="51" t="inlineStr">
+        <is>
+          <t>dash branch (front WS inline)</t>
+        </is>
+      </c>
       <c r="AA84" s="52" t="inlineStr"/>
       <c r="AB84" s="53" t="inlineStr"/>
       <c r="AC84" s="54" t="inlineStr"/>
       <c r="AD84" s="54" t="inlineStr"/>
       <c r="AE84" s="54" t="inlineStr">
         <is>
-          <t>DRB102 45 = 'spare (size 16) - was the A/C coolant switch signal, deleted (S35)'</t>
+          <t>channels.csv ecu_a A23 DI 3 (DI3_WSS_FL)</t>
         </is>
       </c>
       <c r="AF84" s="54" t="inlineStr">
@@ -10980,8 +11026,16 @@
       <c r="AG84" s="54" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="23" t="inlineStr"/>
-      <c r="B85" s="23" t="inlineStr"/>
+      <c r="A85" s="23" t="inlineStr">
+        <is>
+          <t>WSSF</t>
+        </is>
+      </c>
+      <c r="B85" s="23" t="inlineStr">
+        <is>
+          <t>cab_fspur_sh</t>
+        </is>
+      </c>
       <c r="C85" s="23" t="inlineStr">
         <is>
           <t>A-cabin</t>
@@ -10995,54 +11049,90 @@
       </c>
       <c r="F85" s="25" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>ix_ws_front_p</t>
         </is>
       </c>
       <c r="G85" s="26" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>FRONT WS INLINE</t>
         </is>
       </c>
       <c r="H85" s="25" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="I85" s="26" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>WS-F screen drain</t>
         </is>
       </c>
       <c r="J85" s="26" t="inlineStr"/>
-      <c r="K85" s="27" t="inlineStr"/>
-      <c r="L85" s="28" t="inlineStr"/>
-      <c r="M85" s="29" t="inlineStr"/>
+      <c r="K85" s="27" t="inlineStr">
+        <is>
+          <t>splice</t>
+        </is>
+      </c>
+      <c r="L85" s="28" t="inlineStr">
+        <is>
+          <t>sp_shield_a</t>
+        </is>
+      </c>
+      <c r="M85" s="29" t="inlineStr">
+        <is>
+          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
+        </is>
+      </c>
       <c r="N85" s="28" t="inlineStr"/>
-      <c r="O85" s="29" t="inlineStr"/>
+      <c r="O85" s="29" t="inlineStr">
+        <is>
+          <t>WS-F screen drain</t>
+        </is>
+      </c>
       <c r="P85" s="29" t="inlineStr"/>
       <c r="Q85" s="30" t="inlineStr">
         <is>
-          <t>DRB102.46</t>
+          <t>ECU-A.A7</t>
         </is>
       </c>
       <c r="R85" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 46)</t>
-        </is>
-      </c>
-      <c r="S85" s="32" t="inlineStr"/>
-      <c r="T85" s="32" t="inlineStr"/>
+          <t>Screen A (ECU A7, SHIELD_A)</t>
+        </is>
+      </c>
+      <c r="S85" s="32" t="inlineStr">
+        <is>
+          <t>sp_shield_a</t>
+        </is>
+      </c>
+      <c r="T85" s="32" t="inlineStr">
+        <is>
+          <t>cab_fspur</t>
+        </is>
+      </c>
       <c r="U85" s="33" t="inlineStr"/>
-      <c r="V85" s="34" t="inlineStr"/>
+      <c r="V85" s="34" t="inlineStr">
+        <is>
+          <t>Shield</t>
+        </is>
+      </c>
       <c r="W85" s="34" t="inlineStr"/>
-      <c r="X85" s="34" t="inlineStr"/>
+      <c r="X85" s="34" t="inlineStr">
+        <is>
+          <t>White-Blue-Blue</t>
+        </is>
+      </c>
       <c r="Y85" s="34" t="inlineStr"/>
-      <c r="Z85" s="35" t="inlineStr"/>
+      <c r="Z85" s="35" t="inlineStr">
+        <is>
+          <t>dash branch (front WS inline)</t>
+        </is>
+      </c>
       <c r="AA85" s="36" t="inlineStr"/>
       <c r="AB85" s="37" t="inlineStr"/>
       <c r="AC85" s="38" t="inlineStr"/>
       <c r="AD85" s="38" t="inlineStr"/>
       <c r="AE85" s="38" t="inlineStr">
         <is>
-          <t>DRB102 46 = 'spare (size 16) - was the A/C coolant switch return, deleted (S35)'</t>
+          <t>splice sp_shield_a: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF85" s="38" t="inlineStr">
@@ -11053,69 +11143,115 @@
       <c r="AG85" s="38" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="39" t="inlineStr"/>
-      <c r="B86" s="39" t="inlineStr"/>
+      <c r="A86" s="39" t="inlineStr">
+        <is>
+          <t>WSSF</t>
+        </is>
+      </c>
+      <c r="B86" s="39" t="inlineStr">
+        <is>
+          <t>cab_fspur_fr_sh_ac</t>
+        </is>
+      </c>
       <c r="C86" s="39" t="inlineStr">
         <is>
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D86" s="39" t="inlineStr"/>
+      <c r="D86" s="39" t="inlineStr">
+        <is>
+          <t>B-cabin</t>
+        </is>
+      </c>
       <c r="E86" s="40" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>cable screen</t>
         </is>
       </c>
       <c r="F86" s="41" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>cab_fspur_fr_ac</t>
         </is>
       </c>
       <c r="G86" s="42" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
-        </is>
-      </c>
-      <c r="H86" s="41" t="n">
-        <v>52</v>
-      </c>
+          <t>cable screen (one end only)</t>
+        </is>
+      </c>
+      <c r="H86" s="41" t="inlineStr"/>
       <c r="I86" s="42" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>FR wheel spd shield</t>
         </is>
       </c>
       <c r="J86" s="42" t="inlineStr"/>
-      <c r="K86" s="43" t="inlineStr"/>
-      <c r="L86" s="44" t="inlineStr"/>
-      <c r="M86" s="45" t="inlineStr"/>
+      <c r="K86" s="43" t="inlineStr">
+        <is>
+          <t>splice</t>
+        </is>
+      </c>
+      <c r="L86" s="44" t="inlineStr">
+        <is>
+          <t>sp_shield_b</t>
+        </is>
+      </c>
+      <c r="M86" s="45" t="inlineStr">
+        <is>
+          <t>splice sp_shield_b on B-cabin</t>
+        </is>
+      </c>
       <c r="N86" s="44" t="inlineStr"/>
-      <c r="O86" s="45" t="inlineStr"/>
-      <c r="P86" s="45" t="inlineStr"/>
+      <c r="O86" s="45" t="inlineStr">
+        <is>
+          <t>FR wheel spd shield</t>
+        </is>
+      </c>
+      <c r="P86" s="45" t="inlineStr">
+        <is>
+          <t>at the ECU-B plug (B-cabin); to ECU-B B17</t>
+        </is>
+      </c>
       <c r="Q86" s="46" t="inlineStr">
         <is>
-          <t>DRB102.52</t>
+          <t>ECU-B.B17</t>
         </is>
       </c>
       <c r="R86" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 52)</t>
+          <t>Screen B (ECU B17, SHIELD_B)</t>
         </is>
       </c>
       <c r="S86" s="48" t="inlineStr"/>
-      <c r="T86" s="48" t="inlineStr"/>
+      <c r="T86" s="48" t="inlineStr">
+        <is>
+          <t>cab_fspur_fr_ac</t>
+        </is>
+      </c>
       <c r="U86" s="49" t="inlineStr"/>
-      <c r="V86" s="50" t="inlineStr"/>
+      <c r="V86" s="50" t="inlineStr">
+        <is>
+          <t>Shield</t>
+        </is>
+      </c>
       <c r="W86" s="50" t="inlineStr"/>
-      <c r="X86" s="50" t="inlineStr"/>
+      <c r="X86" s="50" t="inlineStr">
+        <is>
+          <t>White-Blue-Blue</t>
+        </is>
+      </c>
       <c r="Y86" s="50" t="inlineStr"/>
-      <c r="Z86" s="51" t="inlineStr"/>
+      <c r="Z86" s="51" t="inlineStr">
+        <is>
+          <t>dash branch (front WS inline)</t>
+        </is>
+      </c>
       <c r="AA86" s="52" t="inlineStr"/>
       <c r="AB86" s="53" t="inlineStr"/>
       <c r="AC86" s="54" t="inlineStr"/>
       <c r="AD86" s="54" t="inlineStr"/>
       <c r="AE86" s="54" t="inlineStr">
         <is>
-          <t>DRB102 52 = 'spare (size 16)'</t>
+          <t>splice sp_shield_b: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF86" s="54" t="inlineStr">
@@ -11123,7 +11259,11 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG86" s="54" t="inlineStr"/>
+      <c r="AG86" s="54" t="inlineStr">
+        <is>
+          <t>screen floats at the far end; owner TBD: a half has no length estimate (drawn today as cab_fspur_fr_sh_ac on A-cabin, ? mm; cab_fspur_fr_sh on B-cabin, ? mm)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="23" t="inlineStr"/>
@@ -11150,7 +11290,7 @@
         </is>
       </c>
       <c r="H87" s="25" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="I87" s="26" t="inlineStr">
         <is>
@@ -11166,12 +11306,12 @@
       <c r="P87" s="29" t="inlineStr"/>
       <c r="Q87" s="30" t="inlineStr">
         <is>
-          <t>DRB102.53</t>
+          <t>DRB102.45</t>
         </is>
       </c>
       <c r="R87" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 53)</t>
+          <t>spare (DRB102 45)</t>
         </is>
       </c>
       <c r="S87" s="32" t="inlineStr"/>
@@ -11188,7 +11328,7 @@
       <c r="AD87" s="38" t="inlineStr"/>
       <c r="AE87" s="38" t="inlineStr">
         <is>
-          <t>DRB102 53 = 'spare (size 16)'</t>
+          <t>DRB102 45 = 'spare (size 16) - was the A/C coolant switch signal, deleted (S35)'</t>
         </is>
       </c>
       <c r="AF87" s="38" t="inlineStr">
@@ -11223,7 +11363,7 @@
         </is>
       </c>
       <c r="H88" s="41" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="I88" s="42" t="inlineStr">
         <is>
@@ -11239,12 +11379,12 @@
       <c r="P88" s="45" t="inlineStr"/>
       <c r="Q88" s="46" t="inlineStr">
         <is>
-          <t>DRB102.57</t>
+          <t>DRB102.46</t>
         </is>
       </c>
       <c r="R88" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 57)</t>
+          <t>spare (DRB102 46)</t>
         </is>
       </c>
       <c r="S88" s="48" t="inlineStr"/>
@@ -11261,7 +11401,7 @@
       <c r="AD88" s="54" t="inlineStr"/>
       <c r="AE88" s="54" t="inlineStr">
         <is>
-          <t>DRB102 57 = 'spare (size 16)'</t>
+          <t>DRB102 46 = 'spare (size 16) - was the A/C coolant switch return, deleted (S35)'</t>
         </is>
       </c>
       <c r="AF88" s="54" t="inlineStr">
@@ -11296,7 +11436,7 @@
         </is>
       </c>
       <c r="H89" s="25" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="I89" s="26" t="inlineStr">
         <is>
@@ -11312,12 +11452,12 @@
       <c r="P89" s="29" t="inlineStr"/>
       <c r="Q89" s="30" t="inlineStr">
         <is>
-          <t>DRB102.58</t>
+          <t>DRB102.52</t>
         </is>
       </c>
       <c r="R89" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 58)</t>
+          <t>spare (DRB102 52)</t>
         </is>
       </c>
       <c r="S89" s="32" t="inlineStr"/>
@@ -11334,7 +11474,7 @@
       <c r="AD89" s="38" t="inlineStr"/>
       <c r="AE89" s="38" t="inlineStr">
         <is>
-          <t>DRB102 58 = 'spare (size 16)'</t>
+          <t>DRB102 52 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF89" s="38" t="inlineStr">
@@ -11369,7 +11509,7 @@
         </is>
       </c>
       <c r="H90" s="41" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="I90" s="42" t="inlineStr">
         <is>
@@ -11385,12 +11525,12 @@
       <c r="P90" s="45" t="inlineStr"/>
       <c r="Q90" s="46" t="inlineStr">
         <is>
-          <t>DRB102.59</t>
+          <t>DRB102.53</t>
         </is>
       </c>
       <c r="R90" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 59)</t>
+          <t>spare (DRB102 53)</t>
         </is>
       </c>
       <c r="S90" s="48" t="inlineStr"/>
@@ -11407,7 +11547,7 @@
       <c r="AD90" s="54" t="inlineStr"/>
       <c r="AE90" s="54" t="inlineStr">
         <is>
-          <t>DRB102 59 = 'spare (size 16)'</t>
+          <t>DRB102 53 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF90" s="54" t="inlineStr">
@@ -11442,7 +11582,7 @@
         </is>
       </c>
       <c r="H91" s="25" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I91" s="26" t="inlineStr">
         <is>
@@ -11458,12 +11598,12 @@
       <c r="P91" s="29" t="inlineStr"/>
       <c r="Q91" s="30" t="inlineStr">
         <is>
-          <t>DRB102.61</t>
+          <t>DRB102.57</t>
         </is>
       </c>
       <c r="R91" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 61)</t>
+          <t>spare (DRB102 57)</t>
         </is>
       </c>
       <c r="S91" s="32" t="inlineStr"/>
@@ -11480,7 +11620,7 @@
       <c r="AD91" s="38" t="inlineStr"/>
       <c r="AE91" s="38" t="inlineStr">
         <is>
-          <t>DRB102 61 = 'spare (size 16)'</t>
+          <t>DRB102 57 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF91" s="38" t="inlineStr">
@@ -11506,16 +11646,16 @@
       </c>
       <c r="F92" s="41" t="inlineStr">
         <is>
-          <t>ix_ws_front_p</t>
+          <t>bh_a_fw</t>
         </is>
       </c>
       <c r="G92" s="42" t="inlineStr">
         <is>
-          <t>FRONT WS INLINE</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="H92" s="41" t="n">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="I92" s="42" t="inlineStr">
         <is>
@@ -11531,12 +11671,12 @@
       <c r="P92" s="45" t="inlineStr"/>
       <c r="Q92" s="46" t="inlineStr">
         <is>
-          <t>ix_ws_front_p.6</t>
+          <t>DRB102.58</t>
         </is>
       </c>
       <c r="R92" s="47" t="inlineStr">
         <is>
-          <t>spare (ix_ws_front_p 6)</t>
+          <t>spare (DRB102 58)</t>
         </is>
       </c>
       <c r="S92" s="48" t="inlineStr"/>
@@ -11551,7 +11691,11 @@
       <c r="AB92" s="53" t="inlineStr"/>
       <c r="AC92" s="54" t="inlineStr"/>
       <c r="AD92" s="54" t="inlineStr"/>
-      <c r="AE92" s="54" t="inlineStr"/>
+      <c r="AE92" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 58 = 'spare (size 16)'</t>
+        </is>
+      </c>
       <c r="AF92" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11575,16 +11719,16 @@
       </c>
       <c r="F93" s="25" t="inlineStr">
         <is>
-          <t>bus_5v_bha_p</t>
+          <t>bh_a_fw</t>
         </is>
       </c>
       <c r="G93" s="26" t="inlineStr">
         <is>
-          <t>+5V BUS</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="H93" s="25" t="n">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="I93" s="26" t="inlineStr">
         <is>
@@ -11600,12 +11744,12 @@
       <c r="P93" s="29" t="inlineStr"/>
       <c r="Q93" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A32</t>
+          <t>DRB102.59</t>
         </is>
       </c>
       <c r="R93" s="31" t="inlineStr">
         <is>
-          <t>+5V sensor (ECU-A A32)</t>
+          <t>spare (DRB102 59)</t>
         </is>
       </c>
       <c r="S93" s="32" t="inlineStr"/>
@@ -11620,7 +11764,11 @@
       <c r="AB93" s="37" t="inlineStr"/>
       <c r="AC93" s="38" t="inlineStr"/>
       <c r="AD93" s="38" t="inlineStr"/>
-      <c r="AE93" s="38" t="inlineStr"/>
+      <c r="AE93" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 59 = 'spare (size 16)'</t>
+        </is>
+      </c>
       <c r="AF93" s="38" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11644,16 +11792,16 @@
       </c>
       <c r="F94" s="41" t="inlineStr">
         <is>
-          <t>bus_gnd_bha_p</t>
+          <t>bh_a_fw</t>
         </is>
       </c>
       <c r="G94" s="42" t="inlineStr">
         <is>
-          <t>SENSOR GND BUS</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="H94" s="41" t="n">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="I94" s="42" t="inlineStr">
         <is>
@@ -11669,12 +11817,12 @@
       <c r="P94" s="45" t="inlineStr"/>
       <c r="Q94" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A24</t>
+          <t>DRB102.61</t>
         </is>
       </c>
       <c r="R94" s="47" t="inlineStr">
         <is>
-          <t>Sensor GND (ECU-A A24)</t>
+          <t>spare (DRB102 61)</t>
         </is>
       </c>
       <c r="S94" s="48" t="inlineStr"/>
@@ -11689,7 +11837,11 @@
       <c r="AB94" s="53" t="inlineStr"/>
       <c r="AC94" s="54" t="inlineStr"/>
       <c r="AD94" s="54" t="inlineStr"/>
-      <c r="AE94" s="54" t="inlineStr"/>
+      <c r="AE94" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 61 = 'spare (size 16)'</t>
+        </is>
+      </c>
       <c r="AF94" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11713,16 +11865,16 @@
       </c>
       <c r="F95" s="25" t="inlineStr">
         <is>
-          <t>bus_gnd_bha_p</t>
+          <t>ix_ws_front_p</t>
         </is>
       </c>
       <c r="G95" s="26" t="inlineStr">
         <is>
-          <t>SENSOR GND BUS</t>
+          <t>FRONT WS INLINE</t>
         </is>
       </c>
       <c r="H95" s="25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I95" s="26" t="inlineStr">
         <is>
@@ -11738,12 +11890,12 @@
       <c r="P95" s="29" t="inlineStr"/>
       <c r="Q95" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A24</t>
+          <t>ix_ws_front_p.6</t>
         </is>
       </c>
       <c r="R95" s="31" t="inlineStr">
         <is>
-          <t>Sensor GND (ECU-A A24)</t>
+          <t>spare (ix_ws_front_p 6)</t>
         </is>
       </c>
       <c r="S95" s="32" t="inlineStr"/>
@@ -11766,8 +11918,215 @@
       </c>
       <c r="AG95" s="38" t="inlineStr"/>
     </row>
+    <row r="96">
+      <c r="A96" s="39" t="inlineStr"/>
+      <c r="B96" s="39" t="inlineStr"/>
+      <c r="C96" s="39" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D96" s="39" t="inlineStr"/>
+      <c r="E96" s="40" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F96" s="41" t="inlineStr">
+        <is>
+          <t>bus_5v_bha_p</t>
+        </is>
+      </c>
+      <c r="G96" s="42" t="inlineStr">
+        <is>
+          <t>+5V BUS</t>
+        </is>
+      </c>
+      <c r="H96" s="41" t="n">
+        <v>8</v>
+      </c>
+      <c r="I96" s="42" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J96" s="42" t="inlineStr"/>
+      <c r="K96" s="43" t="inlineStr"/>
+      <c r="L96" s="44" t="inlineStr"/>
+      <c r="M96" s="45" t="inlineStr"/>
+      <c r="N96" s="44" t="inlineStr"/>
+      <c r="O96" s="45" t="inlineStr"/>
+      <c r="P96" s="45" t="inlineStr"/>
+      <c r="Q96" s="46" t="inlineStr">
+        <is>
+          <t>ECU-A.A32</t>
+        </is>
+      </c>
+      <c r="R96" s="47" t="inlineStr">
+        <is>
+          <t>+5V sensor (ECU-A A32)</t>
+        </is>
+      </c>
+      <c r="S96" s="48" t="inlineStr"/>
+      <c r="T96" s="48" t="inlineStr"/>
+      <c r="U96" s="49" t="inlineStr"/>
+      <c r="V96" s="50" t="inlineStr"/>
+      <c r="W96" s="50" t="inlineStr"/>
+      <c r="X96" s="50" t="inlineStr"/>
+      <c r="Y96" s="50" t="inlineStr"/>
+      <c r="Z96" s="51" t="inlineStr"/>
+      <c r="AA96" s="52" t="inlineStr"/>
+      <c r="AB96" s="53" t="inlineStr"/>
+      <c r="AC96" s="54" t="inlineStr"/>
+      <c r="AD96" s="54" t="inlineStr"/>
+      <c r="AE96" s="54" t="inlineStr"/>
+      <c r="AF96" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG96" s="54" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="23" t="inlineStr"/>
+      <c r="B97" s="23" t="inlineStr"/>
+      <c r="C97" s="23" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D97" s="23" t="inlineStr"/>
+      <c r="E97" s="24" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F97" s="25" t="inlineStr">
+        <is>
+          <t>bus_gnd_bha_p</t>
+        </is>
+      </c>
+      <c r="G97" s="26" t="inlineStr">
+        <is>
+          <t>SENSOR GND BUS</t>
+        </is>
+      </c>
+      <c r="H97" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="I97" s="26" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J97" s="26" t="inlineStr"/>
+      <c r="K97" s="27" t="inlineStr"/>
+      <c r="L97" s="28" t="inlineStr"/>
+      <c r="M97" s="29" t="inlineStr"/>
+      <c r="N97" s="28" t="inlineStr"/>
+      <c r="O97" s="29" t="inlineStr"/>
+      <c r="P97" s="29" t="inlineStr"/>
+      <c r="Q97" s="30" t="inlineStr">
+        <is>
+          <t>ECU-A.A24</t>
+        </is>
+      </c>
+      <c r="R97" s="31" t="inlineStr">
+        <is>
+          <t>Sensor GND (ECU-A A24)</t>
+        </is>
+      </c>
+      <c r="S97" s="32" t="inlineStr"/>
+      <c r="T97" s="32" t="inlineStr"/>
+      <c r="U97" s="33" t="inlineStr"/>
+      <c r="V97" s="34" t="inlineStr"/>
+      <c r="W97" s="34" t="inlineStr"/>
+      <c r="X97" s="34" t="inlineStr"/>
+      <c r="Y97" s="34" t="inlineStr"/>
+      <c r="Z97" s="35" t="inlineStr"/>
+      <c r="AA97" s="36" t="inlineStr"/>
+      <c r="AB97" s="37" t="inlineStr"/>
+      <c r="AC97" s="38" t="inlineStr"/>
+      <c r="AD97" s="38" t="inlineStr"/>
+      <c r="AE97" s="38" t="inlineStr"/>
+      <c r="AF97" s="38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG97" s="38" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="39" t="inlineStr"/>
+      <c r="B98" s="39" t="inlineStr"/>
+      <c r="C98" s="39" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D98" s="39" t="inlineStr"/>
+      <c r="E98" s="40" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F98" s="41" t="inlineStr">
+        <is>
+          <t>bus_gnd_bha_p</t>
+        </is>
+      </c>
+      <c r="G98" s="42" t="inlineStr">
+        <is>
+          <t>SENSOR GND BUS</t>
+        </is>
+      </c>
+      <c r="H98" s="41" t="n">
+        <v>8</v>
+      </c>
+      <c r="I98" s="42" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J98" s="42" t="inlineStr"/>
+      <c r="K98" s="43" t="inlineStr"/>
+      <c r="L98" s="44" t="inlineStr"/>
+      <c r="M98" s="45" t="inlineStr"/>
+      <c r="N98" s="44" t="inlineStr"/>
+      <c r="O98" s="45" t="inlineStr"/>
+      <c r="P98" s="45" t="inlineStr"/>
+      <c r="Q98" s="46" t="inlineStr">
+        <is>
+          <t>ECU-A.A24</t>
+        </is>
+      </c>
+      <c r="R98" s="47" t="inlineStr">
+        <is>
+          <t>Sensor GND (ECU-A A24)</t>
+        </is>
+      </c>
+      <c r="S98" s="48" t="inlineStr"/>
+      <c r="T98" s="48" t="inlineStr"/>
+      <c r="U98" s="49" t="inlineStr"/>
+      <c r="V98" s="50" t="inlineStr"/>
+      <c r="W98" s="50" t="inlineStr"/>
+      <c r="X98" s="50" t="inlineStr"/>
+      <c r="Y98" s="50" t="inlineStr"/>
+      <c r="Z98" s="51" t="inlineStr"/>
+      <c r="AA98" s="52" t="inlineStr"/>
+      <c r="AB98" s="53" t="inlineStr"/>
+      <c r="AC98" s="54" t="inlineStr"/>
+      <c r="AD98" s="54" t="inlineStr"/>
+      <c r="AE98" s="54" t="inlineStr"/>
+      <c r="AF98" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG98" s="54" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AG95"/>
+  <autoFilter ref="A2:AG98"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -11779,7 +12138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11972,7 +12331,7 @@
       </c>
       <c r="L3" s="38" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12387,7 @@
       </c>
       <c r="L4" s="54" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -12084,7 +12443,7 @@
       </c>
       <c r="L5" s="38" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -12140,7 +12499,7 @@
       </c>
       <c r="L6" s="54" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -12196,7 +12555,7 @@
       </c>
       <c r="L7" s="38" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -12252,7 +12611,7 @@
       </c>
       <c r="L8" s="54" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -12308,7 +12667,7 @@
       </c>
       <c r="L9" s="38" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -12364,7 +12723,7 @@
       </c>
       <c r="L10" s="54" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -12420,12 +12779,68 @@
       </c>
       <c r="L11" s="38" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="39" t="inlineStr">
+        <is>
+          <t>sp_a5</t>
+        </is>
+      </c>
+      <c r="B12" s="57" t="inlineStr">
+        <is>
+          <t>At ECU-A plug - SP-A5: ECU main feed (SW12 + IG2 diode)</t>
+        </is>
+      </c>
+      <c r="C12" s="39" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D12" s="46" t="inlineStr">
+        <is>
+          <t>LOGIC.BUS2-2</t>
+        </is>
+      </c>
+      <c r="E12" s="47" t="inlineStr">
+        <is>
+          <t>+12V switched (LOGIC SW12 bus)</t>
+        </is>
+      </c>
+      <c r="F12" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="48" t="inlineStr">
+        <is>
+          <t>18+20+18</t>
+        </is>
+      </c>
+      <c r="H12" s="48" t="n">
+        <v>4270</v>
+      </c>
+      <c r="I12" s="48" t="n">
+        <v>12</v>
+      </c>
+      <c r="J12" s="58" t="inlineStr">
+        <is>
+          <t>SPLICE, SOLDERED, ADHESIVE HEATSHRINK OVER</t>
+        </is>
+      </c>
+      <c r="K12" s="52" t="inlineStr">
+        <is>
+          <t>At ECU-A plug (layout node b_bp_1080)</t>
+        </is>
+      </c>
+      <c r="L12" s="54" t="inlineStr">
+        <is>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:L11"/>
+  <autoFilter ref="A2:L12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/harness/wirelist/A-cabin-wirelist.xlsx
+++ b/docs/harness/wirelist/A-cabin-wirelist.xlsx
@@ -11158,11 +11158,7 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D86" s="39" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
+      <c r="D86" s="39" t="inlineStr"/>
       <c r="E86" s="40" t="inlineStr">
         <is>
           <t>cable screen</t>
@@ -11192,12 +11188,12 @@
       </c>
       <c r="L86" s="44" t="inlineStr">
         <is>
-          <t>sp_shield_b</t>
+          <t>sp_shield_a</t>
         </is>
       </c>
       <c r="M86" s="45" t="inlineStr">
         <is>
-          <t>splice sp_shield_b on B-cabin</t>
+          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
         </is>
       </c>
       <c r="N86" s="44" t="inlineStr"/>
@@ -11206,22 +11202,22 @@
           <t>FR wheel spd shield</t>
         </is>
       </c>
-      <c r="P86" s="45" t="inlineStr">
-        <is>
-          <t>at the ECU-B plug (B-cabin); to ECU-B B17</t>
-        </is>
-      </c>
+      <c r="P86" s="45" t="inlineStr"/>
       <c r="Q86" s="46" t="inlineStr">
         <is>
-          <t>ECU-B.B17</t>
+          <t>ECU-A.A7</t>
         </is>
       </c>
       <c r="R86" s="47" t="inlineStr">
         <is>
-          <t>Screen B (ECU B17, SHIELD_B)</t>
-        </is>
-      </c>
-      <c r="S86" s="48" t="inlineStr"/>
+          <t>Screen A (ECU A7, SHIELD_A)</t>
+        </is>
+      </c>
+      <c r="S86" s="48" t="inlineStr">
+        <is>
+          <t>sp_shield_a</t>
+        </is>
+      </c>
       <c r="T86" s="48" t="inlineStr">
         <is>
           <t>cab_fspur_fr_ac</t>
@@ -11251,7 +11247,7 @@
       <c r="AD86" s="54" t="inlineStr"/>
       <c r="AE86" s="54" t="inlineStr">
         <is>
-          <t>splice sp_shield_b: node of the wire list (SoT)</t>
+          <t>splice sp_shield_a: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF86" s="54" t="inlineStr">
@@ -11261,7 +11257,7 @@
       </c>
       <c r="AG86" s="54" t="inlineStr">
         <is>
-          <t>screen floats at the far end; owner TBD: a half has no length estimate (drawn today as cab_fspur_fr_sh_ac on A-cabin, ? mm; cab_fspur_fr_sh on B-cabin, ? mm)</t>
+          <t>tied at the A end only; the far (B) end floats, dressed back at the ECU-B plug (no A-B shield bridge)</t>
         </is>
       </c>
     </row>
@@ -12418,7 +12414,7 @@
         </is>
       </c>
       <c r="F5" s="32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5" s="32" t="inlineStr">
         <is>

--- a/docs/harness/wirelist/A-cabin-wirelist.xlsx
+++ b/docs/harness/wirelist/A-cabin-wirelist.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Mates" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wire list'!$A$2:$AG$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wire list'!$A$2:$AG$100</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Wire list'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Splices'!$A$2:$L$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Splices'!$A$2:$L$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Splices'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Connectors'!$A$2:$G$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Connectors'!$1:$2</definedName>
@@ -745,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AG98"/>
+  <dimension ref="A1:AG100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -759,14 +759,14 @@
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="36" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="36" customWidth="1" min="16" max="16"/>
     <col width="45" customWidth="1" min="17" max="17"/>
     <col width="32" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
     <col width="18" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="9" customWidth="1" min="22" max="22"/>
@@ -8014,12 +8014,12 @@
     <row r="61">
       <c r="A61" s="23" t="inlineStr">
         <is>
-          <t>CRANKC</t>
+          <t>SHLD</t>
         </is>
       </c>
       <c r="B61" s="23" t="inlineStr">
         <is>
-          <t>w_shc_crank</t>
+          <t>w_shd_a_aps</t>
         </is>
       </c>
       <c r="C61" s="23" t="inlineStr">
@@ -8030,25 +8030,23 @@
       <c r="D61" s="23" t="inlineStr"/>
       <c r="E61" s="24" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="F61" s="25" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>sp_shield_a_aps</t>
         </is>
       </c>
       <c r="G61" s="26" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
-        </is>
-      </c>
-      <c r="H61" s="25" t="n">
-        <v>11</v>
-      </c>
+          <t>splice sp_shield_a_aps (SP-SHIELD-A-APS)</t>
+        </is>
+      </c>
+      <c r="H61" s="25" t="inlineStr"/>
       <c r="I61" s="26" t="inlineStr">
         <is>
-          <t>Crank sensor shield</t>
+          <t>Shield drain</t>
         </is>
       </c>
       <c r="J61" s="26" t="inlineStr"/>
@@ -8064,13 +8062,13 @@
       </c>
       <c r="M61" s="29" t="inlineStr">
         <is>
-          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
+          <t>splice sp_shield_a (SP-SHIELD-A)</t>
         </is>
       </c>
       <c r="N61" s="28" t="inlineStr"/>
       <c r="O61" s="29" t="inlineStr">
         <is>
-          <t>Crank sensor shield</t>
+          <t>Shield drain</t>
         </is>
       </c>
       <c r="P61" s="29" t="inlineStr"/>
@@ -8105,22 +8103,18 @@
       </c>
       <c r="X61" s="34" t="inlineStr">
         <is>
-          <t>White-Blue-White</t>
+          <t>White-Yellow-Blue</t>
         </is>
       </c>
       <c r="Y61" s="34" t="inlineStr"/>
-      <c r="Z61" s="35" t="inlineStr">
-        <is>
-          <t>trunk ECU-A to bulkhead (RH firewall)</t>
-        </is>
-      </c>
+      <c r="Z61" s="35" t="inlineStr"/>
       <c r="AA61" s="36" t="inlineStr"/>
       <c r="AB61" s="37" t="inlineStr"/>
       <c r="AC61" s="38" t="inlineStr"/>
       <c r="AD61" s="38" t="inlineStr"/>
       <c r="AE61" s="38" t="inlineStr">
         <is>
-          <t>DRB102 11 = section A c33 'Crank VR screen'; splice sp_shield_a: node of the wire list (SoT)</t>
+          <t>splice sp_shield_a_aps: node of the wire list (SoT); splice sp_shield_a: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF61" s="38" t="inlineStr">
@@ -8130,19 +8124,19 @@
       </c>
       <c r="AG61" s="38" t="inlineStr">
         <is>
-          <t>build (R30): this drain is the one crimped into A7</t>
+          <t>branch-point join (R207): the device drain meets the loom shield trunk where its signal wires join the main loom, then runs to the ECU splice</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="39" t="inlineStr">
         <is>
-          <t>CAM</t>
+          <t>SHLD</t>
         </is>
       </c>
       <c r="B62" s="39" t="inlineStr">
         <is>
-          <t>w_shc_cam</t>
+          <t>w_shd_a_wsf</t>
         </is>
       </c>
       <c r="C62" s="39" t="inlineStr">
@@ -8153,25 +8147,23 @@
       <c r="D62" s="39" t="inlineStr"/>
       <c r="E62" s="40" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="F62" s="41" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>sp_shield_a_wsf</t>
         </is>
       </c>
       <c r="G62" s="42" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
-        </is>
-      </c>
-      <c r="H62" s="41" t="n">
-        <v>15</v>
-      </c>
+          <t>splice sp_shield_a_wsf (SP-SHIELD-A-WSF)</t>
+        </is>
+      </c>
+      <c r="H62" s="41" t="inlineStr"/>
       <c r="I62" s="42" t="inlineStr">
         <is>
-          <t>Cam sensor shield</t>
+          <t>Shield drain</t>
         </is>
       </c>
       <c r="J62" s="42" t="inlineStr"/>
@@ -8187,13 +8179,13 @@
       </c>
       <c r="M62" s="45" t="inlineStr">
         <is>
-          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
+          <t>splice sp_shield_a (SP-SHIELD-A)</t>
         </is>
       </c>
       <c r="N62" s="44" t="inlineStr"/>
       <c r="O62" s="45" t="inlineStr">
         <is>
-          <t>Cam sensor shield</t>
+          <t>Shield drain</t>
         </is>
       </c>
       <c r="P62" s="45" t="inlineStr"/>
@@ -8228,22 +8220,18 @@
       </c>
       <c r="X62" s="50" t="inlineStr">
         <is>
-          <t>Yellow-Yellow</t>
+          <t>White-Yellow-Blue</t>
         </is>
       </c>
       <c r="Y62" s="50" t="inlineStr"/>
-      <c r="Z62" s="51" t="inlineStr">
-        <is>
-          <t>trunk ECU-A to bulkhead (RH firewall)</t>
-        </is>
-      </c>
+      <c r="Z62" s="51" t="inlineStr"/>
       <c r="AA62" s="52" t="inlineStr"/>
       <c r="AB62" s="53" t="inlineStr"/>
       <c r="AC62" s="54" t="inlineStr"/>
       <c r="AD62" s="54" t="inlineStr"/>
       <c r="AE62" s="54" t="inlineStr">
         <is>
-          <t>DRB102 15 = section A c34 'Cam Hall screen'; splice sp_shield_a: node of the wire list (SoT)</t>
+          <t>splice sp_shield_a_wsf: node of the wire list (SoT); splice sp_shield_a: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF62" s="54" t="inlineStr">
@@ -8251,17 +8239,21 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG62" s="54" t="inlineStr"/>
+      <c r="AG62" s="54" t="inlineStr">
+        <is>
+          <t>branch-point join (R207): the device drain meets the loom shield trunk where its signal wires join the main loom, then runs to the ECU splice</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="23" t="inlineStr">
         <is>
-          <t>TURBO</t>
+          <t>CRANKC</t>
         </is>
       </c>
       <c r="B63" s="23" t="inlineStr">
         <is>
-          <t>w_shc_turbo</t>
+          <t>w_shc_crank</t>
         </is>
       </c>
       <c r="C63" s="23" t="inlineStr">
@@ -8286,11 +8278,11 @@
         </is>
       </c>
       <c r="H63" s="25" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I63" s="26" t="inlineStr">
         <is>
-          <t>Turbo speed shield</t>
+          <t>Crank sensor shield</t>
         </is>
       </c>
       <c r="J63" s="26" t="inlineStr"/>
@@ -8312,7 +8304,7 @@
       <c r="N63" s="28" t="inlineStr"/>
       <c r="O63" s="29" t="inlineStr">
         <is>
-          <t>Turbo speed shield</t>
+          <t>Crank sensor shield</t>
         </is>
       </c>
       <c r="P63" s="29" t="inlineStr"/>
@@ -8347,7 +8339,7 @@
       </c>
       <c r="X63" s="34" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>White-Blue-White</t>
         </is>
       </c>
       <c r="Y63" s="34" t="inlineStr"/>
@@ -8362,7 +8354,7 @@
       <c r="AD63" s="38" t="inlineStr"/>
       <c r="AE63" s="38" t="inlineStr">
         <is>
-          <t>DRB102 19 = section A c6 'Turbo speed screen (to A7)'; splice sp_shield_a: node of the wire list (SoT)</t>
+          <t>DRB102 11 = section A c33 'Crank VR screen'; splice sp_shield_a: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF63" s="38" t="inlineStr">
@@ -8370,17 +8362,21 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG63" s="38" t="inlineStr"/>
+      <c r="AG63" s="38" t="inlineStr">
+        <is>
+          <t>build (R30): this drain is the one crimped into A7</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="39" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>CAM</t>
         </is>
       </c>
       <c r="B64" s="39" t="inlineStr">
         <is>
-          <t>w_shc_flex</t>
+          <t>w_shc_cam</t>
         </is>
       </c>
       <c r="C64" s="39" t="inlineStr">
@@ -8405,11 +8401,11 @@
         </is>
       </c>
       <c r="H64" s="41" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I64" s="42" t="inlineStr">
         <is>
-          <t>Flex fuel shield</t>
+          <t>Cam sensor shield</t>
         </is>
       </c>
       <c r="J64" s="42" t="inlineStr"/>
@@ -8431,7 +8427,7 @@
       <c r="N64" s="44" t="inlineStr"/>
       <c r="O64" s="45" t="inlineStr">
         <is>
-          <t>Flex fuel shield</t>
+          <t>Cam sensor shield</t>
         </is>
       </c>
       <c r="P64" s="45" t="inlineStr"/>
@@ -8466,7 +8462,7 @@
       </c>
       <c r="X64" s="50" t="inlineStr">
         <is>
-          <t>White-Blue</t>
+          <t>Yellow-Yellow</t>
         </is>
       </c>
       <c r="Y64" s="50" t="inlineStr"/>
@@ -8481,7 +8477,7 @@
       <c r="AD64" s="54" t="inlineStr"/>
       <c r="AE64" s="54" t="inlineStr">
         <is>
-          <t>DRB102 22 = section A c10 'Flex fuel screen (to A7)'; splice sp_shield_a: node of the wire list (SoT)</t>
+          <t>DRB102 15 = section A c34 'Cam Hall screen'; splice sp_shield_a: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF64" s="54" t="inlineStr">
@@ -8494,12 +8490,12 @@
     <row r="65">
       <c r="A65" s="23" t="inlineStr">
         <is>
-          <t>ETBS</t>
+          <t>TURBO</t>
         </is>
       </c>
       <c r="B65" s="23" t="inlineStr">
         <is>
-          <t>w_shc_etbs</t>
+          <t>w_shc_turbo</t>
         </is>
       </c>
       <c r="C65" s="23" t="inlineStr">
@@ -8524,11 +8520,11 @@
         </is>
       </c>
       <c r="H65" s="25" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I65" s="26" t="inlineStr">
         <is>
-          <t>Throttle shield</t>
+          <t>Turbo speed shield</t>
         </is>
       </c>
       <c r="J65" s="26" t="inlineStr"/>
@@ -8550,7 +8546,7 @@
       <c r="N65" s="28" t="inlineStr"/>
       <c r="O65" s="29" t="inlineStr">
         <is>
-          <t>Throttle shield</t>
+          <t>Turbo speed shield</t>
         </is>
       </c>
       <c r="P65" s="29" t="inlineStr"/>
@@ -8585,7 +8581,7 @@
       </c>
       <c r="X65" s="34" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>White</t>
         </is>
       </c>
       <c r="Y65" s="34" t="inlineStr"/>
@@ -8600,7 +8596,7 @@
       <c r="AD65" s="38" t="inlineStr"/>
       <c r="AE65" s="38" t="inlineStr">
         <is>
-          <t>DRB102 27 = section A c11 'ETB sensor group screen (to A7)'; splice sp_shield_a: node of the wire list (SoT)</t>
+          <t>DRB102 19 = section A c6 'Turbo speed screen (to A7)'; splice sp_shield_a: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF65" s="38" t="inlineStr">
@@ -8613,12 +8609,12 @@
     <row r="66">
       <c r="A66" s="39" t="inlineStr">
         <is>
-          <t>FP</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="B66" s="39" t="inlineStr">
         <is>
-          <t>w_fp85</t>
+          <t>w_shc_flex</t>
         </is>
       </c>
       <c r="C66" s="39" t="inlineStr">
@@ -8626,11 +8622,7 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D66" s="39" t="inlineStr">
-        <is>
-          <t>HeavyDC</t>
-        </is>
-      </c>
+      <c r="D66" s="39" t="inlineStr"/>
       <c r="E66" s="40" t="inlineStr">
         <is>
           <t>connector</t>
@@ -8638,85 +8630,83 @@
       </c>
       <c r="F66" s="41" t="inlineStr">
         <is>
-          <t>k_fp</t>
+          <t>bh_a_fw</t>
         </is>
       </c>
       <c r="G66" s="42" t="inlineStr">
         <is>
-          <t>FP RELAY K1</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="H66" s="41" t="n">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="I66" s="42" t="inlineStr">
         <is>
-          <t>Fuel pump relay (-)</t>
-        </is>
-      </c>
-      <c r="J66" s="42" t="inlineStr">
-        <is>
-          <t>Battery relay block (trunk) relay K1 fuel pump, pin 85</t>
-        </is>
-      </c>
+          <t>Flex fuel shield</t>
+        </is>
+      </c>
+      <c r="J66" s="42" t="inlineStr"/>
       <c r="K66" s="43" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="L66" s="44" t="inlineStr">
         <is>
-          <t>ecu_a</t>
+          <t>sp_shield_a</t>
         </is>
       </c>
       <c r="M66" s="45" t="inlineStr">
         <is>
-          <t>ECU-A</t>
-        </is>
-      </c>
-      <c r="N66" s="44" t="inlineStr">
-        <is>
-          <t>A19</t>
-        </is>
-      </c>
+          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
+        </is>
+      </c>
+      <c r="N66" s="44" t="inlineStr"/>
       <c r="O66" s="45" t="inlineStr">
         <is>
-          <t>Fuel pump relay (-)</t>
+          <t>Flex fuel shield</t>
         </is>
       </c>
       <c r="P66" s="45" t="inlineStr"/>
       <c r="Q66" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A19</t>
+          <t>ECU-A.A7</t>
         </is>
       </c>
       <c r="R66" s="47" t="inlineStr">
         <is>
-          <t>Fuel pump relay (-) (ECU-A A19)</t>
-        </is>
-      </c>
-      <c r="S66" s="48" t="inlineStr"/>
+          <t>Screen A (ECU A7, SHIELD_A)</t>
+        </is>
+      </c>
+      <c r="S66" s="48" t="inlineStr">
+        <is>
+          <t>sp_shield_a</t>
+        </is>
+      </c>
       <c r="T66" s="48" t="inlineStr"/>
       <c r="U66" s="49" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V66" s="50" t="inlineStr">
         <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="W66" s="50" t="inlineStr"/>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="W66" s="50" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
       <c r="X66" s="50" t="inlineStr">
         <is>
-          <t>White-White-Blue</t>
-        </is>
-      </c>
-      <c r="Y66" s="50" t="n">
-        <v>390</v>
-      </c>
+          <t>White-Blue</t>
+        </is>
+      </c>
+      <c r="Y66" s="50" t="inlineStr"/>
       <c r="Z66" s="51" t="inlineStr">
         <is>
-          <t>glove-box branch (POWER / LOGIC boxes)</t>
+          <t>trunk ECU-A to bulkhead (RH firewall)</t>
         </is>
       </c>
       <c r="AA66" s="52" t="inlineStr"/>
@@ -8725,7 +8715,7 @@
       <c r="AD66" s="54" t="inlineStr"/>
       <c r="AE66" s="54" t="inlineStr">
         <is>
-          <t>fuse-box plan k_fp 85 (18 AWG); channels.csv ecu_a A19 Aux 3 (AUX3_FP_RLY)</t>
+          <t>DRB102 22 = section A c10 'Flex fuel screen (to A7)'; splice sp_shield_a: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF66" s="54" t="inlineStr">
@@ -8733,21 +8723,17 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG66" s="54" t="inlineStr">
-        <is>
-          <t>owner proposed: longer half (drawn today as w_fp85 on A-cabin, 390 mm; w_fp85_h on HeavyDC, 150 mm)</t>
-        </is>
-      </c>
+      <c r="AG66" s="54" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="23" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>ETBS</t>
         </is>
       </c>
       <c r="B67" s="23" t="inlineStr">
         <is>
-          <t>w_str85</t>
+          <t>w_shc_etbs</t>
         </is>
       </c>
       <c r="C67" s="23" t="inlineStr">
@@ -8755,11 +8741,7 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D67" s="23" t="inlineStr">
-        <is>
-          <t>CabinPower</t>
-        </is>
-      </c>
+      <c r="D67" s="23" t="inlineStr"/>
       <c r="E67" s="24" t="inlineStr">
         <is>
           <t>connector</t>
@@ -8767,85 +8749,83 @@
       </c>
       <c r="F67" s="25" t="inlineStr">
         <is>
-          <t>k_str</t>
+          <t>bh_a_fw</t>
         </is>
       </c>
       <c r="G67" s="26" t="inlineStr">
         <is>
-          <t>POWER R3</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="H67" s="25" t="n">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="I67" s="26" t="inlineStr">
         <is>
-          <t>Start relay coil (-)</t>
-        </is>
-      </c>
-      <c r="J67" s="26" t="inlineStr">
-        <is>
-          <t>POWER box (glove box) relay R3 start, pin 85</t>
-        </is>
-      </c>
+          <t>Throttle shield</t>
+        </is>
+      </c>
+      <c r="J67" s="26" t="inlineStr"/>
       <c r="K67" s="27" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="L67" s="28" t="inlineStr">
         <is>
-          <t>ecu_a</t>
+          <t>sp_shield_a</t>
         </is>
       </c>
       <c r="M67" s="29" t="inlineStr">
         <is>
-          <t>ECU-A</t>
-        </is>
-      </c>
-      <c r="N67" s="28" t="inlineStr">
-        <is>
-          <t>A26</t>
-        </is>
-      </c>
+          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
+        </is>
+      </c>
+      <c r="N67" s="28" t="inlineStr"/>
       <c r="O67" s="29" t="inlineStr">
         <is>
-          <t>Start relay coil (-)</t>
+          <t>Throttle shield</t>
         </is>
       </c>
       <c r="P67" s="29" t="inlineStr"/>
       <c r="Q67" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A26</t>
+          <t>ECU-A.A7</t>
         </is>
       </c>
       <c r="R67" s="31" t="inlineStr">
         <is>
-          <t>Start relay coil (-) (ECU-A A26)</t>
-        </is>
-      </c>
-      <c r="S67" s="32" t="inlineStr"/>
+          <t>Screen A (ECU A7, SHIELD_A)</t>
+        </is>
+      </c>
+      <c r="S67" s="32" t="inlineStr">
+        <is>
+          <t>sp_shield_a</t>
+        </is>
+      </c>
       <c r="T67" s="32" t="inlineStr"/>
       <c r="U67" s="33" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V67" s="34" t="inlineStr">
         <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="W67" s="34" t="inlineStr"/>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="W67" s="34" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
       <c r="X67" s="34" t="inlineStr">
         <is>
-          <t>White-Yellow</t>
-        </is>
-      </c>
-      <c r="Y67" s="34" t="n">
-        <v>400</v>
-      </c>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="Y67" s="34" t="inlineStr"/>
       <c r="Z67" s="35" t="inlineStr">
         <is>
-          <t>glove-box branch (POWER / LOGIC boxes)</t>
+          <t>trunk ECU-A to bulkhead (RH firewall)</t>
         </is>
       </c>
       <c r="AA67" s="36" t="inlineStr"/>
@@ -8854,7 +8834,7 @@
       <c r="AD67" s="38" t="inlineStr"/>
       <c r="AE67" s="38" t="inlineStr">
         <is>
-          <t>fuse-box plan k_str 85 (18 AWG); channels.csv ecu_a A26 Aux 8 (AUX8_START_RLY)</t>
+          <t>DRB102 27 = section A c11 'ETB sensor group screen (to A7)'; splice sp_shield_a: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF67" s="38" t="inlineStr">
@@ -8862,21 +8842,17 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG67" s="38" t="inlineStr">
-        <is>
-          <t>owner proposed: longer half (drawn today as w_str85 on A-cabin, 400 mm; w_str85_cp on CabinPower, 400 mm)</t>
-        </is>
-      </c>
+      <c r="AG67" s="38" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="39" t="inlineStr">
         <is>
-          <t>FAN</t>
+          <t>FP</t>
         </is>
       </c>
       <c r="B68" s="39" t="inlineStr">
         <is>
-          <t>w_fan85</t>
+          <t>w_fp85</t>
         </is>
       </c>
       <c r="C68" s="39" t="inlineStr">
@@ -8886,7 +8862,7 @@
       </c>
       <c r="D68" s="39" t="inlineStr">
         <is>
-          <t>CabinPower</t>
+          <t>HeavyDC</t>
         </is>
       </c>
       <c r="E68" s="40" t="inlineStr">
@@ -8896,12 +8872,12 @@
       </c>
       <c r="F68" s="41" t="inlineStr">
         <is>
-          <t>k_fan</t>
+          <t>k_fp</t>
         </is>
       </c>
       <c r="G68" s="42" t="inlineStr">
         <is>
-          <t>POWER R4</t>
+          <t>FP RELAY K1</t>
         </is>
       </c>
       <c r="H68" s="41" t="n">
@@ -8909,12 +8885,12 @@
       </c>
       <c r="I68" s="42" t="inlineStr">
         <is>
-          <t>Rad fan relay (-)</t>
+          <t>Fuel pump relay (-)</t>
         </is>
       </c>
       <c r="J68" s="42" t="inlineStr">
         <is>
-          <t>POWER box (glove box) relay R4 radiator fan, pin 85</t>
+          <t>Battery relay block (trunk) relay K1 fuel pump, pin 85</t>
         </is>
       </c>
       <c r="K68" s="43" t="inlineStr">
@@ -8934,23 +8910,23 @@
       </c>
       <c r="N68" s="44" t="inlineStr">
         <is>
-          <t>A29</t>
+          <t>A19</t>
         </is>
       </c>
       <c r="O68" s="45" t="inlineStr">
         <is>
-          <t>Rad fan relay (-)</t>
+          <t>Fuel pump relay (-)</t>
         </is>
       </c>
       <c r="P68" s="45" t="inlineStr"/>
       <c r="Q68" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A29</t>
+          <t>ECU-A.A19</t>
         </is>
       </c>
       <c r="R68" s="47" t="inlineStr">
         <is>
-          <t>Rad fan relay (-) (ECU-A A29)</t>
+          <t>Fuel pump relay (-) (ECU-A A19)</t>
         </is>
       </c>
       <c r="S68" s="48" t="inlineStr"/>
@@ -8966,11 +8942,11 @@
       <c r="W68" s="50" t="inlineStr"/>
       <c r="X68" s="50" t="inlineStr">
         <is>
-          <t>Yellow-White</t>
+          <t>White-White-Blue</t>
         </is>
       </c>
       <c r="Y68" s="50" t="n">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="Z68" s="51" t="inlineStr">
         <is>
@@ -8983,7 +8959,7 @@
       <c r="AD68" s="54" t="inlineStr"/>
       <c r="AE68" s="54" t="inlineStr">
         <is>
-          <t>fuse-box plan k_fan 85 (18 AWG); channels.csv ecu_a A29 Aux 5 (AUX5_RAD_FAN)</t>
+          <t>fuse-box plan k_fp 85 (18 AWG); channels.csv ecu_a A19 Aux 3 (AUX3_FP_RLY)</t>
         </is>
       </c>
       <c r="AF68" s="54" t="inlineStr">
@@ -8993,19 +8969,19 @@
       </c>
       <c r="AG68" s="54" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_fan85 on A-cabin, 410 mm; w_fan85_cp on CabinPower, 400 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_fp85 on A-cabin, 390 mm; w_fp85_h on HeavyDC, 150 mm)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="23" t="inlineStr">
         <is>
-          <t>EPS</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="B69" s="23" t="inlineStr">
         <is>
-          <t>w_eps_rly</t>
+          <t>w_str85</t>
         </is>
       </c>
       <c r="C69" s="23" t="inlineStr">
@@ -9025,12 +9001,12 @@
       </c>
       <c r="F69" s="25" t="inlineStr">
         <is>
-          <t>k_eps</t>
+          <t>k_str</t>
         </is>
       </c>
       <c r="G69" s="26" t="inlineStr">
         <is>
-          <t>EHPS RELAY</t>
+          <t>POWER R3</t>
         </is>
       </c>
       <c r="H69" s="25" t="n">
@@ -9038,12 +9014,12 @@
       </c>
       <c r="I69" s="26" t="inlineStr">
         <is>
-          <t>EHPS relay coil (-)</t>
+          <t>Start relay coil (-)</t>
         </is>
       </c>
       <c r="J69" s="26" t="inlineStr">
         <is>
-          <t>EHPS pump relay (glove box), pin 85</t>
+          <t>POWER box (glove box) relay R3 start, pin 85</t>
         </is>
       </c>
       <c r="K69" s="27" t="inlineStr">
@@ -9053,31 +9029,33 @@
       </c>
       <c r="L69" s="28" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>ecu_a</t>
         </is>
       </c>
       <c r="M69" s="29" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
-        </is>
-      </c>
-      <c r="N69" s="28" t="n">
-        <v>56</v>
+          <t>ECU-A</t>
+        </is>
+      </c>
+      <c r="N69" s="28" t="inlineStr">
+        <is>
+          <t>A26</t>
+        </is>
       </c>
       <c r="O69" s="29" t="inlineStr">
         <is>
-          <t>EHPS relay coil (-)</t>
+          <t>Start relay coil (-)</t>
         </is>
       </c>
       <c r="P69" s="29" t="inlineStr"/>
       <c r="Q69" s="30" t="inlineStr">
         <is>
-          <t>DRB102.56</t>
+          <t>ECU-A.A26</t>
         </is>
       </c>
       <c r="R69" s="31" t="inlineStr">
         <is>
-          <t>EHPS relay coil (-) (DRB102 56)</t>
+          <t>Start relay coil (-) (ECU-A A26)</t>
         </is>
       </c>
       <c r="S69" s="32" t="inlineStr"/>
@@ -9087,21 +9065,21 @@
       </c>
       <c r="V69" s="34" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W69" s="34" t="inlineStr"/>
       <c r="X69" s="34" t="inlineStr">
         <is>
-          <t>Blue-Blue-Blue</t>
+          <t>White-Yellow</t>
         </is>
       </c>
       <c r="Y69" s="34" t="n">
-        <v>530</v>
+        <v>400</v>
       </c>
       <c r="Z69" s="35" t="inlineStr">
         <is>
-          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
+          <t>glove-box branch (POWER / LOGIC boxes)</t>
         </is>
       </c>
       <c r="AA69" s="36" t="inlineStr"/>
@@ -9110,7 +9088,7 @@
       <c r="AD69" s="38" t="inlineStr"/>
       <c r="AE69" s="38" t="inlineStr">
         <is>
-          <t>channels.csv k_eps c2 Coil 85 (MRS_RLY); DRB102 56 = section A c27 'EPS relay coil 85 (R22) - from the MR-S pump B5'</t>
+          <t>fuse-box plan k_str 85 (18 AWG); channels.csv ecu_a A26 Aux 8 (AUX8_START_RLY)</t>
         </is>
       </c>
       <c r="AF69" s="38" t="inlineStr">
@@ -9120,19 +9098,19 @@
       </c>
       <c r="AG69" s="38" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_eps_rly on A-cabin, 530 mm; w_eps_rly_cp on CabinPower, 400 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_str85 on A-cabin, 400 mm; w_str85_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="39" t="inlineStr">
         <is>
-          <t>ACKILL</t>
+          <t>FAN</t>
         </is>
       </c>
       <c r="B70" s="39" t="inlineStr">
         <is>
-          <t>w_ac_kill</t>
+          <t>w_fan85</t>
         </is>
       </c>
       <c r="C70" s="39" t="inlineStr">
@@ -9140,7 +9118,11 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D70" s="39" t="inlineStr"/>
+      <c r="D70" s="39" t="inlineStr">
+        <is>
+          <t>CabinPower</t>
+        </is>
+      </c>
       <c r="E70" s="40" t="inlineStr">
         <is>
           <t>connector</t>
@@ -9148,110 +9130,94 @@
       </c>
       <c r="F70" s="41" t="inlineStr">
         <is>
+          <t>k_fan</t>
+        </is>
+      </c>
+      <c r="G70" s="42" t="inlineStr">
+        <is>
+          <t>POWER R4</t>
+        </is>
+      </c>
+      <c r="H70" s="41" t="n">
+        <v>85</v>
+      </c>
+      <c r="I70" s="42" t="inlineStr">
+        <is>
+          <t>Rad fan relay (-)</t>
+        </is>
+      </c>
+      <c r="J70" s="42" t="inlineStr">
+        <is>
+          <t>POWER box (glove box) relay R4 radiator fan, pin 85</t>
+        </is>
+      </c>
+      <c r="K70" s="43" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="L70" s="44" t="inlineStr">
+        <is>
           <t>ecu_a</t>
         </is>
       </c>
-      <c r="G70" s="42" t="inlineStr">
+      <c r="M70" s="45" t="inlineStr">
         <is>
           <t>ECU-A</t>
         </is>
       </c>
-      <c r="H70" s="41" t="inlineStr">
-        <is>
-          <t>A18</t>
-        </is>
-      </c>
-      <c r="I70" s="42" t="inlineStr">
-        <is>
-          <t>A/C cancel (ACT)</t>
-        </is>
-      </c>
-      <c r="J70" s="42" t="inlineStr"/>
-      <c r="K70" s="43" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="L70" s="44" t="inlineStr">
-        <is>
-          <t>A18 (factory)</t>
-        </is>
-      </c>
-      <c r="M70" s="45" t="inlineStr">
-        <is>
-          <t>OEM A/C amplifier</t>
-        </is>
-      </c>
-      <c r="N70" s="44" t="n">
-        <v>11</v>
+      <c r="N70" s="44" t="inlineStr">
+        <is>
+          <t>A29</t>
+        </is>
       </c>
       <c r="O70" s="45" t="inlineStr">
         <is>
-          <t>A/C cancel (ACT)</t>
-        </is>
-      </c>
-      <c r="P70" s="45" t="inlineStr">
-        <is>
-          <t>A/C amp A18 pin 11 (1993: A15), behind the glove box. Solder splice onto the factory G-Y lead. EWD 1992 p.93 / p.218; locator 1990 p.17.</t>
-        </is>
-      </c>
+          <t>Rad fan relay (-)</t>
+        </is>
+      </c>
+      <c r="P70" s="45" t="inlineStr"/>
       <c r="Q70" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A18</t>
+          <t>ECU-A.A29</t>
         </is>
       </c>
       <c r="R70" s="47" t="inlineStr">
         <is>
-          <t>A/C cancel (ACT) (ECU-A A18)</t>
+          <t>Rad fan relay (-) (ECU-A A29)</t>
         </is>
       </c>
       <c r="S70" s="48" t="inlineStr"/>
       <c r="T70" s="48" t="inlineStr"/>
       <c r="U70" s="49" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="V70" s="50" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W70" s="50" t="inlineStr"/>
       <c r="X70" s="50" t="inlineStr">
         <is>
-          <t>White-Yellow-Yellow</t>
+          <t>Yellow-White</t>
         </is>
       </c>
       <c r="Y70" s="50" t="n">
-        <v>600</v>
+        <v>410</v>
       </c>
       <c r="Z70" s="51" t="inlineStr">
         <is>
-          <t>A/C amp branch (behind dash)</t>
-        </is>
-      </c>
-      <c r="AA70" s="52" t="inlineStr">
-        <is>
-          <t>A/C amplifier A18 (1993 book: A15), passenger side behind the glove box, on the bottom of the evaporator housing; tap point on the lead at the amplifier, distance TBD</t>
-        </is>
-      </c>
-      <c r="AB70" s="53" t="inlineStr">
-        <is>
-          <t>G-Y</t>
-        </is>
-      </c>
-      <c r="AC70" s="54" t="inlineStr">
-        <is>
-          <t>1992 Celica EWD132U p.93 and p.218 (docs/electrical/ewd-snips/1992-celica-ewd132u-a17-act-p093.png, 1992-celica-ewd132u-a17-clutch-p218.png); 1990 ST185 book locator A18; 1992 EWD132U p.93 and p.218 (A17-11 = A18-11); locator 1990 ST185 EWD p.17 Instrument Panel (ewd-snips/1990-st185-locations-dash.png); Mitchell locations (docs/research/AUTO-AC-AMP-OPTIONS.html)</t>
-        </is>
-      </c>
-      <c r="AD70" s="54" t="inlineStr">
-        <is>
-          <t>solder splice onto the factory G-Y ACT lead at the A/C amplifier</t>
-        </is>
-      </c>
+          <t>glove-box branch (POWER / LOGIC boxes)</t>
+        </is>
+      </c>
+      <c r="AA70" s="52" t="inlineStr"/>
+      <c r="AB70" s="53" t="inlineStr"/>
+      <c r="AC70" s="54" t="inlineStr"/>
+      <c r="AD70" s="54" t="inlineStr"/>
       <c r="AE70" s="54" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A18 Aux 4 (AUX4_AC_KILL); flying lead FL_ACAMP_ACT: EWD A18 pin 11 G-Y</t>
+          <t>fuse-box plan k_fan 85 (18 AWG); channels.csv ecu_a A29 Aux 5 (AUX5_RAD_FAN)</t>
         </is>
       </c>
       <c r="AF70" s="54" t="inlineStr">
@@ -9259,17 +9225,21 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG70" s="54" t="inlineStr"/>
+      <c r="AG70" s="54" t="inlineStr">
+        <is>
+          <t>owner proposed: longer half (drawn today as w_fan85 on A-cabin, 410 mm; w_fan85_cp on CabinPower, 400 mm)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="23" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="B71" s="23" t="inlineStr">
         <is>
-          <t>w_ac_psw_in</t>
+          <t>w_eps_rly</t>
         </is>
       </c>
       <c r="C71" s="23" t="inlineStr">
@@ -9279,122 +9249,102 @@
       </c>
       <c r="D71" s="23" t="inlineStr">
         <is>
-          <t>EngineRoom-C</t>
+          <t>CabinPower</t>
         </is>
       </c>
       <c r="E71" s="24" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="F71" s="25" t="inlineStr">
         <is>
-          <t>A5 (factory)</t>
+          <t>k_eps</t>
         </is>
       </c>
       <c r="G71" s="26" t="inlineStr">
         <is>
-          <t>OEM A5, factory Y-R lead</t>
+          <t>EHPS RELAY</t>
         </is>
       </c>
       <c r="H71" s="25" t="n">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="I71" s="26" t="inlineStr">
         <is>
-          <t>A/C pressure sw out</t>
+          <t>EHPS relay coil (-)</t>
         </is>
       </c>
       <c r="J71" s="26" t="inlineStr">
         <is>
-          <t>Runs on in ST185-EngineRoom-C to A/C pressure switch A5 pin 4 (engine bay): new wire to the switch's own mating plug, plug part TBD. EWD 1990 p.152.</t>
+          <t>EHPS pump relay (glove box), pin 85</t>
         </is>
       </c>
       <c r="K71" s="27" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="L71" s="28" t="inlineStr">
         <is>
-          <t>sp_ac_psw</t>
+          <t>bh_a_fw</t>
         </is>
       </c>
       <c r="M71" s="29" t="inlineStr">
         <is>
-          <t>splice sp_ac_psw (SP-AC-PSW: A/C pressure switch output)</t>
-        </is>
-      </c>
-      <c r="N71" s="28" t="inlineStr"/>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="N71" s="28" t="n">
+        <v>56</v>
+      </c>
       <c r="O71" s="29" t="inlineStr">
         <is>
-          <t>A/C pressure sw out</t>
+          <t>EHPS relay coil (-)</t>
         </is>
       </c>
       <c r="P71" s="29" t="inlineStr"/>
       <c r="Q71" s="30" t="inlineStr">
         <is>
-          <t>A5.4</t>
+          <t>DRB102.56</t>
         </is>
       </c>
       <c r="R71" s="31" t="inlineStr">
         <is>
-          <t>A/C pressure-switched relay coil +</t>
-        </is>
-      </c>
-      <c r="S71" s="32" t="inlineStr">
-        <is>
-          <t>sp_ac_psw</t>
-        </is>
-      </c>
+          <t>EHPS relay coil (-) (DRB102 56)</t>
+        </is>
+      </c>
+      <c r="S71" s="32" t="inlineStr"/>
       <c r="T71" s="32" t="inlineStr"/>
       <c r="U71" s="33" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="V71" s="34" t="inlineStr">
         <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="W71" s="34" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
+          <t>Violet</t>
+        </is>
+      </c>
+      <c r="W71" s="34" t="inlineStr"/>
       <c r="X71" s="34" t="inlineStr">
         <is>
-          <t>Yellow-Blue</t>
-        </is>
-      </c>
-      <c r="Y71" s="34" t="inlineStr"/>
+          <t>Blue-Blue-Blue</t>
+        </is>
+      </c>
+      <c r="Y71" s="34" t="n">
+        <v>530</v>
+      </c>
       <c r="Z71" s="35" t="inlineStr">
         <is>
-          <t>A/C amp branch (behind dash)</t>
-        </is>
-      </c>
-      <c r="AA71" s="36" t="inlineStr">
-        <is>
-          <t>A/C pressure switch A5, engine bay; exact spot TBD (no locator figure in the repo)</t>
-        </is>
-      </c>
-      <c r="AB71" s="37" t="inlineStr">
-        <is>
-          <t>Y-R (factory wiring; new wire here)</t>
-        </is>
-      </c>
-      <c r="AC71" s="38" t="inlineStr">
-        <is>
-          <t>1990 ST185 EWD p.152 (docs/electrical/ewd-snips/1990-st185-autoac-pressure-clutch-p152.png); 1990 ST185 EWD p.152 (A5 pin 4 Y-R)</t>
-        </is>
-      </c>
-      <c r="AD71" s="38" t="inlineStr">
-        <is>
-          <t>new-wire run terminated at the switch's own mating plug (no factory engine-bay wire reused, Section 39, 2026-10-04); plug part number not yet chosen</t>
-        </is>
-      </c>
+          <t>glove-box branch (POWER / LOGIC boxes) / trunk ECU-A to bulkhead (RH firewall)</t>
+        </is>
+      </c>
+      <c r="AA71" s="36" t="inlineStr"/>
+      <c r="AB71" s="37" t="inlineStr"/>
+      <c r="AC71" s="38" t="inlineStr"/>
+      <c r="AD71" s="38" t="inlineStr"/>
       <c r="AE71" s="38" t="inlineStr">
         <is>
-          <t>flying lead FL_A5_4: EWD A5 pin 4 Y-R (factory wiring; new wire here); splice sp_ac_psw: node of the wire list (SoT)</t>
+          <t>channels.csv k_eps c2 Coil 85 (MRS_RLY); DRB102 56 = section A c27 'EPS relay coil 85 (R22) - from the MR-S pump B5'</t>
         </is>
       </c>
       <c r="AF71" s="38" t="inlineStr">
@@ -9404,19 +9354,19 @@
       </c>
       <c r="AG71" s="38" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as w_ac_psw_in on A-cabin, ? mm; w_ac_psw on EngineRoom-C, 100 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_eps_rly on A-cabin, 530 mm; w_eps_rly_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="39" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>ACKILL</t>
         </is>
       </c>
       <c r="B72" s="39" t="inlineStr">
         <is>
-          <t>w_ac_psw_sw</t>
+          <t>w_ac_kill</t>
         </is>
       </c>
       <c r="C72" s="39" t="inlineStr">
@@ -9427,89 +9377,87 @@
       <c r="D72" s="39" t="inlineStr"/>
       <c r="E72" s="40" t="inlineStr">
         <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F72" s="41" t="inlineStr">
+        <is>
+          <t>ecu_a</t>
+        </is>
+      </c>
+      <c r="G72" s="42" t="inlineStr">
+        <is>
+          <t>ECU-A</t>
+        </is>
+      </c>
+      <c r="H72" s="41" t="inlineStr">
+        <is>
+          <t>A18</t>
+        </is>
+      </c>
+      <c r="I72" s="42" t="inlineStr">
+        <is>
+          <t>A/C cancel (ACT)</t>
+        </is>
+      </c>
+      <c r="J72" s="42" t="inlineStr"/>
+      <c r="K72" s="43" t="inlineStr">
+        <is>
           <t>OEM</t>
         </is>
       </c>
-      <c r="F72" s="41" t="inlineStr">
+      <c r="L72" s="44" t="inlineStr">
         <is>
           <t>A18 (factory)</t>
         </is>
       </c>
-      <c r="G72" s="42" t="inlineStr">
+      <c r="M72" s="45" t="inlineStr">
         <is>
           <t>OEM A/C amplifier</t>
         </is>
       </c>
-      <c r="H72" s="41" t="n">
-        <v>13</v>
-      </c>
-      <c r="I72" s="42" t="inlineStr">
-        <is>
-          <t>A/C pressure sw out</t>
-        </is>
-      </c>
-      <c r="J72" s="42" t="inlineStr">
-        <is>
-          <t>A/C amp A18 pin 13 (1993: A15), behind the glove box. Solder splice onto the factory Y-R lead. EWD 1990 p.152; locator 1990 p.17.</t>
-        </is>
-      </c>
-      <c r="K72" s="43" t="inlineStr">
-        <is>
-          <t>splice</t>
-        </is>
-      </c>
-      <c r="L72" s="44" t="inlineStr">
-        <is>
-          <t>sp_ac_psw</t>
-        </is>
-      </c>
-      <c r="M72" s="45" t="inlineStr">
-        <is>
-          <t>splice sp_ac_psw (SP-AC-PSW: A/C pressure switch output)</t>
-        </is>
-      </c>
-      <c r="N72" s="44" t="inlineStr"/>
+      <c r="N72" s="44" t="n">
+        <v>11</v>
+      </c>
       <c r="O72" s="45" t="inlineStr">
         <is>
-          <t>A/C pressure sw out</t>
-        </is>
-      </c>
-      <c r="P72" s="45" t="inlineStr"/>
+          <t>A/C cancel (ACT)</t>
+        </is>
+      </c>
+      <c r="P72" s="45" t="inlineStr">
+        <is>
+          <t>A/C amp A18 pin 11 (1993: A15), behind the glove box. Solder splice onto the factory G-Y lead. EWD 1992 p.93 / p.218; locator 1990 p.17.</t>
+        </is>
+      </c>
       <c r="Q72" s="46" t="inlineStr">
         <is>
-          <t>A5.4</t>
+          <t>ECU-A.A18</t>
         </is>
       </c>
       <c r="R72" s="47" t="inlineStr">
         <is>
-          <t>A/C pressure-switched relay coil +</t>
-        </is>
-      </c>
-      <c r="S72" s="48" t="inlineStr">
-        <is>
-          <t>sp_ac_psw</t>
-        </is>
-      </c>
+          <t>A/C cancel (ACT) (ECU-A A18)</t>
+        </is>
+      </c>
+      <c r="S72" s="48" t="inlineStr"/>
       <c r="T72" s="48" t="inlineStr"/>
       <c r="U72" s="49" t="n">
         <v>20</v>
       </c>
       <c r="V72" s="50" t="inlineStr">
         <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="W72" s="50" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
+          <t>Gray</t>
+        </is>
+      </c>
+      <c r="W72" s="50" t="inlineStr"/>
       <c r="X72" s="50" t="inlineStr">
         <is>
-          <t>Yellow-Blue</t>
-        </is>
-      </c>
-      <c r="Y72" s="50" t="inlineStr"/>
+          <t>White-Yellow-Yellow</t>
+        </is>
+      </c>
+      <c r="Y72" s="50" t="n">
+        <v>600</v>
+      </c>
       <c r="Z72" s="51" t="inlineStr">
         <is>
           <t>A/C amp branch (behind dash)</t>
@@ -9522,22 +9470,22 @@
       </c>
       <c r="AB72" s="53" t="inlineStr">
         <is>
-          <t>Y-R</t>
+          <t>G-Y</t>
         </is>
       </c>
       <c r="AC72" s="54" t="inlineStr">
         <is>
-          <t>1990 ST185 EWD p.152 (docs/electrical/ewd-snips/1990-st185-autoac-pressure-clutch-p152.png); 1992 EWD132U p.219 A17-13 (ewd-snips/1992-celica-ewd132u-a17-pressure-p219.png); 1990 ST185 EWD p.152; 1992 EWD132U p.219 (A17-13); locator 1990 ST185 EWD p.17 Instrument Panel (ewd-snips/1990-st185-locations-dash.png); Mitchell locations (docs/research/AUTO-AC-AMP-OPTIONS.html)</t>
+          <t>1992 Celica EWD132U p.93 and p.218 (docs/electrical/ewd-snips/1992-celica-ewd132u-a17-act-p093.png, 1992-celica-ewd132u-a17-clutch-p218.png); 1990 ST185 book locator A18; 1992 EWD132U p.93 and p.218 (A17-11 = A18-11); locator 1990 ST185 EWD p.17 Instrument Panel (ewd-snips/1990-st185-locations-dash.png); Mitchell locations (docs/research/AUTO-AC-AMP-OPTIONS.html)</t>
         </is>
       </c>
       <c r="AD72" s="54" t="inlineStr">
         <is>
-          <t>solder splice onto the factory Y-R lead at the A/C amplifier</t>
+          <t>solder splice onto the factory G-Y ACT lead at the A/C amplifier</t>
         </is>
       </c>
       <c r="AE72" s="54" t="inlineStr">
         <is>
-          <t>flying lead FL_ACAMP_PSW: EWD A18 pin 13 Y-R; splice sp_ac_psw: node of the wire list (SoT)</t>
+          <t>channels.csv ecu_a A18 Aux 4 (AUX4_AC_KILL); flying lead FL_ACAMP_ACT: EWD A18 pin 11 G-Y</t>
         </is>
       </c>
       <c r="AF72" s="54" t="inlineStr">
@@ -9555,7 +9503,7 @@
       </c>
       <c r="B73" s="23" t="inlineStr">
         <is>
-          <t>w_acc86</t>
+          <t>w_ac_psw_in</t>
         </is>
       </c>
       <c r="C73" s="23" t="inlineStr">
@@ -9565,59 +9513,59 @@
       </c>
       <c r="D73" s="23" t="inlineStr">
         <is>
-          <t>CabinPower</t>
+          <t>EngineRoom-C</t>
         </is>
       </c>
       <c r="E73" s="24" t="inlineStr">
         <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="F73" s="25" t="inlineStr">
+        <is>
+          <t>A5 (factory)</t>
+        </is>
+      </c>
+      <c r="G73" s="26" t="inlineStr">
+        <is>
+          <t>OEM A5, factory Y-R lead</t>
+        </is>
+      </c>
+      <c r="H73" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I73" s="26" t="inlineStr">
+        <is>
+          <t>A/C pressure sw out</t>
+        </is>
+      </c>
+      <c r="J73" s="26" t="inlineStr">
+        <is>
+          <t>Runs on in ST185-EngineRoom-C to A/C pressure switch A5 pin 4 (engine bay): new wire to the switch's own mating plug, plug part TBD. EWD 1990 p.152.</t>
+        </is>
+      </c>
+      <c r="K73" s="27" t="inlineStr">
+        <is>
           <t>splice</t>
         </is>
       </c>
-      <c r="F73" s="25" t="inlineStr">
+      <c r="L73" s="28" t="inlineStr">
         <is>
           <t>sp_ac_psw</t>
         </is>
       </c>
-      <c r="G73" s="26" t="inlineStr">
+      <c r="M73" s="29" t="inlineStr">
         <is>
           <t>splice sp_ac_psw (SP-AC-PSW: A/C pressure switch output)</t>
         </is>
       </c>
-      <c r="H73" s="25" t="inlineStr"/>
-      <c r="I73" s="26" t="inlineStr">
-        <is>
-          <t>A/C clutch relay (+)</t>
-        </is>
-      </c>
-      <c r="J73" s="26" t="inlineStr"/>
-      <c r="K73" s="27" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="L73" s="28" t="inlineStr">
-        <is>
-          <t>k_acc</t>
-        </is>
-      </c>
-      <c r="M73" s="29" t="inlineStr">
-        <is>
-          <t>LOGIC M5</t>
-        </is>
-      </c>
-      <c r="N73" s="28" t="n">
-        <v>86</v>
-      </c>
+      <c r="N73" s="28" t="inlineStr"/>
       <c r="O73" s="29" t="inlineStr">
         <is>
-          <t>A/C clutch relay (+)</t>
-        </is>
-      </c>
-      <c r="P73" s="29" t="inlineStr">
-        <is>
-          <t>LOGIC box (glove box) relay M15 A/C clutch, pin 86</t>
-        </is>
-      </c>
+          <t>A/C pressure sw out</t>
+        </is>
+      </c>
+      <c r="P73" s="29" t="inlineStr"/>
       <c r="Q73" s="30" t="inlineStr">
         <is>
           <t>A5.4</t>
@@ -9635,7 +9583,7 @@
       </c>
       <c r="T73" s="32" t="inlineStr"/>
       <c r="U73" s="33" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V73" s="34" t="inlineStr">
         <is>
@@ -9658,13 +9606,29 @@
           <t>A/C amp branch (behind dash)</t>
         </is>
       </c>
-      <c r="AA73" s="36" t="inlineStr"/>
-      <c r="AB73" s="37" t="inlineStr"/>
-      <c r="AC73" s="38" t="inlineStr"/>
-      <c r="AD73" s="38" t="inlineStr"/>
+      <c r="AA73" s="36" t="inlineStr">
+        <is>
+          <t>A/C pressure switch A5, engine bay; exact spot TBD (no locator figure in the repo)</t>
+        </is>
+      </c>
+      <c r="AB73" s="37" t="inlineStr">
+        <is>
+          <t>Y-R (factory wiring; new wire here)</t>
+        </is>
+      </c>
+      <c r="AC73" s="38" t="inlineStr">
+        <is>
+          <t>1990 ST185 EWD p.152 (docs/electrical/ewd-snips/1990-st185-autoac-pressure-clutch-p152.png); 1990 ST185 EWD p.152 (A5 pin 4 Y-R)</t>
+        </is>
+      </c>
+      <c r="AD73" s="38" t="inlineStr">
+        <is>
+          <t>new-wire run terminated at the switch's own mating plug (no factory engine-bay wire reused, Section 39, 2026-10-04); plug part number not yet chosen</t>
+        </is>
+      </c>
       <c r="AE73" s="38" t="inlineStr">
         <is>
-          <t>splice sp_ac_psw: node of the wire list (SoT); fuse-box plan k_acc 86 (18 AWG)</t>
+          <t>flying lead FL_A5_4: EWD A5 pin 4 Y-R (factory wiring; new wire here); splice sp_ac_psw: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF73" s="38" t="inlineStr">
@@ -9674,19 +9638,19 @@
       </c>
       <c r="AG73" s="38" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as w_acc86 on A-cabin, ? mm; w_acc86_cp on CabinPower, 400 mm)</t>
+          <t>owner TBD: a half has no length estimate (drawn today as w_ac_psw_in on A-cabin, ? mm; w_ac_psw on EngineRoom-C, 100 mm)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="39" t="inlineStr">
         <is>
-          <t>5V</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B74" s="39" t="inlineStr">
         <is>
-          <t>w_aps_vc1</t>
+          <t>w_ac_psw_sw</t>
         </is>
       </c>
       <c r="C74" s="39" t="inlineStr">
@@ -9697,28 +9661,32 @@
       <c r="D74" s="39" t="inlineStr"/>
       <c r="E74" s="40" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="F74" s="41" t="inlineStr">
         <is>
-          <t>aps</t>
+          <t>A18 (factory)</t>
         </is>
       </c>
       <c r="G74" s="42" t="inlineStr">
         <is>
-          <t>PEDAL</t>
+          <t>OEM A/C amplifier</t>
         </is>
       </c>
       <c r="H74" s="41" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I74" s="42" t="inlineStr">
         <is>
-          <t>+5 V pedal sensor 1</t>
-        </is>
-      </c>
-      <c r="J74" s="42" t="inlineStr"/>
+          <t>A/C pressure sw out</t>
+        </is>
+      </c>
+      <c r="J74" s="42" t="inlineStr">
+        <is>
+          <t>A/C amp A18 pin 13 (1993: A15), behind the glove box. Solder splice onto the factory Y-R lead. EWD 1990 p.152; locator 1990 p.17.</t>
+        </is>
+      </c>
       <c r="K74" s="43" t="inlineStr">
         <is>
           <t>splice</t>
@@ -9726,68 +9694,84 @@
       </c>
       <c r="L74" s="44" t="inlineStr">
         <is>
-          <t>sp_5v_2</t>
+          <t>sp_ac_psw</t>
         </is>
       </c>
       <c r="M74" s="45" t="inlineStr">
         <is>
-          <t>splice sp_5v_2 (SP-5V-PEDAL: +5 V to pedal + cruise)</t>
+          <t>splice sp_ac_psw (SP-AC-PSW: A/C pressure switch output)</t>
         </is>
       </c>
       <c r="N74" s="44" t="inlineStr"/>
       <c r="O74" s="45" t="inlineStr">
         <is>
-          <t>+5 V pedal sensor 1</t>
+          <t>A/C pressure sw out</t>
         </is>
       </c>
       <c r="P74" s="45" t="inlineStr"/>
       <c r="Q74" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A32</t>
+          <t>A5.4</t>
         </is>
       </c>
       <c r="R74" s="47" t="inlineStr">
         <is>
-          <t>+5V sensor (ECU-A A32)</t>
+          <t>A/C pressure-switched relay coil +</t>
         </is>
       </c>
       <c r="S74" s="48" t="inlineStr">
         <is>
-          <t>sp_5v_2</t>
-        </is>
-      </c>
-      <c r="T74" s="48" t="inlineStr">
-        <is>
-          <t>cab_aps1</t>
-        </is>
-      </c>
+          <t>sp_ac_psw</t>
+        </is>
+      </c>
+      <c r="T74" s="48" t="inlineStr"/>
       <c r="U74" s="49" t="n">
         <v>20</v>
       </c>
       <c r="V74" s="50" t="inlineStr">
         <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="W74" s="50" t="inlineStr">
+        <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="W74" s="50" t="inlineStr"/>
       <c r="X74" s="50" t="inlineStr">
         <is>
-          <t>Blue-Blue</t>
+          <t>Yellow-Blue</t>
         </is>
       </c>
       <c r="Y74" s="50" t="inlineStr"/>
       <c r="Z74" s="51" t="inlineStr">
         <is>
-          <t>pedal branch (driver footwell)</t>
-        </is>
-      </c>
-      <c r="AA74" s="52" t="inlineStr"/>
-      <c r="AB74" s="53" t="inlineStr"/>
-      <c r="AC74" s="54" t="inlineStr"/>
-      <c r="AD74" s="54" t="inlineStr"/>
+          <t>A/C amp branch (behind dash)</t>
+        </is>
+      </c>
+      <c r="AA74" s="52" t="inlineStr">
+        <is>
+          <t>A/C amplifier A18 (1993 book: A15), passenger side behind the glove box, on the bottom of the evaporator housing; tap point on the lead at the amplifier, distance TBD</t>
+        </is>
+      </c>
+      <c r="AB74" s="53" t="inlineStr">
+        <is>
+          <t>Y-R</t>
+        </is>
+      </c>
+      <c r="AC74" s="54" t="inlineStr">
+        <is>
+          <t>1990 ST185 EWD p.152 (docs/electrical/ewd-snips/1990-st185-autoac-pressure-clutch-p152.png); 1992 EWD132U p.219 A17-13 (ewd-snips/1992-celica-ewd132u-a17-pressure-p219.png); 1990 ST185 EWD p.152; 1992 EWD132U p.219 (A17-13); locator 1990 ST185 EWD p.17 Instrument Panel (ewd-snips/1990-st185-locations-dash.png); Mitchell locations (docs/research/AUTO-AC-AMP-OPTIONS.html)</t>
+        </is>
+      </c>
+      <c r="AD74" s="54" t="inlineStr">
+        <is>
+          <t>solder splice onto the factory Y-R lead at the A/C amplifier</t>
+        </is>
+      </c>
       <c r="AE74" s="54" t="inlineStr">
         <is>
-          <t>splice sp_5v_2: node of the wire list (SoT)</t>
+          <t>flying lead FL_ACAMP_PSW: EWD A18 pin 13 Y-R; splice sp_ac_psw: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF74" s="54" t="inlineStr">
@@ -9795,21 +9779,17 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG74" s="54" t="inlineStr">
-        <is>
-          <t>pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
-        </is>
-      </c>
+      <c r="AG74" s="54" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="23" t="inlineStr">
         <is>
-          <t>SGND</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B75" s="23" t="inlineStr">
         <is>
-          <t>w40</t>
+          <t>w_acc86</t>
         </is>
       </c>
       <c r="C75" s="23" t="inlineStr">
@@ -9817,91 +9797,99 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D75" s="23" t="inlineStr"/>
+      <c r="D75" s="23" t="inlineStr">
+        <is>
+          <t>CabinPower</t>
+        </is>
+      </c>
       <c r="E75" s="24" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="F75" s="25" t="inlineStr">
         <is>
-          <t>aps</t>
+          <t>sp_ac_psw</t>
         </is>
       </c>
       <c r="G75" s="26" t="inlineStr">
         <is>
-          <t>PEDAL</t>
-        </is>
-      </c>
-      <c r="H75" s="25" t="n">
-        <v>5</v>
-      </c>
+          <t>splice sp_ac_psw (SP-AC-PSW: A/C pressure switch output)</t>
+        </is>
+      </c>
+      <c r="H75" s="25" t="inlineStr"/>
       <c r="I75" s="26" t="inlineStr">
         <is>
-          <t>Pedal 1 ground</t>
+          <t>A/C clutch relay (+)</t>
         </is>
       </c>
       <c r="J75" s="26" t="inlineStr"/>
       <c r="K75" s="27" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="L75" s="28" t="inlineStr">
         <is>
-          <t>sp_gndout</t>
+          <t>k_acc</t>
         </is>
       </c>
       <c r="M75" s="29" t="inlineStr">
         <is>
-          <t>splice sp_gndout (SP-GNDOUT-A: sensor ground)</t>
-        </is>
-      </c>
-      <c r="N75" s="28" t="inlineStr"/>
+          <t>LOGIC M5</t>
+        </is>
+      </c>
+      <c r="N75" s="28" t="n">
+        <v>86</v>
+      </c>
       <c r="O75" s="29" t="inlineStr">
         <is>
-          <t>Pedal 1 ground</t>
-        </is>
-      </c>
-      <c r="P75" s="29" t="inlineStr"/>
+          <t>A/C clutch relay (+)</t>
+        </is>
+      </c>
+      <c r="P75" s="29" t="inlineStr">
+        <is>
+          <t>LOGIC box (glove box) relay M15 A/C clutch, pin 86</t>
+        </is>
+      </c>
       <c r="Q75" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A24</t>
+          <t>A5.4</t>
         </is>
       </c>
       <c r="R75" s="31" t="inlineStr">
         <is>
-          <t>Sensor GND (ECU-A A24)</t>
+          <t>A/C pressure-switched relay coil +</t>
         </is>
       </c>
       <c r="S75" s="32" t="inlineStr">
         <is>
-          <t>sp_gndout</t>
-        </is>
-      </c>
-      <c r="T75" s="32" t="inlineStr">
-        <is>
-          <t>cab_aps1</t>
-        </is>
-      </c>
+          <t>sp_ac_psw</t>
+        </is>
+      </c>
+      <c r="T75" s="32" t="inlineStr"/>
       <c r="U75" s="33" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="V75" s="34" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
       </c>
-      <c r="W75" s="34" t="inlineStr"/>
+      <c r="W75" s="34" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="X75" s="34" t="inlineStr">
         <is>
-          <t>Yellow-Yellow-Blue</t>
+          <t>Yellow-Blue</t>
         </is>
       </c>
       <c r="Y75" s="34" t="inlineStr"/>
       <c r="Z75" s="35" t="inlineStr">
         <is>
-          <t>pedal branch (driver footwell)</t>
+          <t>A/C amp branch (behind dash)</t>
         </is>
       </c>
       <c r="AA75" s="36" t="inlineStr"/>
@@ -9910,7 +9898,7 @@
       <c r="AD75" s="38" t="inlineStr"/>
       <c r="AE75" s="38" t="inlineStr">
         <is>
-          <t>splice sp_gndout: node of the wire list (SoT)</t>
+          <t>splice sp_ac_psw: node of the wire list (SoT); fuse-box plan k_acc 86 (18 AWG)</t>
         </is>
       </c>
       <c r="AF75" s="38" t="inlineStr">
@@ -9920,19 +9908,19 @@
       </c>
       <c r="AG75" s="38" t="inlineStr">
         <is>
-          <t>pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
+          <t>owner TBD: a half has no length estimate (drawn today as w_acc86 on A-cabin, ? mm; w_acc86_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="39" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="B76" s="39" t="inlineStr">
         <is>
-          <t>w38</t>
+          <t>w_aps_vc1</t>
         </is>
       </c>
       <c r="C76" s="39" t="inlineStr">
@@ -9957,51 +9945,51 @@
         </is>
       </c>
       <c r="H76" s="41" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I76" s="42" t="inlineStr">
         <is>
-          <t>Pedal 1 signal main</t>
+          <t>+5 V pedal sensor 1</t>
         </is>
       </c>
       <c r="J76" s="42" t="inlineStr"/>
       <c r="K76" s="43" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="L76" s="44" t="inlineStr">
         <is>
-          <t>ecu_a</t>
+          <t>sp_5v_2</t>
         </is>
       </c>
       <c r="M76" s="45" t="inlineStr">
         <is>
-          <t>ECU-A</t>
-        </is>
-      </c>
-      <c r="N76" s="44" t="inlineStr">
-        <is>
-          <t>A14</t>
-        </is>
-      </c>
+          <t>splice sp_5v_2 (SP-5V-PEDAL: +5 V to pedal + cruise)</t>
+        </is>
+      </c>
+      <c r="N76" s="44" t="inlineStr"/>
       <c r="O76" s="45" t="inlineStr">
         <is>
-          <t>Pedal 1 signal main</t>
+          <t>+5 V pedal sensor 1</t>
         </is>
       </c>
       <c r="P76" s="45" t="inlineStr"/>
       <c r="Q76" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A14</t>
+          <t>ECU-A.A32</t>
         </is>
       </c>
       <c r="R76" s="47" t="inlineStr">
         <is>
-          <t>Pedal 1 signal main (ECU-A A14)</t>
-        </is>
-      </c>
-      <c r="S76" s="48" t="inlineStr"/>
+          <t>+5V sensor (ECU-A A32)</t>
+        </is>
+      </c>
+      <c r="S76" s="48" t="inlineStr">
+        <is>
+          <t>sp_5v_2</t>
+        </is>
+      </c>
       <c r="T76" s="48" t="inlineStr">
         <is>
           <t>cab_aps1</t>
@@ -10012,18 +10000,16 @@
       </c>
       <c r="V76" s="50" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W76" s="50" t="inlineStr"/>
       <c r="X76" s="50" t="inlineStr">
         <is>
-          <t>White-Blue-Yellow</t>
-        </is>
-      </c>
-      <c r="Y76" s="50" t="n">
-        <v>1050</v>
-      </c>
+          <t>Blue-Blue</t>
+        </is>
+      </c>
+      <c r="Y76" s="50" t="inlineStr"/>
       <c r="Z76" s="51" t="inlineStr">
         <is>
           <t>pedal branch (driver footwell)</t>
@@ -10035,7 +10021,7 @@
       <c r="AD76" s="54" t="inlineStr"/>
       <c r="AE76" s="54" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A14 An Volt 4 (AV4_APS_MAIN)</t>
+          <t>splice sp_5v_2: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF76" s="54" t="inlineStr">
@@ -10052,12 +10038,12 @@
     <row r="77">
       <c r="A77" s="23" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>SGND</t>
         </is>
       </c>
       <c r="B77" s="23" t="inlineStr">
         <is>
-          <t>cab_aps1_sh</t>
+          <t>w40</t>
         </is>
       </c>
       <c r="C77" s="23" t="inlineStr">
@@ -10068,23 +10054,25 @@
       <c r="D77" s="23" t="inlineStr"/>
       <c r="E77" s="24" t="inlineStr">
         <is>
-          <t>cable screen</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="F77" s="25" t="inlineStr">
         <is>
-          <t>cab_aps1</t>
+          <t>aps</t>
         </is>
       </c>
       <c r="G77" s="26" t="inlineStr">
         <is>
-          <t>cable screen (one end only)</t>
-        </is>
-      </c>
-      <c r="H77" s="25" t="inlineStr"/>
+          <t>PEDAL</t>
+        </is>
+      </c>
+      <c r="H77" s="25" t="n">
+        <v>5</v>
+      </c>
       <c r="I77" s="26" t="inlineStr">
         <is>
-          <t>Pedal 1 cable shield</t>
+          <t>Pedal 1 ground</t>
         </is>
       </c>
       <c r="J77" s="26" t="inlineStr"/>
@@ -10095,34 +10083,34 @@
       </c>
       <c r="L77" s="28" t="inlineStr">
         <is>
-          <t>sp_shield_a</t>
+          <t>sp_gndout</t>
         </is>
       </c>
       <c r="M77" s="29" t="inlineStr">
         <is>
-          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
+          <t>splice sp_gndout (SP-GNDOUT-A: sensor ground)</t>
         </is>
       </c>
       <c r="N77" s="28" t="inlineStr"/>
       <c r="O77" s="29" t="inlineStr">
         <is>
-          <t>Pedal 1 cable shield</t>
+          <t>Pedal 1 ground</t>
         </is>
       </c>
       <c r="P77" s="29" t="inlineStr"/>
       <c r="Q77" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A7</t>
+          <t>ECU-A.A24</t>
         </is>
       </c>
       <c r="R77" s="31" t="inlineStr">
         <is>
-          <t>Screen A (ECU A7, SHIELD_A)</t>
+          <t>Sensor GND (ECU-A A24)</t>
         </is>
       </c>
       <c r="S77" s="32" t="inlineStr">
         <is>
-          <t>sp_shield_a</t>
+          <t>sp_gndout</t>
         </is>
       </c>
       <c r="T77" s="32" t="inlineStr">
@@ -10130,22 +10118,24 @@
           <t>cab_aps1</t>
         </is>
       </c>
-      <c r="U77" s="33" t="inlineStr"/>
+      <c r="U77" s="33" t="n">
+        <v>20</v>
+      </c>
       <c r="V77" s="34" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W77" s="34" t="inlineStr"/>
       <c r="X77" s="34" t="inlineStr">
         <is>
-          <t>White-Blue-Yellow</t>
+          <t>Yellow-Yellow-Blue</t>
         </is>
       </c>
       <c r="Y77" s="34" t="inlineStr"/>
       <c r="Z77" s="35" t="inlineStr">
         <is>
-          <t>at ECU-A plug</t>
+          <t>pedal branch (driver footwell)</t>
         </is>
       </c>
       <c r="AA77" s="36" t="inlineStr"/>
@@ -10154,7 +10144,7 @@
       <c r="AD77" s="38" t="inlineStr"/>
       <c r="AE77" s="38" t="inlineStr">
         <is>
-          <t>splice sp_shield_a: node of the wire list (SoT)</t>
+          <t>splice sp_gndout: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF77" s="38" t="inlineStr">
@@ -10164,19 +10154,19 @@
       </c>
       <c r="AG77" s="38" t="inlineStr">
         <is>
-          <t>screen floats at the far end; pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
+          <t>pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="39" t="inlineStr">
         <is>
-          <t>5V</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="B78" s="39" t="inlineStr">
         <is>
-          <t>w210</t>
+          <t>w38</t>
         </is>
       </c>
       <c r="C78" s="39" t="inlineStr">
@@ -10201,54 +10191,54 @@
         </is>
       </c>
       <c r="H78" s="41" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I78" s="42" t="inlineStr">
         <is>
-          <t>+5 V pedal sensor 2</t>
+          <t>Pedal 1 signal main</t>
         </is>
       </c>
       <c r="J78" s="42" t="inlineStr"/>
       <c r="K78" s="43" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="L78" s="44" t="inlineStr">
         <is>
-          <t>sp_5v_2</t>
+          <t>ecu_a</t>
         </is>
       </c>
       <c r="M78" s="45" t="inlineStr">
         <is>
-          <t>splice sp_5v_2 (SP-5V-PEDAL: +5 V to pedal + cruise)</t>
-        </is>
-      </c>
-      <c r="N78" s="44" t="inlineStr"/>
+          <t>ECU-A</t>
+        </is>
+      </c>
+      <c r="N78" s="44" t="inlineStr">
+        <is>
+          <t>A14</t>
+        </is>
+      </c>
       <c r="O78" s="45" t="inlineStr">
         <is>
-          <t>+5 V pedal sensor 2</t>
+          <t>Pedal 1 signal main</t>
         </is>
       </c>
       <c r="P78" s="45" t="inlineStr"/>
       <c r="Q78" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A32</t>
+          <t>ECU-A.A14</t>
         </is>
       </c>
       <c r="R78" s="47" t="inlineStr">
         <is>
-          <t>+5V sensor (ECU-A A32)</t>
-        </is>
-      </c>
-      <c r="S78" s="48" t="inlineStr">
-        <is>
-          <t>sp_5v_2</t>
-        </is>
-      </c>
+          <t>Pedal 1 signal main (ECU-A A14)</t>
+        </is>
+      </c>
+      <c r="S78" s="48" t="inlineStr"/>
       <c r="T78" s="48" t="inlineStr">
         <is>
-          <t>cab_aps2</t>
+          <t>cab_aps1</t>
         </is>
       </c>
       <c r="U78" s="49" t="n">
@@ -10256,16 +10246,18 @@
       </c>
       <c r="V78" s="50" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="W78" s="50" t="inlineStr"/>
       <c r="X78" s="50" t="inlineStr">
         <is>
-          <t>Blue-Blue</t>
-        </is>
-      </c>
-      <c r="Y78" s="50" t="inlineStr"/>
+          <t>White-Blue-Yellow</t>
+        </is>
+      </c>
+      <c r="Y78" s="50" t="n">
+        <v>1050</v>
+      </c>
       <c r="Z78" s="51" t="inlineStr">
         <is>
           <t>pedal branch (driver footwell)</t>
@@ -10277,7 +10269,7 @@
       <c r="AD78" s="54" t="inlineStr"/>
       <c r="AE78" s="54" t="inlineStr">
         <is>
-          <t>splice sp_5v_2: node of the wire list (SoT)</t>
+          <t>channels.csv ecu_a A14 An Volt 4 (AV4_APS_MAIN)</t>
         </is>
       </c>
       <c r="AF78" s="54" t="inlineStr">
@@ -10294,12 +10286,12 @@
     <row r="79">
       <c r="A79" s="23" t="inlineStr">
         <is>
-          <t>SGND</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="B79" s="23" t="inlineStr">
         <is>
-          <t>w_aps_gnd2</t>
+          <t>cab_aps1_sh</t>
         </is>
       </c>
       <c r="C79" s="23" t="inlineStr">
@@ -10310,25 +10302,23 @@
       <c r="D79" s="23" t="inlineStr"/>
       <c r="E79" s="24" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>cable screen</t>
         </is>
       </c>
       <c r="F79" s="25" t="inlineStr">
         <is>
-          <t>aps</t>
+          <t>cab_aps1</t>
         </is>
       </c>
       <c r="G79" s="26" t="inlineStr">
         <is>
-          <t>PEDAL</t>
-        </is>
-      </c>
-      <c r="H79" s="25" t="n">
-        <v>2</v>
-      </c>
+          <t>cable screen (one end only)</t>
+        </is>
+      </c>
+      <c r="H79" s="25" t="inlineStr"/>
       <c r="I79" s="26" t="inlineStr">
         <is>
-          <t>Pedal 2 ground</t>
+          <t>Pedal 1 cable shield</t>
         </is>
       </c>
       <c r="J79" s="26" t="inlineStr"/>
@@ -10339,59 +10329,57 @@
       </c>
       <c r="L79" s="28" t="inlineStr">
         <is>
-          <t>sp_gndout</t>
+          <t>sp_shield_a_aps</t>
         </is>
       </c>
       <c r="M79" s="29" t="inlineStr">
         <is>
-          <t>splice sp_gndout (SP-GNDOUT-A: sensor ground)</t>
+          <t>splice sp_shield_a_aps (SP-SHIELD-A-APS)</t>
         </is>
       </c>
       <c r="N79" s="28" t="inlineStr"/>
       <c r="O79" s="29" t="inlineStr">
         <is>
-          <t>Pedal 2 ground</t>
+          <t>Pedal 1 cable shield</t>
         </is>
       </c>
       <c r="P79" s="29" t="inlineStr"/>
       <c r="Q79" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A24</t>
+          <t>ECU-A.A7</t>
         </is>
       </c>
       <c r="R79" s="31" t="inlineStr">
         <is>
-          <t>Sensor GND (ECU-A A24)</t>
+          <t>Screen A (ECU A7, SHIELD_A)</t>
         </is>
       </c>
       <c r="S79" s="32" t="inlineStr">
         <is>
-          <t>sp_gndout</t>
+          <t>sp_shield_a_aps</t>
         </is>
       </c>
       <c r="T79" s="32" t="inlineStr">
         <is>
-          <t>cab_aps2</t>
-        </is>
-      </c>
-      <c r="U79" s="33" t="n">
-        <v>20</v>
-      </c>
+          <t>cab_aps1</t>
+        </is>
+      </c>
+      <c r="U79" s="33" t="inlineStr"/>
       <c r="V79" s="34" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Shield</t>
         </is>
       </c>
       <c r="W79" s="34" t="inlineStr"/>
       <c r="X79" s="34" t="inlineStr">
         <is>
-          <t>Yellow-Yellow-Blue</t>
+          <t>White-Blue-Yellow</t>
         </is>
       </c>
       <c r="Y79" s="34" t="inlineStr"/>
       <c r="Z79" s="35" t="inlineStr">
         <is>
-          <t>pedal branch (driver footwell)</t>
+          <t>at ECU-A plug</t>
         </is>
       </c>
       <c r="AA79" s="36" t="inlineStr"/>
@@ -10400,7 +10388,7 @@
       <c r="AD79" s="38" t="inlineStr"/>
       <c r="AE79" s="38" t="inlineStr">
         <is>
-          <t>splice sp_gndout: node of the wire list (SoT)</t>
+          <t>splice sp_shield_a_aps: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF79" s="38" t="inlineStr">
@@ -10410,19 +10398,19 @@
       </c>
       <c r="AG79" s="38" t="inlineStr">
         <is>
-          <t>pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
+          <t>screen floats at the far end; pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="39" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="B80" s="39" t="inlineStr">
         <is>
-          <t>w_aps_vpa2</t>
+          <t>w210</t>
         </is>
       </c>
       <c r="C80" s="39" t="inlineStr">
@@ -10430,11 +10418,7 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D80" s="39" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
+      <c r="D80" s="39" t="inlineStr"/>
       <c r="E80" s="40" t="inlineStr">
         <is>
           <t>connector</t>
@@ -10451,55 +10435,51 @@
         </is>
       </c>
       <c r="H80" s="41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I80" s="42" t="inlineStr">
         <is>
-          <t>Pedal 2 signal sub</t>
+          <t>+5 V pedal sensor 2</t>
         </is>
       </c>
       <c r="J80" s="42" t="inlineStr"/>
       <c r="K80" s="43" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="L80" s="44" t="inlineStr">
         <is>
-          <t>ecu_b</t>
+          <t>sp_5v_2</t>
         </is>
       </c>
       <c r="M80" s="45" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
-        </is>
-      </c>
-      <c r="N80" s="44" t="inlineStr">
-        <is>
-          <t>B33</t>
-        </is>
-      </c>
+          <t>splice sp_5v_2 (SP-5V-PEDAL: +5 V to pedal + cruise)</t>
+        </is>
+      </c>
+      <c r="N80" s="44" t="inlineStr"/>
       <c r="O80" s="45" t="inlineStr">
         <is>
-          <t>Pedal 2 signal sub</t>
-        </is>
-      </c>
-      <c r="P80" s="45" t="inlineStr">
-        <is>
-          <t>ECU-B plug pin B33 (Link G4X, centre dash); VPA2</t>
-        </is>
-      </c>
+          <t>+5 V pedal sensor 2</t>
+        </is>
+      </c>
+      <c r="P80" s="45" t="inlineStr"/>
       <c r="Q80" s="46" t="inlineStr">
         <is>
-          <t>ECU-B.B33</t>
+          <t>ECU-A.A32</t>
         </is>
       </c>
       <c r="R80" s="47" t="inlineStr">
         <is>
-          <t>Pedal 2 signal sub (ECU-B B33)</t>
-        </is>
-      </c>
-      <c r="S80" s="48" t="inlineStr"/>
+          <t>+5V sensor (ECU-A A32)</t>
+        </is>
+      </c>
+      <c r="S80" s="48" t="inlineStr">
+        <is>
+          <t>sp_5v_2</t>
+        </is>
+      </c>
       <c r="T80" s="48" t="inlineStr">
         <is>
           <t>cab_aps2</t>
@@ -10510,21 +10490,19 @@
       </c>
       <c r="V80" s="50" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W80" s="50" t="inlineStr"/>
       <c r="X80" s="50" t="inlineStr">
         <is>
-          <t>White-Blue-Yellow</t>
-        </is>
-      </c>
-      <c r="Y80" s="50" t="n">
-        <v>1720</v>
-      </c>
+          <t>Blue-Blue</t>
+        </is>
+      </c>
+      <c r="Y80" s="50" t="inlineStr"/>
       <c r="Z80" s="51" t="inlineStr">
         <is>
-          <t>pedal branch (driver footwell) / to ECU-B plug (beside ECU-A)</t>
+          <t>pedal branch (driver footwell)</t>
         </is>
       </c>
       <c r="AA80" s="52" t="inlineStr"/>
@@ -10533,7 +10511,7 @@
       <c r="AD80" s="54" t="inlineStr"/>
       <c r="AE80" s="54" t="inlineStr">
         <is>
-          <t>channels.csv ecu_b B33 An Volt 5 (AV5_APS_SUB)</t>
+          <t>splice sp_5v_2: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF80" s="54" t="inlineStr">
@@ -10543,19 +10521,19 @@
       </c>
       <c r="AG80" s="54" t="inlineStr">
         <is>
-          <t>pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143); owner proposed: longer half (drawn today as w_aps_vpa2 on A-cabin, 1720 mm; w39 on B-cabin, 1250 mm)</t>
+          <t>pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="23" t="inlineStr">
         <is>
-          <t>APS</t>
+          <t>SGND</t>
         </is>
       </c>
       <c r="B81" s="23" t="inlineStr">
         <is>
-          <t>cab_aps_sh</t>
+          <t>w_aps_gnd2</t>
         </is>
       </c>
       <c r="C81" s="23" t="inlineStr">
@@ -10566,23 +10544,25 @@
       <c r="D81" s="23" t="inlineStr"/>
       <c r="E81" s="24" t="inlineStr">
         <is>
-          <t>cable screen</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="F81" s="25" t="inlineStr">
         <is>
-          <t>cab_aps2</t>
+          <t>aps</t>
         </is>
       </c>
       <c r="G81" s="26" t="inlineStr">
         <is>
-          <t>cable screen (one end only)</t>
-        </is>
-      </c>
-      <c r="H81" s="25" t="inlineStr"/>
+          <t>PEDAL</t>
+        </is>
+      </c>
+      <c r="H81" s="25" t="n">
+        <v>2</v>
+      </c>
       <c r="I81" s="26" t="inlineStr">
         <is>
-          <t>Pedal 2 cable shield</t>
+          <t>Pedal 2 ground</t>
         </is>
       </c>
       <c r="J81" s="26" t="inlineStr"/>
@@ -10593,34 +10573,34 @@
       </c>
       <c r="L81" s="28" t="inlineStr">
         <is>
-          <t>sp_shield_a</t>
+          <t>sp_gndout</t>
         </is>
       </c>
       <c r="M81" s="29" t="inlineStr">
         <is>
-          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
+          <t>splice sp_gndout (SP-GNDOUT-A: sensor ground)</t>
         </is>
       </c>
       <c r="N81" s="28" t="inlineStr"/>
       <c r="O81" s="29" t="inlineStr">
         <is>
-          <t>Pedal 2 cable shield</t>
+          <t>Pedal 2 ground</t>
         </is>
       </c>
       <c r="P81" s="29" t="inlineStr"/>
       <c r="Q81" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A7</t>
+          <t>ECU-A.A24</t>
         </is>
       </c>
       <c r="R81" s="31" t="inlineStr">
         <is>
-          <t>Screen A (ECU A7, SHIELD_A)</t>
+          <t>Sensor GND (ECU-A A24)</t>
         </is>
       </c>
       <c r="S81" s="32" t="inlineStr">
         <is>
-          <t>sp_shield_a</t>
+          <t>sp_gndout</t>
         </is>
       </c>
       <c r="T81" s="32" t="inlineStr">
@@ -10628,22 +10608,24 @@
           <t>cab_aps2</t>
         </is>
       </c>
-      <c r="U81" s="33" t="inlineStr"/>
+      <c r="U81" s="33" t="n">
+        <v>20</v>
+      </c>
       <c r="V81" s="34" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W81" s="34" t="inlineStr"/>
       <c r="X81" s="34" t="inlineStr">
         <is>
-          <t>White-Blue-Yellow</t>
+          <t>Yellow-Yellow-Blue</t>
         </is>
       </c>
       <c r="Y81" s="34" t="inlineStr"/>
       <c r="Z81" s="35" t="inlineStr">
         <is>
-          <t>at ECU-A plug</t>
+          <t>pedal branch (driver footwell)</t>
         </is>
       </c>
       <c r="AA81" s="36" t="inlineStr"/>
@@ -10652,7 +10634,7 @@
       <c r="AD81" s="38" t="inlineStr"/>
       <c r="AE81" s="38" t="inlineStr">
         <is>
-          <t>splice sp_shield_a: node of the wire list (SoT)</t>
+          <t>splice sp_gndout: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF81" s="38" t="inlineStr">
@@ -10662,19 +10644,19 @@
       </c>
       <c r="AG81" s="38" t="inlineStr">
         <is>
-          <t>screen floats at the far end; pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
+          <t>pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="39" t="inlineStr">
         <is>
-          <t>5V</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="B82" s="39" t="inlineStr">
         <is>
-          <t>cab_fspur_5v</t>
+          <t>w_aps_vpa2</t>
         </is>
       </c>
       <c r="C82" s="39" t="inlineStr">
@@ -10682,7 +10664,11 @@
           <t>A-cabin</t>
         </is>
       </c>
-      <c r="D82" s="39" t="inlineStr"/>
+      <c r="D82" s="39" t="inlineStr">
+        <is>
+          <t>B-cabin</t>
+        </is>
+      </c>
       <c r="E82" s="40" t="inlineStr">
         <is>
           <t>connector</t>
@@ -10690,63 +10676,67 @@
       </c>
       <c r="F82" s="41" t="inlineStr">
         <is>
-          <t>ix_ws_front_p</t>
+          <t>aps</t>
         </is>
       </c>
       <c r="G82" s="42" t="inlineStr">
         <is>
-          <t>FRONT WS INLINE</t>
+          <t>PEDAL</t>
         </is>
       </c>
       <c r="H82" s="41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I82" s="42" t="inlineStr">
         <is>
-          <t>VRC-F +5V</t>
+          <t>Pedal 2 signal sub</t>
         </is>
       </c>
       <c r="J82" s="42" t="inlineStr"/>
       <c r="K82" s="43" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="L82" s="44" t="inlineStr">
         <is>
-          <t>sp_5v</t>
+          <t>ecu_b</t>
         </is>
       </c>
       <c r="M82" s="45" t="inlineStr">
         <is>
-          <t>splice sp_5v (SP-5V-A: +5 V sensor supply)</t>
-        </is>
-      </c>
-      <c r="N82" s="44" t="inlineStr"/>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
+        </is>
+      </c>
+      <c r="N82" s="44" t="inlineStr">
+        <is>
+          <t>B33</t>
+        </is>
+      </c>
       <c r="O82" s="45" t="inlineStr">
         <is>
-          <t>VRC-F +5V</t>
-        </is>
-      </c>
-      <c r="P82" s="45" t="inlineStr"/>
+          <t>Pedal 2 signal sub</t>
+        </is>
+      </c>
+      <c r="P82" s="45" t="inlineStr">
+        <is>
+          <t>ECU-B plug pin B33 (Link G4X, centre dash); VPA2</t>
+        </is>
+      </c>
       <c r="Q82" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A32</t>
+          <t>ECU-B.B33</t>
         </is>
       </c>
       <c r="R82" s="47" t="inlineStr">
         <is>
-          <t>+5V sensor (ECU-A A32)</t>
-        </is>
-      </c>
-      <c r="S82" s="48" t="inlineStr">
-        <is>
-          <t>sp_5v</t>
-        </is>
-      </c>
+          <t>Pedal 2 signal sub (ECU-B B33)</t>
+        </is>
+      </c>
+      <c r="S82" s="48" t="inlineStr"/>
       <c r="T82" s="48" t="inlineStr">
         <is>
-          <t>cab_fspur</t>
+          <t>cab_aps2</t>
         </is>
       </c>
       <c r="U82" s="49" t="n">
@@ -10754,19 +10744,21 @@
       </c>
       <c r="V82" s="50" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="W82" s="50" t="inlineStr"/>
       <c r="X82" s="50" t="inlineStr">
         <is>
-          <t>Blue-Blue</t>
-        </is>
-      </c>
-      <c r="Y82" s="50" t="inlineStr"/>
+          <t>White-Blue-Yellow</t>
+        </is>
+      </c>
+      <c r="Y82" s="50" t="n">
+        <v>1720</v>
+      </c>
       <c r="Z82" s="51" t="inlineStr">
         <is>
-          <t>dash branch (front WS inline)</t>
+          <t>pedal branch (driver footwell) / to ECU-B plug (beside ECU-A)</t>
         </is>
       </c>
       <c r="AA82" s="52" t="inlineStr"/>
@@ -10775,7 +10767,7 @@
       <c r="AD82" s="54" t="inlineStr"/>
       <c r="AE82" s="54" t="inlineStr">
         <is>
-          <t>splice sp_5v: node of the wire list (SoT)</t>
+          <t>channels.csv ecu_b B33 An Volt 5 (AV5_APS_SUB)</t>
         </is>
       </c>
       <c r="AF82" s="54" t="inlineStr">
@@ -10783,17 +10775,21 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG82" s="54" t="inlineStr"/>
+      <c r="AG82" s="54" t="inlineStr">
+        <is>
+          <t>pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143); owner proposed: longer half (drawn today as w_aps_vpa2 on A-cabin, 1720 mm; w39 on B-cabin, 1250 mm)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="23" t="inlineStr">
         <is>
-          <t>SGND</t>
+          <t>APS</t>
         </is>
       </c>
       <c r="B83" s="23" t="inlineStr">
         <is>
-          <t>cab_fspur_gnd</t>
+          <t>cab_aps_sh</t>
         </is>
       </c>
       <c r="C83" s="23" t="inlineStr">
@@ -10804,25 +10800,23 @@
       <c r="D83" s="23" t="inlineStr"/>
       <c r="E83" s="24" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>cable screen</t>
         </is>
       </c>
       <c r="F83" s="25" t="inlineStr">
         <is>
-          <t>ix_ws_front_p</t>
+          <t>cab_aps2</t>
         </is>
       </c>
       <c r="G83" s="26" t="inlineStr">
         <is>
-          <t>FRONT WS INLINE</t>
-        </is>
-      </c>
-      <c r="H83" s="25" t="n">
-        <v>2</v>
-      </c>
+          <t>cable screen (one end only)</t>
+        </is>
+      </c>
+      <c r="H83" s="25" t="inlineStr"/>
       <c r="I83" s="26" t="inlineStr">
         <is>
-          <t>VRC-F GND</t>
+          <t>Pedal 2 cable shield</t>
         </is>
       </c>
       <c r="J83" s="26" t="inlineStr"/>
@@ -10833,59 +10827,57 @@
       </c>
       <c r="L83" s="28" t="inlineStr">
         <is>
-          <t>sp_gndout</t>
+          <t>sp_shield_a_aps</t>
         </is>
       </c>
       <c r="M83" s="29" t="inlineStr">
         <is>
-          <t>splice sp_gndout (SP-GNDOUT-A: sensor ground)</t>
+          <t>splice sp_shield_a_aps (SP-SHIELD-A-APS)</t>
         </is>
       </c>
       <c r="N83" s="28" t="inlineStr"/>
       <c r="O83" s="29" t="inlineStr">
         <is>
-          <t>VRC-F GND</t>
+          <t>Pedal 2 cable shield</t>
         </is>
       </c>
       <c r="P83" s="29" t="inlineStr"/>
       <c r="Q83" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A24</t>
+          <t>ECU-A.A7</t>
         </is>
       </c>
       <c r="R83" s="31" t="inlineStr">
         <is>
-          <t>Sensor GND (ECU-A A24)</t>
+          <t>Screen A (ECU A7, SHIELD_A)</t>
         </is>
       </c>
       <c r="S83" s="32" t="inlineStr">
         <is>
-          <t>sp_gndout</t>
+          <t>sp_shield_a_aps</t>
         </is>
       </c>
       <c r="T83" s="32" t="inlineStr">
         <is>
-          <t>cab_fspur</t>
-        </is>
-      </c>
-      <c r="U83" s="33" t="n">
-        <v>20</v>
-      </c>
+          <t>cab_aps2</t>
+        </is>
+      </c>
+      <c r="U83" s="33" t="inlineStr"/>
       <c r="V83" s="34" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Shield</t>
         </is>
       </c>
       <c r="W83" s="34" t="inlineStr"/>
       <c r="X83" s="34" t="inlineStr">
         <is>
-          <t>Yellow-Yellow-Blue</t>
+          <t>White-Blue-Yellow</t>
         </is>
       </c>
       <c r="Y83" s="34" t="inlineStr"/>
       <c r="Z83" s="35" t="inlineStr">
         <is>
-          <t>dash branch (front WS inline)</t>
+          <t>at ECU-A plug</t>
         </is>
       </c>
       <c r="AA83" s="36" t="inlineStr"/>
@@ -10894,7 +10886,7 @@
       <c r="AD83" s="38" t="inlineStr"/>
       <c r="AE83" s="38" t="inlineStr">
         <is>
-          <t>splice sp_gndout: node of the wire list (SoT)</t>
+          <t>splice sp_shield_a_aps: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF83" s="38" t="inlineStr">
@@ -10902,17 +10894,21 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG83" s="38" t="inlineStr"/>
+      <c r="AG83" s="38" t="inlineStr">
+        <is>
+          <t>screen floats at the far end; pedal branch length is a placeholder: measure at the car (OPEN-ITEMS row 143)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="39" t="inlineStr">
         <is>
-          <t>WSSF</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="B84" s="39" t="inlineStr">
         <is>
-          <t>cab_fspur_l</t>
+          <t>cab_fspur_5v</t>
         </is>
       </c>
       <c r="C84" s="39" t="inlineStr">
@@ -10937,51 +10933,51 @@
         </is>
       </c>
       <c r="H84" s="41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I84" s="42" t="inlineStr">
         <is>
-          <t>FL conditioned out</t>
+          <t>VRC-F +5V</t>
         </is>
       </c>
       <c r="J84" s="42" t="inlineStr"/>
       <c r="K84" s="43" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="L84" s="44" t="inlineStr">
         <is>
-          <t>ecu_a</t>
+          <t>sp_5v</t>
         </is>
       </c>
       <c r="M84" s="45" t="inlineStr">
         <is>
-          <t>ECU-A</t>
-        </is>
-      </c>
-      <c r="N84" s="44" t="inlineStr">
-        <is>
-          <t>A23</t>
-        </is>
-      </c>
+          <t>splice sp_5v (SP-5V-A: +5 V sensor supply)</t>
+        </is>
+      </c>
+      <c r="N84" s="44" t="inlineStr"/>
       <c r="O84" s="45" t="inlineStr">
         <is>
-          <t>FL conditioned out</t>
+          <t>VRC-F +5V</t>
         </is>
       </c>
       <c r="P84" s="45" t="inlineStr"/>
       <c r="Q84" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A23</t>
+          <t>ECU-A.A32</t>
         </is>
       </c>
       <c r="R84" s="47" t="inlineStr">
         <is>
-          <t>FL conditioned out (ECU-A A23)</t>
-        </is>
-      </c>
-      <c r="S84" s="48" t="inlineStr"/>
+          <t>+5V sensor (ECU-A A32)</t>
+        </is>
+      </c>
+      <c r="S84" s="48" t="inlineStr">
+        <is>
+          <t>sp_5v</t>
+        </is>
+      </c>
       <c r="T84" s="48" t="inlineStr">
         <is>
           <t>cab_fspur</t>
@@ -10992,18 +10988,16 @@
       </c>
       <c r="V84" s="50" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W84" s="50" t="inlineStr"/>
       <c r="X84" s="50" t="inlineStr">
         <is>
-          <t>White-Blue-Blue</t>
-        </is>
-      </c>
-      <c r="Y84" s="50" t="n">
-        <v>330</v>
-      </c>
+          <t>Blue-Blue</t>
+        </is>
+      </c>
+      <c r="Y84" s="50" t="inlineStr"/>
       <c r="Z84" s="51" t="inlineStr">
         <is>
           <t>dash branch (front WS inline)</t>
@@ -11015,7 +11009,7 @@
       <c r="AD84" s="54" t="inlineStr"/>
       <c r="AE84" s="54" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A23 DI 3 (DI3_WSS_FL)</t>
+          <t>splice sp_5v: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF84" s="54" t="inlineStr">
@@ -11028,12 +11022,12 @@
     <row r="85">
       <c r="A85" s="23" t="inlineStr">
         <is>
-          <t>WSSF</t>
+          <t>SGND</t>
         </is>
       </c>
       <c r="B85" s="23" t="inlineStr">
         <is>
-          <t>cab_fspur_sh</t>
+          <t>cab_fspur_gnd</t>
         </is>
       </c>
       <c r="C85" s="23" t="inlineStr">
@@ -11058,11 +11052,11 @@
         </is>
       </c>
       <c r="H85" s="25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I85" s="26" t="inlineStr">
         <is>
-          <t>WS-F screen drain</t>
+          <t>VRC-F GND</t>
         </is>
       </c>
       <c r="J85" s="26" t="inlineStr"/>
@@ -11073,34 +11067,34 @@
       </c>
       <c r="L85" s="28" t="inlineStr">
         <is>
-          <t>sp_shield_a</t>
+          <t>sp_gndout</t>
         </is>
       </c>
       <c r="M85" s="29" t="inlineStr">
         <is>
-          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
+          <t>splice sp_gndout (SP-GNDOUT-A: sensor ground)</t>
         </is>
       </c>
       <c r="N85" s="28" t="inlineStr"/>
       <c r="O85" s="29" t="inlineStr">
         <is>
-          <t>WS-F screen drain</t>
+          <t>VRC-F GND</t>
         </is>
       </c>
       <c r="P85" s="29" t="inlineStr"/>
       <c r="Q85" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A7</t>
+          <t>ECU-A.A24</t>
         </is>
       </c>
       <c r="R85" s="31" t="inlineStr">
         <is>
-          <t>Screen A (ECU A7, SHIELD_A)</t>
+          <t>Sensor GND (ECU-A A24)</t>
         </is>
       </c>
       <c r="S85" s="32" t="inlineStr">
         <is>
-          <t>sp_shield_a</t>
+          <t>sp_gndout</t>
         </is>
       </c>
       <c r="T85" s="32" t="inlineStr">
@@ -11108,16 +11102,18 @@
           <t>cab_fspur</t>
         </is>
       </c>
-      <c r="U85" s="33" t="inlineStr"/>
+      <c r="U85" s="33" t="n">
+        <v>20</v>
+      </c>
       <c r="V85" s="34" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W85" s="34" t="inlineStr"/>
       <c r="X85" s="34" t="inlineStr">
         <is>
-          <t>White-Blue-Blue</t>
+          <t>Yellow-Yellow-Blue</t>
         </is>
       </c>
       <c r="Y85" s="34" t="inlineStr"/>
@@ -11132,7 +11128,7 @@
       <c r="AD85" s="38" t="inlineStr"/>
       <c r="AE85" s="38" t="inlineStr">
         <is>
-          <t>splice sp_shield_a: node of the wire list (SoT)</t>
+          <t>splice sp_gndout: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF85" s="38" t="inlineStr">
@@ -11150,7 +11146,7 @@
       </c>
       <c r="B86" s="39" t="inlineStr">
         <is>
-          <t>cab_fspur_fr_sh_ac</t>
+          <t>cab_fspur_l</t>
         </is>
       </c>
       <c r="C86" s="39" t="inlineStr">
@@ -11161,72 +11157,76 @@
       <c r="D86" s="39" t="inlineStr"/>
       <c r="E86" s="40" t="inlineStr">
         <is>
-          <t>cable screen</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="F86" s="41" t="inlineStr">
         <is>
-          <t>cab_fspur_fr_ac</t>
+          <t>ix_ws_front_p</t>
         </is>
       </c>
       <c r="G86" s="42" t="inlineStr">
         <is>
-          <t>cable screen (one end only)</t>
-        </is>
-      </c>
-      <c r="H86" s="41" t="inlineStr"/>
+          <t>FRONT WS INLINE</t>
+        </is>
+      </c>
+      <c r="H86" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="I86" s="42" t="inlineStr">
         <is>
-          <t>FR wheel spd shield</t>
+          <t>FL conditioned out</t>
         </is>
       </c>
       <c r="J86" s="42" t="inlineStr"/>
       <c r="K86" s="43" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="L86" s="44" t="inlineStr">
         <is>
-          <t>sp_shield_a</t>
+          <t>ecu_a</t>
         </is>
       </c>
       <c r="M86" s="45" t="inlineStr">
         <is>
-          <t>splice sp_shield_a (SP-SHIELD-A: shield drains)</t>
-        </is>
-      </c>
-      <c r="N86" s="44" t="inlineStr"/>
+          <t>ECU-A</t>
+        </is>
+      </c>
+      <c r="N86" s="44" t="inlineStr">
+        <is>
+          <t>A23</t>
+        </is>
+      </c>
       <c r="O86" s="45" t="inlineStr">
         <is>
-          <t>FR wheel spd shield</t>
+          <t>FL conditioned out</t>
         </is>
       </c>
       <c r="P86" s="45" t="inlineStr"/>
       <c r="Q86" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A7</t>
+          <t>ECU-A.A23</t>
         </is>
       </c>
       <c r="R86" s="47" t="inlineStr">
         <is>
-          <t>Screen A (ECU A7, SHIELD_A)</t>
-        </is>
-      </c>
-      <c r="S86" s="48" t="inlineStr">
-        <is>
-          <t>sp_shield_a</t>
-        </is>
-      </c>
+          <t>FL conditioned out (ECU-A A23)</t>
+        </is>
+      </c>
+      <c r="S86" s="48" t="inlineStr"/>
       <c r="T86" s="48" t="inlineStr">
         <is>
-          <t>cab_fspur_fr_ac</t>
-        </is>
-      </c>
-      <c r="U86" s="49" t="inlineStr"/>
+          <t>cab_fspur</t>
+        </is>
+      </c>
+      <c r="U86" s="49" t="n">
+        <v>20</v>
+      </c>
       <c r="V86" s="50" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="W86" s="50" t="inlineStr"/>
@@ -11235,7 +11235,9 @@
           <t>White-Blue-Blue</t>
         </is>
       </c>
-      <c r="Y86" s="50" t="inlineStr"/>
+      <c r="Y86" s="50" t="n">
+        <v>330</v>
+      </c>
       <c r="Z86" s="51" t="inlineStr">
         <is>
           <t>dash branch (front WS inline)</t>
@@ -11247,7 +11249,7 @@
       <c r="AD86" s="54" t="inlineStr"/>
       <c r="AE86" s="54" t="inlineStr">
         <is>
-          <t>splice sp_shield_a: node of the wire list (SoT)</t>
+          <t>channels.csv ecu_a A23 DI 3 (DI3_WSS_FL)</t>
         </is>
       </c>
       <c r="AF86" s="54" t="inlineStr">
@@ -11255,15 +11257,19 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG86" s="54" t="inlineStr">
-        <is>
-          <t>tied at the A end only; the far (B) end floats, dressed back at the ECU-B plug (no A-B shield bridge)</t>
-        </is>
-      </c>
+      <c r="AG86" s="54" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="23" t="inlineStr"/>
-      <c r="B87" s="23" t="inlineStr"/>
+      <c r="A87" s="23" t="inlineStr">
+        <is>
+          <t>WSSF</t>
+        </is>
+      </c>
+      <c r="B87" s="23" t="inlineStr">
+        <is>
+          <t>cab_fspur_sh</t>
+        </is>
+      </c>
       <c r="C87" s="23" t="inlineStr">
         <is>
           <t>A-cabin</t>
@@ -11277,54 +11283,90 @@
       </c>
       <c r="F87" s="25" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>ix_ws_front_p</t>
         </is>
       </c>
       <c r="G87" s="26" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>FRONT WS INLINE</t>
         </is>
       </c>
       <c r="H87" s="25" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="I87" s="26" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>WS-F screen drain</t>
         </is>
       </c>
       <c r="J87" s="26" t="inlineStr"/>
-      <c r="K87" s="27" t="inlineStr"/>
-      <c r="L87" s="28" t="inlineStr"/>
-      <c r="M87" s="29" t="inlineStr"/>
+      <c r="K87" s="27" t="inlineStr">
+        <is>
+          <t>splice</t>
+        </is>
+      </c>
+      <c r="L87" s="28" t="inlineStr">
+        <is>
+          <t>sp_shield_a_wsf</t>
+        </is>
+      </c>
+      <c r="M87" s="29" t="inlineStr">
+        <is>
+          <t>splice sp_shield_a_wsf (SP-SHIELD-A-WSF)</t>
+        </is>
+      </c>
       <c r="N87" s="28" t="inlineStr"/>
-      <c r="O87" s="29" t="inlineStr"/>
+      <c r="O87" s="29" t="inlineStr">
+        <is>
+          <t>WS-F screen drain</t>
+        </is>
+      </c>
       <c r="P87" s="29" t="inlineStr"/>
       <c r="Q87" s="30" t="inlineStr">
         <is>
-          <t>DRB102.45</t>
+          <t>ECU-A.A7</t>
         </is>
       </c>
       <c r="R87" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 45)</t>
-        </is>
-      </c>
-      <c r="S87" s="32" t="inlineStr"/>
-      <c r="T87" s="32" t="inlineStr"/>
+          <t>Screen A (ECU A7, SHIELD_A)</t>
+        </is>
+      </c>
+      <c r="S87" s="32" t="inlineStr">
+        <is>
+          <t>sp_shield_a_wsf</t>
+        </is>
+      </c>
+      <c r="T87" s="32" t="inlineStr">
+        <is>
+          <t>cab_fspur</t>
+        </is>
+      </c>
       <c r="U87" s="33" t="inlineStr"/>
-      <c r="V87" s="34" t="inlineStr"/>
+      <c r="V87" s="34" t="inlineStr">
+        <is>
+          <t>Shield</t>
+        </is>
+      </c>
       <c r="W87" s="34" t="inlineStr"/>
-      <c r="X87" s="34" t="inlineStr"/>
+      <c r="X87" s="34" t="inlineStr">
+        <is>
+          <t>White-Blue-Blue</t>
+        </is>
+      </c>
       <c r="Y87" s="34" t="inlineStr"/>
-      <c r="Z87" s="35" t="inlineStr"/>
+      <c r="Z87" s="35" t="inlineStr">
+        <is>
+          <t>dash branch (front WS inline)</t>
+        </is>
+      </c>
       <c r="AA87" s="36" t="inlineStr"/>
       <c r="AB87" s="37" t="inlineStr"/>
       <c r="AC87" s="38" t="inlineStr"/>
       <c r="AD87" s="38" t="inlineStr"/>
       <c r="AE87" s="38" t="inlineStr">
         <is>
-          <t>DRB102 45 = 'spare (size 16) - was the A/C coolant switch signal, deleted (S35)'</t>
+          <t>splice sp_shield_a_wsf: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF87" s="38" t="inlineStr">
@@ -11335,8 +11377,16 @@
       <c r="AG87" s="38" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="39" t="inlineStr"/>
-      <c r="B88" s="39" t="inlineStr"/>
+      <c r="A88" s="39" t="inlineStr">
+        <is>
+          <t>WSSF</t>
+        </is>
+      </c>
+      <c r="B88" s="39" t="inlineStr">
+        <is>
+          <t>cab_fspur_fr_sh_ac</t>
+        </is>
+      </c>
       <c r="C88" s="39" t="inlineStr">
         <is>
           <t>A-cabin</t>
@@ -11345,59 +11395,93 @@
       <c r="D88" s="39" t="inlineStr"/>
       <c r="E88" s="40" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>cable screen</t>
         </is>
       </c>
       <c r="F88" s="41" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>cab_fspur_fr_ac</t>
         </is>
       </c>
       <c r="G88" s="42" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
-        </is>
-      </c>
-      <c r="H88" s="41" t="n">
-        <v>46</v>
-      </c>
+          <t>cable screen (one end only)</t>
+        </is>
+      </c>
+      <c r="H88" s="41" t="inlineStr"/>
       <c r="I88" s="42" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>FR wheel spd shield</t>
         </is>
       </c>
       <c r="J88" s="42" t="inlineStr"/>
-      <c r="K88" s="43" t="inlineStr"/>
-      <c r="L88" s="44" t="inlineStr"/>
-      <c r="M88" s="45" t="inlineStr"/>
+      <c r="K88" s="43" t="inlineStr">
+        <is>
+          <t>splice</t>
+        </is>
+      </c>
+      <c r="L88" s="44" t="inlineStr">
+        <is>
+          <t>sp_shield_a_wsf</t>
+        </is>
+      </c>
+      <c r="M88" s="45" t="inlineStr">
+        <is>
+          <t>splice sp_shield_a_wsf (SP-SHIELD-A-WSF)</t>
+        </is>
+      </c>
       <c r="N88" s="44" t="inlineStr"/>
-      <c r="O88" s="45" t="inlineStr"/>
+      <c r="O88" s="45" t="inlineStr">
+        <is>
+          <t>FR wheel spd shield</t>
+        </is>
+      </c>
       <c r="P88" s="45" t="inlineStr"/>
       <c r="Q88" s="46" t="inlineStr">
         <is>
-          <t>DRB102.46</t>
+          <t>ECU-A.A7</t>
         </is>
       </c>
       <c r="R88" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 46)</t>
-        </is>
-      </c>
-      <c r="S88" s="48" t="inlineStr"/>
-      <c r="T88" s="48" t="inlineStr"/>
+          <t>Screen A (ECU A7, SHIELD_A)</t>
+        </is>
+      </c>
+      <c r="S88" s="48" t="inlineStr">
+        <is>
+          <t>sp_shield_a_wsf</t>
+        </is>
+      </c>
+      <c r="T88" s="48" t="inlineStr">
+        <is>
+          <t>cab_fspur_fr_ac</t>
+        </is>
+      </c>
       <c r="U88" s="49" t="inlineStr"/>
-      <c r="V88" s="50" t="inlineStr"/>
+      <c r="V88" s="50" t="inlineStr">
+        <is>
+          <t>Shield</t>
+        </is>
+      </c>
       <c r="W88" s="50" t="inlineStr"/>
-      <c r="X88" s="50" t="inlineStr"/>
+      <c r="X88" s="50" t="inlineStr">
+        <is>
+          <t>White-Blue-Blue</t>
+        </is>
+      </c>
       <c r="Y88" s="50" t="inlineStr"/>
-      <c r="Z88" s="51" t="inlineStr"/>
+      <c r="Z88" s="51" t="inlineStr">
+        <is>
+          <t>dash branch (front WS inline)</t>
+        </is>
+      </c>
       <c r="AA88" s="52" t="inlineStr"/>
       <c r="AB88" s="53" t="inlineStr"/>
       <c r="AC88" s="54" t="inlineStr"/>
       <c r="AD88" s="54" t="inlineStr"/>
       <c r="AE88" s="54" t="inlineStr">
         <is>
-          <t>DRB102 46 = 'spare (size 16) - was the A/C coolant switch return, deleted (S35)'</t>
+          <t>splice sp_shield_a_wsf: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF88" s="54" t="inlineStr">
@@ -11405,7 +11489,11 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG88" s="54" t="inlineStr"/>
+      <c r="AG88" s="54" t="inlineStr">
+        <is>
+          <t>tied at the A end only; the far (B) end floats, dressed back at the ECU-B plug (no A-B shield bridge)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="23" t="inlineStr"/>
@@ -11432,7 +11520,7 @@
         </is>
       </c>
       <c r="H89" s="25" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="I89" s="26" t="inlineStr">
         <is>
@@ -11448,12 +11536,12 @@
       <c r="P89" s="29" t="inlineStr"/>
       <c r="Q89" s="30" t="inlineStr">
         <is>
-          <t>DRB102.52</t>
+          <t>DRB102.45</t>
         </is>
       </c>
       <c r="R89" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 52)</t>
+          <t>spare (DRB102 45)</t>
         </is>
       </c>
       <c r="S89" s="32" t="inlineStr"/>
@@ -11470,7 +11558,7 @@
       <c r="AD89" s="38" t="inlineStr"/>
       <c r="AE89" s="38" t="inlineStr">
         <is>
-          <t>DRB102 52 = 'spare (size 16)'</t>
+          <t>DRB102 45 = 'spare (size 16) - was the A/C coolant switch signal, deleted (S35)'</t>
         </is>
       </c>
       <c r="AF89" s="38" t="inlineStr">
@@ -11505,7 +11593,7 @@
         </is>
       </c>
       <c r="H90" s="41" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="I90" s="42" t="inlineStr">
         <is>
@@ -11521,12 +11609,12 @@
       <c r="P90" s="45" t="inlineStr"/>
       <c r="Q90" s="46" t="inlineStr">
         <is>
-          <t>DRB102.53</t>
+          <t>DRB102.46</t>
         </is>
       </c>
       <c r="R90" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 53)</t>
+          <t>spare (DRB102 46)</t>
         </is>
       </c>
       <c r="S90" s="48" t="inlineStr"/>
@@ -11543,7 +11631,7 @@
       <c r="AD90" s="54" t="inlineStr"/>
       <c r="AE90" s="54" t="inlineStr">
         <is>
-          <t>DRB102 53 = 'spare (size 16)'</t>
+          <t>DRB102 46 = 'spare (size 16) - was the A/C coolant switch return, deleted (S35)'</t>
         </is>
       </c>
       <c r="AF90" s="54" t="inlineStr">
@@ -11578,7 +11666,7 @@
         </is>
       </c>
       <c r="H91" s="25" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="I91" s="26" t="inlineStr">
         <is>
@@ -11594,12 +11682,12 @@
       <c r="P91" s="29" t="inlineStr"/>
       <c r="Q91" s="30" t="inlineStr">
         <is>
-          <t>DRB102.57</t>
+          <t>DRB102.52</t>
         </is>
       </c>
       <c r="R91" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 57)</t>
+          <t>spare (DRB102 52)</t>
         </is>
       </c>
       <c r="S91" s="32" t="inlineStr"/>
@@ -11616,7 +11704,7 @@
       <c r="AD91" s="38" t="inlineStr"/>
       <c r="AE91" s="38" t="inlineStr">
         <is>
-          <t>DRB102 57 = 'spare (size 16)'</t>
+          <t>DRB102 52 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF91" s="38" t="inlineStr">
@@ -11651,7 +11739,7 @@
         </is>
       </c>
       <c r="H92" s="41" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I92" s="42" t="inlineStr">
         <is>
@@ -11667,12 +11755,12 @@
       <c r="P92" s="45" t="inlineStr"/>
       <c r="Q92" s="46" t="inlineStr">
         <is>
-          <t>DRB102.58</t>
+          <t>DRB102.53</t>
         </is>
       </c>
       <c r="R92" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 58)</t>
+          <t>spare (DRB102 53)</t>
         </is>
       </c>
       <c r="S92" s="48" t="inlineStr"/>
@@ -11689,7 +11777,7 @@
       <c r="AD92" s="54" t="inlineStr"/>
       <c r="AE92" s="54" t="inlineStr">
         <is>
-          <t>DRB102 58 = 'spare (size 16)'</t>
+          <t>DRB102 53 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF92" s="54" t="inlineStr">
@@ -11724,7 +11812,7 @@
         </is>
       </c>
       <c r="H93" s="25" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I93" s="26" t="inlineStr">
         <is>
@@ -11740,12 +11828,12 @@
       <c r="P93" s="29" t="inlineStr"/>
       <c r="Q93" s="30" t="inlineStr">
         <is>
-          <t>DRB102.59</t>
+          <t>DRB102.57</t>
         </is>
       </c>
       <c r="R93" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 59)</t>
+          <t>spare (DRB102 57)</t>
         </is>
       </c>
       <c r="S93" s="32" t="inlineStr"/>
@@ -11762,7 +11850,7 @@
       <c r="AD93" s="38" t="inlineStr"/>
       <c r="AE93" s="38" t="inlineStr">
         <is>
-          <t>DRB102 59 = 'spare (size 16)'</t>
+          <t>DRB102 57 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF93" s="38" t="inlineStr">
@@ -11797,7 +11885,7 @@
         </is>
       </c>
       <c r="H94" s="41" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I94" s="42" t="inlineStr">
         <is>
@@ -11813,12 +11901,12 @@
       <c r="P94" s="45" t="inlineStr"/>
       <c r="Q94" s="46" t="inlineStr">
         <is>
-          <t>DRB102.61</t>
+          <t>DRB102.58</t>
         </is>
       </c>
       <c r="R94" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 61)</t>
+          <t>spare (DRB102 58)</t>
         </is>
       </c>
       <c r="S94" s="48" t="inlineStr"/>
@@ -11835,7 +11923,7 @@
       <c r="AD94" s="54" t="inlineStr"/>
       <c r="AE94" s="54" t="inlineStr">
         <is>
-          <t>DRB102 61 = 'spare (size 16)'</t>
+          <t>DRB102 58 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF94" s="54" t="inlineStr">
@@ -11861,16 +11949,16 @@
       </c>
       <c r="F95" s="25" t="inlineStr">
         <is>
-          <t>ix_ws_front_p</t>
+          <t>bh_a_fw</t>
         </is>
       </c>
       <c r="G95" s="26" t="inlineStr">
         <is>
-          <t>FRONT WS INLINE</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="H95" s="25" t="n">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="I95" s="26" t="inlineStr">
         <is>
@@ -11886,12 +11974,12 @@
       <c r="P95" s="29" t="inlineStr"/>
       <c r="Q95" s="30" t="inlineStr">
         <is>
-          <t>ix_ws_front_p.6</t>
+          <t>DRB102.59</t>
         </is>
       </c>
       <c r="R95" s="31" t="inlineStr">
         <is>
-          <t>spare (ix_ws_front_p 6)</t>
+          <t>spare (DRB102 59)</t>
         </is>
       </c>
       <c r="S95" s="32" t="inlineStr"/>
@@ -11906,7 +11994,11 @@
       <c r="AB95" s="37" t="inlineStr"/>
       <c r="AC95" s="38" t="inlineStr"/>
       <c r="AD95" s="38" t="inlineStr"/>
-      <c r="AE95" s="38" t="inlineStr"/>
+      <c r="AE95" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 59 = 'spare (size 16)'</t>
+        </is>
+      </c>
       <c r="AF95" s="38" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11930,16 +12022,16 @@
       </c>
       <c r="F96" s="41" t="inlineStr">
         <is>
-          <t>bus_5v_bha_p</t>
+          <t>bh_a_fw</t>
         </is>
       </c>
       <c r="G96" s="42" t="inlineStr">
         <is>
-          <t>+5V BUS</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="H96" s="41" t="n">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="I96" s="42" t="inlineStr">
         <is>
@@ -11955,12 +12047,12 @@
       <c r="P96" s="45" t="inlineStr"/>
       <c r="Q96" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A32</t>
+          <t>DRB102.61</t>
         </is>
       </c>
       <c r="R96" s="47" t="inlineStr">
         <is>
-          <t>+5V sensor (ECU-A A32)</t>
+          <t>spare (DRB102 61)</t>
         </is>
       </c>
       <c r="S96" s="48" t="inlineStr"/>
@@ -11975,7 +12067,11 @@
       <c r="AB96" s="53" t="inlineStr"/>
       <c r="AC96" s="54" t="inlineStr"/>
       <c r="AD96" s="54" t="inlineStr"/>
-      <c r="AE96" s="54" t="inlineStr"/>
+      <c r="AE96" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 61 = 'spare (size 16)'</t>
+        </is>
+      </c>
       <c r="AF96" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11999,16 +12095,16 @@
       </c>
       <c r="F97" s="25" t="inlineStr">
         <is>
-          <t>bus_gnd_bha_p</t>
+          <t>ix_ws_front_p</t>
         </is>
       </c>
       <c r="G97" s="26" t="inlineStr">
         <is>
-          <t>SENSOR GND BUS</t>
+          <t>FRONT WS INLINE</t>
         </is>
       </c>
       <c r="H97" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I97" s="26" t="inlineStr">
         <is>
@@ -12024,12 +12120,12 @@
       <c r="P97" s="29" t="inlineStr"/>
       <c r="Q97" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A24</t>
+          <t>ix_ws_front_p.6</t>
         </is>
       </c>
       <c r="R97" s="31" t="inlineStr">
         <is>
-          <t>Sensor GND (ECU-A A24)</t>
+          <t>spare (ix_ws_front_p 6)</t>
         </is>
       </c>
       <c r="S97" s="32" t="inlineStr"/>
@@ -12068,12 +12164,12 @@
       </c>
       <c r="F98" s="41" t="inlineStr">
         <is>
-          <t>bus_gnd_bha_p</t>
+          <t>bus_5v_bha_p</t>
         </is>
       </c>
       <c r="G98" s="42" t="inlineStr">
         <is>
-          <t>SENSOR GND BUS</t>
+          <t>+5V BUS</t>
         </is>
       </c>
       <c r="H98" s="41" t="n">
@@ -12093,12 +12189,12 @@
       <c r="P98" s="45" t="inlineStr"/>
       <c r="Q98" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A24</t>
+          <t>ECU-A.A32</t>
         </is>
       </c>
       <c r="R98" s="47" t="inlineStr">
         <is>
-          <t>Sensor GND (ECU-A A24)</t>
+          <t>+5V sensor (ECU-A A32)</t>
         </is>
       </c>
       <c r="S98" s="48" t="inlineStr"/>
@@ -12121,8 +12217,146 @@
       </c>
       <c r="AG98" s="54" t="inlineStr"/>
     </row>
+    <row r="99">
+      <c r="A99" s="23" t="inlineStr"/>
+      <c r="B99" s="23" t="inlineStr"/>
+      <c r="C99" s="23" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D99" s="23" t="inlineStr"/>
+      <c r="E99" s="24" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F99" s="25" t="inlineStr">
+        <is>
+          <t>bus_gnd_bha_p</t>
+        </is>
+      </c>
+      <c r="G99" s="26" t="inlineStr">
+        <is>
+          <t>SENSOR GND BUS</t>
+        </is>
+      </c>
+      <c r="H99" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="I99" s="26" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J99" s="26" t="inlineStr"/>
+      <c r="K99" s="27" t="inlineStr"/>
+      <c r="L99" s="28" t="inlineStr"/>
+      <c r="M99" s="29" t="inlineStr"/>
+      <c r="N99" s="28" t="inlineStr"/>
+      <c r="O99" s="29" t="inlineStr"/>
+      <c r="P99" s="29" t="inlineStr"/>
+      <c r="Q99" s="30" t="inlineStr">
+        <is>
+          <t>ECU-A.A24</t>
+        </is>
+      </c>
+      <c r="R99" s="31" t="inlineStr">
+        <is>
+          <t>Sensor GND (ECU-A A24)</t>
+        </is>
+      </c>
+      <c r="S99" s="32" t="inlineStr"/>
+      <c r="T99" s="32" t="inlineStr"/>
+      <c r="U99" s="33" t="inlineStr"/>
+      <c r="V99" s="34" t="inlineStr"/>
+      <c r="W99" s="34" t="inlineStr"/>
+      <c r="X99" s="34" t="inlineStr"/>
+      <c r="Y99" s="34" t="inlineStr"/>
+      <c r="Z99" s="35" t="inlineStr"/>
+      <c r="AA99" s="36" t="inlineStr"/>
+      <c r="AB99" s="37" t="inlineStr"/>
+      <c r="AC99" s="38" t="inlineStr"/>
+      <c r="AD99" s="38" t="inlineStr"/>
+      <c r="AE99" s="38" t="inlineStr"/>
+      <c r="AF99" s="38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG99" s="38" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="39" t="inlineStr"/>
+      <c r="B100" s="39" t="inlineStr"/>
+      <c r="C100" s="39" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D100" s="39" t="inlineStr"/>
+      <c r="E100" s="40" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F100" s="41" t="inlineStr">
+        <is>
+          <t>bus_gnd_bha_p</t>
+        </is>
+      </c>
+      <c r="G100" s="42" t="inlineStr">
+        <is>
+          <t>SENSOR GND BUS</t>
+        </is>
+      </c>
+      <c r="H100" s="41" t="n">
+        <v>8</v>
+      </c>
+      <c r="I100" s="42" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J100" s="42" t="inlineStr"/>
+      <c r="K100" s="43" t="inlineStr"/>
+      <c r="L100" s="44" t="inlineStr"/>
+      <c r="M100" s="45" t="inlineStr"/>
+      <c r="N100" s="44" t="inlineStr"/>
+      <c r="O100" s="45" t="inlineStr"/>
+      <c r="P100" s="45" t="inlineStr"/>
+      <c r="Q100" s="46" t="inlineStr">
+        <is>
+          <t>ECU-A.A24</t>
+        </is>
+      </c>
+      <c r="R100" s="47" t="inlineStr">
+        <is>
+          <t>Sensor GND (ECU-A A24)</t>
+        </is>
+      </c>
+      <c r="S100" s="48" t="inlineStr"/>
+      <c r="T100" s="48" t="inlineStr"/>
+      <c r="U100" s="49" t="inlineStr"/>
+      <c r="V100" s="50" t="inlineStr"/>
+      <c r="W100" s="50" t="inlineStr"/>
+      <c r="X100" s="50" t="inlineStr"/>
+      <c r="Y100" s="50" t="inlineStr"/>
+      <c r="Z100" s="51" t="inlineStr"/>
+      <c r="AA100" s="52" t="inlineStr"/>
+      <c r="AB100" s="53" t="inlineStr"/>
+      <c r="AC100" s="54" t="inlineStr"/>
+      <c r="AD100" s="54" t="inlineStr"/>
+      <c r="AE100" s="54" t="inlineStr"/>
+      <c r="AF100" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG100" s="54" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AG98"/>
+  <autoFilter ref="A2:AG100"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -12134,16 +12368,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="10"/>
@@ -12414,18 +12648,18 @@
         </is>
       </c>
       <c r="F5" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="G5" s="32" t="inlineStr">
+        <is>
+          <t>20+20+20+20+20+20+20+20</t>
+        </is>
+      </c>
+      <c r="H5" s="32" t="n">
+        <v>8176</v>
+      </c>
+      <c r="I5" s="32" t="n">
         <v>10</v>
-      </c>
-      <c r="G5" s="32" t="inlineStr">
-        <is>
-          <t>20+20+20+20+20+20 + shield</t>
-        </is>
-      </c>
-      <c r="H5" s="32" t="n">
-        <v>6132</v>
-      </c>
-      <c r="I5" s="32" t="n">
-        <v>12</v>
       </c>
       <c r="J5" s="56" t="inlineStr">
         <is>
@@ -12835,8 +13069,120 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>sp_shield_a_aps</t>
+        </is>
+      </c>
+      <c r="B13" s="55" t="inlineStr">
+        <is>
+          <t>At the pedal branch - SP-SHIELD-A-APS: pedal drains</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D13" s="30" t="inlineStr">
+        <is>
+          <t>ECU-A.A7</t>
+        </is>
+      </c>
+      <c r="E13" s="31" t="inlineStr">
+        <is>
+          <t>Screen A (ECU A7, SHIELD_A)</t>
+        </is>
+      </c>
+      <c r="F13" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="32" t="inlineStr">
+        <is>
+          <t>20 + shield</t>
+        </is>
+      </c>
+      <c r="H13" s="32" t="n">
+        <v>1022</v>
+      </c>
+      <c r="I13" s="32" t="n">
+        <v>20</v>
+      </c>
+      <c r="J13" s="56" t="inlineStr">
+        <is>
+          <t>SPLICE, SOLDERED, ADHESIVE HEATSHRINK OVER</t>
+        </is>
+      </c>
+      <c r="K13" s="36" t="inlineStr">
+        <is>
+          <t>At the pedal branch (layout node bp_960)</t>
+        </is>
+      </c>
+      <c r="L13" s="38" t="inlineStr">
+        <is>
+          <t>node of the wire list (SoT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="39" t="inlineStr">
+        <is>
+          <t>sp_shield_a_wsf</t>
+        </is>
+      </c>
+      <c r="B14" s="57" t="inlineStr">
+        <is>
+          <t>At the front WS inline - SP-SHIELD-A-WSF: front wheel-speed drains</t>
+        </is>
+      </c>
+      <c r="C14" s="39" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D14" s="46" t="inlineStr">
+        <is>
+          <t>ECU-A.A7</t>
+        </is>
+      </c>
+      <c r="E14" s="47" t="inlineStr">
+        <is>
+          <t>Screen A (ECU A7, SHIELD_A)</t>
+        </is>
+      </c>
+      <c r="F14" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="48" t="inlineStr">
+        <is>
+          <t>20 + shield</t>
+        </is>
+      </c>
+      <c r="H14" s="48" t="n">
+        <v>1022</v>
+      </c>
+      <c r="I14" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="J14" s="58" t="inlineStr">
+        <is>
+          <t>SPLICE, SOLDERED, ADHESIVE HEATSHRINK OVER</t>
+        </is>
+      </c>
+      <c r="K14" s="52" t="inlineStr">
+        <is>
+          <t>At the front WS inline (layout node bp_1020)</t>
+        </is>
+      </c>
+      <c r="L14" s="54" t="inlineStr">
+        <is>
+          <t>node of the wire list (SoT)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:L12"/>
+  <autoFilter ref="A2:L14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/harness/wirelist/A-cabin-wirelist.xlsx
+++ b/docs/harness/wirelist/A-cabin-wirelist.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Mates" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wire list'!$A$2:$AG$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wire list'!$A$2:$AG$120</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Wire list'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Splices'!$A$2:$L$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Splices'!$1:$2</definedName>
@@ -745,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AG100"/>
+  <dimension ref="A1:AG120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="N3" s="28" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="O3" s="29" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
       <c r="AD3" s="38" t="inlineStr"/>
       <c r="AE3" s="38" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A4 Inj 1 (INJ1); DRB102 31 = section A c13 'ECU-A A4'</t>
+          <t>channels.csv ecu_a A4 Inj 1 (INJ1); DRB102 21 = loom A c21 'ECU-A A4'</t>
         </is>
       </c>
       <c r="AF3" s="38" t="inlineStr">
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="N4" s="44" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="O4" s="45" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
       <c r="AD4" s="54" t="inlineStr"/>
       <c r="AE4" s="54" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A3 Inj 2 (INJ2); DRB102 32 = section A c14 'ECU-A A3'</t>
+          <t>channels.csv ecu_a A3 Inj 2 (INJ2); DRB102 22 = loom A c22 'ECU-A A3'</t>
         </is>
       </c>
       <c r="AF4" s="54" t="inlineStr">
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="N5" s="28" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="O5" s="29" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
       <c r="AD5" s="38" t="inlineStr"/>
       <c r="AE5" s="38" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A2 Inj 3 (INJ3); DRB102 33 = section A c15 'ECU-A A2'</t>
+          <t>channels.csv ecu_a A2 Inj 3 (INJ3); DRB102 23 = loom A c23 'ECU-A A2'</t>
         </is>
       </c>
       <c r="AF5" s="38" t="inlineStr">
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="N6" s="44" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="O6" s="45" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
       <c r="AD6" s="54" t="inlineStr"/>
       <c r="AE6" s="54" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A1 Inj 4 (INJ4); DRB102 34 = section A c16 'ECU-A A1'</t>
+          <t>channels.csv ecu_a A1 Inj 4 (INJ4); DRB102 24 = loom A c24 'ECU-A A1'</t>
         </is>
       </c>
       <c r="AF6" s="54" t="inlineStr">
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="N7" s="28" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="O7" s="29" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
       <c r="AD7" s="38" t="inlineStr"/>
       <c r="AE7" s="38" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A13 Ign 1 (IGN1); DRB102 35 = section A c17 'ECU-A A13'</t>
+          <t>channels.csv ecu_a A13 Ign 1 (IGN1); DRB102 9 = loom A c9 'ECU-A A13'</t>
         </is>
       </c>
       <c r="AF7" s="38" t="inlineStr">
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="N8" s="44" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="O8" s="45" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
       <c r="AD8" s="54" t="inlineStr"/>
       <c r="AE8" s="54" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A12 Ign 2 (IGN2); DRB102 36 = section A c18 'ECU-A A12'</t>
+          <t>channels.csv ecu_a A12 Ign 2 (IGN2); DRB102 10 = loom A c10 'ECU-A A12'</t>
         </is>
       </c>
       <c r="AF8" s="54" t="inlineStr">
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="N9" s="28" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="O9" s="29" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       <c r="AD9" s="38" t="inlineStr"/>
       <c r="AE9" s="38" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A11 Ign 3 (IGN3); DRB102 37 = section A c19 'ECU-A A11'</t>
+          <t>channels.csv ecu_a A11 Ign 3 (IGN3); DRB102 11 = loom A c11 'ECU-A A11'</t>
         </is>
       </c>
       <c r="AF9" s="38" t="inlineStr">
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="N10" s="44" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="O10" s="45" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
       <c r="AD10" s="54" t="inlineStr"/>
       <c r="AE10" s="54" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A10 Ign 4 (IGN4); DRB102 38 = section A c20 'ECU-A A10'</t>
+          <t>channels.csv ecu_a A10 Ign 4 (IGN4); DRB102 12 = loom A c12 'ECU-A A10'</t>
         </is>
       </c>
       <c r="AF10" s="54" t="inlineStr">
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="N11" s="28" t="n">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="O11" s="29" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
       <c r="AD11" s="38" t="inlineStr"/>
       <c r="AE11" s="38" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A8 Trigger 1 (TRIG1_CRANK); DRB102 9 = section A c24 'ECU-A A8'</t>
+          <t>channels.csv ecu_a A8 Trigger 1 (TRIG1_CRANK); DRB102 74 = loom A c74 'ECU-A A8'</t>
         </is>
       </c>
       <c r="AF11" s="38" t="inlineStr">
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="N12" s="44" t="n">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="O12" s="45" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
       <c r="AD12" s="54" t="inlineStr"/>
       <c r="AE12" s="54" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A30 DI 1 (DI1_TURBO_SPD); DRB102 17 = section A c7 'ECU-A A30'</t>
+          <t>channels.csv ecu_a A30 DI 1 (DI1_TURBO_SPD); DRB102 53 = loom A c53 'ECU-A A30'</t>
         </is>
       </c>
       <c r="AF12" s="54" t="inlineStr">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="N13" s="28" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="O13" s="29" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
       <c r="AD13" s="38" t="inlineStr"/>
       <c r="AE13" s="38" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A31 DI 2 (DI2_FLEX); DRB102 21 = section A c9 'ECU-A A31'</t>
+          <t>channels.csv ecu_a A31 DI 2 (DI2_FLEX); DRB102 31 = loom A c31 'ECU-A A31'</t>
         </is>
       </c>
       <c r="AF13" s="38" t="inlineStr">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="N14" s="44" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="O14" s="45" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
       <c r="AD14" s="54" t="inlineStr"/>
       <c r="AE14" s="54" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A22 An Volt 2 (AV2_TPS_MAIN); DRB102 24 = section A c21 'ECU-A A22'</t>
+          <t>channels.csv ecu_a A22 An Volt 2 (AV2_TPS_MAIN); DRB102 42 = loom A c42 'ECU-A A22'</t>
         </is>
       </c>
       <c r="AF14" s="54" t="inlineStr">
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="N15" s="28" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="O15" s="29" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
       <c r="AD15" s="38" t="inlineStr"/>
       <c r="AE15" s="38" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A33 An Volt 3 (AV3_TPS_SUB); DRB102 25 = section A c22 'ECU-A A33'</t>
+          <t>channels.csv ecu_a A33 An Volt 3 (AV3_TPS_SUB); DRB102 44 = loom A c44 'ECU-A A33'</t>
         </is>
       </c>
       <c r="AF15" s="38" t="inlineStr">
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="N16" s="44" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="O16" s="45" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
       <c r="AD16" s="54" t="inlineStr"/>
       <c r="AE16" s="54" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A17 An Volt 1 (AV1_MAP); DRB102 30 = section A c8 'ECU-A A17'</t>
+          <t>channels.csv ecu_a A17 An Volt 1 (AV1_MAP); DRB102 17 = loom A c17 'ECU-A A17'</t>
         </is>
       </c>
       <c r="AF16" s="54" t="inlineStr">
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="N17" s="28" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="O17" s="29" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
       <c r="AD17" s="38" t="inlineStr"/>
       <c r="AE17" s="38" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A21 Aux 1 (AUX1_BOOST); DRB102 39 = section A c23 'ECU-A A21'</t>
+          <t>channels.csv ecu_a A21 Aux 1 (AUX1_BOOST); DRB102 58 = loom A c58 'ECU-A A21'</t>
         </is>
       </c>
       <c r="AF17" s="38" t="inlineStr">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="N18" s="44" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="O18" s="45" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
       <c r="AD18" s="54" t="inlineStr"/>
       <c r="AE18" s="54" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A15 Temp 1 (TEMP1_ECT); DRB102 40 = section A c25 'ECU-A A15'</t>
+          <t>channels.csv ecu_a A15 Temp 1 (TEMP1_ECT); DRB102 70 = loom A c70 'ECU-A A15'</t>
         </is>
       </c>
       <c r="AF18" s="54" t="inlineStr">
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="N19" s="28" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="O19" s="29" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
       <c r="AD19" s="38" t="inlineStr"/>
       <c r="AE19" s="38" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A16 Temp 2 (TEMP2_IAT); DRB102 41 = section A c26 'ECU-A A16'</t>
+          <t>channels.csv ecu_a A16 Temp 2 (TEMP2_IAT); DRB102 33 = loom A c33 'ECU-A A16'</t>
         </is>
       </c>
       <c r="AF19" s="38" t="inlineStr">
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="N20" s="44" t="n">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="O20" s="45" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
       <c r="AD20" s="54" t="inlineStr"/>
       <c r="AE20" s="54" t="inlineStr">
         <is>
-          <t>channels.csv ecu_a A27 Aux 7 (AUX7_MRS_SPD); DRB102 44 = section A c36 'Aux 7 MRS speed-out (ECU A27)'</t>
+          <t>channels.csv ecu_a A27 Aux 7 (AUX7_MRS_SPD); DRB102 84 = loom A c84 'ECU-A A27'</t>
         </is>
       </c>
       <c r="AF20" s="54" t="inlineStr">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="N22" s="44" t="n">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="O22" s="45" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       <c r="AD22" s="54" t="inlineStr"/>
       <c r="AE22" s="54" t="inlineStr">
         <is>
-          <t>splice sp_trig2: node of the wire list (SoT); DRB102 13 = section A c29 'ECU-A A9'</t>
+          <t>splice sp_trig2: node of the wire list (SoT); DRB102 64 = loom A c64 'Cam sensor signal'</t>
         </is>
       </c>
       <c r="AF22" s="54" t="inlineStr">
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="N26" s="44" t="n">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="O26" s="45" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
       <c r="AD26" s="54" t="inlineStr"/>
       <c r="AE26" s="54" t="inlineStr">
         <is>
-          <t>splice sp_8v: node of the wire list (SoT); DRB102 12 = section A c4 '+8V Out to cam Hall'</t>
+          <t>splice sp_8v: node of the wire list (SoT); DRB102 63 = loom A c63 '+8 V to cam sensor'</t>
         </is>
       </c>
       <c r="AF26" s="54" t="inlineStr">
@@ -4218,7 +4218,7 @@
         </is>
       </c>
       <c r="N29" s="28" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="O29" s="29" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
       <c r="AD29" s="38" t="inlineStr"/>
       <c r="AE29" s="38" t="inlineStr">
         <is>
-          <t>DRB102 23 = section A c2 '+5V Out to engine sensors (+5 V bus plug bus_5v_bh'</t>
+          <t>DRB102 41 = loom A c41 '+5 V throttle sensor'</t>
         </is>
       </c>
       <c r="AF29" s="38" t="inlineStr">
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="N30" s="44" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="O30" s="45" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
       <c r="AD30" s="54" t="inlineStr"/>
       <c r="AE30" s="54" t="inlineStr">
         <is>
-          <t>DRB102 28 = section A c39 '+5V Out to engine sensors (+5 V bus plug bus_5v_bh'</t>
+          <t>DRB102 16 = loom A c16 '+5 V MAP sensor'</t>
         </is>
       </c>
       <c r="AF30" s="54" t="inlineStr">
@@ -4448,7 +4448,7 @@
         </is>
       </c>
       <c r="N31" s="28" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="O31" s="29" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
       <c r="AD31" s="38" t="inlineStr"/>
       <c r="AE31" s="38" t="inlineStr">
         <is>
-          <t>DRB102 16 = section A c40 '+5V Out to engine sensors (+5 V bus plug bus_5v_bh'</t>
+          <t>DRB102 52 = loom A c52 '+5 V turbo speed'</t>
         </is>
       </c>
       <c r="AF31" s="38" t="inlineStr">
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="N32" s="44" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="O32" s="45" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
       <c r="AD32" s="54" t="inlineStr"/>
       <c r="AE32" s="54" t="inlineStr">
         <is>
-          <t>DRB102 47 = section A c45 '+5V Out to B engine sensors via IX_B_RAIL - oil pr'</t>
+          <t>DRB102 27 = loom A c27 '+5 V oil pressure'</t>
         </is>
       </c>
       <c r="AF32" s="54" t="inlineStr">
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="N33" s="28" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="O33" s="29" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
       <c r="AD33" s="38" t="inlineStr"/>
       <c r="AE33" s="38" t="inlineStr">
         <is>
-          <t>DRB102 50 = section A c46 '+5V Out to B engine sensors via IX_B_RAIL - fuel p'</t>
+          <t>DRB102 13 = loom A c13 '+5 V fuel pressure'</t>
         </is>
       </c>
       <c r="AF33" s="38" t="inlineStr">
@@ -4793,7 +4793,7 @@
         </is>
       </c>
       <c r="N34" s="44" t="n">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="O34" s="45" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
       <c r="AD34" s="54" t="inlineStr"/>
       <c r="AE34" s="54" t="inlineStr">
         <is>
-          <t>DRB102 51 = section A c47 '+5V Out to B engine sensors via IX_B_RAIL - coolan'</t>
+          <t>DRB102 25 = loom A c25 '+5 V coolant press'</t>
         </is>
       </c>
       <c r="AF34" s="54" t="inlineStr">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="N40" s="44" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="O40" s="45" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
       <c r="AD40" s="54" t="inlineStr"/>
       <c r="AE40" s="54" t="inlineStr">
         <is>
-          <t>DRB102 26 = section A c3 'Gnd Out to engine sensors (sensor GND bus plug bus'</t>
+          <t>DRB102 34 = loom A c34 'Gnd IAT/TPS/coolant'</t>
         </is>
       </c>
       <c r="AF40" s="54" t="inlineStr">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="N41" s="28" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="O41" s="29" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
       <c r="AD41" s="38" t="inlineStr"/>
       <c r="AE41" s="38" t="inlineStr">
         <is>
-          <t>DRB102 10 = section A c41 'Gnd Out to engine sensors (sensor GND bus plug bus'</t>
+          <t>DRB102 75 = loom A c75 'Gnd crank sensor'</t>
         </is>
       </c>
       <c r="AF41" s="38" t="inlineStr">
@@ -5751,7 +5751,7 @@
         </is>
       </c>
       <c r="N42" s="44" t="n">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="O42" s="45" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
       <c r="AD42" s="54" t="inlineStr"/>
       <c r="AE42" s="54" t="inlineStr">
         <is>
-          <t>DRB102 14 = section A c42 'Gnd Out to engine sensors (sensor GND bus plug bus'</t>
+          <t>DRB102 65 = loom A c65 'Gnd cam sensor'</t>
         </is>
       </c>
       <c r="AF42" s="54" t="inlineStr">
@@ -5870,7 +5870,7 @@
         </is>
       </c>
       <c r="N43" s="28" t="n">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="O43" s="29" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
       <c r="AD43" s="38" t="inlineStr"/>
       <c r="AE43" s="38" t="inlineStr">
         <is>
-          <t>DRB102 18 = section A c43 'Gnd Out to engine sensors (sensor GND bus plug bus'</t>
+          <t>DRB102 56 = loom A c56 'Gnd turbo speed'</t>
         </is>
       </c>
       <c r="AF43" s="38" t="inlineStr">
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="N44" s="44" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="O44" s="45" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
       <c r="AD44" s="54" t="inlineStr"/>
       <c r="AE44" s="54" t="inlineStr">
         <is>
-          <t>DRB102 29 = section A c44 'Gnd Out to engine sensors (sensor GND bus plug bus'</t>
+          <t>DRB102 18 = loom A c18 'Gnd flex + MAP'</t>
         </is>
       </c>
       <c r="AF44" s="54" t="inlineStr">
@@ -6709,7 +6709,7 @@
         </is>
       </c>
       <c r="N50" s="44" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O50" s="45" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
       <c r="AD50" s="54" t="inlineStr"/>
       <c r="AE50" s="54" t="inlineStr">
         <is>
-          <t>splice sp_sw12: node of the wire list (SoT); DRB102 20 = section A c5 'Switched 12V to engine sensors'</t>
+          <t>splice sp_sw12: node of the wire list (SoT); DRB102 30 = loom A c30 '+12 V boost + flex'</t>
         </is>
       </c>
       <c r="AF50" s="54" t="inlineStr">
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="N51" s="28" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="O51" s="29" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
       <c r="AD51" s="38" t="inlineStr"/>
       <c r="AE51" s="38" t="inlineStr">
         <is>
-          <t>splice sp_sw12: node of the wire list (SoT); DRB102 90 = section B c20 'Switched 12V to gearbox VSS (from sp_sw12)'</t>
+          <t>splice sp_sw12: node of the wire list (SoT); DRB102 67 = loom B c67 '+12 V gearbox speed'</t>
         </is>
       </c>
       <c r="AF51" s="38" t="inlineStr">
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="N52" s="44" t="n">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="O52" s="45" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
       <c r="AD52" s="54" t="inlineStr"/>
       <c r="AE52" s="54" t="inlineStr">
         <is>
-          <t>fuse-box plan fb_logic BUS2-12 (20 AWG); DRB102 42 = section A c35 'MRS EPS pump logic enable (fuse box LOGIC MRS, 7.5'</t>
+          <t>fuse-box plan fb_logic BUS2-12 (20 AWG); DRB102 83 = loom A c83 'EHPS enable +12 V'</t>
         </is>
       </c>
       <c r="AF52" s="54" t="inlineStr">
@@ -7630,7 +7630,7 @@
       <c r="AD57" s="38" t="inlineStr"/>
       <c r="AE57" s="38" t="inlineStr">
         <is>
-          <t>DRB102 96 = section B c4 'CAN-Lambda ground to cabin chassis ground (14 AWG)'; splice sp_chassis: node of the wire list (SoT)</t>
+          <t>DRB102 96 = loom B c96 'CAN-Lambda ground'; splice sp_chassis: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF57" s="38" t="inlineStr">
@@ -8278,7 +8278,7 @@
         </is>
       </c>
       <c r="H63" s="25" t="n">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="I63" s="26" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
       <c r="AD63" s="38" t="inlineStr"/>
       <c r="AE63" s="38" t="inlineStr">
         <is>
-          <t>DRB102 11 = section A c33 'Crank VR screen'; splice sp_shield_a: node of the wire list (SoT)</t>
+          <t>DRB102 76 = loom A c76 'Crank sensor shield'; splice sp_shield_a: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF63" s="38" t="inlineStr">
@@ -8401,7 +8401,7 @@
         </is>
       </c>
       <c r="H64" s="41" t="n">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="I64" s="42" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
       <c r="AD64" s="54" t="inlineStr"/>
       <c r="AE64" s="54" t="inlineStr">
         <is>
-          <t>DRB102 15 = section A c34 'Cam Hall screen'; splice sp_shield_a: node of the wire list (SoT)</t>
+          <t>DRB102 66 = loom A c66 'Cam sensor shield'; splice sp_shield_a: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF64" s="54" t="inlineStr">
@@ -8520,7 +8520,7 @@
         </is>
       </c>
       <c r="H65" s="25" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="I65" s="26" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
       <c r="AD65" s="38" t="inlineStr"/>
       <c r="AE65" s="38" t="inlineStr">
         <is>
-          <t>DRB102 19 = section A c6 'Turbo speed screen (to A7)'; splice sp_shield_a: node of the wire list (SoT)</t>
+          <t>DRB102 57 = loom A c57 'Turbo speed shield'; splice sp_shield_a: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF65" s="38" t="inlineStr">
@@ -8639,7 +8639,7 @@
         </is>
       </c>
       <c r="H66" s="41" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I66" s="42" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
       <c r="AD66" s="54" t="inlineStr"/>
       <c r="AE66" s="54" t="inlineStr">
         <is>
-          <t>DRB102 22 = section A c10 'Flex fuel screen (to A7)'; splice sp_shield_a: node of the wire list (SoT)</t>
+          <t>DRB102 32 = loom A c32 'Flex fuel shield'; splice sp_shield_a: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF66" s="54" t="inlineStr">
@@ -8758,7 +8758,7 @@
         </is>
       </c>
       <c r="H67" s="25" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="I67" s="26" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
       <c r="AD67" s="38" t="inlineStr"/>
       <c r="AE67" s="38" t="inlineStr">
         <is>
-          <t>DRB102 27 = section A c11 'ETB sensor group screen (to A7)'; splice sp_shield_a: node of the wire list (SoT)</t>
+          <t>DRB102 47 = loom A c47 'Throttle shield'; splice sp_shield_a: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF67" s="38" t="inlineStr">
@@ -9296,7 +9296,7 @@
         </is>
       </c>
       <c r="N71" s="28" t="n">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="O71" s="29" t="inlineStr">
         <is>
@@ -9306,12 +9306,12 @@
       <c r="P71" s="29" t="inlineStr"/>
       <c r="Q71" s="30" t="inlineStr">
         <is>
-          <t>DRB102.56</t>
+          <t>DRB102.85</t>
         </is>
       </c>
       <c r="R71" s="31" t="inlineStr">
         <is>
-          <t>EHPS relay coil (-) (DRB102 56)</t>
+          <t>EHPS relay coil (-) (DRB102 85)</t>
         </is>
       </c>
       <c r="S71" s="32" t="inlineStr"/>
@@ -9344,7 +9344,7 @@
       <c r="AD71" s="38" t="inlineStr"/>
       <c r="AE71" s="38" t="inlineStr">
         <is>
-          <t>channels.csv k_eps c2 Coil 85 (MRS_RLY); DRB102 56 = section A c27 'EPS relay coil 85 (R22) - from the MR-S pump B5'</t>
+          <t>channels.csv k_eps c2 Coil 85 (MRS_RLY); DRB102 85 = loom A c85 'EHPS relay coil (-)'</t>
         </is>
       </c>
       <c r="AF71" s="38" t="inlineStr">
@@ -11511,16 +11511,16 @@
       </c>
       <c r="F89" s="25" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>ix_ws_front_p</t>
         </is>
       </c>
       <c r="G89" s="26" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>FRONT WS INLINE</t>
         </is>
       </c>
       <c r="H89" s="25" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="I89" s="26" t="inlineStr">
         <is>
@@ -11536,12 +11536,12 @@
       <c r="P89" s="29" t="inlineStr"/>
       <c r="Q89" s="30" t="inlineStr">
         <is>
-          <t>DRB102.45</t>
+          <t>ix_ws_front_p.6</t>
         </is>
       </c>
       <c r="R89" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 45)</t>
+          <t>spare (ix_ws_front_p 6)</t>
         </is>
       </c>
       <c r="S89" s="32" t="inlineStr"/>
@@ -11556,11 +11556,7 @@
       <c r="AB89" s="37" t="inlineStr"/>
       <c r="AC89" s="38" t="inlineStr"/>
       <c r="AD89" s="38" t="inlineStr"/>
-      <c r="AE89" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 45 = 'spare (size 16) - was the A/C coolant switch signal, deleted (S35)'</t>
-        </is>
-      </c>
+      <c r="AE89" s="38" t="inlineStr"/>
       <c r="AF89" s="38" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11584,16 +11580,16 @@
       </c>
       <c r="F90" s="41" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>bus_5v_bha_p</t>
         </is>
       </c>
       <c r="G90" s="42" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>+5V BUS</t>
         </is>
       </c>
       <c r="H90" s="41" t="n">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="I90" s="42" t="inlineStr">
         <is>
@@ -11609,12 +11605,12 @@
       <c r="P90" s="45" t="inlineStr"/>
       <c r="Q90" s="46" t="inlineStr">
         <is>
-          <t>DRB102.46</t>
+          <t>ECU-A.A32</t>
         </is>
       </c>
       <c r="R90" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 46)</t>
+          <t>+5V sensor (ECU-A A32)</t>
         </is>
       </c>
       <c r="S90" s="48" t="inlineStr"/>
@@ -11629,11 +11625,7 @@
       <c r="AB90" s="53" t="inlineStr"/>
       <c r="AC90" s="54" t="inlineStr"/>
       <c r="AD90" s="54" t="inlineStr"/>
-      <c r="AE90" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 46 = 'spare (size 16) - was the A/C coolant switch return, deleted (S35)'</t>
-        </is>
-      </c>
+      <c r="AE90" s="54" t="inlineStr"/>
       <c r="AF90" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11657,16 +11649,16 @@
       </c>
       <c r="F91" s="25" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>bus_gnd_bha_p</t>
         </is>
       </c>
       <c r="G91" s="26" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>SENSOR GND BUS</t>
         </is>
       </c>
       <c r="H91" s="25" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="I91" s="26" t="inlineStr">
         <is>
@@ -11682,12 +11674,12 @@
       <c r="P91" s="29" t="inlineStr"/>
       <c r="Q91" s="30" t="inlineStr">
         <is>
-          <t>DRB102.52</t>
+          <t>ECU-A.A24</t>
         </is>
       </c>
       <c r="R91" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 52)</t>
+          <t>Sensor GND (ECU-A A24)</t>
         </is>
       </c>
       <c r="S91" s="32" t="inlineStr"/>
@@ -11702,11 +11694,7 @@
       <c r="AB91" s="37" t="inlineStr"/>
       <c r="AC91" s="38" t="inlineStr"/>
       <c r="AD91" s="38" t="inlineStr"/>
-      <c r="AE91" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 52 = 'spare (size 16)'</t>
-        </is>
-      </c>
+      <c r="AE91" s="38" t="inlineStr"/>
       <c r="AF91" s="38" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11730,16 +11718,16 @@
       </c>
       <c r="F92" s="41" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>bus_gnd_bha_p</t>
         </is>
       </c>
       <c r="G92" s="42" t="inlineStr">
         <is>
-          <t>BULKHEAD</t>
+          <t>SENSOR GND BUS</t>
         </is>
       </c>
       <c r="H92" s="41" t="n">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="I92" s="42" t="inlineStr">
         <is>
@@ -11755,12 +11743,12 @@
       <c r="P92" s="45" t="inlineStr"/>
       <c r="Q92" s="46" t="inlineStr">
         <is>
-          <t>DRB102.53</t>
+          <t>ECU-A.A24</t>
         </is>
       </c>
       <c r="R92" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 53)</t>
+          <t>Sensor GND (ECU-A A24)</t>
         </is>
       </c>
       <c r="S92" s="48" t="inlineStr"/>
@@ -11775,11 +11763,7 @@
       <c r="AB92" s="53" t="inlineStr"/>
       <c r="AC92" s="54" t="inlineStr"/>
       <c r="AD92" s="54" t="inlineStr"/>
-      <c r="AE92" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 53 = 'spare (size 16)'</t>
-        </is>
-      </c>
+      <c r="AE92" s="54" t="inlineStr"/>
       <c r="AF92" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -11812,7 +11796,7 @@
         </is>
       </c>
       <c r="H93" s="25" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="I93" s="26" t="inlineStr">
         <is>
@@ -11828,12 +11812,12 @@
       <c r="P93" s="29" t="inlineStr"/>
       <c r="Q93" s="30" t="inlineStr">
         <is>
-          <t>DRB102.57</t>
+          <t>DRB102.3</t>
         </is>
       </c>
       <c r="R93" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 57)</t>
+          <t>spare (DRB102 3)</t>
         </is>
       </c>
       <c r="S93" s="32" t="inlineStr"/>
@@ -11850,7 +11834,7 @@
       <c r="AD93" s="38" t="inlineStr"/>
       <c r="AE93" s="38" t="inlineStr">
         <is>
-          <t>DRB102 57 = 'spare (size 16)'</t>
+          <t>DRB102 3 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF93" s="38" t="inlineStr">
@@ -11885,7 +11869,7 @@
         </is>
       </c>
       <c r="H94" s="41" t="n">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="I94" s="42" t="inlineStr">
         <is>
@@ -11901,12 +11885,12 @@
       <c r="P94" s="45" t="inlineStr"/>
       <c r="Q94" s="46" t="inlineStr">
         <is>
-          <t>DRB102.58</t>
+          <t>DRB102.4</t>
         </is>
       </c>
       <c r="R94" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 58)</t>
+          <t>spare (DRB102 4)</t>
         </is>
       </c>
       <c r="S94" s="48" t="inlineStr"/>
@@ -11923,7 +11907,7 @@
       <c r="AD94" s="54" t="inlineStr"/>
       <c r="AE94" s="54" t="inlineStr">
         <is>
-          <t>DRB102 58 = 'spare (size 16)'</t>
+          <t>DRB102 4 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF94" s="54" t="inlineStr">
@@ -11958,7 +11942,7 @@
         </is>
       </c>
       <c r="H95" s="25" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="I95" s="26" t="inlineStr">
         <is>
@@ -11974,12 +11958,12 @@
       <c r="P95" s="29" t="inlineStr"/>
       <c r="Q95" s="30" t="inlineStr">
         <is>
-          <t>DRB102.59</t>
+          <t>DRB102.5</t>
         </is>
       </c>
       <c r="R95" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 59)</t>
+          <t>spare (DRB102 5)</t>
         </is>
       </c>
       <c r="S95" s="32" t="inlineStr"/>
@@ -11996,7 +11980,7 @@
       <c r="AD95" s="38" t="inlineStr"/>
       <c r="AE95" s="38" t="inlineStr">
         <is>
-          <t>DRB102 59 = 'spare (size 16)'</t>
+          <t>DRB102 5 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF95" s="38" t="inlineStr">
@@ -12031,7 +12015,7 @@
         </is>
       </c>
       <c r="H96" s="41" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="I96" s="42" t="inlineStr">
         <is>
@@ -12047,12 +12031,12 @@
       <c r="P96" s="45" t="inlineStr"/>
       <c r="Q96" s="46" t="inlineStr">
         <is>
-          <t>DRB102.61</t>
+          <t>DRB102.6</t>
         </is>
       </c>
       <c r="R96" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 61)</t>
+          <t>spare (DRB102 6)</t>
         </is>
       </c>
       <c r="S96" s="48" t="inlineStr"/>
@@ -12069,7 +12053,7 @@
       <c r="AD96" s="54" t="inlineStr"/>
       <c r="AE96" s="54" t="inlineStr">
         <is>
-          <t>DRB102 61 = 'spare (size 16)'</t>
+          <t>DRB102 6 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF96" s="54" t="inlineStr">
@@ -12095,16 +12079,16 @@
       </c>
       <c r="F97" s="25" t="inlineStr">
         <is>
-          <t>ix_ws_front_p</t>
+          <t>bh_a_fw</t>
         </is>
       </c>
       <c r="G97" s="26" t="inlineStr">
         <is>
-          <t>FRONT WS INLINE</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="H97" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I97" s="26" t="inlineStr">
         <is>
@@ -12120,12 +12104,12 @@
       <c r="P97" s="29" t="inlineStr"/>
       <c r="Q97" s="30" t="inlineStr">
         <is>
-          <t>ix_ws_front_p.6</t>
+          <t>DRB102.7</t>
         </is>
       </c>
       <c r="R97" s="31" t="inlineStr">
         <is>
-          <t>spare (ix_ws_front_p 6)</t>
+          <t>spare (DRB102 7)</t>
         </is>
       </c>
       <c r="S97" s="32" t="inlineStr"/>
@@ -12140,7 +12124,11 @@
       <c r="AB97" s="37" t="inlineStr"/>
       <c r="AC97" s="38" t="inlineStr"/>
       <c r="AD97" s="38" t="inlineStr"/>
-      <c r="AE97" s="38" t="inlineStr"/>
+      <c r="AE97" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 7 = 'spare (size 12)'</t>
+        </is>
+      </c>
       <c r="AF97" s="38" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12164,12 +12152,12 @@
       </c>
       <c r="F98" s="41" t="inlineStr">
         <is>
-          <t>bus_5v_bha_p</t>
+          <t>bh_a_fw</t>
         </is>
       </c>
       <c r="G98" s="42" t="inlineStr">
         <is>
-          <t>+5V BUS</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="H98" s="41" t="n">
@@ -12189,12 +12177,12 @@
       <c r="P98" s="45" t="inlineStr"/>
       <c r="Q98" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A32</t>
+          <t>DRB102.8</t>
         </is>
       </c>
       <c r="R98" s="47" t="inlineStr">
         <is>
-          <t>+5V sensor (ECU-A A32)</t>
+          <t>spare (DRB102 8)</t>
         </is>
       </c>
       <c r="S98" s="48" t="inlineStr"/>
@@ -12209,7 +12197,11 @@
       <c r="AB98" s="53" t="inlineStr"/>
       <c r="AC98" s="54" t="inlineStr"/>
       <c r="AD98" s="54" t="inlineStr"/>
-      <c r="AE98" s="54" t="inlineStr"/>
+      <c r="AE98" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 8 = 'spare (size 12)'</t>
+        </is>
+      </c>
       <c r="AF98" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12233,16 +12225,16 @@
       </c>
       <c r="F99" s="25" t="inlineStr">
         <is>
-          <t>bus_gnd_bha_p</t>
+          <t>bh_a_fw</t>
         </is>
       </c>
       <c r="G99" s="26" t="inlineStr">
         <is>
-          <t>SENSOR GND BUS</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="H99" s="25" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="I99" s="26" t="inlineStr">
         <is>
@@ -12258,12 +12250,12 @@
       <c r="P99" s="29" t="inlineStr"/>
       <c r="Q99" s="30" t="inlineStr">
         <is>
-          <t>ECU-A.A24</t>
+          <t>DRB102.19</t>
         </is>
       </c>
       <c r="R99" s="31" t="inlineStr">
         <is>
-          <t>Sensor GND (ECU-A A24)</t>
+          <t>spare (DRB102 19)</t>
         </is>
       </c>
       <c r="S99" s="32" t="inlineStr"/>
@@ -12278,7 +12270,11 @@
       <c r="AB99" s="37" t="inlineStr"/>
       <c r="AC99" s="38" t="inlineStr"/>
       <c r="AD99" s="38" t="inlineStr"/>
-      <c r="AE99" s="38" t="inlineStr"/>
+      <c r="AE99" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 19 = 'spare (size 16)'</t>
+        </is>
+      </c>
       <c r="AF99" s="38" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12302,16 +12298,16 @@
       </c>
       <c r="F100" s="41" t="inlineStr">
         <is>
-          <t>bus_gnd_bha_p</t>
+          <t>bh_a_fw</t>
         </is>
       </c>
       <c r="G100" s="42" t="inlineStr">
         <is>
-          <t>SENSOR GND BUS</t>
+          <t>BULKHEAD</t>
         </is>
       </c>
       <c r="H100" s="41" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I100" s="42" t="inlineStr">
         <is>
@@ -12327,12 +12323,12 @@
       <c r="P100" s="45" t="inlineStr"/>
       <c r="Q100" s="46" t="inlineStr">
         <is>
-          <t>ECU-A.A24</t>
+          <t>DRB102.20</t>
         </is>
       </c>
       <c r="R100" s="47" t="inlineStr">
         <is>
-          <t>Sensor GND (ECU-A A24)</t>
+          <t>spare (DRB102 20)</t>
         </is>
       </c>
       <c r="S100" s="48" t="inlineStr"/>
@@ -12347,7 +12343,11 @@
       <c r="AB100" s="53" t="inlineStr"/>
       <c r="AC100" s="54" t="inlineStr"/>
       <c r="AD100" s="54" t="inlineStr"/>
-      <c r="AE100" s="54" t="inlineStr"/>
+      <c r="AE100" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 20 = 'spare (size 16)'</t>
+        </is>
+      </c>
       <c r="AF100" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -12355,8 +12355,1468 @@
       </c>
       <c r="AG100" s="54" t="inlineStr"/>
     </row>
+    <row r="101">
+      <c r="A101" s="23" t="inlineStr"/>
+      <c r="B101" s="23" t="inlineStr"/>
+      <c r="C101" s="23" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D101" s="23" t="inlineStr"/>
+      <c r="E101" s="24" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F101" s="25" t="inlineStr">
+        <is>
+          <t>bh_a_fw</t>
+        </is>
+      </c>
+      <c r="G101" s="26" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="H101" s="25" t="n">
+        <v>35</v>
+      </c>
+      <c r="I101" s="26" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J101" s="26" t="inlineStr"/>
+      <c r="K101" s="27" t="inlineStr"/>
+      <c r="L101" s="28" t="inlineStr"/>
+      <c r="M101" s="29" t="inlineStr"/>
+      <c r="N101" s="28" t="inlineStr"/>
+      <c r="O101" s="29" t="inlineStr"/>
+      <c r="P101" s="29" t="inlineStr"/>
+      <c r="Q101" s="30" t="inlineStr">
+        <is>
+          <t>DRB102.35</t>
+        </is>
+      </c>
+      <c r="R101" s="31" t="inlineStr">
+        <is>
+          <t>spare (DRB102 35)</t>
+        </is>
+      </c>
+      <c r="S101" s="32" t="inlineStr"/>
+      <c r="T101" s="32" t="inlineStr"/>
+      <c r="U101" s="33" t="inlineStr"/>
+      <c r="V101" s="34" t="inlineStr"/>
+      <c r="W101" s="34" t="inlineStr"/>
+      <c r="X101" s="34" t="inlineStr"/>
+      <c r="Y101" s="34" t="inlineStr"/>
+      <c r="Z101" s="35" t="inlineStr"/>
+      <c r="AA101" s="36" t="inlineStr"/>
+      <c r="AB101" s="37" t="inlineStr"/>
+      <c r="AC101" s="38" t="inlineStr"/>
+      <c r="AD101" s="38" t="inlineStr"/>
+      <c r="AE101" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 35 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF101" s="38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG101" s="38" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="39" t="inlineStr"/>
+      <c r="B102" s="39" t="inlineStr"/>
+      <c r="C102" s="39" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D102" s="39" t="inlineStr"/>
+      <c r="E102" s="40" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F102" s="41" t="inlineStr">
+        <is>
+          <t>bh_a_fw</t>
+        </is>
+      </c>
+      <c r="G102" s="42" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="H102" s="41" t="n">
+        <v>36</v>
+      </c>
+      <c r="I102" s="42" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J102" s="42" t="inlineStr"/>
+      <c r="K102" s="43" t="inlineStr"/>
+      <c r="L102" s="44" t="inlineStr"/>
+      <c r="M102" s="45" t="inlineStr"/>
+      <c r="N102" s="44" t="inlineStr"/>
+      <c r="O102" s="45" t="inlineStr"/>
+      <c r="P102" s="45" t="inlineStr"/>
+      <c r="Q102" s="46" t="inlineStr">
+        <is>
+          <t>DRB102.36</t>
+        </is>
+      </c>
+      <c r="R102" s="47" t="inlineStr">
+        <is>
+          <t>spare (DRB102 36)</t>
+        </is>
+      </c>
+      <c r="S102" s="48" t="inlineStr"/>
+      <c r="T102" s="48" t="inlineStr"/>
+      <c r="U102" s="49" t="inlineStr"/>
+      <c r="V102" s="50" t="inlineStr"/>
+      <c r="W102" s="50" t="inlineStr"/>
+      <c r="X102" s="50" t="inlineStr"/>
+      <c r="Y102" s="50" t="inlineStr"/>
+      <c r="Z102" s="51" t="inlineStr"/>
+      <c r="AA102" s="52" t="inlineStr"/>
+      <c r="AB102" s="53" t="inlineStr"/>
+      <c r="AC102" s="54" t="inlineStr"/>
+      <c r="AD102" s="54" t="inlineStr"/>
+      <c r="AE102" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 36 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF102" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG102" s="54" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="23" t="inlineStr"/>
+      <c r="B103" s="23" t="inlineStr"/>
+      <c r="C103" s="23" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D103" s="23" t="inlineStr"/>
+      <c r="E103" s="24" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F103" s="25" t="inlineStr">
+        <is>
+          <t>bh_a_fw</t>
+        </is>
+      </c>
+      <c r="G103" s="26" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="H103" s="25" t="n">
+        <v>37</v>
+      </c>
+      <c r="I103" s="26" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J103" s="26" t="inlineStr"/>
+      <c r="K103" s="27" t="inlineStr"/>
+      <c r="L103" s="28" t="inlineStr"/>
+      <c r="M103" s="29" t="inlineStr"/>
+      <c r="N103" s="28" t="inlineStr"/>
+      <c r="O103" s="29" t="inlineStr"/>
+      <c r="P103" s="29" t="inlineStr"/>
+      <c r="Q103" s="30" t="inlineStr">
+        <is>
+          <t>DRB102.37</t>
+        </is>
+      </c>
+      <c r="R103" s="31" t="inlineStr">
+        <is>
+          <t>spare (DRB102 37)</t>
+        </is>
+      </c>
+      <c r="S103" s="32" t="inlineStr"/>
+      <c r="T103" s="32" t="inlineStr"/>
+      <c r="U103" s="33" t="inlineStr"/>
+      <c r="V103" s="34" t="inlineStr"/>
+      <c r="W103" s="34" t="inlineStr"/>
+      <c r="X103" s="34" t="inlineStr"/>
+      <c r="Y103" s="34" t="inlineStr"/>
+      <c r="Z103" s="35" t="inlineStr"/>
+      <c r="AA103" s="36" t="inlineStr"/>
+      <c r="AB103" s="37" t="inlineStr"/>
+      <c r="AC103" s="38" t="inlineStr"/>
+      <c r="AD103" s="38" t="inlineStr"/>
+      <c r="AE103" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 37 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF103" s="38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG103" s="38" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="39" t="inlineStr"/>
+      <c r="B104" s="39" t="inlineStr"/>
+      <c r="C104" s="39" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D104" s="39" t="inlineStr"/>
+      <c r="E104" s="40" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F104" s="41" t="inlineStr">
+        <is>
+          <t>bh_a_fw</t>
+        </is>
+      </c>
+      <c r="G104" s="42" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="H104" s="41" t="n">
+        <v>38</v>
+      </c>
+      <c r="I104" s="42" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J104" s="42" t="inlineStr"/>
+      <c r="K104" s="43" t="inlineStr"/>
+      <c r="L104" s="44" t="inlineStr"/>
+      <c r="M104" s="45" t="inlineStr"/>
+      <c r="N104" s="44" t="inlineStr"/>
+      <c r="O104" s="45" t="inlineStr"/>
+      <c r="P104" s="45" t="inlineStr"/>
+      <c r="Q104" s="46" t="inlineStr">
+        <is>
+          <t>DRB102.38</t>
+        </is>
+      </c>
+      <c r="R104" s="47" t="inlineStr">
+        <is>
+          <t>spare (DRB102 38)</t>
+        </is>
+      </c>
+      <c r="S104" s="48" t="inlineStr"/>
+      <c r="T104" s="48" t="inlineStr"/>
+      <c r="U104" s="49" t="inlineStr"/>
+      <c r="V104" s="50" t="inlineStr"/>
+      <c r="W104" s="50" t="inlineStr"/>
+      <c r="X104" s="50" t="inlineStr"/>
+      <c r="Y104" s="50" t="inlineStr"/>
+      <c r="Z104" s="51" t="inlineStr"/>
+      <c r="AA104" s="52" t="inlineStr"/>
+      <c r="AB104" s="53" t="inlineStr"/>
+      <c r="AC104" s="54" t="inlineStr"/>
+      <c r="AD104" s="54" t="inlineStr"/>
+      <c r="AE104" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 38 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF104" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG104" s="54" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="23" t="inlineStr"/>
+      <c r="B105" s="23" t="inlineStr"/>
+      <c r="C105" s="23" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D105" s="23" t="inlineStr"/>
+      <c r="E105" s="24" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F105" s="25" t="inlineStr">
+        <is>
+          <t>bh_a_fw</t>
+        </is>
+      </c>
+      <c r="G105" s="26" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="H105" s="25" t="n">
+        <v>39</v>
+      </c>
+      <c r="I105" s="26" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J105" s="26" t="inlineStr"/>
+      <c r="K105" s="27" t="inlineStr"/>
+      <c r="L105" s="28" t="inlineStr"/>
+      <c r="M105" s="29" t="inlineStr"/>
+      <c r="N105" s="28" t="inlineStr"/>
+      <c r="O105" s="29" t="inlineStr"/>
+      <c r="P105" s="29" t="inlineStr"/>
+      <c r="Q105" s="30" t="inlineStr">
+        <is>
+          <t>DRB102.39</t>
+        </is>
+      </c>
+      <c r="R105" s="31" t="inlineStr">
+        <is>
+          <t>spare (DRB102 39)</t>
+        </is>
+      </c>
+      <c r="S105" s="32" t="inlineStr"/>
+      <c r="T105" s="32" t="inlineStr"/>
+      <c r="U105" s="33" t="inlineStr"/>
+      <c r="V105" s="34" t="inlineStr"/>
+      <c r="W105" s="34" t="inlineStr"/>
+      <c r="X105" s="34" t="inlineStr"/>
+      <c r="Y105" s="34" t="inlineStr"/>
+      <c r="Z105" s="35" t="inlineStr"/>
+      <c r="AA105" s="36" t="inlineStr"/>
+      <c r="AB105" s="37" t="inlineStr"/>
+      <c r="AC105" s="38" t="inlineStr"/>
+      <c r="AD105" s="38" t="inlineStr"/>
+      <c r="AE105" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 39 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF105" s="38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG105" s="38" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="39" t="inlineStr"/>
+      <c r="B106" s="39" t="inlineStr"/>
+      <c r="C106" s="39" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D106" s="39" t="inlineStr"/>
+      <c r="E106" s="40" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F106" s="41" t="inlineStr">
+        <is>
+          <t>bh_a_fw</t>
+        </is>
+      </c>
+      <c r="G106" s="42" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="H106" s="41" t="n">
+        <v>40</v>
+      </c>
+      <c r="I106" s="42" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J106" s="42" t="inlineStr"/>
+      <c r="K106" s="43" t="inlineStr"/>
+      <c r="L106" s="44" t="inlineStr"/>
+      <c r="M106" s="45" t="inlineStr"/>
+      <c r="N106" s="44" t="inlineStr"/>
+      <c r="O106" s="45" t="inlineStr"/>
+      <c r="P106" s="45" t="inlineStr"/>
+      <c r="Q106" s="46" t="inlineStr">
+        <is>
+          <t>DRB102.40</t>
+        </is>
+      </c>
+      <c r="R106" s="47" t="inlineStr">
+        <is>
+          <t>spare (DRB102 40)</t>
+        </is>
+      </c>
+      <c r="S106" s="48" t="inlineStr"/>
+      <c r="T106" s="48" t="inlineStr"/>
+      <c r="U106" s="49" t="inlineStr"/>
+      <c r="V106" s="50" t="inlineStr"/>
+      <c r="W106" s="50" t="inlineStr"/>
+      <c r="X106" s="50" t="inlineStr"/>
+      <c r="Y106" s="50" t="inlineStr"/>
+      <c r="Z106" s="51" t="inlineStr"/>
+      <c r="AA106" s="52" t="inlineStr"/>
+      <c r="AB106" s="53" t="inlineStr"/>
+      <c r="AC106" s="54" t="inlineStr"/>
+      <c r="AD106" s="54" t="inlineStr"/>
+      <c r="AE106" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 40 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF106" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG106" s="54" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="23" t="inlineStr"/>
+      <c r="B107" s="23" t="inlineStr"/>
+      <c r="C107" s="23" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D107" s="23" t="inlineStr"/>
+      <c r="E107" s="24" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F107" s="25" t="inlineStr">
+        <is>
+          <t>bh_a_fw</t>
+        </is>
+      </c>
+      <c r="G107" s="26" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="H107" s="25" t="n">
+        <v>43</v>
+      </c>
+      <c r="I107" s="26" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J107" s="26" t="inlineStr"/>
+      <c r="K107" s="27" t="inlineStr"/>
+      <c r="L107" s="28" t="inlineStr"/>
+      <c r="M107" s="29" t="inlineStr"/>
+      <c r="N107" s="28" t="inlineStr"/>
+      <c r="O107" s="29" t="inlineStr"/>
+      <c r="P107" s="29" t="inlineStr"/>
+      <c r="Q107" s="30" t="inlineStr">
+        <is>
+          <t>DRB102.43</t>
+        </is>
+      </c>
+      <c r="R107" s="31" t="inlineStr">
+        <is>
+          <t>spare (DRB102 43)</t>
+        </is>
+      </c>
+      <c r="S107" s="32" t="inlineStr"/>
+      <c r="T107" s="32" t="inlineStr"/>
+      <c r="U107" s="33" t="inlineStr"/>
+      <c r="V107" s="34" t="inlineStr"/>
+      <c r="W107" s="34" t="inlineStr"/>
+      <c r="X107" s="34" t="inlineStr"/>
+      <c r="Y107" s="34" t="inlineStr"/>
+      <c r="Z107" s="35" t="inlineStr"/>
+      <c r="AA107" s="36" t="inlineStr"/>
+      <c r="AB107" s="37" t="inlineStr"/>
+      <c r="AC107" s="38" t="inlineStr"/>
+      <c r="AD107" s="38" t="inlineStr"/>
+      <c r="AE107" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 43 = 'spare (size 4)'</t>
+        </is>
+      </c>
+      <c r="AF107" s="38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG107" s="38" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="39" t="inlineStr"/>
+      <c r="B108" s="39" t="inlineStr"/>
+      <c r="C108" s="39" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D108" s="39" t="inlineStr"/>
+      <c r="E108" s="40" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F108" s="41" t="inlineStr">
+        <is>
+          <t>bh_a_fw</t>
+        </is>
+      </c>
+      <c r="G108" s="42" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="H108" s="41" t="n">
+        <v>48</v>
+      </c>
+      <c r="I108" s="42" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J108" s="42" t="inlineStr"/>
+      <c r="K108" s="43" t="inlineStr"/>
+      <c r="L108" s="44" t="inlineStr"/>
+      <c r="M108" s="45" t="inlineStr"/>
+      <c r="N108" s="44" t="inlineStr"/>
+      <c r="O108" s="45" t="inlineStr"/>
+      <c r="P108" s="45" t="inlineStr"/>
+      <c r="Q108" s="46" t="inlineStr">
+        <is>
+          <t>DRB102.48</t>
+        </is>
+      </c>
+      <c r="R108" s="47" t="inlineStr">
+        <is>
+          <t>spare (DRB102 48)</t>
+        </is>
+      </c>
+      <c r="S108" s="48" t="inlineStr"/>
+      <c r="T108" s="48" t="inlineStr"/>
+      <c r="U108" s="49" t="inlineStr"/>
+      <c r="V108" s="50" t="inlineStr"/>
+      <c r="W108" s="50" t="inlineStr"/>
+      <c r="X108" s="50" t="inlineStr"/>
+      <c r="Y108" s="50" t="inlineStr"/>
+      <c r="Z108" s="51" t="inlineStr"/>
+      <c r="AA108" s="52" t="inlineStr"/>
+      <c r="AB108" s="53" t="inlineStr"/>
+      <c r="AC108" s="54" t="inlineStr"/>
+      <c r="AD108" s="54" t="inlineStr"/>
+      <c r="AE108" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 48 = 'spare (size 8)'</t>
+        </is>
+      </c>
+      <c r="AF108" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG108" s="54" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="23" t="inlineStr"/>
+      <c r="B109" s="23" t="inlineStr"/>
+      <c r="C109" s="23" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D109" s="23" t="inlineStr"/>
+      <c r="E109" s="24" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F109" s="25" t="inlineStr">
+        <is>
+          <t>bh_a_fw</t>
+        </is>
+      </c>
+      <c r="G109" s="26" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="H109" s="25" t="n">
+        <v>49</v>
+      </c>
+      <c r="I109" s="26" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J109" s="26" t="inlineStr"/>
+      <c r="K109" s="27" t="inlineStr"/>
+      <c r="L109" s="28" t="inlineStr"/>
+      <c r="M109" s="29" t="inlineStr"/>
+      <c r="N109" s="28" t="inlineStr"/>
+      <c r="O109" s="29" t="inlineStr"/>
+      <c r="P109" s="29" t="inlineStr"/>
+      <c r="Q109" s="30" t="inlineStr">
+        <is>
+          <t>DRB102.49</t>
+        </is>
+      </c>
+      <c r="R109" s="31" t="inlineStr">
+        <is>
+          <t>spare (DRB102 49)</t>
+        </is>
+      </c>
+      <c r="S109" s="32" t="inlineStr"/>
+      <c r="T109" s="32" t="inlineStr"/>
+      <c r="U109" s="33" t="inlineStr"/>
+      <c r="V109" s="34" t="inlineStr"/>
+      <c r="W109" s="34" t="inlineStr"/>
+      <c r="X109" s="34" t="inlineStr"/>
+      <c r="Y109" s="34" t="inlineStr"/>
+      <c r="Z109" s="35" t="inlineStr"/>
+      <c r="AA109" s="36" t="inlineStr"/>
+      <c r="AB109" s="37" t="inlineStr"/>
+      <c r="AC109" s="38" t="inlineStr"/>
+      <c r="AD109" s="38" t="inlineStr"/>
+      <c r="AE109" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 49 = 'spare (size 8)'</t>
+        </is>
+      </c>
+      <c r="AF109" s="38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG109" s="38" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="39" t="inlineStr"/>
+      <c r="B110" s="39" t="inlineStr"/>
+      <c r="C110" s="39" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D110" s="39" t="inlineStr"/>
+      <c r="E110" s="40" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F110" s="41" t="inlineStr">
+        <is>
+          <t>bh_a_fw</t>
+        </is>
+      </c>
+      <c r="G110" s="42" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="H110" s="41" t="n">
+        <v>54</v>
+      </c>
+      <c r="I110" s="42" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J110" s="42" t="inlineStr"/>
+      <c r="K110" s="43" t="inlineStr"/>
+      <c r="L110" s="44" t="inlineStr"/>
+      <c r="M110" s="45" t="inlineStr"/>
+      <c r="N110" s="44" t="inlineStr"/>
+      <c r="O110" s="45" t="inlineStr"/>
+      <c r="P110" s="45" t="inlineStr"/>
+      <c r="Q110" s="46" t="inlineStr">
+        <is>
+          <t>DRB102.54</t>
+        </is>
+      </c>
+      <c r="R110" s="47" t="inlineStr">
+        <is>
+          <t>spare (DRB102 54)</t>
+        </is>
+      </c>
+      <c r="S110" s="48" t="inlineStr"/>
+      <c r="T110" s="48" t="inlineStr"/>
+      <c r="U110" s="49" t="inlineStr"/>
+      <c r="V110" s="50" t="inlineStr"/>
+      <c r="W110" s="50" t="inlineStr"/>
+      <c r="X110" s="50" t="inlineStr"/>
+      <c r="Y110" s="50" t="inlineStr"/>
+      <c r="Z110" s="51" t="inlineStr"/>
+      <c r="AA110" s="52" t="inlineStr"/>
+      <c r="AB110" s="53" t="inlineStr"/>
+      <c r="AC110" s="54" t="inlineStr"/>
+      <c r="AD110" s="54" t="inlineStr"/>
+      <c r="AE110" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 54 = 'spare (size 8)'</t>
+        </is>
+      </c>
+      <c r="AF110" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG110" s="54" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="23" t="inlineStr"/>
+      <c r="B111" s="23" t="inlineStr"/>
+      <c r="C111" s="23" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D111" s="23" t="inlineStr"/>
+      <c r="E111" s="24" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F111" s="25" t="inlineStr">
+        <is>
+          <t>bh_a_fw</t>
+        </is>
+      </c>
+      <c r="G111" s="26" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="H111" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="I111" s="26" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J111" s="26" t="inlineStr"/>
+      <c r="K111" s="27" t="inlineStr"/>
+      <c r="L111" s="28" t="inlineStr"/>
+      <c r="M111" s="29" t="inlineStr"/>
+      <c r="N111" s="28" t="inlineStr"/>
+      <c r="O111" s="29" t="inlineStr"/>
+      <c r="P111" s="29" t="inlineStr"/>
+      <c r="Q111" s="30" t="inlineStr">
+        <is>
+          <t>DRB102.55</t>
+        </is>
+      </c>
+      <c r="R111" s="31" t="inlineStr">
+        <is>
+          <t>spare (DRB102 55)</t>
+        </is>
+      </c>
+      <c r="S111" s="32" t="inlineStr"/>
+      <c r="T111" s="32" t="inlineStr"/>
+      <c r="U111" s="33" t="inlineStr"/>
+      <c r="V111" s="34" t="inlineStr"/>
+      <c r="W111" s="34" t="inlineStr"/>
+      <c r="X111" s="34" t="inlineStr"/>
+      <c r="Y111" s="34" t="inlineStr"/>
+      <c r="Z111" s="35" t="inlineStr"/>
+      <c r="AA111" s="36" t="inlineStr"/>
+      <c r="AB111" s="37" t="inlineStr"/>
+      <c r="AC111" s="38" t="inlineStr"/>
+      <c r="AD111" s="38" t="inlineStr"/>
+      <c r="AE111" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 55 = 'spare (size 8)'</t>
+        </is>
+      </c>
+      <c r="AF111" s="38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG111" s="38" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="39" t="inlineStr"/>
+      <c r="B112" s="39" t="inlineStr"/>
+      <c r="C112" s="39" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D112" s="39" t="inlineStr"/>
+      <c r="E112" s="40" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F112" s="41" t="inlineStr">
+        <is>
+          <t>bh_a_fw</t>
+        </is>
+      </c>
+      <c r="G112" s="42" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="H112" s="41" t="n">
+        <v>86</v>
+      </c>
+      <c r="I112" s="42" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J112" s="42" t="inlineStr"/>
+      <c r="K112" s="43" t="inlineStr"/>
+      <c r="L112" s="44" t="inlineStr"/>
+      <c r="M112" s="45" t="inlineStr"/>
+      <c r="N112" s="44" t="inlineStr"/>
+      <c r="O112" s="45" t="inlineStr"/>
+      <c r="P112" s="45" t="inlineStr"/>
+      <c r="Q112" s="46" t="inlineStr">
+        <is>
+          <t>DRB102.86</t>
+        </is>
+      </c>
+      <c r="R112" s="47" t="inlineStr">
+        <is>
+          <t>spare (DRB102 86)</t>
+        </is>
+      </c>
+      <c r="S112" s="48" t="inlineStr"/>
+      <c r="T112" s="48" t="inlineStr"/>
+      <c r="U112" s="49" t="inlineStr"/>
+      <c r="V112" s="50" t="inlineStr"/>
+      <c r="W112" s="50" t="inlineStr"/>
+      <c r="X112" s="50" t="inlineStr"/>
+      <c r="Y112" s="50" t="inlineStr"/>
+      <c r="Z112" s="51" t="inlineStr"/>
+      <c r="AA112" s="52" t="inlineStr"/>
+      <c r="AB112" s="53" t="inlineStr"/>
+      <c r="AC112" s="54" t="inlineStr"/>
+      <c r="AD112" s="54" t="inlineStr"/>
+      <c r="AE112" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 86 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF112" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG112" s="54" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="23" t="inlineStr"/>
+      <c r="B113" s="23" t="inlineStr"/>
+      <c r="C113" s="23" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D113" s="23" t="inlineStr"/>
+      <c r="E113" s="24" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F113" s="25" t="inlineStr">
+        <is>
+          <t>bh_a_fw</t>
+        </is>
+      </c>
+      <c r="G113" s="26" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="H113" s="25" t="n">
+        <v>87</v>
+      </c>
+      <c r="I113" s="26" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J113" s="26" t="inlineStr"/>
+      <c r="K113" s="27" t="inlineStr"/>
+      <c r="L113" s="28" t="inlineStr"/>
+      <c r="M113" s="29" t="inlineStr"/>
+      <c r="N113" s="28" t="inlineStr"/>
+      <c r="O113" s="29" t="inlineStr"/>
+      <c r="P113" s="29" t="inlineStr"/>
+      <c r="Q113" s="30" t="inlineStr">
+        <is>
+          <t>DRB102.87</t>
+        </is>
+      </c>
+      <c r="R113" s="31" t="inlineStr">
+        <is>
+          <t>spare (DRB102 87)</t>
+        </is>
+      </c>
+      <c r="S113" s="32" t="inlineStr"/>
+      <c r="T113" s="32" t="inlineStr"/>
+      <c r="U113" s="33" t="inlineStr"/>
+      <c r="V113" s="34" t="inlineStr"/>
+      <c r="W113" s="34" t="inlineStr"/>
+      <c r="X113" s="34" t="inlineStr"/>
+      <c r="Y113" s="34" t="inlineStr"/>
+      <c r="Z113" s="35" t="inlineStr"/>
+      <c r="AA113" s="36" t="inlineStr"/>
+      <c r="AB113" s="37" t="inlineStr"/>
+      <c r="AC113" s="38" t="inlineStr"/>
+      <c r="AD113" s="38" t="inlineStr"/>
+      <c r="AE113" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 87 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF113" s="38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG113" s="38" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="39" t="inlineStr"/>
+      <c r="B114" s="39" t="inlineStr"/>
+      <c r="C114" s="39" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D114" s="39" t="inlineStr"/>
+      <c r="E114" s="40" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F114" s="41" t="inlineStr">
+        <is>
+          <t>bh_a_fw</t>
+        </is>
+      </c>
+      <c r="G114" s="42" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="H114" s="41" t="n">
+        <v>88</v>
+      </c>
+      <c r="I114" s="42" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J114" s="42" t="inlineStr"/>
+      <c r="K114" s="43" t="inlineStr"/>
+      <c r="L114" s="44" t="inlineStr"/>
+      <c r="M114" s="45" t="inlineStr"/>
+      <c r="N114" s="44" t="inlineStr"/>
+      <c r="O114" s="45" t="inlineStr"/>
+      <c r="P114" s="45" t="inlineStr"/>
+      <c r="Q114" s="46" t="inlineStr">
+        <is>
+          <t>DRB102.88</t>
+        </is>
+      </c>
+      <c r="R114" s="47" t="inlineStr">
+        <is>
+          <t>spare (DRB102 88)</t>
+        </is>
+      </c>
+      <c r="S114" s="48" t="inlineStr"/>
+      <c r="T114" s="48" t="inlineStr"/>
+      <c r="U114" s="49" t="inlineStr"/>
+      <c r="V114" s="50" t="inlineStr"/>
+      <c r="W114" s="50" t="inlineStr"/>
+      <c r="X114" s="50" t="inlineStr"/>
+      <c r="Y114" s="50" t="inlineStr"/>
+      <c r="Z114" s="51" t="inlineStr"/>
+      <c r="AA114" s="52" t="inlineStr"/>
+      <c r="AB114" s="53" t="inlineStr"/>
+      <c r="AC114" s="54" t="inlineStr"/>
+      <c r="AD114" s="54" t="inlineStr"/>
+      <c r="AE114" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 88 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF114" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG114" s="54" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="23" t="inlineStr"/>
+      <c r="B115" s="23" t="inlineStr"/>
+      <c r="C115" s="23" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D115" s="23" t="inlineStr"/>
+      <c r="E115" s="24" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F115" s="25" t="inlineStr">
+        <is>
+          <t>bh_a_fw</t>
+        </is>
+      </c>
+      <c r="G115" s="26" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="H115" s="25" t="n">
+        <v>89</v>
+      </c>
+      <c r="I115" s="26" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J115" s="26" t="inlineStr"/>
+      <c r="K115" s="27" t="inlineStr"/>
+      <c r="L115" s="28" t="inlineStr"/>
+      <c r="M115" s="29" t="inlineStr"/>
+      <c r="N115" s="28" t="inlineStr"/>
+      <c r="O115" s="29" t="inlineStr"/>
+      <c r="P115" s="29" t="inlineStr"/>
+      <c r="Q115" s="30" t="inlineStr">
+        <is>
+          <t>DRB102.89</t>
+        </is>
+      </c>
+      <c r="R115" s="31" t="inlineStr">
+        <is>
+          <t>spare (DRB102 89)</t>
+        </is>
+      </c>
+      <c r="S115" s="32" t="inlineStr"/>
+      <c r="T115" s="32" t="inlineStr"/>
+      <c r="U115" s="33" t="inlineStr"/>
+      <c r="V115" s="34" t="inlineStr"/>
+      <c r="W115" s="34" t="inlineStr"/>
+      <c r="X115" s="34" t="inlineStr"/>
+      <c r="Y115" s="34" t="inlineStr"/>
+      <c r="Z115" s="35" t="inlineStr"/>
+      <c r="AA115" s="36" t="inlineStr"/>
+      <c r="AB115" s="37" t="inlineStr"/>
+      <c r="AC115" s="38" t="inlineStr"/>
+      <c r="AD115" s="38" t="inlineStr"/>
+      <c r="AE115" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 89 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF115" s="38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG115" s="38" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="39" t="inlineStr"/>
+      <c r="B116" s="39" t="inlineStr"/>
+      <c r="C116" s="39" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D116" s="39" t="inlineStr"/>
+      <c r="E116" s="40" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F116" s="41" t="inlineStr">
+        <is>
+          <t>bh_a_fw</t>
+        </is>
+      </c>
+      <c r="G116" s="42" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="H116" s="41" t="n">
+        <v>90</v>
+      </c>
+      <c r="I116" s="42" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J116" s="42" t="inlineStr"/>
+      <c r="K116" s="43" t="inlineStr"/>
+      <c r="L116" s="44" t="inlineStr"/>
+      <c r="M116" s="45" t="inlineStr"/>
+      <c r="N116" s="44" t="inlineStr"/>
+      <c r="O116" s="45" t="inlineStr"/>
+      <c r="P116" s="45" t="inlineStr"/>
+      <c r="Q116" s="46" t="inlineStr">
+        <is>
+          <t>DRB102.90</t>
+        </is>
+      </c>
+      <c r="R116" s="47" t="inlineStr">
+        <is>
+          <t>spare (DRB102 90)</t>
+        </is>
+      </c>
+      <c r="S116" s="48" t="inlineStr"/>
+      <c r="T116" s="48" t="inlineStr"/>
+      <c r="U116" s="49" t="inlineStr"/>
+      <c r="V116" s="50" t="inlineStr"/>
+      <c r="W116" s="50" t="inlineStr"/>
+      <c r="X116" s="50" t="inlineStr"/>
+      <c r="Y116" s="50" t="inlineStr"/>
+      <c r="Z116" s="51" t="inlineStr"/>
+      <c r="AA116" s="52" t="inlineStr"/>
+      <c r="AB116" s="53" t="inlineStr"/>
+      <c r="AC116" s="54" t="inlineStr"/>
+      <c r="AD116" s="54" t="inlineStr"/>
+      <c r="AE116" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 90 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF116" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG116" s="54" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="23" t="inlineStr"/>
+      <c r="B117" s="23" t="inlineStr"/>
+      <c r="C117" s="23" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D117" s="23" t="inlineStr"/>
+      <c r="E117" s="24" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F117" s="25" t="inlineStr">
+        <is>
+          <t>bh_a_fw</t>
+        </is>
+      </c>
+      <c r="G117" s="26" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="H117" s="25" t="n">
+        <v>91</v>
+      </c>
+      <c r="I117" s="26" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J117" s="26" t="inlineStr"/>
+      <c r="K117" s="27" t="inlineStr"/>
+      <c r="L117" s="28" t="inlineStr"/>
+      <c r="M117" s="29" t="inlineStr"/>
+      <c r="N117" s="28" t="inlineStr"/>
+      <c r="O117" s="29" t="inlineStr"/>
+      <c r="P117" s="29" t="inlineStr"/>
+      <c r="Q117" s="30" t="inlineStr">
+        <is>
+          <t>DRB102.91</t>
+        </is>
+      </c>
+      <c r="R117" s="31" t="inlineStr">
+        <is>
+          <t>spare (DRB102 91)</t>
+        </is>
+      </c>
+      <c r="S117" s="32" t="inlineStr"/>
+      <c r="T117" s="32" t="inlineStr"/>
+      <c r="U117" s="33" t="inlineStr"/>
+      <c r="V117" s="34" t="inlineStr"/>
+      <c r="W117" s="34" t="inlineStr"/>
+      <c r="X117" s="34" t="inlineStr"/>
+      <c r="Y117" s="34" t="inlineStr"/>
+      <c r="Z117" s="35" t="inlineStr"/>
+      <c r="AA117" s="36" t="inlineStr"/>
+      <c r="AB117" s="37" t="inlineStr"/>
+      <c r="AC117" s="38" t="inlineStr"/>
+      <c r="AD117" s="38" t="inlineStr"/>
+      <c r="AE117" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 91 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF117" s="38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG117" s="38" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="39" t="inlineStr"/>
+      <c r="B118" s="39" t="inlineStr"/>
+      <c r="C118" s="39" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D118" s="39" t="inlineStr"/>
+      <c r="E118" s="40" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F118" s="41" t="inlineStr">
+        <is>
+          <t>bh_a_fw</t>
+        </is>
+      </c>
+      <c r="G118" s="42" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="H118" s="41" t="n">
+        <v>92</v>
+      </c>
+      <c r="I118" s="42" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J118" s="42" t="inlineStr"/>
+      <c r="K118" s="43" t="inlineStr"/>
+      <c r="L118" s="44" t="inlineStr"/>
+      <c r="M118" s="45" t="inlineStr"/>
+      <c r="N118" s="44" t="inlineStr"/>
+      <c r="O118" s="45" t="inlineStr"/>
+      <c r="P118" s="45" t="inlineStr"/>
+      <c r="Q118" s="46" t="inlineStr">
+        <is>
+          <t>DRB102.92</t>
+        </is>
+      </c>
+      <c r="R118" s="47" t="inlineStr">
+        <is>
+          <t>spare (DRB102 92)</t>
+        </is>
+      </c>
+      <c r="S118" s="48" t="inlineStr"/>
+      <c r="T118" s="48" t="inlineStr"/>
+      <c r="U118" s="49" t="inlineStr"/>
+      <c r="V118" s="50" t="inlineStr"/>
+      <c r="W118" s="50" t="inlineStr"/>
+      <c r="X118" s="50" t="inlineStr"/>
+      <c r="Y118" s="50" t="inlineStr"/>
+      <c r="Z118" s="51" t="inlineStr"/>
+      <c r="AA118" s="52" t="inlineStr"/>
+      <c r="AB118" s="53" t="inlineStr"/>
+      <c r="AC118" s="54" t="inlineStr"/>
+      <c r="AD118" s="54" t="inlineStr"/>
+      <c r="AE118" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 92 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF118" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG118" s="54" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="23" t="inlineStr"/>
+      <c r="B119" s="23" t="inlineStr"/>
+      <c r="C119" s="23" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D119" s="23" t="inlineStr"/>
+      <c r="E119" s="24" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F119" s="25" t="inlineStr">
+        <is>
+          <t>bh_a_fw</t>
+        </is>
+      </c>
+      <c r="G119" s="26" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="H119" s="25" t="n">
+        <v>93</v>
+      </c>
+      <c r="I119" s="26" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J119" s="26" t="inlineStr"/>
+      <c r="K119" s="27" t="inlineStr"/>
+      <c r="L119" s="28" t="inlineStr"/>
+      <c r="M119" s="29" t="inlineStr"/>
+      <c r="N119" s="28" t="inlineStr"/>
+      <c r="O119" s="29" t="inlineStr"/>
+      <c r="P119" s="29" t="inlineStr"/>
+      <c r="Q119" s="30" t="inlineStr">
+        <is>
+          <t>DRB102.93</t>
+        </is>
+      </c>
+      <c r="R119" s="31" t="inlineStr">
+        <is>
+          <t>spare (DRB102 93)</t>
+        </is>
+      </c>
+      <c r="S119" s="32" t="inlineStr"/>
+      <c r="T119" s="32" t="inlineStr"/>
+      <c r="U119" s="33" t="inlineStr"/>
+      <c r="V119" s="34" t="inlineStr"/>
+      <c r="W119" s="34" t="inlineStr"/>
+      <c r="X119" s="34" t="inlineStr"/>
+      <c r="Y119" s="34" t="inlineStr"/>
+      <c r="Z119" s="35" t="inlineStr"/>
+      <c r="AA119" s="36" t="inlineStr"/>
+      <c r="AB119" s="37" t="inlineStr"/>
+      <c r="AC119" s="38" t="inlineStr"/>
+      <c r="AD119" s="38" t="inlineStr"/>
+      <c r="AE119" s="38" t="inlineStr">
+        <is>
+          <t>DRB102 93 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF119" s="38" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG119" s="38" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="39" t="inlineStr"/>
+      <c r="B120" s="39" t="inlineStr"/>
+      <c r="C120" s="39" t="inlineStr">
+        <is>
+          <t>A-cabin</t>
+        </is>
+      </c>
+      <c r="D120" s="39" t="inlineStr"/>
+      <c r="E120" s="40" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F120" s="41" t="inlineStr">
+        <is>
+          <t>bh_a_fw</t>
+        </is>
+      </c>
+      <c r="G120" s="42" t="inlineStr">
+        <is>
+          <t>BULKHEAD</t>
+        </is>
+      </c>
+      <c r="H120" s="41" t="n">
+        <v>94</v>
+      </c>
+      <c r="I120" s="42" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J120" s="42" t="inlineStr"/>
+      <c r="K120" s="43" t="inlineStr"/>
+      <c r="L120" s="44" t="inlineStr"/>
+      <c r="M120" s="45" t="inlineStr"/>
+      <c r="N120" s="44" t="inlineStr"/>
+      <c r="O120" s="45" t="inlineStr"/>
+      <c r="P120" s="45" t="inlineStr"/>
+      <c r="Q120" s="46" t="inlineStr">
+        <is>
+          <t>DRB102.94</t>
+        </is>
+      </c>
+      <c r="R120" s="47" t="inlineStr">
+        <is>
+          <t>spare (DRB102 94)</t>
+        </is>
+      </c>
+      <c r="S120" s="48" t="inlineStr"/>
+      <c r="T120" s="48" t="inlineStr"/>
+      <c r="U120" s="49" t="inlineStr"/>
+      <c r="V120" s="50" t="inlineStr"/>
+      <c r="W120" s="50" t="inlineStr"/>
+      <c r="X120" s="50" t="inlineStr"/>
+      <c r="Y120" s="50" t="inlineStr"/>
+      <c r="Z120" s="51" t="inlineStr"/>
+      <c r="AA120" s="52" t="inlineStr"/>
+      <c r="AB120" s="53" t="inlineStr"/>
+      <c r="AC120" s="54" t="inlineStr"/>
+      <c r="AD120" s="54" t="inlineStr"/>
+      <c r="AE120" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 94 = 'spare (size 16)'</t>
+        </is>
+      </c>
+      <c r="AF120" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG120" s="54" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AG100"/>
+  <autoFilter ref="A2:AG120"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -13338,7 +14798,7 @@
       </c>
       <c r="G4" s="52" t="inlineStr">
         <is>
-          <t>shared DRB102 (section A here, section B on B-cabin)</t>
+          <t>shared DRB102 (loom A wires here, loom B wires on B-cabin)</t>
         </is>
       </c>
     </row>
@@ -13688,7 +15148,7 @@
         </is>
       </c>
       <c r="C3" s="25" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D3" s="26" t="inlineStr">
         <is>
@@ -13706,7 +15166,7 @@
         </is>
       </c>
       <c r="G3" s="28" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H3" s="29" t="inlineStr">
         <is>
@@ -13736,7 +15196,7 @@
         </is>
       </c>
       <c r="C4" s="41" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D4" s="42" t="inlineStr">
         <is>
@@ -13754,7 +15214,7 @@
         </is>
       </c>
       <c r="G4" s="44" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="H4" s="45" t="inlineStr">
         <is>
@@ -13784,7 +15244,7 @@
         </is>
       </c>
       <c r="C5" s="25" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D5" s="26" t="inlineStr">
         <is>
@@ -13802,7 +15262,7 @@
         </is>
       </c>
       <c r="G5" s="28" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="H5" s="29" t="inlineStr">
         <is>
@@ -13832,7 +15292,7 @@
         </is>
       </c>
       <c r="C6" s="41" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D6" s="42" t="inlineStr">
         <is>
@@ -13850,7 +15310,7 @@
         </is>
       </c>
       <c r="G6" s="44" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="H6" s="45" t="inlineStr">
         <is>
@@ -13880,7 +15340,7 @@
         </is>
       </c>
       <c r="C7" s="25" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D7" s="26" t="inlineStr">
         <is>
@@ -13898,7 +15358,7 @@
         </is>
       </c>
       <c r="G7" s="28" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="H7" s="29" t="inlineStr">
         <is>
@@ -13928,7 +15388,7 @@
         </is>
       </c>
       <c r="C8" s="41" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D8" s="42" t="inlineStr">
         <is>
@@ -13946,7 +15406,7 @@
         </is>
       </c>
       <c r="G8" s="44" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="H8" s="45" t="inlineStr">
         <is>
@@ -13976,7 +15436,7 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D9" s="26" t="inlineStr">
         <is>
@@ -13994,7 +15454,7 @@
         </is>
       </c>
       <c r="G9" s="28" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="H9" s="29" t="inlineStr">
         <is>
@@ -14024,7 +15484,7 @@
         </is>
       </c>
       <c r="C10" s="41" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="D10" s="42" t="inlineStr">
         <is>
@@ -14042,7 +15502,7 @@
         </is>
       </c>
       <c r="G10" s="44" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="H10" s="45" t="inlineStr">
         <is>
@@ -14072,7 +15532,7 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="D11" s="26" t="inlineStr">
         <is>
@@ -14090,7 +15550,7 @@
         </is>
       </c>
       <c r="G11" s="28" t="n">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="H11" s="29" t="inlineStr">
         <is>
@@ -14120,7 +15580,7 @@
         </is>
       </c>
       <c r="C12" s="41" t="n">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="D12" s="42" t="inlineStr">
         <is>
@@ -14138,7 +15598,7 @@
         </is>
       </c>
       <c r="G12" s="44" t="n">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="H12" s="45" t="inlineStr">
         <is>
@@ -14168,7 +15628,7 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D13" s="26" t="inlineStr">
         <is>
@@ -14186,7 +15646,7 @@
         </is>
       </c>
       <c r="G13" s="28" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H13" s="29" t="inlineStr">
         <is>
@@ -14216,7 +15676,7 @@
         </is>
       </c>
       <c r="C14" s="41" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D14" s="42" t="inlineStr">
         <is>
@@ -14234,7 +15694,7 @@
         </is>
       </c>
       <c r="G14" s="44" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="H14" s="45" t="inlineStr">
         <is>
@@ -14264,7 +15724,7 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D15" s="26" t="inlineStr">
         <is>
@@ -14282,7 +15742,7 @@
         </is>
       </c>
       <c r="G15" s="28" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="H15" s="29" t="inlineStr">
         <is>
@@ -14312,7 +15772,7 @@
         </is>
       </c>
       <c r="C16" s="41" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D16" s="42" t="inlineStr">
         <is>
@@ -14330,7 +15790,7 @@
         </is>
       </c>
       <c r="G16" s="44" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H16" s="45" t="inlineStr">
         <is>
@@ -14360,7 +15820,7 @@
         </is>
       </c>
       <c r="C17" s="25" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="D17" s="26" t="inlineStr">
         <is>
@@ -14378,7 +15838,7 @@
         </is>
       </c>
       <c r="G17" s="28" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="H17" s="29" t="inlineStr">
         <is>
@@ -14408,7 +15868,7 @@
         </is>
       </c>
       <c r="C18" s="41" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D18" s="42" t="inlineStr">
         <is>
@@ -14426,7 +15886,7 @@
         </is>
       </c>
       <c r="G18" s="44" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="H18" s="45" t="inlineStr">
         <is>
@@ -14456,7 +15916,7 @@
         </is>
       </c>
       <c r="C19" s="25" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D19" s="26" t="inlineStr">
         <is>
@@ -14474,7 +15934,7 @@
         </is>
       </c>
       <c r="G19" s="28" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="H19" s="29" t="inlineStr">
         <is>
@@ -14504,7 +15964,7 @@
         </is>
       </c>
       <c r="C20" s="41" t="n">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="D20" s="42" t="inlineStr">
         <is>
@@ -14522,7 +15982,7 @@
         </is>
       </c>
       <c r="G20" s="44" t="n">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="H20" s="45" t="inlineStr">
         <is>
@@ -14552,7 +16012,7 @@
         </is>
       </c>
       <c r="C21" s="25" t="n">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D21" s="26" t="inlineStr">
         <is>
@@ -14570,7 +16030,7 @@
         </is>
       </c>
       <c r="G21" s="28" t="n">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="H21" s="29" t="inlineStr">
         <is>
@@ -14600,7 +16060,7 @@
         </is>
       </c>
       <c r="C22" s="41" t="n">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="D22" s="42" t="inlineStr">
         <is>
@@ -14618,7 +16078,7 @@
         </is>
       </c>
       <c r="G22" s="44" t="n">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="H22" s="45" t="inlineStr">
         <is>
@@ -14648,7 +16108,7 @@
         </is>
       </c>
       <c r="C23" s="25" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D23" s="26" t="inlineStr">
         <is>
@@ -14666,7 +16126,7 @@
         </is>
       </c>
       <c r="G23" s="28" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H23" s="29" t="inlineStr">
         <is>
@@ -14696,7 +16156,7 @@
         </is>
       </c>
       <c r="C24" s="41" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D24" s="42" t="inlineStr">
         <is>
@@ -14714,7 +16174,7 @@
         </is>
       </c>
       <c r="G24" s="44" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H24" s="45" t="inlineStr">
         <is>
@@ -14744,7 +16204,7 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="D25" s="26" t="inlineStr">
         <is>
@@ -14762,7 +16222,7 @@
         </is>
       </c>
       <c r="G25" s="28" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="H25" s="29" t="inlineStr">
         <is>
@@ -14792,7 +16252,7 @@
         </is>
       </c>
       <c r="C26" s="41" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="D26" s="42" t="inlineStr">
         <is>
@@ -14810,7 +16270,7 @@
         </is>
       </c>
       <c r="G26" s="44" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H26" s="45" t="inlineStr">
         <is>
@@ -14840,7 +16300,7 @@
         </is>
       </c>
       <c r="C27" s="25" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="D27" s="26" t="inlineStr">
         <is>
@@ -14858,7 +16318,7 @@
         </is>
       </c>
       <c r="G27" s="28" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="H27" s="29" t="inlineStr">
         <is>
@@ -14888,7 +16348,7 @@
         </is>
       </c>
       <c r="C28" s="41" t="n">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="D28" s="42" t="inlineStr">
         <is>
@@ -14906,7 +16366,7 @@
         </is>
       </c>
       <c r="G28" s="44" t="n">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="H28" s="45" t="inlineStr">
         <is>
@@ -14936,7 +16396,7 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D29" s="26" t="inlineStr">
         <is>
@@ -14954,7 +16414,7 @@
         </is>
       </c>
       <c r="G29" s="28" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="H29" s="29" t="inlineStr">
         <is>
@@ -14984,7 +16444,7 @@
         </is>
       </c>
       <c r="C30" s="41" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="D30" s="42" t="inlineStr">
         <is>
@@ -15002,7 +16462,7 @@
         </is>
       </c>
       <c r="G30" s="44" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="H30" s="45" t="inlineStr">
         <is>
@@ -15032,7 +16492,7 @@
         </is>
       </c>
       <c r="C31" s="25" t="n">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="D31" s="26" t="inlineStr">
         <is>
@@ -15050,7 +16510,7 @@
         </is>
       </c>
       <c r="G31" s="28" t="n">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="H31" s="29" t="inlineStr">
         <is>
@@ -15080,7 +16540,7 @@
         </is>
       </c>
       <c r="C32" s="41" t="n">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="D32" s="42" t="inlineStr">
         <is>
@@ -15098,7 +16558,7 @@
         </is>
       </c>
       <c r="G32" s="44" t="n">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="H32" s="45" t="inlineStr">
         <is>
@@ -15128,7 +16588,7 @@
         </is>
       </c>
       <c r="C33" s="25" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D33" s="26" t="inlineStr">
         <is>
@@ -15146,7 +16606,7 @@
         </is>
       </c>
       <c r="G33" s="28" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H33" s="29" t="inlineStr">
         <is>
@@ -15176,7 +16636,7 @@
         </is>
       </c>
       <c r="C34" s="41" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D34" s="42" t="inlineStr">
         <is>
@@ -15194,7 +16654,7 @@
         </is>
       </c>
       <c r="G34" s="44" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H34" s="45" t="inlineStr">
         <is>
@@ -15224,7 +16684,7 @@
         </is>
       </c>
       <c r="C35" s="25" t="n">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="D35" s="26" t="inlineStr">
         <is>
@@ -15242,7 +16702,7 @@
         </is>
       </c>
       <c r="G35" s="28" t="n">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="H35" s="29" t="inlineStr">
         <is>
@@ -15272,7 +16732,7 @@
         </is>
       </c>
       <c r="C36" s="41" t="n">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="D36" s="42" t="inlineStr">
         <is>
@@ -15290,7 +16750,7 @@
         </is>
       </c>
       <c r="G36" s="44" t="n">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="H36" s="45" t="inlineStr">
         <is>
@@ -15320,7 +16780,7 @@
         </is>
       </c>
       <c r="C37" s="25" t="n">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="D37" s="26" t="inlineStr">
         <is>
@@ -15338,7 +16798,7 @@
         </is>
       </c>
       <c r="G37" s="28" t="n">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="H37" s="29" t="inlineStr">
         <is>
@@ -15368,7 +16828,7 @@
         </is>
       </c>
       <c r="C38" s="41" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="D38" s="42" t="inlineStr">
         <is>
@@ -15386,7 +16846,7 @@
         </is>
       </c>
       <c r="G38" s="44" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="H38" s="45" t="inlineStr">
         <is>
@@ -15416,7 +16876,7 @@
         </is>
       </c>
       <c r="C39" s="25" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D39" s="26" t="inlineStr">
         <is>
@@ -15434,7 +16894,7 @@
         </is>
       </c>
       <c r="G39" s="28" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H39" s="29" t="inlineStr">
         <is>
@@ -15464,7 +16924,7 @@
         </is>
       </c>
       <c r="C40" s="41" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="D40" s="42" t="inlineStr">
         <is>
@@ -15482,7 +16942,7 @@
         </is>
       </c>
       <c r="G40" s="44" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="H40" s="45" t="inlineStr">
         <is>
@@ -15512,7 +16972,7 @@
         </is>
       </c>
       <c r="C41" s="25" t="n">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="D41" s="26" t="inlineStr">
         <is>
@@ -15530,7 +16990,7 @@
         </is>
       </c>
       <c r="G41" s="28" t="n">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="H41" s="29" t="inlineStr">
         <is>
@@ -15539,7 +16999,7 @@
       </c>
       <c r="I41" s="59" t="inlineStr">
         <is>
-          <t>EHPS relay coil (-) (DRB102 56)</t>
+          <t>EHPS relay coil (-) (DRB102 85)</t>
         </is>
       </c>
       <c r="J41" s="60" t="inlineStr">
@@ -15560,7 +17020,7 @@
         </is>
       </c>
       <c r="C42" s="41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" s="42" t="inlineStr">
         <is>
@@ -15578,7 +17038,7 @@
         </is>
       </c>
       <c r="G42" s="44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42" s="45" t="inlineStr">
         <is>
@@ -15608,7 +17068,7 @@
         </is>
       </c>
       <c r="C43" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" s="26" t="inlineStr">
         <is>
@@ -15626,7 +17086,7 @@
         </is>
       </c>
       <c r="G43" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43" s="29" t="inlineStr">
         <is>

--- a/docs/harness/wirelist/A-cabin-wirelist.xlsx
+++ b/docs/harness/wirelist/A-cabin-wirelist.xlsx
@@ -1201,7 +1201,7 @@
       </c>
       <c r="V3" s="34" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W3" s="34" t="inlineStr"/>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="V4" s="50" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W4" s="50" t="inlineStr"/>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="V5" s="34" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W5" s="34" t="inlineStr"/>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="V6" s="50" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W6" s="50" t="inlineStr"/>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="V7" s="34" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W7" s="34" t="inlineStr"/>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="V8" s="50" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W8" s="50" t="inlineStr"/>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="V9" s="34" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W9" s="34" t="inlineStr"/>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="V10" s="50" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W10" s="50" t="inlineStr"/>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="V11" s="34" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W11" s="34" t="inlineStr"/>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="V12" s="50" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W12" s="50" t="inlineStr"/>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="V13" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W13" s="34" t="inlineStr"/>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="V17" s="34" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W17" s="34" t="inlineStr"/>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="V18" s="50" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W18" s="50" t="inlineStr"/>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="V19" s="34" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W19" s="34" t="inlineStr"/>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="V20" s="50" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W20" s="50" t="inlineStr"/>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="V21" s="34" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W21" s="34" t="inlineStr"/>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="V22" s="50" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W22" s="50" t="inlineStr"/>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="V23" s="34" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W23" s="34" t="inlineStr"/>
@@ -3657,11 +3657,7 @@
           <t>Orange</t>
         </is>
       </c>
-      <c r="W24" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+      <c r="W24" s="50" t="inlineStr"/>
       <c r="X24" s="50" t="inlineStr">
         <is>
           <t>Yellow-Yellow</t>
@@ -3778,11 +3774,7 @@
           <t>Orange</t>
         </is>
       </c>
-      <c r="W25" s="34" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+      <c r="W25" s="34" t="inlineStr"/>
       <c r="X25" s="34" t="inlineStr">
         <is>
           <t>Yellow-Blue-Yellow</t>
@@ -3897,11 +3889,7 @@
           <t>Orange</t>
         </is>
       </c>
-      <c r="W26" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+      <c r="W26" s="50" t="inlineStr"/>
       <c r="X26" s="50" t="inlineStr">
         <is>
           <t>Yellow-Blue-Yellow</t>
@@ -5302,14 +5290,10 @@
       </c>
       <c r="V38" s="50" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W38" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W38" s="50" t="inlineStr"/>
       <c r="X38" s="50" t="inlineStr">
         <is>
           <t>Yellow-Yellow-Blue</t>
@@ -5421,14 +5405,10 @@
       </c>
       <c r="V39" s="34" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W39" s="34" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W39" s="34" t="inlineStr"/>
       <c r="X39" s="34" t="inlineStr">
         <is>
           <t>Yellow-Yellow-Blue</t>
@@ -5538,14 +5518,10 @@
       </c>
       <c r="V40" s="50" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W40" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W40" s="50" t="inlineStr"/>
       <c r="X40" s="50" t="inlineStr">
         <is>
           <t>Yellow-Yellow-Blue</t>
@@ -5657,14 +5633,10 @@
       </c>
       <c r="V41" s="34" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W41" s="34" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W41" s="34" t="inlineStr"/>
       <c r="X41" s="34" t="inlineStr">
         <is>
           <t>Yellow-Yellow-Blue</t>
@@ -5776,14 +5748,10 @@
       </c>
       <c r="V42" s="50" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W42" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W42" s="50" t="inlineStr"/>
       <c r="X42" s="50" t="inlineStr">
         <is>
           <t>Yellow-Yellow-Blue</t>
@@ -5895,14 +5863,10 @@
       </c>
       <c r="V43" s="34" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W43" s="34" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W43" s="34" t="inlineStr"/>
       <c r="X43" s="34" t="inlineStr">
         <is>
           <t>Yellow-Yellow-Blue</t>
@@ -6014,14 +5978,10 @@
       </c>
       <c r="V44" s="50" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W44" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W44" s="50" t="inlineStr"/>
       <c r="X44" s="50" t="inlineStr">
         <is>
           <t>Yellow-Yellow-Blue</t>
@@ -6373,7 +6333,7 @@
       </c>
       <c r="V47" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W47" s="34" t="inlineStr"/>
@@ -7975,11 +7935,7 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="W60" s="50" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+      <c r="W60" s="50" t="inlineStr"/>
       <c r="X60" s="50" t="inlineStr">
         <is>
           <t>White-Yellow-Blue</t>
@@ -8096,11 +8052,7 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="W61" s="34" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+      <c r="W61" s="34" t="inlineStr"/>
       <c r="X61" s="34" t="inlineStr">
         <is>
           <t>White-Yellow-Blue</t>
@@ -8213,11 +8165,7 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="W62" s="50" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+      <c r="W62" s="50" t="inlineStr"/>
       <c r="X62" s="50" t="inlineStr">
         <is>
           <t>White-Yellow-Blue</t>
@@ -8332,11 +8280,7 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="W63" s="34" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+      <c r="W63" s="34" t="inlineStr"/>
       <c r="X63" s="34" t="inlineStr">
         <is>
           <t>White-Blue-White</t>
@@ -8455,11 +8399,7 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="W64" s="50" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+      <c r="W64" s="50" t="inlineStr"/>
       <c r="X64" s="50" t="inlineStr">
         <is>
           <t>Yellow-Yellow</t>
@@ -8574,11 +8514,7 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="W65" s="34" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+      <c r="W65" s="34" t="inlineStr"/>
       <c r="X65" s="34" t="inlineStr">
         <is>
           <t>White</t>
@@ -8693,11 +8629,7 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="W66" s="50" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+      <c r="W66" s="50" t="inlineStr"/>
       <c r="X66" s="50" t="inlineStr">
         <is>
           <t>White-Blue</t>
@@ -8812,11 +8744,7 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="W67" s="34" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+      <c r="W67" s="34" t="inlineStr"/>
       <c r="X67" s="34" t="inlineStr">
         <is>
           <t>Yellow</t>
@@ -9321,7 +9249,7 @@
       </c>
       <c r="V71" s="34" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W71" s="34" t="inlineStr"/>
@@ -9446,7 +9374,7 @@
       </c>
       <c r="V72" s="50" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W72" s="50" t="inlineStr"/>
@@ -9590,11 +9518,7 @@
           <t>Yellow</t>
         </is>
       </c>
-      <c r="W73" s="34" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
+      <c r="W73" s="34" t="inlineStr"/>
       <c r="X73" s="34" t="inlineStr">
         <is>
           <t>Yellow-Blue</t>
@@ -9733,11 +9657,7 @@
           <t>Yellow</t>
         </is>
       </c>
-      <c r="W74" s="50" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
+      <c r="W74" s="50" t="inlineStr"/>
       <c r="X74" s="50" t="inlineStr">
         <is>
           <t>Yellow-Blue</t>
@@ -9873,14 +9793,10 @@
       </c>
       <c r="V75" s="34" t="inlineStr">
         <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="W75" s="34" t="inlineStr">
-        <is>
           <t>Red</t>
         </is>
       </c>
+      <c r="W75" s="34" t="inlineStr"/>
       <c r="X75" s="34" t="inlineStr">
         <is>
           <t>Yellow-Blue</t>
